--- a/Quant Strategy(2026-27).xlsx
+++ b/Quant Strategy(2026-27).xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2292" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2301" uniqueCount="309">
   <si>
     <t>Sudeep</t>
   </si>
@@ -948,6 +948,9 @@
   </si>
   <si>
     <t>ATS1526</t>
+  </si>
+  <si>
+    <t>XTS38/ATS</t>
   </si>
 </sst>
 </file>
@@ -2285,7 +2288,14 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="389">
+  <dxfs count="390">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -5340,7 +5350,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:V74"/>
+  <dimension ref="A1:AE74"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" style="133" customWidth="1" outlineLevel="1"/>
@@ -5350,18 +5360,18 @@
     <col min="5" max="5" width="9.7109375" style="133" customWidth="1"/>
     <col min="6" max="6" width="6.5703125" style="133" customWidth="1"/>
     <col min="7" max="7" width="1.7109375" style="133" customWidth="1"/>
-    <col min="8" max="10" width="11.28515625" style="133" customWidth="1" outlineLevel="1"/>
-    <col min="11" max="11" width="11.28515625" style="133" customWidth="1"/>
-    <col min="12" max="12" width="10.42578125" style="133" customWidth="1" outlineLevel="1"/>
-    <col min="13" max="13" width="10.7109375" style="133" customWidth="1" outlineLevel="1"/>
-    <col min="14" max="19" width="9.140625" style="133"/>
-    <col min="20" max="20" width="14.140625" style="133" customWidth="1"/>
-    <col min="21" max="21" width="12" style="133" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="133"/>
+    <col min="8" max="19" width="11.28515625" style="133" customWidth="1" outlineLevel="1"/>
+    <col min="20" max="20" width="11.28515625" style="133" customWidth="1"/>
+    <col min="21" max="21" width="10.42578125" style="133" customWidth="1" outlineLevel="1"/>
+    <col min="22" max="22" width="10.7109375" style="133" customWidth="1" outlineLevel="1"/>
+    <col min="23" max="28" width="9.140625" style="133"/>
+    <col min="29" max="29" width="14.140625" style="133" customWidth="1"/>
+    <col min="30" max="30" width="12" style="133" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="133"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G2" s="221"/>
       <c r="H2" s="222">
         <v>46237</v>
@@ -5372,15 +5382,42 @@
       <c r="J2" s="256">
         <v>46239</v>
       </c>
-      <c r="K2" s="183"/>
-      <c r="L2" s="184" t="s">
+      <c r="K2" s="256">
+        <v>46240</v>
+      </c>
+      <c r="L2" s="256">
+        <v>46241</v>
+      </c>
+      <c r="M2" s="256">
+        <v>46244</v>
+      </c>
+      <c r="N2" s="256">
+        <v>46245</v>
+      </c>
+      <c r="O2" s="256">
+        <v>46246</v>
+      </c>
+      <c r="P2" s="256">
+        <v>46247</v>
+      </c>
+      <c r="Q2" s="256">
+        <v>46248</v>
+      </c>
+      <c r="R2" s="256">
+        <v>46251</v>
+      </c>
+      <c r="S2" s="256">
+        <v>46252</v>
+      </c>
+      <c r="T2" s="183"/>
+      <c r="U2" s="184" t="s">
         <v>278</v>
       </c>
-      <c r="M2" s="185" t="s">
+      <c r="V2" s="185" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="186" t="s">
         <v>54</v>
       </c>
@@ -5409,17 +5446,44 @@
       <c r="J3" s="179" t="s">
         <v>237</v>
       </c>
-      <c r="K3" s="180"/>
-      <c r="L3" s="189"/>
-      <c r="M3" s="180"/>
-      <c r="T3" s="133" t="s">
+      <c r="K3" s="179" t="s">
+        <v>236</v>
+      </c>
+      <c r="L3" s="179" t="s">
+        <v>235</v>
+      </c>
+      <c r="M3" s="179" t="s">
+        <v>234</v>
+      </c>
+      <c r="N3" s="179" t="s">
+        <v>233</v>
+      </c>
+      <c r="O3" s="179" t="s">
+        <v>237</v>
+      </c>
+      <c r="P3" s="179" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q3" s="179" t="s">
+        <v>235</v>
+      </c>
+      <c r="R3" s="179" t="s">
+        <v>234</v>
+      </c>
+      <c r="S3" s="179" t="s">
+        <v>233</v>
+      </c>
+      <c r="T3" s="180"/>
+      <c r="U3" s="189"/>
+      <c r="V3" s="180"/>
+      <c r="AC3" s="133" t="s">
         <v>198</v>
       </c>
-      <c r="U3" s="133">
+      <c r="AD3" s="133">
         <v>13780</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="142" t="s">
         <v>216</v>
       </c>
@@ -5448,23 +5512,50 @@
       <c r="J4" s="158">
         <v>-5027</v>
       </c>
-      <c r="K4" s="211"/>
-      <c r="L4" s="171">
-        <f t="shared" ref="L4:L35" si="0">SUM(H4:K4)</f>
-        <v>-11682</v>
-      </c>
-      <c r="M4" s="149">
-        <f t="shared" ref="M4:M35" si="1">IFERROR(L4/F4*100,0)/10000000</f>
-        <v>-0.23363999999999999</v>
-      </c>
-      <c r="T4" s="133" t="s">
+      <c r="K4" s="158">
+        <v>0</v>
+      </c>
+      <c r="L4" s="158">
+        <v>0</v>
+      </c>
+      <c r="M4" s="158">
+        <v>0</v>
+      </c>
+      <c r="N4" s="158">
+        <v>4435</v>
+      </c>
+      <c r="O4" s="158">
+        <v>3777</v>
+      </c>
+      <c r="P4" s="158">
+        <v>-5412</v>
+      </c>
+      <c r="Q4" s="158">
+        <v>-5358</v>
+      </c>
+      <c r="R4" s="158">
+        <v>-5142</v>
+      </c>
+      <c r="S4" s="158">
+        <v>3804</v>
+      </c>
+      <c r="T4" s="211"/>
+      <c r="U4" s="171">
+        <f t="shared" ref="U4:U35" si="0">SUM(H4:T4)</f>
+        <v>-15578</v>
+      </c>
+      <c r="V4" s="149">
+        <f t="shared" ref="V4:V35" si="1">IFERROR(U4/F4*100,0)/10000000</f>
+        <v>-0.31156</v>
+      </c>
+      <c r="AC4" s="133" t="s">
         <v>170</v>
       </c>
-      <c r="U4" s="133">
+      <c r="AD4" s="133">
         <v>2865</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="142" t="s">
         <v>30</v>
       </c>
@@ -5493,17 +5584,44 @@
       <c r="J5" s="147">
         <v>-215813</v>
       </c>
-      <c r="K5" s="174"/>
-      <c r="L5" s="171">
+      <c r="K5" s="147">
+        <v>-211</v>
+      </c>
+      <c r="L5" s="147">
+        <v>0</v>
+      </c>
+      <c r="M5" s="147">
+        <v>0</v>
+      </c>
+      <c r="N5" s="147">
+        <v>0</v>
+      </c>
+      <c r="O5" s="147">
+        <v>0</v>
+      </c>
+      <c r="P5" s="147">
+        <v>12100</v>
+      </c>
+      <c r="Q5" s="147">
+        <v>8886</v>
+      </c>
+      <c r="R5" s="147">
+        <v>-116700</v>
+      </c>
+      <c r="S5" s="147">
+        <v>-1406</v>
+      </c>
+      <c r="T5" s="174"/>
+      <c r="U5" s="171">
         <f t="shared" si="0"/>
-        <v>-196109</v>
-      </c>
-      <c r="M5" s="149">
+        <v>-293440</v>
+      </c>
+      <c r="V5" s="149">
         <f t="shared" si="1"/>
-        <v>-0.65369666666666659</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+        <v>-0.97813333333333319</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="142" t="s">
         <v>134</v>
       </c>
@@ -5532,21 +5650,48 @@
       <c r="J6" s="147">
         <v>-2231</v>
       </c>
-      <c r="K6" s="174"/>
-      <c r="L6" s="171">
+      <c r="K6" s="147">
+        <v>-181591</v>
+      </c>
+      <c r="L6" s="147">
+        <v>12214</v>
+      </c>
+      <c r="M6" s="147">
+        <v>88446</v>
+      </c>
+      <c r="N6" s="147">
+        <v>-44038</v>
+      </c>
+      <c r="O6" s="147">
+        <v>-41301</v>
+      </c>
+      <c r="P6" s="147">
+        <v>-22826</v>
+      </c>
+      <c r="Q6" s="147">
+        <v>-167661</v>
+      </c>
+      <c r="R6" s="147">
+        <v>117900</v>
+      </c>
+      <c r="S6" s="147">
+        <v>-13808</v>
+      </c>
+      <c r="T6" s="174"/>
+      <c r="U6" s="171">
         <f t="shared" si="0"/>
-        <v>14042</v>
-      </c>
-      <c r="M6" s="149">
+        <v>-238623</v>
+      </c>
+      <c r="V6" s="149">
         <f t="shared" si="1"/>
-        <v>4.680666666666667E-2</v>
-      </c>
-      <c r="O6" s="5"/>
-      <c r="P6" s="134">
-        <v>-4644</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+        <v>-0.79540999999999995</v>
+      </c>
+      <c r="X6" s="5"/>
+      <c r="Y6" s="134">
+        <v>7471</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="142" t="s">
         <v>217</v>
       </c>
@@ -5575,21 +5720,48 @@
       <c r="J7" s="147">
         <v>13534</v>
       </c>
-      <c r="K7" s="174"/>
-      <c r="L7" s="171">
+      <c r="K7" s="147">
+        <v>-5676</v>
+      </c>
+      <c r="L7" s="147">
+        <v>12716</v>
+      </c>
+      <c r="M7" s="147">
+        <v>-16434</v>
+      </c>
+      <c r="N7" s="147">
+        <v>16330</v>
+      </c>
+      <c r="O7" s="147">
+        <v>29593</v>
+      </c>
+      <c r="P7" s="147">
+        <v>-50409</v>
+      </c>
+      <c r="Q7" s="147">
+        <v>-31294</v>
+      </c>
+      <c r="R7" s="147">
+        <v>13376</v>
+      </c>
+      <c r="S7" s="147">
+        <v>-20176</v>
+      </c>
+      <c r="T7" s="174"/>
+      <c r="U7" s="171">
         <f t="shared" si="0"/>
-        <v>33535</v>
-      </c>
-      <c r="M7" s="149">
+        <v>-18439</v>
+      </c>
+      <c r="V7" s="149">
         <f t="shared" si="1"/>
-        <v>0.22356666666666669</v>
-      </c>
-      <c r="O7" s="134">
-        <v>141323</v>
-      </c>
-      <c r="P7" s="134"/>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+        <v>-0.12292666666666666</v>
+      </c>
+      <c r="X7" s="134">
+        <v>103961</v>
+      </c>
+      <c r="Y7" s="134"/>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="142" t="s">
         <v>217</v>
       </c>
@@ -5616,24 +5788,51 @@
       <c r="J8" s="147">
         <v>-1954</v>
       </c>
-      <c r="K8" s="174"/>
-      <c r="L8" s="171">
+      <c r="K8" s="147">
+        <v>-3231</v>
+      </c>
+      <c r="L8" s="147">
+        <v>8750</v>
+      </c>
+      <c r="M8" s="147">
+        <v>-40412</v>
+      </c>
+      <c r="N8" s="147">
+        <v>-1107</v>
+      </c>
+      <c r="O8" s="147">
+        <v>14170</v>
+      </c>
+      <c r="P8" s="147">
+        <v>-20113</v>
+      </c>
+      <c r="Q8" s="147">
+        <v>-18521</v>
+      </c>
+      <c r="R8" s="147">
+        <v>2800</v>
+      </c>
+      <c r="S8" s="147">
+        <v>-1318</v>
+      </c>
+      <c r="T8" s="174"/>
+      <c r="U8" s="171">
         <f t="shared" si="0"/>
-        <v>-1810</v>
-      </c>
-      <c r="M8" s="149">
+        <v>-60792</v>
+      </c>
+      <c r="V8" s="149">
         <f t="shared" si="1"/>
-        <v>-3.0166666666666668E-2</v>
-      </c>
-      <c r="O8" s="134">
-        <v>136678</v>
-      </c>
-      <c r="P8" s="134">
-        <f>(O8+O7)/10000000*13780</f>
-        <v>383.08537799999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+        <v>-1.0132000000000001</v>
+      </c>
+      <c r="X8" s="134">
+        <v>111432</v>
+      </c>
+      <c r="Y8" s="134">
+        <f>(X8+X7)/10000000*13780</f>
+        <v>296.811554</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="143" t="s">
         <v>35</v>
       </c>
@@ -5662,19 +5861,46 @@
       <c r="J9" s="147">
         <v>0</v>
       </c>
-      <c r="K9" s="174"/>
-      <c r="L9" s="171">
+      <c r="K9" s="147">
+        <v>0</v>
+      </c>
+      <c r="L9" s="147">
+        <v>0</v>
+      </c>
+      <c r="M9" s="147">
+        <v>0</v>
+      </c>
+      <c r="N9" s="147">
+        <v>167470</v>
+      </c>
+      <c r="O9" s="147">
+        <v>0</v>
+      </c>
+      <c r="P9" s="147">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="147">
+        <v>0</v>
+      </c>
+      <c r="R9" s="147">
+        <v>10000</v>
+      </c>
+      <c r="S9" s="147">
+        <v>1753</v>
+      </c>
+      <c r="T9" s="174"/>
+      <c r="U9" s="171">
         <f t="shared" si="0"/>
-        <v>-814500</v>
-      </c>
-      <c r="M9" s="149">
+        <v>-635277</v>
+      </c>
+      <c r="V9" s="149">
         <f t="shared" si="1"/>
-        <v>-0.54300000000000004</v>
-      </c>
-      <c r="O9" s="134"/>
-      <c r="P9" s="134"/>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+        <v>-0.42351800000000001</v>
+      </c>
+      <c r="X9" s="134"/>
+      <c r="Y9" s="134"/>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="143" t="s">
         <v>137</v>
       </c>
@@ -5703,19 +5929,46 @@
       <c r="J10" s="147">
         <v>0</v>
       </c>
-      <c r="K10" s="174"/>
-      <c r="L10" s="171">
+      <c r="K10" s="147">
+        <v>0</v>
+      </c>
+      <c r="L10" s="147">
+        <v>0</v>
+      </c>
+      <c r="M10" s="147">
+        <v>0</v>
+      </c>
+      <c r="N10" s="147">
+        <v>57626</v>
+      </c>
+      <c r="O10" s="147">
+        <v>0</v>
+      </c>
+      <c r="P10" s="147">
+        <v>6150</v>
+      </c>
+      <c r="Q10" s="147">
+        <v>0</v>
+      </c>
+      <c r="R10" s="147">
+        <v>-6939</v>
+      </c>
+      <c r="S10" s="147">
+        <v>33782</v>
+      </c>
+      <c r="T10" s="174"/>
+      <c r="U10" s="171">
         <f t="shared" si="0"/>
-        <v>85911</v>
-      </c>
-      <c r="M10" s="149">
+        <v>176530</v>
+      </c>
+      <c r="V10" s="149">
         <f t="shared" si="1"/>
-        <v>0.14318500000000001</v>
-      </c>
-      <c r="O10" s="134"/>
-      <c r="P10" s="134"/>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+        <v>0.29421666666666668</v>
+      </c>
+      <c r="X10" s="134"/>
+      <c r="Y10" s="134"/>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="143" t="s">
         <v>42</v>
       </c>
@@ -5744,19 +5997,46 @@
       <c r="J11" s="147">
         <v>3534</v>
       </c>
-      <c r="K11" s="174"/>
-      <c r="L11" s="171">
+      <c r="K11" s="147">
+        <v>2106</v>
+      </c>
+      <c r="L11" s="147">
+        <v>3485</v>
+      </c>
+      <c r="M11" s="147">
+        <v>987</v>
+      </c>
+      <c r="N11" s="147">
+        <v>486</v>
+      </c>
+      <c r="O11" s="147">
+        <v>1505</v>
+      </c>
+      <c r="P11" s="147">
+        <v>-2000</v>
+      </c>
+      <c r="Q11" s="147">
+        <v>-214</v>
+      </c>
+      <c r="R11" s="147">
+        <v>1576</v>
+      </c>
+      <c r="S11" s="147">
+        <v>-810</v>
+      </c>
+      <c r="T11" s="174"/>
+      <c r="U11" s="171">
         <f t="shared" si="0"/>
-        <v>4662</v>
-      </c>
-      <c r="M11" s="149">
+        <v>11783</v>
+      </c>
+      <c r="V11" s="149">
         <f t="shared" si="1"/>
-        <v>4.6620000000000002E-2</v>
-      </c>
-      <c r="O11" s="134"/>
-      <c r="P11" s="134"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+        <v>0.11783</v>
+      </c>
+      <c r="X11" s="134"/>
+      <c r="Y11" s="134"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="142" t="s">
         <v>212</v>
       </c>
@@ -5785,19 +6065,46 @@
       <c r="J12" s="147">
         <v>-32279</v>
       </c>
-      <c r="K12" s="174"/>
-      <c r="L12" s="171">
+      <c r="K12" s="147">
+        <v>0</v>
+      </c>
+      <c r="L12" s="147">
+        <v>0</v>
+      </c>
+      <c r="M12" s="147">
+        <v>0</v>
+      </c>
+      <c r="N12" s="147">
+        <v>19385</v>
+      </c>
+      <c r="O12" s="147">
+        <v>3256</v>
+      </c>
+      <c r="P12" s="147">
+        <v>15500</v>
+      </c>
+      <c r="Q12" s="147">
+        <v>22429</v>
+      </c>
+      <c r="R12" s="147">
+        <v>-77515</v>
+      </c>
+      <c r="S12" s="147">
+        <v>29621</v>
+      </c>
+      <c r="T12" s="174"/>
+      <c r="U12" s="171">
         <f t="shared" si="0"/>
-        <v>-84149</v>
-      </c>
-      <c r="M12" s="149">
+        <v>-71473</v>
+      </c>
+      <c r="V12" s="149">
         <f t="shared" si="1"/>
-        <v>-0.33659600000000001</v>
-      </c>
-      <c r="O12" s="134"/>
-      <c r="P12" s="134"/>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+        <v>-0.28589199999999998</v>
+      </c>
+      <c r="X12" s="134"/>
+      <c r="Y12" s="134"/>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="142" t="s">
         <v>51</v>
       </c>
@@ -5826,32 +6133,59 @@
       <c r="J13" s="147">
         <v>-29607</v>
       </c>
-      <c r="K13" s="174"/>
-      <c r="L13" s="171">
+      <c r="K13" s="147">
+        <v>0</v>
+      </c>
+      <c r="L13" s="147">
+        <v>0</v>
+      </c>
+      <c r="M13" s="147">
+        <v>0</v>
+      </c>
+      <c r="N13" s="147">
+        <v>0</v>
+      </c>
+      <c r="O13" s="147">
+        <v>0</v>
+      </c>
+      <c r="P13" s="147">
+        <v>17300</v>
+      </c>
+      <c r="Q13" s="147">
+        <v>22984</v>
+      </c>
+      <c r="R13" s="147">
+        <v>-68810</v>
+      </c>
+      <c r="S13" s="147">
+        <v>27894</v>
+      </c>
+      <c r="T13" s="174"/>
+      <c r="U13" s="171">
         <f t="shared" si="0"/>
-        <v>-69794</v>
-      </c>
-      <c r="M13" s="149">
+        <v>-70426</v>
+      </c>
+      <c r="V13" s="149">
         <f t="shared" si="1"/>
-        <v>-0.31724545454545455</v>
-      </c>
-      <c r="O13" s="134"/>
-      <c r="P13" s="193">
-        <f>P6-P8</f>
-        <v>-5027.0853779999998</v>
-      </c>
-      <c r="S13" s="133">
-        <v>4722</v>
-      </c>
-      <c r="T13" s="133">
-        <v>2932</v>
-      </c>
-      <c r="U13" s="133">
-        <f>T13+S13</f>
-        <v>7654</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+        <v>-0.3201181818181818</v>
+      </c>
+      <c r="X13" s="134"/>
+      <c r="Y13" s="193">
+        <f>Y6-Y8</f>
+        <v>7174.1884460000001</v>
+      </c>
+      <c r="AB13" s="133">
+        <v>-67693</v>
+      </c>
+      <c r="AC13" s="133">
+        <v>-49000</v>
+      </c>
+      <c r="AD13" s="133">
+        <f>AC13+AB13</f>
+        <v>-116693</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="142" t="s">
         <v>62</v>
       </c>
@@ -5880,19 +6214,46 @@
       <c r="J14" s="147">
         <v>0</v>
       </c>
-      <c r="K14" s="174"/>
-      <c r="L14" s="171">
+      <c r="K14" s="147">
+        <v>0</v>
+      </c>
+      <c r="L14" s="147">
+        <v>0</v>
+      </c>
+      <c r="M14" s="147">
+        <v>0</v>
+      </c>
+      <c r="N14" s="147">
+        <v>0</v>
+      </c>
+      <c r="O14" s="147">
+        <v>0</v>
+      </c>
+      <c r="P14" s="147">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="147">
+        <v>0</v>
+      </c>
+      <c r="R14" s="147">
+        <v>0</v>
+      </c>
+      <c r="S14" s="147">
+        <v>0</v>
+      </c>
+      <c r="T14" s="174"/>
+      <c r="U14" s="171">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M14" s="149">
+      <c r="V14" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O14" s="134"/>
-      <c r="P14" s="134"/>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="X14" s="134"/>
+      <c r="Y14" s="134"/>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="142" t="s">
         <v>43</v>
       </c>
@@ -5921,17 +6282,44 @@
       <c r="J15" s="147">
         <v>11053</v>
       </c>
-      <c r="K15" s="174"/>
-      <c r="L15" s="171">
+      <c r="K15" s="147">
+        <v>5179</v>
+      </c>
+      <c r="L15" s="147">
+        <v>8058</v>
+      </c>
+      <c r="M15" s="147">
+        <v>5020</v>
+      </c>
+      <c r="N15" s="147">
+        <v>-913</v>
+      </c>
+      <c r="O15" s="147">
+        <v>1571</v>
+      </c>
+      <c r="P15" s="147">
+        <v>-1353</v>
+      </c>
+      <c r="Q15" s="147">
+        <v>-1664</v>
+      </c>
+      <c r="R15" s="147">
+        <v>1591</v>
+      </c>
+      <c r="S15" s="147">
+        <v>-8331</v>
+      </c>
+      <c r="T15" s="174"/>
+      <c r="U15" s="171">
         <f t="shared" si="0"/>
-        <v>23043</v>
-      </c>
-      <c r="M15" s="149">
+        <v>32201</v>
+      </c>
+      <c r="V15" s="149">
         <f t="shared" si="1"/>
-        <v>0.23043</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+        <v>0.32201000000000002</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="142" t="s">
         <v>24</v>
       </c>
@@ -5960,17 +6348,44 @@
       <c r="J16" s="147">
         <v>-74800</v>
       </c>
-      <c r="K16" s="174"/>
-      <c r="L16" s="171">
+      <c r="K16" s="147">
+        <v>0</v>
+      </c>
+      <c r="L16" s="147">
+        <v>0</v>
+      </c>
+      <c r="M16" s="147">
+        <v>0</v>
+      </c>
+      <c r="N16" s="147">
+        <v>0</v>
+      </c>
+      <c r="O16" s="147">
+        <v>0</v>
+      </c>
+      <c r="P16" s="147">
+        <v>18503</v>
+      </c>
+      <c r="Q16" s="147">
+        <v>0</v>
+      </c>
+      <c r="R16" s="147">
+        <v>-4900</v>
+      </c>
+      <c r="S16" s="147">
+        <v>-15557</v>
+      </c>
+      <c r="T16" s="174"/>
+      <c r="U16" s="171">
         <f t="shared" si="0"/>
-        <v>-106373</v>
-      </c>
-      <c r="M16" s="149">
+        <v>-108327</v>
+      </c>
+      <c r="V16" s="149">
         <f t="shared" si="1"/>
-        <v>-0.42549199999999998</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+        <v>-0.43330800000000003</v>
+      </c>
+    </row>
+    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A17" s="142" t="s">
         <v>23</v>
       </c>
@@ -5999,17 +6414,44 @@
       <c r="J17" s="147">
         <v>4580</v>
       </c>
-      <c r="K17" s="174"/>
-      <c r="L17" s="171">
+      <c r="K17" s="147">
+        <v>0</v>
+      </c>
+      <c r="L17" s="147">
+        <v>0</v>
+      </c>
+      <c r="M17" s="147">
+        <v>0</v>
+      </c>
+      <c r="N17" s="147">
+        <v>0</v>
+      </c>
+      <c r="O17" s="147">
+        <v>0</v>
+      </c>
+      <c r="P17" s="147">
+        <v>-10722</v>
+      </c>
+      <c r="Q17" s="147">
+        <v>0</v>
+      </c>
+      <c r="R17" s="147">
+        <v>-2553</v>
+      </c>
+      <c r="S17" s="147">
+        <v>5667</v>
+      </c>
+      <c r="T17" s="174"/>
+      <c r="U17" s="171">
         <f t="shared" si="0"/>
-        <v>7825</v>
-      </c>
-      <c r="M17" s="149">
+        <v>217</v>
+      </c>
+      <c r="V17" s="149">
         <f t="shared" si="1"/>
-        <v>1.95625E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+        <v>5.4250000000000001E-4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A18" s="142" t="s">
         <v>275</v>
       </c>
@@ -6038,17 +6480,44 @@
       <c r="J18" s="147">
         <v>0</v>
       </c>
-      <c r="K18" s="174"/>
-      <c r="L18" s="171">
+      <c r="K18" s="147">
+        <v>0</v>
+      </c>
+      <c r="L18" s="147">
+        <v>0</v>
+      </c>
+      <c r="M18" s="147">
+        <v>0</v>
+      </c>
+      <c r="N18" s="147">
+        <v>0</v>
+      </c>
+      <c r="O18" s="147">
+        <v>0</v>
+      </c>
+      <c r="P18" s="147">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="147">
+        <v>0</v>
+      </c>
+      <c r="R18" s="147">
+        <v>0</v>
+      </c>
+      <c r="S18" s="147">
+        <v>0</v>
+      </c>
+      <c r="T18" s="174"/>
+      <c r="U18" s="171">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M18" s="149">
+      <c r="V18" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A19" s="142" t="s">
         <v>165</v>
       </c>
@@ -6077,17 +6546,44 @@
       <c r="J19" s="147">
         <v>-69757</v>
       </c>
-      <c r="K19" s="174"/>
-      <c r="L19" s="171">
+      <c r="K19" s="147">
+        <v>3222</v>
+      </c>
+      <c r="L19" s="147">
+        <v>1223</v>
+      </c>
+      <c r="M19" s="147">
+        <v>98532</v>
+      </c>
+      <c r="N19" s="147">
+        <v>75645</v>
+      </c>
+      <c r="O19" s="147">
+        <v>17176</v>
+      </c>
+      <c r="P19" s="147">
+        <v>19367</v>
+      </c>
+      <c r="Q19" s="147">
+        <v>-107297</v>
+      </c>
+      <c r="R19" s="147">
+        <v>8922</v>
+      </c>
+      <c r="S19" s="147">
+        <v>40153</v>
+      </c>
+      <c r="T19" s="174"/>
+      <c r="U19" s="171">
         <f t="shared" si="0"/>
-        <v>-77519</v>
-      </c>
-      <c r="M19" s="149">
+        <v>79424</v>
+      </c>
+      <c r="V19" s="149">
         <f t="shared" si="1"/>
-        <v>-0.51679333333333344</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+        <v>0.52949333333333337</v>
+      </c>
+    </row>
+    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A20" s="142" t="s">
         <v>110</v>
       </c>
@@ -6116,17 +6612,44 @@
       <c r="J20" s="147">
         <v>-57099</v>
       </c>
-      <c r="K20" s="174"/>
-      <c r="L20" s="171">
+      <c r="K20" s="147">
+        <v>-5506</v>
+      </c>
+      <c r="L20" s="147">
+        <v>18880</v>
+      </c>
+      <c r="M20" s="147">
+        <v>20615</v>
+      </c>
+      <c r="N20" s="147">
+        <v>29331</v>
+      </c>
+      <c r="O20" s="147">
+        <v>8450</v>
+      </c>
+      <c r="P20" s="147">
+        <v>24145</v>
+      </c>
+      <c r="Q20" s="147">
+        <v>12577</v>
+      </c>
+      <c r="R20" s="147">
+        <v>-9860</v>
+      </c>
+      <c r="S20" s="147">
+        <v>4884</v>
+      </c>
+      <c r="T20" s="174"/>
+      <c r="U20" s="171">
         <f t="shared" si="0"/>
-        <v>-57635</v>
-      </c>
-      <c r="M20" s="149">
+        <v>45881</v>
+      </c>
+      <c r="V20" s="149">
         <f t="shared" si="1"/>
-        <v>-0.52395454545454545</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+        <v>0.41710000000000003</v>
+      </c>
+    </row>
+    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A21" s="142"/>
       <c r="B21" s="141" t="s">
         <v>111</v>
@@ -6153,17 +6676,44 @@
       <c r="J21" s="147">
         <v>-17457</v>
       </c>
-      <c r="K21" s="174"/>
-      <c r="L21" s="171">
+      <c r="K21" s="147">
+        <v>-1700</v>
+      </c>
+      <c r="L21" s="147">
+        <v>0</v>
+      </c>
+      <c r="M21" s="147">
+        <v>0</v>
+      </c>
+      <c r="N21" s="147">
+        <v>0</v>
+      </c>
+      <c r="O21" s="147">
+        <v>3259</v>
+      </c>
+      <c r="P21" s="147">
+        <v>3563</v>
+      </c>
+      <c r="Q21" s="147">
+        <v>14397</v>
+      </c>
+      <c r="R21" s="147">
+        <v>676</v>
+      </c>
+      <c r="S21" s="147">
+        <v>8961</v>
+      </c>
+      <c r="T21" s="174"/>
+      <c r="U21" s="171">
         <f t="shared" si="0"/>
-        <v>-51822</v>
-      </c>
-      <c r="M21" s="149">
+        <v>-22666</v>
+      </c>
+      <c r="V21" s="149">
         <f t="shared" si="1"/>
-        <v>-2.0728800000000001</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+        <v>-0.90664</v>
+      </c>
+    </row>
+    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A22" s="142"/>
       <c r="B22" s="141" t="s">
         <v>282</v>
@@ -6190,17 +6740,44 @@
       <c r="J22" s="147">
         <v>7140</v>
       </c>
-      <c r="K22" s="174"/>
-      <c r="L22" s="171">
+      <c r="K22" s="147">
+        <v>4504</v>
+      </c>
+      <c r="L22" s="147">
+        <v>-3214</v>
+      </c>
+      <c r="M22" s="147">
+        <v>-100</v>
+      </c>
+      <c r="N22" s="147">
+        <v>-516</v>
+      </c>
+      <c r="O22" s="147">
+        <v>4214</v>
+      </c>
+      <c r="P22" s="147">
+        <v>3242</v>
+      </c>
+      <c r="Q22" s="147">
+        <v>1087</v>
+      </c>
+      <c r="R22" s="147">
+        <v>0</v>
+      </c>
+      <c r="S22" s="147">
+        <v>0</v>
+      </c>
+      <c r="T22" s="174"/>
+      <c r="U22" s="171">
         <f t="shared" si="0"/>
-        <v>15902</v>
-      </c>
-      <c r="M22" s="149">
+        <v>25119</v>
+      </c>
+      <c r="V22" s="149">
         <f t="shared" si="1"/>
-        <v>7.9509999999999997E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+        <v>0.12559500000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A23" s="142" t="s">
         <v>32</v>
       </c>
@@ -6229,17 +6806,44 @@
       <c r="J23" s="147">
         <v>-110528</v>
       </c>
-      <c r="K23" s="174"/>
-      <c r="L23" s="171">
+      <c r="K23" s="147">
+        <v>-24394</v>
+      </c>
+      <c r="L23" s="147">
+        <v>-100</v>
+      </c>
+      <c r="M23" s="147">
+        <v>7500</v>
+      </c>
+      <c r="N23" s="147">
+        <v>42348</v>
+      </c>
+      <c r="O23" s="147">
+        <v>41000</v>
+      </c>
+      <c r="P23" s="147">
+        <v>-9140</v>
+      </c>
+      <c r="Q23" s="147">
+        <v>240</v>
+      </c>
+      <c r="R23" s="147">
+        <v>31750</v>
+      </c>
+      <c r="S23" s="147">
+        <v>7174</v>
+      </c>
+      <c r="T23" s="174"/>
+      <c r="U23" s="171">
         <f t="shared" si="0"/>
-        <v>-108839</v>
-      </c>
-      <c r="M23" s="149">
+        <v>-12461</v>
+      </c>
+      <c r="V23" s="149">
         <f t="shared" si="1"/>
-        <v>-0.98944545454545452</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+        <v>-0.11328181818181819</v>
+      </c>
+    </row>
+    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A24" s="142" t="s">
         <v>97</v>
       </c>
@@ -6268,17 +6872,44 @@
       <c r="J24" s="147">
         <v>41570</v>
       </c>
-      <c r="K24" s="174"/>
-      <c r="L24" s="171">
+      <c r="K24" s="147">
+        <v>-96668</v>
+      </c>
+      <c r="L24" s="147">
+        <v>9856</v>
+      </c>
+      <c r="M24" s="147">
+        <v>42818</v>
+      </c>
+      <c r="N24" s="147">
+        <v>-133800</v>
+      </c>
+      <c r="O24" s="147">
+        <v>-116337</v>
+      </c>
+      <c r="P24" s="147">
+        <v>29186</v>
+      </c>
+      <c r="Q24" s="147">
+        <v>-96417</v>
+      </c>
+      <c r="R24" s="147">
+        <v>-4028</v>
+      </c>
+      <c r="S24" s="147">
+        <v>-100640</v>
+      </c>
+      <c r="T24" s="174"/>
+      <c r="U24" s="171">
         <f t="shared" si="0"/>
-        <v>243866</v>
-      </c>
-      <c r="M24" s="149">
+        <v>-222164</v>
+      </c>
+      <c r="V24" s="149">
         <f t="shared" si="1"/>
-        <v>1.0602869565217392</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+        <v>-0.96593043478260876</v>
+      </c>
+    </row>
+    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A25" s="142" t="s">
         <v>302</v>
       </c>
@@ -6305,17 +6936,44 @@
       <c r="J25" s="147">
         <v>2778</v>
       </c>
-      <c r="K25" s="174"/>
-      <c r="L25" s="171">
+      <c r="K25" s="147">
+        <v>-700</v>
+      </c>
+      <c r="L25" s="147">
+        <v>-931</v>
+      </c>
+      <c r="M25" s="147">
+        <v>-1415</v>
+      </c>
+      <c r="N25" s="147">
+        <v>-297</v>
+      </c>
+      <c r="O25" s="147">
+        <v>-485</v>
+      </c>
+      <c r="P25" s="147">
+        <v>1107</v>
+      </c>
+      <c r="Q25" s="147">
+        <v>-2756</v>
+      </c>
+      <c r="R25" s="147">
+        <v>-2866</v>
+      </c>
+      <c r="S25" s="147">
+        <v>-2782</v>
+      </c>
+      <c r="T25" s="174"/>
+      <c r="U25" s="171">
         <f t="shared" si="0"/>
-        <v>2629</v>
-      </c>
-      <c r="M25" s="149">
+        <v>-8496</v>
+      </c>
+      <c r="V25" s="149">
         <f t="shared" si="1"/>
-        <v>0.13145000000000001</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+        <v>-0.42480000000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A26" s="142" t="s">
         <v>29</v>
       </c>
@@ -6344,17 +7002,44 @@
       <c r="J26" s="147">
         <v>-19970</v>
       </c>
-      <c r="K26" s="174"/>
-      <c r="L26" s="171">
+      <c r="K26" s="147">
+        <v>0</v>
+      </c>
+      <c r="L26" s="147">
+        <v>0</v>
+      </c>
+      <c r="M26" s="147">
+        <v>0</v>
+      </c>
+      <c r="N26" s="147">
+        <v>0</v>
+      </c>
+      <c r="O26" s="147">
+        <v>0</v>
+      </c>
+      <c r="P26" s="147">
+        <v>11590</v>
+      </c>
+      <c r="Q26" s="147">
+        <v>0</v>
+      </c>
+      <c r="R26" s="147">
+        <v>-7000</v>
+      </c>
+      <c r="S26" s="147">
+        <v>0</v>
+      </c>
+      <c r="T26" s="174"/>
+      <c r="U26" s="171">
         <f t="shared" si="0"/>
-        <v>-86170</v>
-      </c>
-      <c r="M26" s="149">
+        <v>-81580</v>
+      </c>
+      <c r="V26" s="149">
         <f t="shared" si="1"/>
-        <v>-0.17233999999999999</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+        <v>-0.16316</v>
+      </c>
+    </row>
+    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A27" s="142" t="s">
         <v>28</v>
       </c>
@@ -6383,17 +7068,44 @@
       <c r="J27" s="147">
         <v>-454519</v>
       </c>
-      <c r="K27" s="174"/>
-      <c r="L27" s="171">
+      <c r="K27" s="147">
+        <v>0</v>
+      </c>
+      <c r="L27" s="147">
+        <v>0</v>
+      </c>
+      <c r="M27" s="147">
+        <v>480</v>
+      </c>
+      <c r="N27" s="147">
+        <v>153600</v>
+      </c>
+      <c r="O27" s="147">
+        <v>-500</v>
+      </c>
+      <c r="P27" s="147">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="147">
+        <v>0</v>
+      </c>
+      <c r="R27" s="147">
+        <v>0</v>
+      </c>
+      <c r="S27" s="147">
+        <v>21715</v>
+      </c>
+      <c r="T27" s="174"/>
+      <c r="U27" s="171">
         <f t="shared" si="0"/>
-        <v>-561931</v>
-      </c>
-      <c r="M27" s="149">
+        <v>-386636</v>
+      </c>
+      <c r="V27" s="149">
         <f t="shared" si="1"/>
-        <v>-0.56193099999999996</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+        <v>-0.38663599999999998</v>
+      </c>
+    </row>
+    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A28" s="142" t="s">
         <v>191</v>
       </c>
@@ -6422,20 +7134,47 @@
       <c r="J28" s="147">
         <v>-586162</v>
       </c>
-      <c r="K28" s="174"/>
-      <c r="L28" s="171">
+      <c r="K28" s="147">
+        <v>0</v>
+      </c>
+      <c r="L28" s="147">
+        <v>0</v>
+      </c>
+      <c r="M28" s="147">
+        <v>0</v>
+      </c>
+      <c r="N28" s="147">
+        <v>0</v>
+      </c>
+      <c r="O28" s="147">
+        <v>0</v>
+      </c>
+      <c r="P28" s="147">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="147">
+        <v>0</v>
+      </c>
+      <c r="R28" s="147">
+        <v>0</v>
+      </c>
+      <c r="S28" s="147">
+        <v>0</v>
+      </c>
+      <c r="T28" s="174"/>
+      <c r="U28" s="171">
         <f t="shared" si="0"/>
         <v>-787722</v>
       </c>
-      <c r="M28" s="149">
+      <c r="V28" s="149">
         <f t="shared" si="1"/>
         <v>-0.60594000000000003</v>
       </c>
-      <c r="P28" s="133">
-        <v>-14953</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y28" s="133">
+        <v>190346</v>
+      </c>
+    </row>
+    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A29" s="142" t="s">
         <v>194</v>
       </c>
@@ -6464,26 +7203,53 @@
       <c r="J29" s="147">
         <v>-259305</v>
       </c>
-      <c r="K29" s="174"/>
-      <c r="L29" s="171">
+      <c r="K29" s="147">
+        <v>0</v>
+      </c>
+      <c r="L29" s="147">
+        <v>0</v>
+      </c>
+      <c r="M29" s="147">
+        <v>0</v>
+      </c>
+      <c r="N29" s="147">
+        <v>0</v>
+      </c>
+      <c r="O29" s="147">
+        <v>0</v>
+      </c>
+      <c r="P29" s="147">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="147">
+        <v>0</v>
+      </c>
+      <c r="R29" s="147">
+        <v>0</v>
+      </c>
+      <c r="S29" s="147">
+        <v>0</v>
+      </c>
+      <c r="T29" s="174"/>
+      <c r="U29" s="171">
         <f t="shared" si="0"/>
         <v>-348894</v>
       </c>
-      <c r="M29" s="149">
+      <c r="V29" s="149">
         <f t="shared" si="1"/>
         <v>-0.58148999999999995</v>
       </c>
-      <c r="P29" s="133">
+      <c r="Y29" s="133">
         <v>916223</v>
       </c>
-      <c r="S29" s="133">
+      <c r="AB29" s="133">
         <v>90975</v>
       </c>
-      <c r="V29" s="133">
+      <c r="AE29" s="133">
         <v>-38200</v>
       </c>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A30" s="142" t="s">
         <v>147</v>
       </c>
@@ -6512,26 +7278,53 @@
       <c r="J30" s="147">
         <v>-65000</v>
       </c>
-      <c r="K30" s="174"/>
-      <c r="L30" s="171">
+      <c r="K30" s="147">
+        <v>0</v>
+      </c>
+      <c r="L30" s="147">
+        <v>0</v>
+      </c>
+      <c r="M30" s="147">
+        <v>0</v>
+      </c>
+      <c r="N30" s="147">
+        <v>0</v>
+      </c>
+      <c r="O30" s="147">
+        <v>0</v>
+      </c>
+      <c r="P30" s="147">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="147">
+        <v>0</v>
+      </c>
+      <c r="R30" s="147">
+        <v>0</v>
+      </c>
+      <c r="S30" s="147">
+        <v>0</v>
+      </c>
+      <c r="T30" s="174"/>
+      <c r="U30" s="171">
         <f t="shared" si="0"/>
         <v>-87345</v>
       </c>
-      <c r="M30" s="149">
+      <c r="V30" s="149">
         <f t="shared" si="1"/>
         <v>-0.58230000000000004</v>
       </c>
-      <c r="P30" s="133">
-        <v>0</v>
-      </c>
-      <c r="S30" s="133">
+      <c r="Y30" s="133">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="133">
         <v>-31616</v>
       </c>
-      <c r="V30" s="133">
+      <c r="AE30" s="133">
         <v>11900</v>
       </c>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A31" s="163" t="s">
         <v>205</v>
       </c>
@@ -6560,17 +7353,44 @@
       <c r="J31" s="151">
         <v>-64850</v>
       </c>
-      <c r="K31" s="174"/>
-      <c r="L31" s="171">
+      <c r="K31" s="151">
+        <v>0</v>
+      </c>
+      <c r="L31" s="151">
+        <v>0</v>
+      </c>
+      <c r="M31" s="151">
+        <v>0</v>
+      </c>
+      <c r="N31" s="151">
+        <v>0</v>
+      </c>
+      <c r="O31" s="151">
+        <v>0</v>
+      </c>
+      <c r="P31" s="151">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="151">
+        <v>0</v>
+      </c>
+      <c r="R31" s="151">
+        <v>0</v>
+      </c>
+      <c r="S31" s="151">
+        <v>0</v>
+      </c>
+      <c r="T31" s="174"/>
+      <c r="U31" s="171">
         <f t="shared" si="0"/>
         <v>-87240</v>
       </c>
-      <c r="M31" s="149">
+      <c r="V31" s="149">
         <f t="shared" si="1"/>
         <v>-0.69791999999999998</v>
       </c>
     </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A32" s="62" t="s">
         <v>1</v>
       </c>
@@ -6599,25 +7419,52 @@
       <c r="J32" s="151">
         <v>-64850</v>
       </c>
-      <c r="K32" s="174"/>
-      <c r="L32" s="171">
+      <c r="K32" s="151">
+        <v>0</v>
+      </c>
+      <c r="L32" s="151">
+        <v>0</v>
+      </c>
+      <c r="M32" s="151">
+        <v>0</v>
+      </c>
+      <c r="N32" s="151">
+        <v>0</v>
+      </c>
+      <c r="O32" s="151">
+        <v>0</v>
+      </c>
+      <c r="P32" s="151">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="151">
+        <v>0</v>
+      </c>
+      <c r="R32" s="151">
+        <v>0</v>
+      </c>
+      <c r="S32" s="151">
+        <v>0</v>
+      </c>
+      <c r="T32" s="174"/>
+      <c r="U32" s="171">
         <f t="shared" si="0"/>
         <v>-87014</v>
       </c>
-      <c r="M32" s="149">
+      <c r="V32" s="149">
         <f t="shared" si="1"/>
         <v>-0.58009333333333335</v>
       </c>
-      <c r="P32" s="133">
-        <f>SUM(P27:P30)</f>
-        <v>901270</v>
-      </c>
-      <c r="S32" s="133">
-        <f>SUM(S29:S30)</f>
+      <c r="Y32" s="133">
+        <f>SUM(Y27:Y30)</f>
+        <v>1106569</v>
+      </c>
+      <c r="AB32" s="133">
+        <f>SUM(AB29:AB30)</f>
         <v>59359</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33" s="142" t="s">
         <v>65</v>
       </c>
@@ -6646,17 +7493,44 @@
       <c r="J33" s="147">
         <v>0</v>
       </c>
-      <c r="K33" s="174"/>
-      <c r="L33" s="171">
+      <c r="K33" s="147">
+        <v>0</v>
+      </c>
+      <c r="L33" s="147">
+        <v>0</v>
+      </c>
+      <c r="M33" s="147">
+        <v>0</v>
+      </c>
+      <c r="N33" s="147">
+        <v>128400</v>
+      </c>
+      <c r="O33" s="147">
+        <v>0</v>
+      </c>
+      <c r="P33" s="147">
+        <v>-5062</v>
+      </c>
+      <c r="Q33" s="147">
+        <v>0</v>
+      </c>
+      <c r="R33" s="147">
+        <v>0</v>
+      </c>
+      <c r="S33" s="147">
+        <v>-3320</v>
+      </c>
+      <c r="T33" s="174"/>
+      <c r="U33" s="171">
         <f t="shared" si="0"/>
-        <v>-486030</v>
-      </c>
-      <c r="M33" s="149">
+        <v>-366012</v>
+      </c>
+      <c r="V33" s="149">
         <f t="shared" si="1"/>
-        <v>-0.97206000000000004</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+        <v>-0.7320239999999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34" s="141" t="s">
         <v>34</v>
       </c>
@@ -6685,17 +7559,44 @@
       <c r="J34" s="147">
         <v>-164313</v>
       </c>
-      <c r="K34" s="174"/>
-      <c r="L34" s="171">
+      <c r="K34" s="147">
+        <v>54389</v>
+      </c>
+      <c r="L34" s="147">
+        <v>163774</v>
+      </c>
+      <c r="M34" s="147">
+        <v>144181</v>
+      </c>
+      <c r="N34" s="147">
+        <v>187738</v>
+      </c>
+      <c r="O34" s="147">
+        <v>97645</v>
+      </c>
+      <c r="P34" s="147">
+        <v>68361</v>
+      </c>
+      <c r="Q34" s="147">
+        <v>75538</v>
+      </c>
+      <c r="R34" s="147">
+        <v>13283</v>
+      </c>
+      <c r="S34" s="147">
+        <v>-79847</v>
+      </c>
+      <c r="T34" s="174"/>
+      <c r="U34" s="171">
         <f t="shared" si="0"/>
-        <v>-122188</v>
-      </c>
-      <c r="M34" s="149">
+        <v>602874</v>
+      </c>
+      <c r="V34" s="149">
         <f t="shared" si="1"/>
-        <v>-0.24437600000000001</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+        <v>1.205748</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A35" s="141" t="s">
         <v>131</v>
       </c>
@@ -6724,17 +7625,44 @@
       <c r="J35" s="147">
         <v>1221</v>
       </c>
-      <c r="K35" s="174"/>
-      <c r="L35" s="171">
+      <c r="K35" s="147">
+        <v>-8694</v>
+      </c>
+      <c r="L35" s="147">
+        <v>10750</v>
+      </c>
+      <c r="M35" s="147">
+        <v>2689</v>
+      </c>
+      <c r="N35" s="147">
+        <v>35950</v>
+      </c>
+      <c r="O35" s="147">
+        <v>-19000</v>
+      </c>
+      <c r="P35" s="147">
+        <v>-10094</v>
+      </c>
+      <c r="Q35" s="147">
+        <v>-34252</v>
+      </c>
+      <c r="R35" s="147">
+        <v>7826</v>
+      </c>
+      <c r="S35" s="147">
+        <v>2697</v>
+      </c>
+      <c r="T35" s="174"/>
+      <c r="U35" s="171">
         <f t="shared" si="0"/>
-        <v>-16213</v>
-      </c>
-      <c r="M35" s="149">
+        <v>-28341</v>
+      </c>
+      <c r="V35" s="149">
         <f t="shared" si="1"/>
-        <v>-0.32425999999999999</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+        <v>-0.56681999999999999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A36" s="43" t="s">
         <v>67</v>
       </c>
@@ -6763,18 +7691,45 @@
       <c r="J36" s="147">
         <v>-11324</v>
       </c>
-      <c r="K36" s="174"/>
-      <c r="L36" s="171">
-        <f t="shared" ref="L36:L61" si="2">SUM(H36:K36)</f>
-        <v>-16332</v>
-      </c>
-      <c r="M36" s="149">
-        <f t="shared" ref="M36:M61" si="3">IFERROR(L36/F36*100,0)/10000000</f>
-        <v>-0.4083</v>
-      </c>
-      <c r="P36" s="134"/>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K36" s="147">
+        <v>7623</v>
+      </c>
+      <c r="L36" s="147">
+        <v>19040</v>
+      </c>
+      <c r="M36" s="147">
+        <v>30623</v>
+      </c>
+      <c r="N36" s="147">
+        <v>48194</v>
+      </c>
+      <c r="O36" s="147">
+        <v>2572</v>
+      </c>
+      <c r="P36" s="147">
+        <v>-4653</v>
+      </c>
+      <c r="Q36" s="147">
+        <v>2936</v>
+      </c>
+      <c r="R36" s="147">
+        <v>-6510</v>
+      </c>
+      <c r="S36" s="147">
+        <v>3100</v>
+      </c>
+      <c r="T36" s="174"/>
+      <c r="U36" s="171">
+        <f t="shared" ref="U36:U61" si="2">SUM(H36:T36)</f>
+        <v>86593</v>
+      </c>
+      <c r="V36" s="149">
+        <f t="shared" ref="V36:V61" si="3">IFERROR(U36/F36*100,0)/10000000</f>
+        <v>2.164825</v>
+      </c>
+      <c r="Y36" s="134"/>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A37" s="43" t="s">
         <v>143</v>
       </c>
@@ -6803,21 +7758,48 @@
       <c r="J37" s="147">
         <v>0</v>
       </c>
-      <c r="K37" s="174"/>
-      <c r="L37" s="171">
+      <c r="K37" s="147">
+        <v>0</v>
+      </c>
+      <c r="L37" s="147">
+        <v>0</v>
+      </c>
+      <c r="M37" s="147">
+        <v>0</v>
+      </c>
+      <c r="N37" s="147">
+        <v>0</v>
+      </c>
+      <c r="O37" s="147">
+        <v>0</v>
+      </c>
+      <c r="P37" s="147">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="147">
+        <v>0</v>
+      </c>
+      <c r="R37" s="147">
+        <v>0</v>
+      </c>
+      <c r="S37" s="147">
+        <v>0</v>
+      </c>
+      <c r="T37" s="174"/>
+      <c r="U37" s="171">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M37" s="149">
+      <c r="V37" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O37" s="5"/>
-      <c r="P37" s="134">
-        <v>-14953</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="X37" s="5"/>
+      <c r="Y37" s="134">
+        <v>-698</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A38" s="43" t="s">
         <v>144</v>
       </c>
@@ -6846,19 +7828,46 @@
       <c r="J38" s="147">
         <v>0</v>
       </c>
-      <c r="K38" s="174"/>
-      <c r="L38" s="171">
+      <c r="K38" s="147">
+        <v>0</v>
+      </c>
+      <c r="L38" s="147">
+        <v>0</v>
+      </c>
+      <c r="M38" s="147">
+        <v>0</v>
+      </c>
+      <c r="N38" s="147">
+        <v>0</v>
+      </c>
+      <c r="O38" s="147">
+        <v>0</v>
+      </c>
+      <c r="P38" s="147">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="147">
+        <v>0</v>
+      </c>
+      <c r="R38" s="147">
+        <v>0</v>
+      </c>
+      <c r="S38" s="147">
+        <v>0</v>
+      </c>
+      <c r="T38" s="174"/>
+      <c r="U38" s="171">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M38" s="149">
+      <c r="V38" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O38" s="5"/>
-      <c r="P38" s="134"/>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="X38" s="5"/>
+      <c r="Y38" s="134"/>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A39" s="142" t="s">
         <v>31</v>
       </c>
@@ -6887,24 +7896,51 @@
       <c r="J39" s="147">
         <v>-86885</v>
       </c>
-      <c r="K39" s="174"/>
-      <c r="L39" s="171">
+      <c r="K39" s="147">
+        <v>-34280</v>
+      </c>
+      <c r="L39" s="147">
+        <v>20570</v>
+      </c>
+      <c r="M39" s="147">
+        <v>34358</v>
+      </c>
+      <c r="N39" s="147">
+        <v>73135</v>
+      </c>
+      <c r="O39" s="147">
+        <v>31750</v>
+      </c>
+      <c r="P39" s="147">
+        <v>64331</v>
+      </c>
+      <c r="Q39" s="147">
+        <v>-37350</v>
+      </c>
+      <c r="R39" s="147">
+        <v>44860</v>
+      </c>
+      <c r="S39" s="147">
+        <v>50987</v>
+      </c>
+      <c r="T39" s="174"/>
+      <c r="U39" s="171">
         <f t="shared" si="2"/>
-        <v>-62629</v>
-      </c>
-      <c r="M39" s="149">
+        <v>185732</v>
+      </c>
+      <c r="V39" s="149">
         <f t="shared" si="3"/>
-        <v>-0.1565725</v>
-      </c>
-      <c r="O39" s="134">
-        <v>916223</v>
-      </c>
-      <c r="P39" s="134">
-        <f>(O40+O39)/10000000*13780</f>
-        <v>2504.5053539999999</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.46433000000000002</v>
+      </c>
+      <c r="X39" s="134">
+        <v>886814</v>
+      </c>
+      <c r="Y39" s="134">
+        <f>(X40+X39)/10000000*13780</f>
+        <v>2622.5944420000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A40" s="142" t="s">
         <v>104</v>
       </c>
@@ -6933,21 +7969,48 @@
       <c r="J40" s="147">
         <v>29559</v>
       </c>
-      <c r="K40" s="174"/>
-      <c r="L40" s="171">
+      <c r="K40" s="147">
+        <v>4260</v>
+      </c>
+      <c r="L40" s="147">
+        <v>4238</v>
+      </c>
+      <c r="M40" s="147">
+        <v>13260</v>
+      </c>
+      <c r="N40" s="147">
+        <v>930</v>
+      </c>
+      <c r="O40" s="147">
+        <v>-11624</v>
+      </c>
+      <c r="P40" s="147">
+        <v>1584</v>
+      </c>
+      <c r="Q40" s="147">
+        <v>-21848</v>
+      </c>
+      <c r="R40" s="147">
+        <v>15497</v>
+      </c>
+      <c r="S40" s="147">
+        <v>-16427</v>
+      </c>
+      <c r="T40" s="174"/>
+      <c r="U40" s="171">
         <f t="shared" si="2"/>
-        <v>74532</v>
-      </c>
-      <c r="M40" s="149">
+        <v>64402</v>
+      </c>
+      <c r="V40" s="149">
         <f t="shared" si="3"/>
-        <v>0.74531999999999998</v>
-      </c>
-      <c r="O40" s="134">
-        <v>901270</v>
-      </c>
-      <c r="P40" s="134"/>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.64402000000000004</v>
+      </c>
+      <c r="X40" s="134">
+        <v>1016375</v>
+      </c>
+      <c r="Y40" s="134"/>
+    </row>
+    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A41" s="142" t="s">
         <v>229</v>
       </c>
@@ -6976,19 +8039,46 @@
       <c r="J41" s="147">
         <v>-8067</v>
       </c>
-      <c r="K41" s="174"/>
-      <c r="L41" s="171">
+      <c r="K41" s="147">
+        <v>0</v>
+      </c>
+      <c r="L41" s="147">
+        <v>0</v>
+      </c>
+      <c r="M41" s="147">
+        <v>0</v>
+      </c>
+      <c r="N41" s="147">
+        <v>5314</v>
+      </c>
+      <c r="O41" s="147">
+        <v>16363</v>
+      </c>
+      <c r="P41" s="147">
+        <v>-12221</v>
+      </c>
+      <c r="Q41" s="147">
+        <v>-10706</v>
+      </c>
+      <c r="R41" s="147">
+        <v>-9471</v>
+      </c>
+      <c r="S41" s="147">
+        <v>11212</v>
+      </c>
+      <c r="T41" s="174"/>
+      <c r="U41" s="171">
         <f t="shared" si="2"/>
-        <v>-23279</v>
-      </c>
-      <c r="M41" s="149">
+        <v>-22788</v>
+      </c>
+      <c r="V41" s="149">
         <f t="shared" si="3"/>
-        <v>-0.46557999999999999</v>
-      </c>
-      <c r="O41" s="134"/>
-      <c r="P41" s="134"/>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+        <v>-0.45576</v>
+      </c>
+      <c r="X41" s="134"/>
+      <c r="Y41" s="134"/>
+    </row>
+    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A42" s="142" t="s">
         <v>52</v>
       </c>
@@ -7017,19 +8107,46 @@
       <c r="J42" s="147">
         <v>-43441</v>
       </c>
-      <c r="K42" s="174"/>
-      <c r="L42" s="171">
+      <c r="K42" s="147">
+        <v>0</v>
+      </c>
+      <c r="L42" s="147">
+        <v>0</v>
+      </c>
+      <c r="M42" s="147">
+        <v>0</v>
+      </c>
+      <c r="N42" s="147">
+        <v>0</v>
+      </c>
+      <c r="O42" s="147">
+        <v>0</v>
+      </c>
+      <c r="P42" s="147">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="147">
+        <v>0</v>
+      </c>
+      <c r="R42" s="147">
+        <v>-14900</v>
+      </c>
+      <c r="S42" s="147">
+        <v>270</v>
+      </c>
+      <c r="T42" s="174"/>
+      <c r="U42" s="171">
         <f t="shared" si="2"/>
-        <v>-87702</v>
-      </c>
-      <c r="M42" s="149">
+        <v>-102332</v>
+      </c>
+      <c r="V42" s="149">
         <f t="shared" si="3"/>
-        <v>-0.29233999999999999</v>
-      </c>
-      <c r="O42" s="134"/>
-      <c r="P42" s="134"/>
-    </row>
-    <row r="43" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>-0.34110666666666667</v>
+      </c>
+      <c r="X42" s="134"/>
+      <c r="Y42" s="134"/>
+    </row>
+    <row r="43" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="142" t="s">
         <v>45</v>
       </c>
@@ -7058,22 +8175,49 @@
       <c r="J43" s="147">
         <v>-55319</v>
       </c>
-      <c r="K43" s="174"/>
-      <c r="L43" s="171">
+      <c r="K43" s="147">
+        <v>-35012</v>
+      </c>
+      <c r="L43" s="147">
+        <v>0</v>
+      </c>
+      <c r="M43" s="147">
+        <v>0</v>
+      </c>
+      <c r="N43" s="147">
+        <v>38600</v>
+      </c>
+      <c r="O43" s="147">
+        <v>-10450</v>
+      </c>
+      <c r="P43" s="147">
+        <v>-17283</v>
+      </c>
+      <c r="Q43" s="147">
+        <v>-10987</v>
+      </c>
+      <c r="R43" s="147">
+        <v>-15470</v>
+      </c>
+      <c r="S43" s="147">
+        <v>-17000</v>
+      </c>
+      <c r="T43" s="174"/>
+      <c r="U43" s="171">
         <f t="shared" si="2"/>
-        <v>-68389</v>
-      </c>
-      <c r="M43" s="149">
+        <v>-135991</v>
+      </c>
+      <c r="V43" s="149">
         <f t="shared" si="3"/>
-        <v>-0.2279633333333333</v>
-      </c>
-      <c r="O43" s="134"/>
-      <c r="P43" s="193">
-        <f>P37-P39</f>
-        <v>-17457.505354000001</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+        <v>-0.45330333333333339</v>
+      </c>
+      <c r="X43" s="134"/>
+      <c r="Y43" s="193">
+        <f>Y37-Y39</f>
+        <v>-3320.5944420000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="142" t="s">
         <v>193</v>
       </c>
@@ -7102,19 +8246,46 @@
       <c r="J44" s="147">
         <v>-55340</v>
       </c>
-      <c r="K44" s="174"/>
-      <c r="L44" s="171">
+      <c r="K44" s="147">
+        <v>-35012</v>
+      </c>
+      <c r="L44" s="147">
+        <v>0</v>
+      </c>
+      <c r="M44" s="147">
+        <v>0</v>
+      </c>
+      <c r="N44" s="147">
+        <v>0</v>
+      </c>
+      <c r="O44" s="147">
+        <v>0</v>
+      </c>
+      <c r="P44" s="147">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="147">
+        <v>0</v>
+      </c>
+      <c r="R44" s="147">
+        <v>0</v>
+      </c>
+      <c r="S44" s="147">
+        <v>0</v>
+      </c>
+      <c r="T44" s="174"/>
+      <c r="U44" s="171">
         <f t="shared" si="2"/>
-        <v>-68912</v>
-      </c>
-      <c r="M44" s="149">
+        <v>-103924</v>
+      </c>
+      <c r="V44" s="149">
         <f t="shared" si="3"/>
-        <v>-0.2297066666666667</v>
-      </c>
-      <c r="O44" s="134"/>
-      <c r="P44" s="193"/>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+        <v>-0.34641333333333335</v>
+      </c>
+      <c r="X44" s="134"/>
+      <c r="Y44" s="193"/>
+    </row>
+    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A45" s="142" t="s">
         <v>292</v>
       </c>
@@ -7141,18 +8312,45 @@
       <c r="J45" s="147">
         <v>21323</v>
       </c>
-      <c r="K45" s="174"/>
-      <c r="L45" s="171">
+      <c r="K45" s="147">
+        <v>-4611</v>
+      </c>
+      <c r="L45" s="147">
+        <v>-20827</v>
+      </c>
+      <c r="M45" s="147">
+        <v>-3911</v>
+      </c>
+      <c r="N45" s="147">
+        <v>-870</v>
+      </c>
+      <c r="O45" s="147">
+        <v>3481</v>
+      </c>
+      <c r="P45" s="147">
+        <v>3737</v>
+      </c>
+      <c r="Q45" s="147">
+        <v>-3692</v>
+      </c>
+      <c r="R45" s="147">
+        <v>12581</v>
+      </c>
+      <c r="S45" s="147">
+        <v>-1948</v>
+      </c>
+      <c r="T45" s="174"/>
+      <c r="U45" s="171">
         <f t="shared" si="2"/>
-        <v>18566</v>
-      </c>
-      <c r="M45" s="149">
+        <v>2506</v>
+      </c>
+      <c r="V45" s="149">
         <f t="shared" si="3"/>
-        <v>1.8566</v>
-      </c>
-      <c r="O45" s="134"/>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.25059999999999999</v>
+      </c>
+      <c r="X45" s="134"/>
+    </row>
+    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A46" s="142" t="s">
         <v>132</v>
       </c>
@@ -7181,17 +8379,44 @@
       <c r="J46" s="147">
         <v>0</v>
       </c>
-      <c r="K46" s="174"/>
-      <c r="L46" s="171">
+      <c r="K46" s="147">
+        <v>0</v>
+      </c>
+      <c r="L46" s="147">
+        <v>0</v>
+      </c>
+      <c r="M46" s="147">
+        <v>0</v>
+      </c>
+      <c r="N46" s="147">
+        <v>0</v>
+      </c>
+      <c r="O46" s="147">
+        <v>0</v>
+      </c>
+      <c r="P46" s="147">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="147">
+        <v>0</v>
+      </c>
+      <c r="R46" s="147">
+        <v>0</v>
+      </c>
+      <c r="S46" s="147">
+        <v>0</v>
+      </c>
+      <c r="T46" s="174"/>
+      <c r="U46" s="171">
         <f t="shared" si="2"/>
         <v>2268</v>
       </c>
-      <c r="M46" s="149">
+      <c r="V46" s="149">
         <f t="shared" si="3"/>
         <v>4.5359999999999998E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A47" s="142"/>
       <c r="B47" s="143" t="s">
         <v>129</v>
@@ -7216,17 +8441,44 @@
       <c r="J47" s="147">
         <v>0</v>
       </c>
-      <c r="K47" s="174"/>
-      <c r="L47" s="171">
-        <f t="shared" ref="L47" si="4">SUM(H47:K47)</f>
-        <v>0</v>
-      </c>
-      <c r="M47" s="149">
-        <f t="shared" ref="M47" si="5">IFERROR(L47/F47*100,0)/10000000</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K47" s="147">
+        <v>0</v>
+      </c>
+      <c r="L47" s="147">
+        <v>0</v>
+      </c>
+      <c r="M47" s="147">
+        <v>0</v>
+      </c>
+      <c r="N47" s="147">
+        <v>0</v>
+      </c>
+      <c r="O47" s="147">
+        <v>0</v>
+      </c>
+      <c r="P47" s="147">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="147">
+        <v>0</v>
+      </c>
+      <c r="R47" s="147">
+        <v>0</v>
+      </c>
+      <c r="S47" s="147">
+        <v>0</v>
+      </c>
+      <c r="T47" s="174"/>
+      <c r="U47" s="171">
+        <f t="shared" ref="U47" si="4">SUM(H47:T47)</f>
+        <v>0</v>
+      </c>
+      <c r="V47" s="149">
+        <f t="shared" ref="V47" si="5">IFERROR(U47/F47*100,0)/10000000</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A48" s="142" t="s">
         <v>48</v>
       </c>
@@ -7255,17 +8507,44 @@
       <c r="J48" s="147">
         <v>43953</v>
       </c>
-      <c r="K48" s="174"/>
-      <c r="L48" s="171">
+      <c r="K48" s="147">
+        <v>39879</v>
+      </c>
+      <c r="L48" s="147">
+        <v>86560</v>
+      </c>
+      <c r="M48" s="147">
+        <v>42093</v>
+      </c>
+      <c r="N48" s="147">
+        <v>30200</v>
+      </c>
+      <c r="O48" s="147">
+        <v>44000</v>
+      </c>
+      <c r="P48" s="147">
+        <v>-89099</v>
+      </c>
+      <c r="Q48" s="147">
+        <v>-33209</v>
+      </c>
+      <c r="R48" s="147">
+        <v>-69573</v>
+      </c>
+      <c r="S48" s="147">
+        <v>184871</v>
+      </c>
+      <c r="T48" s="174"/>
+      <c r="U48" s="171">
         <f t="shared" si="2"/>
-        <v>275056</v>
-      </c>
-      <c r="M48" s="149">
+        <v>510778</v>
+      </c>
+      <c r="V48" s="149">
         <f t="shared" si="3"/>
-        <v>2.7505600000000001</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+        <v>5.10778</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A49" s="142" t="s">
         <v>301</v>
       </c>
@@ -7292,17 +8571,44 @@
       <c r="J49" s="147">
         <v>-1257</v>
       </c>
-      <c r="K49" s="174"/>
-      <c r="L49" s="171">
+      <c r="K49" s="147">
+        <v>-591</v>
+      </c>
+      <c r="L49" s="147">
+        <v>1604</v>
+      </c>
+      <c r="M49" s="147">
+        <v>-555</v>
+      </c>
+      <c r="N49" s="147">
+        <v>3060</v>
+      </c>
+      <c r="O49" s="147">
+        <v>1742</v>
+      </c>
+      <c r="P49" s="147">
+        <v>-4119</v>
+      </c>
+      <c r="Q49" s="147">
+        <v>642</v>
+      </c>
+      <c r="R49" s="147">
+        <v>-842</v>
+      </c>
+      <c r="S49" s="147">
+        <v>781</v>
+      </c>
+      <c r="T49" s="174"/>
+      <c r="U49" s="171">
         <f t="shared" si="2"/>
-        <v>-361</v>
-      </c>
-      <c r="M49" s="149">
+        <v>1361</v>
+      </c>
+      <c r="V49" s="149">
         <f t="shared" si="3"/>
-        <v>-3.61E-2</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+        <v>0.1361</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A50" s="142" t="s">
         <v>201</v>
       </c>
@@ -7325,17 +8631,44 @@
       <c r="J50" s="147">
         <v>-5450</v>
       </c>
-      <c r="K50" s="174"/>
-      <c r="L50" s="171">
+      <c r="K50" s="147">
+        <v>0</v>
+      </c>
+      <c r="L50" s="147">
+        <v>0</v>
+      </c>
+      <c r="M50" s="147">
+        <v>0</v>
+      </c>
+      <c r="N50" s="147">
+        <v>0</v>
+      </c>
+      <c r="O50" s="147">
+        <v>0</v>
+      </c>
+      <c r="P50" s="147">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="147">
+        <v>0</v>
+      </c>
+      <c r="R50" s="147">
+        <v>0</v>
+      </c>
+      <c r="S50" s="147">
+        <v>0</v>
+      </c>
+      <c r="T50" s="174"/>
+      <c r="U50" s="171">
         <f t="shared" si="2"/>
         <v>-9015</v>
       </c>
-      <c r="M50" s="149">
+      <c r="V50" s="149">
         <f t="shared" si="3"/>
         <v>-9.0149999999999994E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A51" s="143" t="s">
         <v>168</v>
       </c>
@@ -7364,17 +8697,44 @@
       <c r="J51" s="147">
         <v>0</v>
       </c>
-      <c r="K51" s="174"/>
-      <c r="L51" s="171">
+      <c r="K51" s="147">
+        <v>0</v>
+      </c>
+      <c r="L51" s="147">
+        <v>0</v>
+      </c>
+      <c r="M51" s="147">
+        <v>0</v>
+      </c>
+      <c r="N51" s="147">
+        <v>0</v>
+      </c>
+      <c r="O51" s="147">
+        <v>7000</v>
+      </c>
+      <c r="P51" s="147">
+        <v>95692</v>
+      </c>
+      <c r="Q51" s="147">
+        <v>0</v>
+      </c>
+      <c r="R51" s="147">
+        <v>0</v>
+      </c>
+      <c r="S51" s="147">
+        <v>0</v>
+      </c>
+      <c r="T51" s="174"/>
+      <c r="U51" s="171">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M51" s="149">
+        <v>102692</v>
+      </c>
+      <c r="V51" s="149">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+        <v>0.25673000000000001</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A52" s="143" t="s">
         <v>202</v>
       </c>
@@ -7403,17 +8763,44 @@
       <c r="J52" s="147">
         <v>0</v>
       </c>
-      <c r="K52" s="174"/>
-      <c r="L52" s="171">
+      <c r="K52" s="147">
+        <v>0</v>
+      </c>
+      <c r="L52" s="147">
+        <v>0</v>
+      </c>
+      <c r="M52" s="147">
+        <v>13100</v>
+      </c>
+      <c r="N52" s="147">
+        <v>129000</v>
+      </c>
+      <c r="O52" s="147">
+        <v>0</v>
+      </c>
+      <c r="P52" s="147">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="147">
+        <v>0</v>
+      </c>
+      <c r="R52" s="147">
+        <v>-32862</v>
+      </c>
+      <c r="S52" s="147">
+        <v>-67554</v>
+      </c>
+      <c r="T52" s="174"/>
+      <c r="U52" s="171">
         <f t="shared" si="2"/>
-        <v>-143525</v>
-      </c>
-      <c r="M52" s="149">
+        <v>-101841</v>
+      </c>
+      <c r="V52" s="149">
         <f t="shared" si="3"/>
-        <v>-0.35881249999999998</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+        <v>-0.25460250000000001</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A53" s="143" t="s">
         <v>33</v>
       </c>
@@ -7442,17 +8829,44 @@
       <c r="J53" s="147">
         <v>-65102</v>
       </c>
-      <c r="K53" s="174"/>
-      <c r="L53" s="171">
+      <c r="K53" s="147">
+        <v>0</v>
+      </c>
+      <c r="L53" s="147">
+        <v>0</v>
+      </c>
+      <c r="M53" s="147">
+        <v>87285</v>
+      </c>
+      <c r="N53" s="147">
+        <v>128480</v>
+      </c>
+      <c r="O53" s="147">
+        <v>54740</v>
+      </c>
+      <c r="P53" s="147">
+        <v>-4082</v>
+      </c>
+      <c r="Q53" s="147">
+        <v>70883</v>
+      </c>
+      <c r="R53" s="147">
+        <v>125257</v>
+      </c>
+      <c r="S53" s="147">
+        <v>-213545</v>
+      </c>
+      <c r="T53" s="174"/>
+      <c r="U53" s="171">
         <f t="shared" si="2"/>
-        <v>-275627</v>
-      </c>
-      <c r="M53" s="149">
+        <v>-26609</v>
+      </c>
+      <c r="V53" s="149">
         <f t="shared" si="3"/>
-        <v>-0.91875666666666678</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+        <v>-8.869666666666666E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A54" s="59" t="s">
         <v>306</v>
       </c>
@@ -7460,14 +8874,14 @@
         <v>304</v>
       </c>
       <c r="C54" s="59" t="s">
-        <v>128</v>
+        <v>308</v>
       </c>
       <c r="D54" s="141"/>
       <c r="E54" s="141" t="s">
         <v>256</v>
       </c>
       <c r="F54" s="114">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G54" s="23"/>
       <c r="H54" s="151">
@@ -7479,17 +8893,44 @@
       <c r="J54" s="151">
         <v>0</v>
       </c>
-      <c r="K54" s="174"/>
-      <c r="L54" s="171">
+      <c r="K54" s="151">
+        <v>-54610</v>
+      </c>
+      <c r="L54" s="151">
+        <v>0</v>
+      </c>
+      <c r="M54" s="151">
+        <v>37076</v>
+      </c>
+      <c r="N54" s="151">
+        <v>796100</v>
+      </c>
+      <c r="O54" s="151">
+        <v>0</v>
+      </c>
+      <c r="P54" s="151">
+        <v>84724</v>
+      </c>
+      <c r="Q54" s="151">
+        <v>29700</v>
+      </c>
+      <c r="R54" s="151">
+        <v>-340250</v>
+      </c>
+      <c r="S54" s="151">
+        <v>60645</v>
+      </c>
+      <c r="T54" s="174"/>
+      <c r="U54" s="171">
         <f t="shared" si="2"/>
-        <v>-465097</v>
-      </c>
-      <c r="M54" s="149">
+        <v>148288</v>
+      </c>
+      <c r="V54" s="149">
         <f t="shared" si="3"/>
-        <v>-0.93019399999999997</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+        <v>0.148288</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A55" s="59" t="s">
         <v>197</v>
       </c>
@@ -7518,17 +8959,44 @@
       <c r="J55" s="151">
         <v>-5750</v>
       </c>
-      <c r="K55" s="174"/>
-      <c r="L55" s="171">
+      <c r="K55" s="151">
+        <v>-6273</v>
+      </c>
+      <c r="L55" s="151">
+        <v>0</v>
+      </c>
+      <c r="M55" s="151">
+        <v>7206</v>
+      </c>
+      <c r="N55" s="151">
+        <v>10630</v>
+      </c>
+      <c r="O55" s="151">
+        <v>-2100</v>
+      </c>
+      <c r="P55" s="151">
+        <v>1783</v>
+      </c>
+      <c r="Q55" s="151">
+        <v>-6230</v>
+      </c>
+      <c r="R55" s="151">
+        <v>2235</v>
+      </c>
+      <c r="S55" s="151">
+        <v>8646</v>
+      </c>
+      <c r="T55" s="174"/>
+      <c r="U55" s="171">
         <f t="shared" si="2"/>
-        <v>-3039</v>
-      </c>
-      <c r="M55" s="149">
+        <v>12858</v>
+      </c>
+      <c r="V55" s="149">
         <f t="shared" si="3"/>
-        <v>-6.0780000000000001E-2</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+        <v>0.25716</v>
+      </c>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A56" s="59" t="s">
         <v>213</v>
       </c>
@@ -7557,17 +9025,44 @@
       <c r="J56" s="151">
         <v>0</v>
       </c>
-      <c r="K56" s="174"/>
-      <c r="L56" s="171">
+      <c r="K56" s="151">
+        <v>0</v>
+      </c>
+      <c r="L56" s="151">
+        <v>0</v>
+      </c>
+      <c r="M56" s="151">
+        <v>0</v>
+      </c>
+      <c r="N56" s="151">
+        <v>392944</v>
+      </c>
+      <c r="O56" s="151">
+        <v>0</v>
+      </c>
+      <c r="P56" s="151">
+        <v>42149</v>
+      </c>
+      <c r="Q56" s="151">
+        <v>2940</v>
+      </c>
+      <c r="R56" s="151">
+        <v>-184242</v>
+      </c>
+      <c r="S56" s="151">
+        <v>86390</v>
+      </c>
+      <c r="T56" s="174"/>
+      <c r="U56" s="171">
         <f t="shared" si="2"/>
-        <v>-77686</v>
-      </c>
-      <c r="M56" s="149">
+        <v>262495</v>
+      </c>
+      <c r="V56" s="149">
         <f t="shared" si="3"/>
-        <v>-0.194215</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+        <v>0.65623750000000003</v>
+      </c>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A57" s="59" t="s">
         <v>214</v>
       </c>
@@ -7596,17 +9091,44 @@
       <c r="J57" s="151">
         <v>0</v>
       </c>
-      <c r="K57" s="174"/>
-      <c r="L57" s="171">
+      <c r="K57" s="151">
+        <v>-25136</v>
+      </c>
+      <c r="L57" s="151">
+        <v>0</v>
+      </c>
+      <c r="M57" s="151">
+        <v>0</v>
+      </c>
+      <c r="N57" s="151">
+        <v>0</v>
+      </c>
+      <c r="O57" s="151">
+        <v>0</v>
+      </c>
+      <c r="P57" s="151">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="151">
+        <v>0</v>
+      </c>
+      <c r="R57" s="151">
+        <v>0</v>
+      </c>
+      <c r="S57" s="151">
+        <v>0</v>
+      </c>
+      <c r="T57" s="174"/>
+      <c r="U57" s="171">
         <f t="shared" si="2"/>
-        <v>-625</v>
-      </c>
-      <c r="M57" s="149">
+        <v>-25761</v>
+      </c>
+      <c r="V57" s="149">
         <f t="shared" si="3"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+        <v>-0.20608799999999999</v>
+      </c>
+    </row>
+    <row r="58" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A58" s="59" t="s">
         <v>49</v>
       </c>
@@ -7635,17 +9157,44 @@
       <c r="J58" s="151">
         <v>0</v>
       </c>
-      <c r="K58" s="174"/>
-      <c r="L58" s="171">
+      <c r="K58" s="151">
+        <v>0</v>
+      </c>
+      <c r="L58" s="151">
+        <v>0</v>
+      </c>
+      <c r="M58" s="151">
+        <v>0</v>
+      </c>
+      <c r="N58" s="151">
+        <v>69111</v>
+      </c>
+      <c r="O58" s="151">
+        <v>0</v>
+      </c>
+      <c r="P58" s="151">
+        <v>-10258</v>
+      </c>
+      <c r="Q58" s="151">
+        <v>0</v>
+      </c>
+      <c r="R58" s="151">
+        <v>0</v>
+      </c>
+      <c r="S58" s="151">
+        <v>38672</v>
+      </c>
+      <c r="T58" s="174"/>
+      <c r="U58" s="171">
         <f t="shared" si="2"/>
-        <v>-241366</v>
-      </c>
-      <c r="M58" s="149">
+        <v>-143841</v>
+      </c>
+      <c r="V58" s="149">
         <f t="shared" si="3"/>
-        <v>-0.80455333333333334</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>-0.47947000000000001</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="59" t="s">
         <v>41</v>
       </c>
@@ -7674,17 +9223,44 @@
       <c r="J59" s="151">
         <v>7757</v>
       </c>
-      <c r="K59" s="174"/>
-      <c r="L59" s="171">
+      <c r="K59" s="151">
+        <v>-39975</v>
+      </c>
+      <c r="L59" s="151">
+        <v>0</v>
+      </c>
+      <c r="M59" s="151">
+        <v>-27796</v>
+      </c>
+      <c r="N59" s="151">
+        <v>51334</v>
+      </c>
+      <c r="O59" s="151">
+        <v>0</v>
+      </c>
+      <c r="P59" s="151">
+        <v>-32505</v>
+      </c>
+      <c r="Q59" s="151">
+        <v>-52117</v>
+      </c>
+      <c r="R59" s="151">
+        <v>12133</v>
+      </c>
+      <c r="S59" s="151">
+        <v>22247</v>
+      </c>
+      <c r="T59" s="174"/>
+      <c r="U59" s="171">
         <f t="shared" si="2"/>
-        <v>-7767</v>
-      </c>
-      <c r="M59" s="149">
+        <v>-74446</v>
+      </c>
+      <c r="V59" s="149">
         <f t="shared" si="3"/>
-        <v>-3.1067999999999998E-2</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+        <v>-0.29778399999999999</v>
+      </c>
+    </row>
+    <row r="60" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A60" s="59" t="s">
         <v>300</v>
       </c>
@@ -7711,17 +9287,44 @@
       <c r="J60" s="151">
         <v>-3400</v>
       </c>
-      <c r="K60" s="174"/>
-      <c r="L60" s="171">
+      <c r="K60" s="151">
+        <v>0</v>
+      </c>
+      <c r="L60" s="151">
+        <v>0</v>
+      </c>
+      <c r="M60" s="151">
+        <v>3845</v>
+      </c>
+      <c r="N60" s="151">
+        <v>44147</v>
+      </c>
+      <c r="O60" s="151">
+        <v>317</v>
+      </c>
+      <c r="P60" s="151">
+        <v>4344</v>
+      </c>
+      <c r="Q60" s="151">
+        <v>0</v>
+      </c>
+      <c r="R60" s="151">
+        <v>0</v>
+      </c>
+      <c r="S60" s="151">
+        <v>280</v>
+      </c>
+      <c r="T60" s="174"/>
+      <c r="U60" s="171">
         <f t="shared" si="2"/>
-        <v>-3651</v>
-      </c>
-      <c r="M60" s="149">
+        <v>49282</v>
+      </c>
+      <c r="V60" s="149">
         <f t="shared" si="3"/>
-        <v>-0.14604</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1.9712799999999999</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="59" t="s">
         <v>288</v>
       </c>
@@ -7748,17 +9351,44 @@
       <c r="J61" s="151">
         <v>-6980</v>
       </c>
-      <c r="K61" s="174"/>
-      <c r="L61" s="171">
+      <c r="K61" s="151">
+        <v>-2604</v>
+      </c>
+      <c r="L61" s="151">
+        <v>2937</v>
+      </c>
+      <c r="M61" s="151">
+        <v>23984</v>
+      </c>
+      <c r="N61" s="151">
+        <v>201153</v>
+      </c>
+      <c r="O61" s="151">
+        <v>-12086</v>
+      </c>
+      <c r="P61" s="151">
+        <v>50799</v>
+      </c>
+      <c r="Q61" s="151">
+        <v>-190</v>
+      </c>
+      <c r="R61" s="151">
+        <v>-1275</v>
+      </c>
+      <c r="S61" s="151">
+        <v>-6307</v>
+      </c>
+      <c r="T61" s="174"/>
+      <c r="U61" s="171">
         <f t="shared" si="2"/>
-        <v>-69999</v>
-      </c>
-      <c r="M61" s="149">
+        <v>186412</v>
+      </c>
+      <c r="V61" s="149">
         <f t="shared" si="3"/>
-        <v>-0.13999800000000001</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0.37282399999999999</v>
+      </c>
+    </row>
+    <row r="62" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="20"/>
       <c r="B62" s="21"/>
       <c r="C62" s="20"/>
@@ -7769,11 +9399,20 @@
       <c r="H62" s="151"/>
       <c r="I62" s="151"/>
       <c r="J62" s="151"/>
-      <c r="K62" s="174"/>
-      <c r="L62" s="171"/>
-      <c r="M62" s="149"/>
-    </row>
-    <row r="63" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K62" s="151"/>
+      <c r="L62" s="151"/>
+      <c r="M62" s="151"/>
+      <c r="N62" s="151"/>
+      <c r="O62" s="151"/>
+      <c r="P62" s="151"/>
+      <c r="Q62" s="151"/>
+      <c r="R62" s="151"/>
+      <c r="S62" s="151"/>
+      <c r="T62" s="174"/>
+      <c r="U62" s="171"/>
+      <c r="V62" s="149"/>
+    </row>
+    <row r="63" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="24"/>
       <c r="B63" s="25"/>
       <c r="C63" s="26"/>
@@ -7782,31 +9421,67 @@
       <c r="F63" s="115"/>
       <c r="G63" s="16"/>
       <c r="H63" s="254">
-        <f>SUM(H4:H61)</f>
+        <f t="shared" ref="H63:T63" si="6">SUM(H4:H61)</f>
         <v>662501</v>
       </c>
       <c r="I63" s="254">
-        <f>SUM(I4:I61)</f>
+        <f t="shared" si="6"/>
         <v>-3280810</v>
       </c>
       <c r="J63" s="254">
-        <f>SUM(J4:J61)</f>
+        <f t="shared" si="6"/>
         <v>-2455834</v>
       </c>
       <c r="K63" s="254">
-        <f>SUM(K4:K61)</f>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>-445313</v>
       </c>
       <c r="L63" s="254">
-        <f>SUM(H63:K63)</f>
-        <v>-5074143</v>
-      </c>
-      <c r="M63" s="255">
-        <f>IFERROR(L63/F63*100,0)/10000000</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" s="249" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="6"/>
+        <v>359583</v>
+      </c>
+      <c r="M63" s="254">
+        <f t="shared" si="6"/>
+        <v>613475</v>
+      </c>
+      <c r="N63" s="254">
+        <f t="shared" si="6"/>
+        <v>2759535</v>
+      </c>
+      <c r="O63" s="254">
+        <f t="shared" si="6"/>
+        <v>173698</v>
+      </c>
+      <c r="P63" s="254">
+        <f t="shared" si="6"/>
+        <v>267906</v>
+      </c>
+      <c r="Q63" s="254">
+        <f t="shared" si="6"/>
+        <v>-376524</v>
+      </c>
+      <c r="R63" s="254">
+        <f t="shared" si="6"/>
+        <v>-559445</v>
+      </c>
+      <c r="S63" s="254">
+        <f t="shared" si="6"/>
+        <v>85430</v>
+      </c>
+      <c r="T63" s="254">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U63" s="254">
+        <f>SUM(H63:T63)</f>
+        <v>-2195798</v>
+      </c>
+      <c r="V63" s="255">
+        <f>IFERROR(U63/F63*100,0)/10000000</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:22" s="249" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="250"/>
       <c r="B64" s="250"/>
       <c r="C64" s="250"/>
@@ -7819,9 +9494,18 @@
       <c r="J64" s="250"/>
       <c r="K64" s="250"/>
       <c r="L64" s="250"/>
-      <c r="M64" s="252"/>
-    </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M64" s="250"/>
+      <c r="N64" s="250"/>
+      <c r="O64" s="250"/>
+      <c r="P64" s="250"/>
+      <c r="Q64" s="250"/>
+      <c r="R64" s="250"/>
+      <c r="S64" s="250"/>
+      <c r="T64" s="250"/>
+      <c r="U64" s="250"/>
+      <c r="V64" s="252"/>
+    </row>
+    <row r="65" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A65" s="202" t="s">
         <v>241</v>
       </c>
@@ -7850,18 +9534,45 @@
       <c r="J65" s="162">
         <v>0</v>
       </c>
-      <c r="K65" s="246"/>
-      <c r="L65" s="247">
-        <f>SUM(H65:K65)</f>
-        <v>-72776</v>
-      </c>
-      <c r="M65" s="248">
-        <f>IFERROR(L65/F65*100,0)/10000000</f>
-        <v>-0.2425866666666667</v>
-      </c>
-      <c r="P65" s="134"/>
-    </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K65" s="162">
+        <v>-11375</v>
+      </c>
+      <c r="L65" s="162">
+        <v>0</v>
+      </c>
+      <c r="M65" s="162">
+        <v>0</v>
+      </c>
+      <c r="N65" s="162">
+        <v>127500</v>
+      </c>
+      <c r="O65" s="162">
+        <v>37317</v>
+      </c>
+      <c r="P65" s="162">
+        <v>65831</v>
+      </c>
+      <c r="Q65" s="162">
+        <v>-40665</v>
+      </c>
+      <c r="R65" s="162">
+        <v>-78380</v>
+      </c>
+      <c r="S65" s="162">
+        <v>156647</v>
+      </c>
+      <c r="T65" s="246"/>
+      <c r="U65" s="247">
+        <f>SUM(H65:T65)</f>
+        <v>184099</v>
+      </c>
+      <c r="V65" s="248">
+        <f>IFERROR(U65/F65*100,0)/10000000</f>
+        <v>0.61366333333333345</v>
+      </c>
+      <c r="Y65" s="134"/>
+    </row>
+    <row r="66" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A66" s="202" t="s">
         <v>273</v>
       </c>
@@ -7888,18 +9599,45 @@
       <c r="J66" s="162">
         <v>0</v>
       </c>
-      <c r="K66" s="174"/>
-      <c r="L66" s="171">
-        <f>SUM(H66:K66)</f>
-        <v>-310900</v>
-      </c>
-      <c r="M66" s="149">
-        <f>IFERROR(L66/F66*100,0)/10000000</f>
-        <v>0</v>
-      </c>
-      <c r="O66" s="134"/>
-    </row>
-    <row r="67" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K66" s="162">
+        <v>0</v>
+      </c>
+      <c r="L66" s="162">
+        <v>100</v>
+      </c>
+      <c r="M66" s="162">
+        <v>0</v>
+      </c>
+      <c r="N66" s="162">
+        <v>276000</v>
+      </c>
+      <c r="O66" s="162">
+        <v>0</v>
+      </c>
+      <c r="P66" s="162">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="162">
+        <v>0</v>
+      </c>
+      <c r="R66" s="162">
+        <v>0</v>
+      </c>
+      <c r="S66" s="162">
+        <v>198600</v>
+      </c>
+      <c r="T66" s="174"/>
+      <c r="U66" s="171">
+        <f>SUM(H66:T66)</f>
+        <v>163800</v>
+      </c>
+      <c r="V66" s="149">
+        <f>IFERROR(U66/F66*100,0)/10000000</f>
+        <v>0</v>
+      </c>
+      <c r="X66" s="134"/>
+    </row>
+    <row r="67" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="198"/>
       <c r="B67" s="20"/>
       <c r="C67" s="20"/>
@@ -7910,14 +9648,23 @@
       <c r="H67" s="151"/>
       <c r="I67" s="151"/>
       <c r="J67" s="151"/>
-      <c r="K67" s="175"/>
-      <c r="L67" s="172"/>
-      <c r="M67" s="66"/>
-      <c r="O67" s="237"/>
-      <c r="P67" s="134"/>
-      <c r="Q67" s="237"/>
-    </row>
-    <row r="68" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K67" s="151"/>
+      <c r="L67" s="151"/>
+      <c r="M67" s="151"/>
+      <c r="N67" s="151"/>
+      <c r="O67" s="151"/>
+      <c r="P67" s="151"/>
+      <c r="Q67" s="151"/>
+      <c r="R67" s="151"/>
+      <c r="S67" s="151"/>
+      <c r="T67" s="175"/>
+      <c r="U67" s="172"/>
+      <c r="V67" s="66"/>
+      <c r="X67" s="237"/>
+      <c r="Y67" s="134"/>
+      <c r="Z67" s="237"/>
+    </row>
+    <row r="68" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="200"/>
       <c r="B68" s="16"/>
       <c r="C68" s="16"/>
@@ -7926,138 +9673,174 @@
       <c r="F68" s="74"/>
       <c r="G68" s="17"/>
       <c r="H68" s="170">
-        <f>SUM(H65:H66)</f>
+        <f t="shared" ref="H68:T68" si="7">SUM(H65:H66)</f>
         <v>4780</v>
       </c>
       <c r="I68" s="170">
-        <f>SUM(I65:I66)</f>
+        <f t="shared" si="7"/>
         <v>-388456</v>
       </c>
       <c r="J68" s="170">
-        <f>SUM(J65:J66)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K68" s="170">
-        <f>SUM(K65:K66)</f>
-        <v>0</v>
-      </c>
-      <c r="L68" s="254">
-        <f>SUM(H68:K68)</f>
-        <v>-383676</v>
-      </c>
-      <c r="M68" s="19"/>
-      <c r="O68" s="5"/>
-      <c r="P68" s="134"/>
-      <c r="Q68" s="237"/>
-    </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="O69" s="134"/>
-      <c r="P69" s="134"/>
-      <c r="Q69" s="237"/>
-    </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="O70" s="134"/>
-      <c r="P70" s="134"/>
-      <c r="Q70" s="237"/>
-    </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="O71" s="134"/>
-      <c r="P71" s="134"/>
-      <c r="Q71" s="237"/>
-    </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="O72" s="134"/>
-      <c r="P72" s="134"/>
-      <c r="Q72" s="237"/>
-    </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="O73" s="134"/>
-      <c r="P73" s="237"/>
-      <c r="Q73" s="237"/>
-    </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="O74" s="237"/>
-      <c r="P74" s="237"/>
-      <c r="Q74" s="237"/>
+        <f t="shared" si="7"/>
+        <v>-11375</v>
+      </c>
+      <c r="L68" s="170">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+      <c r="M68" s="170">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="N68" s="170">
+        <f t="shared" si="7"/>
+        <v>403500</v>
+      </c>
+      <c r="O68" s="170">
+        <f t="shared" si="7"/>
+        <v>37317</v>
+      </c>
+      <c r="P68" s="170">
+        <f t="shared" si="7"/>
+        <v>65831</v>
+      </c>
+      <c r="Q68" s="170">
+        <f t="shared" si="7"/>
+        <v>-40665</v>
+      </c>
+      <c r="R68" s="170">
+        <f t="shared" si="7"/>
+        <v>-78380</v>
+      </c>
+      <c r="S68" s="170">
+        <f t="shared" si="7"/>
+        <v>355247</v>
+      </c>
+      <c r="T68" s="170">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U68" s="254">
+        <f>SUM(H68:T68)</f>
+        <v>347899</v>
+      </c>
+      <c r="V68" s="19"/>
+      <c r="X68" s="5"/>
+      <c r="Y68" s="134"/>
+      <c r="Z68" s="237"/>
+    </row>
+    <row r="69" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="X69" s="134"/>
+      <c r="Y69" s="134"/>
+      <c r="Z69" s="237"/>
+    </row>
+    <row r="70" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="X70" s="134"/>
+      <c r="Y70" s="134"/>
+      <c r="Z70" s="237"/>
+    </row>
+    <row r="71" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="X71" s="134"/>
+      <c r="Y71" s="134"/>
+      <c r="Z71" s="237"/>
+    </row>
+    <row r="72" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="X72" s="134"/>
+      <c r="Y72" s="134"/>
+      <c r="Z72" s="237"/>
+    </row>
+    <row r="73" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="X73" s="134"/>
+      <c r="Y73" s="237"/>
+      <c r="Z73" s="237"/>
+    </row>
+    <row r="74" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="X74" s="237"/>
+      <c r="Y74" s="237"/>
+      <c r="Z74" s="237"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G2 A3:G3 M43:M44 M51:M53 M63:M64 M46 M9:M17 M23:M24 M19:M21 L9:L24 L5:M8 L26:L46 M26:M39 L61:M62 L50:L53 M68 L54:M59 H2:M3 A65:M67 A63:G63 L48:M48 A4:K62 A68:K68">
-    <cfRule type="expression" dxfId="388" priority="16">
+  <conditionalFormatting sqref="G2 A3:G3 V43:V44 V51:V53 V63:V64 V46 V9:V17 V23:V24 V19:V21 U9:U24 U5:V8 U26:U46 V26:V39 U61:V62 U50:U53 V68 U54:V59 H2:V3 A65:V67 A63:G63 U48:V48 A4:T62 A68:T68">
+    <cfRule type="expression" dxfId="389" priority="16">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M40">
-    <cfRule type="expression" dxfId="387" priority="15">
+  <conditionalFormatting sqref="V40">
+    <cfRule type="expression" dxfId="388" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M42">
-    <cfRule type="expression" dxfId="386" priority="14">
+  <conditionalFormatting sqref="V42">
+    <cfRule type="expression" dxfId="387" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L4:M4">
-    <cfRule type="expression" dxfId="385" priority="13">
+  <conditionalFormatting sqref="U4:V4">
+    <cfRule type="expression" dxfId="386" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M41">
-    <cfRule type="expression" dxfId="384" priority="12">
+  <conditionalFormatting sqref="V41">
+    <cfRule type="expression" dxfId="385" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M18">
-    <cfRule type="expression" dxfId="383" priority="11">
+  <conditionalFormatting sqref="V18">
+    <cfRule type="expression" dxfId="384" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M50">
-    <cfRule type="expression" dxfId="382" priority="10">
+  <conditionalFormatting sqref="V50">
+    <cfRule type="expression" dxfId="383" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M22">
-    <cfRule type="expression" dxfId="381" priority="9">
+  <conditionalFormatting sqref="V22">
+    <cfRule type="expression" dxfId="382" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L63">
-    <cfRule type="expression" dxfId="380" priority="8">
+  <conditionalFormatting sqref="U63">
+    <cfRule type="expression" dxfId="381" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M45">
-    <cfRule type="expression" dxfId="379" priority="7">
+  <conditionalFormatting sqref="V45">
+    <cfRule type="expression" dxfId="380" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L25:M25">
-    <cfRule type="expression" dxfId="378" priority="6">
+  <conditionalFormatting sqref="U25:V25">
+    <cfRule type="expression" dxfId="379" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L60:M60">
-    <cfRule type="expression" dxfId="377" priority="5">
+  <conditionalFormatting sqref="U60:V60">
+    <cfRule type="expression" dxfId="378" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L49:M49">
-    <cfRule type="expression" dxfId="376" priority="4">
+  <conditionalFormatting sqref="U49:V49">
+    <cfRule type="expression" dxfId="377" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L68">
-    <cfRule type="expression" dxfId="375" priority="3">
+  <conditionalFormatting sqref="U68">
+    <cfRule type="expression" dxfId="376" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H63:K63">
-    <cfRule type="expression" dxfId="374" priority="2">
+  <conditionalFormatting sqref="H63:T63">
+    <cfRule type="expression" dxfId="375" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L47:M47">
-    <cfRule type="expression" dxfId="373" priority="1">
+  <conditionalFormatting sqref="U47:V47">
+    <cfRule type="expression" dxfId="374" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14353,72 +16136,72 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2 A3:G3 AF43:AF44 AF50:AF52 AF62:AF63 H2:AF3 AF46:AF47 AF9:AF17 AF23:AF24 AF19:AF21 AE9:AE24 AE5:AF8 AE26:AE47 AF26:AF39 AE60:AF61 AE49:AE52 A64:AF66 AF67 A67:AD67 AE53:AF58 A4:AD62">
-    <cfRule type="expression" dxfId="372" priority="18">
+    <cfRule type="expression" dxfId="373" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF40">
-    <cfRule type="expression" dxfId="371" priority="17">
+    <cfRule type="expression" dxfId="372" priority="17">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF42">
-    <cfRule type="expression" dxfId="370" priority="16">
+    <cfRule type="expression" dxfId="371" priority="16">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE4:AF4">
-    <cfRule type="expression" dxfId="369" priority="14">
+    <cfRule type="expression" dxfId="370" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF41">
-    <cfRule type="expression" dxfId="368" priority="12">
+    <cfRule type="expression" dxfId="369" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF18">
-    <cfRule type="expression" dxfId="367" priority="11">
+    <cfRule type="expression" dxfId="368" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF49">
-    <cfRule type="expression" dxfId="366" priority="10">
+    <cfRule type="expression" dxfId="367" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF22">
-    <cfRule type="expression" dxfId="365" priority="9">
+    <cfRule type="expression" dxfId="366" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE62">
-    <cfRule type="expression" dxfId="364" priority="8">
+    <cfRule type="expression" dxfId="365" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF45">
-    <cfRule type="expression" dxfId="363" priority="7">
+    <cfRule type="expression" dxfId="364" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE25:AF25">
-    <cfRule type="expression" dxfId="362" priority="4">
+    <cfRule type="expression" dxfId="363" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE59:AF59">
-    <cfRule type="expression" dxfId="361" priority="3">
+    <cfRule type="expression" dxfId="362" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE48:AF48">
-    <cfRule type="expression" dxfId="360" priority="2">
+    <cfRule type="expression" dxfId="361" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE67">
-    <cfRule type="expression" dxfId="359" priority="1">
+    <cfRule type="expression" dxfId="360" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14534,12 +16317,12 @@
         <v>-0.33282</v>
       </c>
       <c r="I4" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-11682</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>-15578</v>
       </c>
       <c r="J4" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-0.23363999999999999</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>-0.31156</v>
       </c>
       <c r="K4" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
@@ -14551,11 +16334,11 @@
       </c>
       <c r="M4" s="71">
         <f t="shared" ref="M4:N58" si="0">G4+I4+K4</f>
-        <v>-28323</v>
+        <v>-32219</v>
       </c>
       <c r="N4" s="166">
         <f t="shared" si="0"/>
-        <v>-0.56645999999999996</v>
+        <v>-0.64437999999999995</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -14586,12 +16369,12 @@
         <v>0.43602000000000002</v>
       </c>
       <c r="I5" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-196109</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>-293440</v>
       </c>
       <c r="J5" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-0.65369666666666659</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>-0.97813333333333319</v>
       </c>
       <c r="K5" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
@@ -14603,11 +16386,11 @@
       </c>
       <c r="M5" s="71">
         <f t="shared" si="0"/>
-        <v>-65303</v>
+        <v>-162634</v>
       </c>
       <c r="N5" s="166">
         <f t="shared" si="0"/>
-        <v>-0.21767666666666657</v>
+        <v>-0.54211333333333322</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -14638,12 +16421,12 @@
         <v>0.13245999999999999</v>
       </c>
       <c r="I6" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>14042</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>-238623</v>
       </c>
       <c r="J6" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>4.680666666666667E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>-0.79540999999999995</v>
       </c>
       <c r="K6" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
@@ -14655,11 +16438,11 @@
       </c>
       <c r="M6" s="71">
         <f t="shared" si="0"/>
-        <v>53780</v>
+        <v>-198885</v>
       </c>
       <c r="N6" s="166">
         <f t="shared" si="0"/>
-        <v>0.17926666666666666</v>
+        <v>-0.66294999999999993</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -14690,12 +16473,12 @@
         <v>-2.1232133333333336</v>
       </c>
       <c r="I7" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>33535</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>-18439</v>
       </c>
       <c r="J7" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>0.22356666666666669</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>-0.12292666666666666</v>
       </c>
       <c r="K7" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
@@ -14707,11 +16490,11 @@
       </c>
       <c r="M7" s="71">
         <f t="shared" si="0"/>
-        <v>-284947</v>
+        <v>-336921</v>
       </c>
       <c r="N7" s="166">
         <f t="shared" si="0"/>
-        <v>-1.8996466666666669</v>
+        <v>-2.2461400000000005</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -14742,12 +16525,12 @@
         <v>1.5575173333333334</v>
       </c>
       <c r="I8" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-814500</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>-635277</v>
       </c>
       <c r="J8" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-0.54300000000000004</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>-0.42351800000000001</v>
       </c>
       <c r="K8" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
@@ -14759,11 +16542,11 @@
       </c>
       <c r="M8" s="71">
         <f t="shared" si="0"/>
-        <v>1521776</v>
+        <v>1700999</v>
       </c>
       <c r="N8" s="166">
         <f t="shared" si="0"/>
-        <v>1.0145173333333335</v>
+        <v>1.1339993333333334</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -14794,12 +16577,12 @@
         <v>0.67657666666666672</v>
       </c>
       <c r="I9" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>85911</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>176530</v>
       </c>
       <c r="J9" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>0.14318500000000001</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>0.29421666666666668</v>
       </c>
       <c r="K9" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
@@ -14811,11 +16594,11 @@
       </c>
       <c r="M9" s="71">
         <f t="shared" si="0"/>
-        <v>491857</v>
+        <v>582476</v>
       </c>
       <c r="N9" s="166">
         <f t="shared" si="0"/>
-        <v>0.81976166666666672</v>
+        <v>0.9707933333333334</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -14846,12 +16629,12 @@
         <v>1.094E-2</v>
       </c>
       <c r="I10" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>4662</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>11783</v>
       </c>
       <c r="J10" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>4.6620000000000002E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>0.11783</v>
       </c>
       <c r="K10" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
@@ -14863,11 +16646,11 @@
       </c>
       <c r="M10" s="71">
         <f t="shared" si="0"/>
-        <v>5756</v>
+        <v>12877</v>
       </c>
       <c r="N10" s="166">
         <f t="shared" si="0"/>
-        <v>5.756E-2</v>
+        <v>0.12877</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -14898,12 +16681,12 @@
         <v>0.83004</v>
       </c>
       <c r="I11" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-84149</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>-71473</v>
       </c>
       <c r="J11" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-0.33659600000000001</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>-0.28589199999999998</v>
       </c>
       <c r="K11" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
@@ -14915,11 +16698,11 @@
       </c>
       <c r="M11" s="71">
         <f t="shared" si="0"/>
-        <v>123361</v>
+        <v>136037</v>
       </c>
       <c r="N11" s="166">
         <f t="shared" si="0"/>
-        <v>0.49344399999999999</v>
+        <v>0.54414800000000008</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -14950,11 +16733,11 @@
         <v>7.4260000000000007E-2</v>
       </c>
       <c r="I12" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="J12" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="K12" s="153">
@@ -15002,12 +16785,12 @@
         <v>0.40267999999999998</v>
       </c>
       <c r="I13" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>23043</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>32201</v>
       </c>
       <c r="J13" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>0.23043</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>0.32201000000000002</v>
       </c>
       <c r="K13" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
@@ -15019,11 +16802,11 @@
       </c>
       <c r="M13" s="71">
         <f t="shared" si="0"/>
-        <v>63311</v>
+        <v>72469</v>
       </c>
       <c r="N13" s="166">
         <f t="shared" si="0"/>
-        <v>0.63310999999999995</v>
+        <v>0.72469000000000006</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -15054,12 +16837,12 @@
         <v>9.3581818181818183E-2</v>
       </c>
       <c r="I14" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-69794</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>-70426</v>
       </c>
       <c r="J14" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-0.31724545454545455</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>-0.3201181818181818</v>
       </c>
       <c r="K14" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
@@ -15071,11 +16854,11 @@
       </c>
       <c r="M14" s="71">
         <f t="shared" ref="M14" si="1">G14+I14+K14</f>
-        <v>-49206</v>
+        <v>-49838</v>
       </c>
       <c r="N14" s="166">
         <f t="shared" ref="N14" si="2">H14+J14+L14</f>
-        <v>-0.22366363636363637</v>
+        <v>-0.22653636363636362</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
@@ -15106,11 +16889,11 @@
         <v>0</v>
       </c>
       <c r="I15" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="J15" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="K15" s="153">
@@ -15158,12 +16941,12 @@
         <v>0.19069599999999998</v>
       </c>
       <c r="I16" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-106373</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>-108327</v>
       </c>
       <c r="J16" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-0.42549199999999998</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>-0.43330800000000003</v>
       </c>
       <c r="K16" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
@@ -15175,11 +16958,11 @@
       </c>
       <c r="M16" s="71">
         <f t="shared" si="0"/>
-        <v>-58699</v>
+        <v>-60653</v>
       </c>
       <c r="N16" s="166">
         <f t="shared" si="0"/>
-        <v>-0.234796</v>
+        <v>-0.24261200000000005</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -15210,12 +16993,12 @@
         <v>0.87504249999999995</v>
       </c>
       <c r="I17" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>7825</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>217</v>
       </c>
       <c r="J17" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>1.95625E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>5.4250000000000001E-4</v>
       </c>
       <c r="K17" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
@@ -15227,11 +17010,11 @@
       </c>
       <c r="M17" s="71">
         <f t="shared" si="0"/>
-        <v>357842</v>
+        <v>350234</v>
       </c>
       <c r="N17" s="166">
         <f t="shared" si="0"/>
-        <v>0.89460499999999998</v>
+        <v>0.87558499999999995</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
@@ -15262,12 +17045,12 @@
         <v>0.54622727272727267</v>
       </c>
       <c r="I18" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-57635</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>45881</v>
       </c>
       <c r="J18" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-0.52395454545454545</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>0.41710000000000003</v>
       </c>
       <c r="K18" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
@@ -15279,11 +17062,11 @@
       </c>
       <c r="M18" s="71">
         <f t="shared" si="0"/>
-        <v>2450</v>
+        <v>105966</v>
       </c>
       <c r="N18" s="166">
         <f t="shared" si="0"/>
-        <v>2.2272727272727222E-2</v>
+        <v>0.9633272727272727</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
@@ -15312,11 +17095,11 @@
         <v>0</v>
       </c>
       <c r="I19" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="J19" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="K19" s="153">
@@ -15362,11 +17145,11 @@
         <v>0</v>
       </c>
       <c r="I20" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="J20" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="K20" s="153">
@@ -15414,12 +17197,12 @@
         <v>0.66898666666666673</v>
       </c>
       <c r="I21" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-77519</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>79424</v>
       </c>
       <c r="J21" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-0.51679333333333344</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>0.52949333333333337</v>
       </c>
       <c r="K21" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
@@ -15431,11 +17214,11 @@
       </c>
       <c r="M21" s="71">
         <f t="shared" si="0"/>
-        <v>22829</v>
+        <v>179772</v>
       </c>
       <c r="N21" s="166">
         <f t="shared" si="0"/>
-        <v>0.15219333333333329</v>
+        <v>1.19848</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
@@ -15466,11 +17249,11 @@
         <v>-0.1855</v>
       </c>
       <c r="I22" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="J22" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="K22" s="153">
@@ -15518,12 +17301,12 @@
         <v>3.0062818181818174</v>
       </c>
       <c r="I23" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-108839</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>-12461</v>
       </c>
       <c r="J23" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-0.98944545454545452</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>-0.11328181818181819</v>
       </c>
       <c r="K23" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
@@ -15535,11 +17318,11 @@
       </c>
       <c r="M23" s="71">
         <f t="shared" si="0"/>
-        <v>221852</v>
+        <v>318230</v>
       </c>
       <c r="N23" s="166">
         <f t="shared" si="0"/>
-        <v>2.0168363636363629</v>
+        <v>2.8929999999999993</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -15570,12 +17353,12 @@
         <v>3.8297043478260866</v>
       </c>
       <c r="I24" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>243866</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>-222164</v>
       </c>
       <c r="J24" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>1.0602869565217392</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>-0.96593043478260876</v>
       </c>
       <c r="K24" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
@@ -15587,11 +17370,11 @@
       </c>
       <c r="M24" s="71">
         <f t="shared" si="0"/>
-        <v>1124698</v>
+        <v>658668</v>
       </c>
       <c r="N24" s="166">
         <f t="shared" si="0"/>
-        <v>4.8899913043478254</v>
+        <v>2.8637739130434778</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
@@ -15620,12 +17403,12 @@
         <v>-0.12470000000000001</v>
       </c>
       <c r="I25" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>2629</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>-8496</v>
       </c>
       <c r="J25" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>0.13145000000000001</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>-0.42480000000000001</v>
       </c>
       <c r="K25" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
@@ -15637,11 +17420,11 @@
       </c>
       <c r="M25" s="71">
         <f t="shared" ref="M25" si="5">G25+I25+K25</f>
-        <v>135</v>
+        <v>-10990</v>
       </c>
       <c r="N25" s="166">
         <f t="shared" ref="N25" si="6">H25+J25+L25</f>
-        <v>6.750000000000006E-3</v>
+        <v>-0.54949999999999999</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
@@ -15672,12 +17455,12 @@
         <v>-0.19694</v>
       </c>
       <c r="I26" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-86170</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>-81580</v>
       </c>
       <c r="J26" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-0.17233999999999999</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>-0.16316</v>
       </c>
       <c r="K26" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
@@ -15689,11 +17472,11 @@
       </c>
       <c r="M26" s="71">
         <f t="shared" si="0"/>
-        <v>-184640</v>
+        <v>-180050</v>
       </c>
       <c r="N26" s="166">
         <f t="shared" si="0"/>
-        <v>-0.36928</v>
+        <v>-0.36009999999999998</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
@@ -15724,12 +17507,12 @@
         <v>3.272097</v>
       </c>
       <c r="I27" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-561931</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>-386636</v>
       </c>
       <c r="J27" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-0.56193099999999996</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>-0.38663599999999998</v>
       </c>
       <c r="K27" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
@@ -15741,11 +17524,11 @@
       </c>
       <c r="M27" s="71">
         <f t="shared" si="0"/>
-        <v>2710166</v>
+        <v>2885461</v>
       </c>
       <c r="N27" s="166">
         <f t="shared" si="0"/>
-        <v>2.7101660000000001</v>
+        <v>2.8854610000000003</v>
       </c>
       <c r="O27" s="131"/>
     </row>
@@ -15777,11 +17560,11 @@
         <v>1.9415292307692309</v>
       </c>
       <c r="I28" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
         <v>-787722</v>
       </c>
       <c r="J28" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
         <v>-0.60594000000000003</v>
       </c>
       <c r="K28" s="153">
@@ -15829,11 +17612,11 @@
         <v>1.7384333333333335</v>
       </c>
       <c r="I29" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
         <v>-87345</v>
       </c>
       <c r="J29" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
         <v>-0.58230000000000004</v>
       </c>
       <c r="K29" s="153">
@@ -15881,11 +17664,11 @@
         <v>1.7532033333333337</v>
       </c>
       <c r="I30" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
         <v>-348894</v>
       </c>
       <c r="J30" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
         <v>-0.58148999999999995</v>
       </c>
       <c r="K30" s="153">
@@ -15933,11 +17716,11 @@
         <v>2.1659760000000001</v>
       </c>
       <c r="I31" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
         <v>-87240</v>
       </c>
       <c r="J31" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
         <v>-0.69791999999999998</v>
       </c>
       <c r="K31" s="153">
@@ -15985,11 +17768,11 @@
         <v>1.8045199999999999</v>
       </c>
       <c r="I32" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
         <v>-87014</v>
       </c>
       <c r="J32" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
         <v>-0.58009333333333335</v>
       </c>
       <c r="K32" s="153">
@@ -16037,12 +17820,12 @@
         <v>2.4106299999999998</v>
       </c>
       <c r="I33" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-486030</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>-366012</v>
       </c>
       <c r="J33" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-0.97206000000000004</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>-0.7320239999999999</v>
       </c>
       <c r="K33" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
@@ -16054,11 +17837,11 @@
       </c>
       <c r="M33" s="71">
         <f t="shared" si="0"/>
-        <v>719285</v>
+        <v>839303</v>
       </c>
       <c r="N33" s="166">
         <f t="shared" si="0"/>
-        <v>1.4385699999999999</v>
+        <v>1.6786059999999998</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
@@ -16089,12 +17872,12 @@
         <v>0.91498999999999997</v>
       </c>
       <c r="I34" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-122188</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>602874</v>
       </c>
       <c r="J34" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-0.24437600000000001</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>1.205748</v>
       </c>
       <c r="K34" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
@@ -16106,11 +17889,11 @@
       </c>
       <c r="M34" s="71">
         <f t="shared" si="0"/>
-        <v>335307</v>
+        <v>1060369</v>
       </c>
       <c r="N34" s="166">
         <f t="shared" si="0"/>
-        <v>0.67061399999999993</v>
+        <v>2.1207380000000002</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
@@ -16141,12 +17924,12 @@
         <v>-0.30049999999999999</v>
       </c>
       <c r="I35" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-16213</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>-28341</v>
       </c>
       <c r="J35" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-0.32425999999999999</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>-0.56681999999999999</v>
       </c>
       <c r="K35" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
@@ -16158,11 +17941,11 @@
       </c>
       <c r="M35" s="71">
         <f t="shared" si="0"/>
-        <v>-31238</v>
+        <v>-43366</v>
       </c>
       <c r="N35" s="166">
         <f t="shared" si="0"/>
-        <v>-0.62475999999999998</v>
+        <v>-0.86731999999999998</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
@@ -16193,12 +17976,12 @@
         <v>-2.9686249999999998</v>
       </c>
       <c r="I36" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-16332</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>86593</v>
       </c>
       <c r="J36" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-0.4083</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>2.164825</v>
       </c>
       <c r="K36" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
@@ -16210,11 +17993,11 @@
       </c>
       <c r="M36" s="71">
         <f t="shared" si="0"/>
-        <v>-135077</v>
+        <v>-32152</v>
       </c>
       <c r="N36" s="166">
         <f t="shared" si="0"/>
-        <v>-3.376925</v>
+        <v>-0.80379999999999985</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
@@ -16245,11 +18028,11 @@
         <v>-4.3029999999999999</v>
       </c>
       <c r="I37" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="J37" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="K37" s="153">
@@ -16297,11 +18080,11 @@
         <v>-1.2910600000000001</v>
       </c>
       <c r="I38" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="J38" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="K38" s="153">
@@ -16349,12 +18132,12 @@
         <v>0.90171250000000003</v>
       </c>
       <c r="I39" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-62629</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>185732</v>
       </c>
       <c r="J39" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-0.1565725</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>0.46433000000000002</v>
       </c>
       <c r="K39" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
@@ -16366,11 +18149,11 @@
       </c>
       <c r="M39" s="71">
         <f t="shared" si="0"/>
-        <v>298056</v>
+        <v>546417</v>
       </c>
       <c r="N39" s="166">
         <f t="shared" si="0"/>
-        <v>0.74514000000000002</v>
+        <v>1.3660425</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
@@ -16401,12 +18184,12 @@
         <v>1.50383</v>
       </c>
       <c r="I40" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>74532</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>64402</v>
       </c>
       <c r="J40" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>0.74531999999999998</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>0.64402000000000004</v>
       </c>
       <c r="K40" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
@@ -16418,11 +18201,11 @@
       </c>
       <c r="M40" s="71">
         <f t="shared" si="0"/>
-        <v>224915</v>
+        <v>214785</v>
       </c>
       <c r="N40" s="166">
         <f t="shared" si="0"/>
-        <v>2.2491500000000002</v>
+        <v>2.14785</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
@@ -16453,12 +18236,12 @@
         <v>-1.0421199999999999</v>
       </c>
       <c r="I41" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-23279</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>-22788</v>
       </c>
       <c r="J41" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-0.46557999999999999</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>-0.45576</v>
       </c>
       <c r="K41" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
@@ -16470,11 +18253,11 @@
       </c>
       <c r="M41" s="71">
         <f t="shared" si="0"/>
-        <v>-75385</v>
+        <v>-74894</v>
       </c>
       <c r="N41" s="166">
         <f t="shared" si="0"/>
-        <v>-1.5076999999999998</v>
+        <v>-1.4978799999999999</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
@@ -16505,12 +18288,12 @@
         <v>0.2639933333333333</v>
       </c>
       <c r="I42" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-68389</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>-135991</v>
       </c>
       <c r="J42" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-0.2279633333333333</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>-0.45330333333333339</v>
       </c>
       <c r="K42" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
@@ -16522,11 +18305,11 @@
       </c>
       <c r="M42" s="71">
         <f t="shared" si="0"/>
-        <v>10809</v>
+        <v>-56793</v>
       </c>
       <c r="N42" s="166">
         <f t="shared" si="0"/>
-        <v>3.6030000000000006E-2</v>
+        <v>-0.18931000000000009</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
@@ -16557,12 +18340,12 @@
         <v>0.21359</v>
       </c>
       <c r="I43" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-68912</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>-103924</v>
       </c>
       <c r="J43" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-0.2297066666666667</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>-0.34641333333333335</v>
       </c>
       <c r="K43" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
@@ -16574,11 +18357,11 @@
       </c>
       <c r="M43" s="71">
         <f t="shared" si="0"/>
-        <v>-4835</v>
+        <v>-39847</v>
       </c>
       <c r="N43" s="166">
         <f t="shared" si="0"/>
-        <v>-1.6116666666666696E-2</v>
+        <v>-0.13282333333333335</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
@@ -16609,12 +18392,12 @@
         <v>0.47612666666666659</v>
       </c>
       <c r="I44" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-87702</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>-102332</v>
       </c>
       <c r="J44" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-0.29233999999999999</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>-0.34110666666666667</v>
       </c>
       <c r="K44" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
@@ -16626,11 +18409,11 @@
       </c>
       <c r="M44" s="71">
         <f t="shared" si="0"/>
-        <v>55136</v>
+        <v>40506</v>
       </c>
       <c r="N44" s="166">
         <f t="shared" si="0"/>
-        <v>0.1837866666666666</v>
+        <v>0.13501999999999992</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
@@ -16659,12 +18442,12 @@
         <v>-1.2015</v>
       </c>
       <c r="I45" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>18566</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>2506</v>
       </c>
       <c r="J45" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>1.8566</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>0.25059999999999999</v>
       </c>
       <c r="K45" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
@@ -16676,11 +18459,11 @@
       </c>
       <c r="M45" s="71">
         <f t="shared" ref="M45" si="9">G45+I45+K45</f>
-        <v>6551</v>
+        <v>-9509</v>
       </c>
       <c r="N45" s="166">
         <f t="shared" ref="N45" si="10">H45+J45+L45</f>
-        <v>0.65510000000000002</v>
+        <v>-0.95090000000000008</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
@@ -16711,11 +18494,11 @@
         <v>0.3206</v>
       </c>
       <c r="I46" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
         <v>2268</v>
       </c>
       <c r="J46" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
         <v>4.5359999999999998E-2</v>
       </c>
       <c r="K46" s="153">
@@ -16763,12 +18546,12 @@
         <v>1.8421700000000001</v>
       </c>
       <c r="I47" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>275056</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>510778</v>
       </c>
       <c r="J47" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>2.7505600000000001</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>5.10778</v>
       </c>
       <c r="K47" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
@@ -16780,11 +18563,11 @@
       </c>
       <c r="M47" s="71">
         <f t="shared" si="0"/>
-        <v>459273</v>
+        <v>694995</v>
       </c>
       <c r="N47" s="166">
         <f t="shared" si="0"/>
-        <v>4.5927300000000004</v>
+        <v>6.9499500000000003</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
@@ -16813,12 +18596,12 @@
         <v>-0.44650000000000001</v>
       </c>
       <c r="I48" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-361</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>1361</v>
       </c>
       <c r="J48" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-3.61E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>0.1361</v>
       </c>
       <c r="K48" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
@@ -16830,11 +18613,11 @@
       </c>
       <c r="M48" s="71">
         <f t="shared" ref="M48" si="11">G48+I48+K48</f>
-        <v>-4826</v>
+        <v>-3104</v>
       </c>
       <c r="N48" s="166">
         <f t="shared" ref="N48" si="12">H48+J48+L48</f>
-        <v>-0.48260000000000003</v>
+        <v>-0.31040000000000001</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
@@ -16865,12 +18648,12 @@
         <v>1.1765933333333332</v>
       </c>
       <c r="I49" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-275627</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>-26609</v>
       </c>
       <c r="J49" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-0.91875666666666678</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>-8.869666666666666E-2</v>
       </c>
       <c r="K49" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
@@ -16882,11 +18665,11 @@
       </c>
       <c r="M49" s="71">
         <f t="shared" si="0"/>
-        <v>77351</v>
+        <v>326369</v>
       </c>
       <c r="N49" s="166">
         <f t="shared" si="0"/>
-        <v>0.25783666666666638</v>
+        <v>1.0878966666666665</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
@@ -16911,11 +18694,11 @@
         <v>-0.11154</v>
       </c>
       <c r="I50" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
         <v>-9015</v>
       </c>
       <c r="J50" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
         <v>-9.0149999999999994E-2</v>
       </c>
       <c r="K50" s="153">
@@ -16963,12 +18746,12 @@
         <v>1.036025</v>
       </c>
       <c r="I51" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>102692</v>
       </c>
       <c r="J51" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>0.25673000000000001</v>
       </c>
       <c r="K51" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
@@ -16980,11 +18763,11 @@
       </c>
       <c r="M51" s="71">
         <f t="shared" si="0"/>
-        <v>414410</v>
+        <v>517102</v>
       </c>
       <c r="N51" s="166">
         <f t="shared" si="0"/>
-        <v>1.036025</v>
+        <v>1.2927550000000001</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
@@ -17015,12 +18798,12 @@
         <v>1.1097874999999999</v>
       </c>
       <c r="I52" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-143525</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>-101841</v>
       </c>
       <c r="J52" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-0.35881249999999998</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>-0.25460250000000001</v>
       </c>
       <c r="K52" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
@@ -17032,11 +18815,11 @@
       </c>
       <c r="M52" s="71">
         <f t="shared" si="0"/>
-        <v>300390</v>
+        <v>342074</v>
       </c>
       <c r="N52" s="166">
         <f t="shared" si="0"/>
-        <v>0.75097499999999995</v>
+        <v>0.85518499999999986</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
@@ -17065,12 +18848,12 @@
         <v>0</v>
       </c>
       <c r="I53" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-465097</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>148288</v>
       </c>
       <c r="J53" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-0.93019399999999997</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>0.148288</v>
       </c>
       <c r="K53" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
@@ -17082,11 +18865,11 @@
       </c>
       <c r="M53" s="71">
         <f t="shared" ref="M53" si="15">G53+I53+K53</f>
-        <v>-464997</v>
+        <v>148388</v>
       </c>
       <c r="N53" s="166">
         <f t="shared" ref="N53" si="16">H53+J53+L53</f>
-        <v>-0.93019399999999997</v>
+        <v>0.148288</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
@@ -17117,12 +18900,12 @@
         <v>-0.54205999999999999</v>
       </c>
       <c r="I54" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-3039</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>12858</v>
       </c>
       <c r="J54" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-6.0780000000000001E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>0.25716</v>
       </c>
       <c r="K54" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
@@ -17134,11 +18917,11 @@
       </c>
       <c r="M54" s="71">
         <f t="shared" si="0"/>
-        <v>-30142</v>
+        <v>-14245</v>
       </c>
       <c r="N54" s="166">
         <f t="shared" si="0"/>
-        <v>-0.60284000000000004</v>
+        <v>-0.28489999999999999</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
@@ -17169,12 +18952,12 @@
         <v>2.1928125000000001</v>
       </c>
       <c r="I55" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-77686</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>262495</v>
       </c>
       <c r="J55" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-0.194215</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>0.65623750000000003</v>
       </c>
       <c r="K55" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
@@ -17186,11 +18969,11 @@
       </c>
       <c r="M55" s="71">
         <f t="shared" si="0"/>
-        <v>799439</v>
+        <v>1139620</v>
       </c>
       <c r="N55" s="166">
         <f t="shared" si="0"/>
-        <v>1.9985975</v>
+        <v>2.8490500000000001</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
@@ -17221,12 +19004,12 @@
         <v>1.6721520000000001</v>
       </c>
       <c r="I56" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-625</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>-25761</v>
       </c>
       <c r="J56" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-5.0000000000000001E-3</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>-0.20608799999999999</v>
       </c>
       <c r="K56" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
@@ -17238,11 +19021,11 @@
       </c>
       <c r="M56" s="71">
         <f t="shared" si="0"/>
-        <v>208394</v>
+        <v>183258</v>
       </c>
       <c r="N56" s="166">
         <f t="shared" si="0"/>
-        <v>1.6671520000000002</v>
+        <v>1.466064</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
@@ -17273,12 +19056,12 @@
         <v>3.214936666666667</v>
       </c>
       <c r="I57" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-241366</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>-143841</v>
       </c>
       <c r="J57" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-0.80455333333333334</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>-0.47947000000000001</v>
       </c>
       <c r="K57" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
@@ -17290,11 +19073,11 @@
       </c>
       <c r="M57" s="71">
         <f t="shared" si="0"/>
-        <v>723115</v>
+        <v>820640</v>
       </c>
       <c r="N57" s="166">
         <f t="shared" si="0"/>
-        <v>2.4103833333333338</v>
+        <v>2.7354666666666669</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
@@ -17325,12 +19108,12 @@
         <v>-0.14077600000000001</v>
       </c>
       <c r="I58" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-7767</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>-74446</v>
       </c>
       <c r="J58" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-3.1067999999999998E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>-0.29778399999999999</v>
       </c>
       <c r="K58" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
@@ -17342,11 +19125,11 @@
       </c>
       <c r="M58" s="71">
         <f t="shared" si="0"/>
-        <v>-42961</v>
+        <v>-109640</v>
       </c>
       <c r="N58" s="166">
         <f t="shared" si="0"/>
-        <v>-0.171844</v>
+        <v>-0.43856000000000001</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
@@ -17375,12 +19158,12 @@
         <v>-0.10024</v>
       </c>
       <c r="I59" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-3651</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>49282</v>
       </c>
       <c r="J59" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-0.14604</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>1.9712799999999999</v>
       </c>
       <c r="K59" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
@@ -17392,11 +19175,11 @@
       </c>
       <c r="M59" s="71">
         <f t="shared" ref="M59" si="17">G59+I59+K59</f>
-        <v>-6157</v>
+        <v>46776</v>
       </c>
       <c r="N59" s="166">
         <f t="shared" ref="N59" si="18">H59+J59+L59</f>
-        <v>-0.24628</v>
+        <v>1.8710399999999998</v>
       </c>
     </row>
     <row r="60" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -17425,12 +19208,12 @@
         <v>0.54629399999999995</v>
       </c>
       <c r="I60" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-69999</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>186412</v>
       </c>
       <c r="J60" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ACU$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-0.13999800000000001</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'AUG-2026'!$A$4:$ADD$119,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DE$2,0),0),0)</f>
+        <v>0.37282399999999999</v>
       </c>
       <c r="K60" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
@@ -17442,11 +19225,11 @@
       </c>
       <c r="M60" s="71">
         <f t="shared" ref="M60" si="19">G60+I60+K60</f>
-        <v>203148</v>
+        <v>459559</v>
       </c>
       <c r="N60" s="166">
         <f t="shared" ref="N60" si="20">H60+J60+L60</f>
-        <v>0.40629599999999993</v>
+        <v>0.91911799999999988</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
@@ -17463,7 +19246,7 @@
       <c r="H61" s="90"/>
       <c r="I61" s="99">
         <f>SUM(I4:I58)</f>
-        <v>-4962763</v>
+        <v>-2373153</v>
       </c>
       <c r="J61" s="100"/>
       <c r="K61" s="109">
@@ -17473,7 +19256,7 @@
       <c r="L61" s="109"/>
       <c r="M61" s="154">
         <f>SUM(M4:M58)</f>
-        <v>12574882</v>
+        <v>15164492</v>
       </c>
       <c r="N61" s="235"/>
     </row>
@@ -17634,417 +19417,417 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A42:C42 A15:F17 A8:C8 A3:F3 L2:L3 A39:C39 A5:F5 A30:F30 F8 F40 F42 A57:C57 A58:E58 A32:F34 E39:F39 A47:F47 M5:N9 A21 A36:F37 A52:F52 F55:F58 E57 G61:N62 A23:F24 M23:N24 A61:E61 C50:F50 G15:H18 M21:N21 G21:H24 A26:F27 A49:F49 G39:H49 G26:H37 G65:N67 F53 G51:H59 G4:L4 A11:H13 K11:N13 K51:N59 K26:N37 K39:N49 K21:L24 K15:N18 I11:I60 G5:I10 K5:L10 J5:J60">
-    <cfRule type="expression" dxfId="358" priority="213">
+    <cfRule type="expression" dxfId="359" priority="213">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:I3">
-    <cfRule type="expression" dxfId="357" priority="212">
+    <cfRule type="expression" dxfId="358" priority="212">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J3">
-    <cfRule type="expression" dxfId="356" priority="211">
+    <cfRule type="expression" dxfId="357" priority="211">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K3">
-    <cfRule type="expression" dxfId="355" priority="210">
+    <cfRule type="expression" dxfId="356" priority="210">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40:C40 E40">
-    <cfRule type="expression" dxfId="354" priority="206">
+    <cfRule type="expression" dxfId="355" priority="206">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E42">
-    <cfRule type="expression" dxfId="353" priority="204">
+    <cfRule type="expression" dxfId="354" priority="204">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18:F18 A19:A20">
-    <cfRule type="expression" dxfId="352" priority="202">
+    <cfRule type="expression" dxfId="353" priority="202">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A44:C44 E44:F44">
-    <cfRule type="expression" dxfId="351" priority="196">
+    <cfRule type="expression" dxfId="352" priority="196">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M23:N23">
-    <cfRule type="expression" dxfId="350" priority="186">
+    <cfRule type="expression" dxfId="351" priority="186">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9:C9 E9:F9">
-    <cfRule type="expression" dxfId="349" priority="191">
+    <cfRule type="expression" dxfId="350" priority="191">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N23">
-    <cfRule type="expression" dxfId="348" priority="187">
+    <cfRule type="expression" dxfId="349" priority="187">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M9:N9">
-    <cfRule type="expression" dxfId="347" priority="172">
+    <cfRule type="expression" dxfId="348" priority="172">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21:C21 E21:F21">
-    <cfRule type="expression" dxfId="346" priority="167">
+    <cfRule type="expression" dxfId="347" priority="167">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N9">
-    <cfRule type="expression" dxfId="345" priority="173">
+    <cfRule type="expression" dxfId="346" priority="173">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A7:F7 A6:C6 E6:F6">
-    <cfRule type="expression" dxfId="344" priority="158">
+    <cfRule type="expression" dxfId="345" priority="158">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N6:N7">
-    <cfRule type="expression" dxfId="343" priority="156">
+    <cfRule type="expression" dxfId="344" priority="156">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M6:N7">
-    <cfRule type="expression" dxfId="342" priority="155">
+    <cfRule type="expression" dxfId="343" priority="155">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A35:C35 E35:F35">
-    <cfRule type="expression" dxfId="341" priority="150">
+    <cfRule type="expression" dxfId="342" priority="150">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M35:N35">
-    <cfRule type="expression" dxfId="340" priority="146">
+    <cfRule type="expression" dxfId="341" priority="146">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N35">
-    <cfRule type="expression" dxfId="339" priority="147">
+    <cfRule type="expression" dxfId="340" priority="147">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A46:C46 E46:F46">
-    <cfRule type="expression" dxfId="338" priority="141">
+    <cfRule type="expression" dxfId="339" priority="141">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N21">
-    <cfRule type="expression" dxfId="337" priority="127">
+    <cfRule type="expression" dxfId="338" priority="127">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M21:N21">
-    <cfRule type="expression" dxfId="336" priority="126">
+    <cfRule type="expression" dxfId="337" priority="126">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A54:C54 E54:F54">
-    <cfRule type="expression" dxfId="335" priority="116">
+    <cfRule type="expression" dxfId="336" priority="116">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L63:L64">
-    <cfRule type="expression" dxfId="334" priority="110">
+    <cfRule type="expression" dxfId="335" priority="110">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G63:I64">
-    <cfRule type="expression" dxfId="333" priority="109">
+    <cfRule type="expression" dxfId="334" priority="109">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J63:J64">
-    <cfRule type="expression" dxfId="332" priority="108">
+    <cfRule type="expression" dxfId="333" priority="108">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K63:K64">
-    <cfRule type="expression" dxfId="331" priority="107">
+    <cfRule type="expression" dxfId="332" priority="107">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A28:F28">
-    <cfRule type="expression" dxfId="330" priority="106">
+    <cfRule type="expression" dxfId="331" priority="106">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A29:F29">
-    <cfRule type="expression" dxfId="329" priority="105">
+    <cfRule type="expression" dxfId="330" priority="105">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A31:F31">
-    <cfRule type="expression" dxfId="328" priority="104">
+    <cfRule type="expression" dxfId="329" priority="104">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8:E8">
-    <cfRule type="expression" dxfId="327" priority="93">
+    <cfRule type="expression" dxfId="328" priority="93">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A55:C56 E55:E56">
-    <cfRule type="expression" dxfId="326" priority="89">
+    <cfRule type="expression" dxfId="327" priority="89">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M55:N56">
-    <cfRule type="expression" dxfId="325" priority="88">
+    <cfRule type="expression" dxfId="326" priority="88">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A43:C43 E43:F43">
-    <cfRule type="expression" dxfId="324" priority="85">
+    <cfRule type="expression" dxfId="325" priority="85">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A51:B51">
-    <cfRule type="expression" dxfId="323" priority="81">
+    <cfRule type="expression" dxfId="324" priority="81">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4:C4 E4:F4">
-    <cfRule type="expression" dxfId="322" priority="76">
+    <cfRule type="expression" dxfId="323" priority="76">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M4:N4">
-    <cfRule type="expression" dxfId="321" priority="75">
+    <cfRule type="expression" dxfId="322" priority="75">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M4:N4">
-    <cfRule type="expression" dxfId="320" priority="72">
+    <cfRule type="expression" dxfId="321" priority="72">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N4">
-    <cfRule type="expression" dxfId="319" priority="73">
+    <cfRule type="expression" dxfId="320" priority="73">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A41:C41 E41:F41">
-    <cfRule type="expression" dxfId="318" priority="67">
+    <cfRule type="expression" dxfId="319" priority="67">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A65:F65 F66">
-    <cfRule type="expression" dxfId="317" priority="66">
+    <cfRule type="expression" dxfId="318" priority="66">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A10:F10">
-    <cfRule type="expression" dxfId="316" priority="58">
+    <cfRule type="expression" dxfId="317" priority="58">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M10:N10">
-    <cfRule type="expression" dxfId="315" priority="57">
+    <cfRule type="expression" dxfId="316" priority="57">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M10:N10">
-    <cfRule type="expression" dxfId="314" priority="54">
+    <cfRule type="expression" dxfId="315" priority="54">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N10">
-    <cfRule type="expression" dxfId="313" priority="55">
+    <cfRule type="expression" dxfId="314" priority="55">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F51">
-    <cfRule type="expression" dxfId="312" priority="47">
+    <cfRule type="expression" dxfId="313" priority="47">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D51:E51">
-    <cfRule type="expression" dxfId="311" priority="46">
+    <cfRule type="expression" dxfId="312" priority="46">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6">
-    <cfRule type="expression" dxfId="310" priority="45">
+    <cfRule type="expression" dxfId="311" priority="45">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4">
-    <cfRule type="expression" dxfId="309" priority="44">
+    <cfRule type="expression" dxfId="310" priority="44">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9">
-    <cfRule type="expression" dxfId="308" priority="43">
+    <cfRule type="expression" dxfId="309" priority="43">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D21">
-    <cfRule type="expression" dxfId="307" priority="42">
+    <cfRule type="expression" dxfId="308" priority="42">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D55:D56">
-    <cfRule type="expression" dxfId="306" priority="31">
+    <cfRule type="expression" dxfId="307" priority="31">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D35">
-    <cfRule type="expression" dxfId="305" priority="41">
+    <cfRule type="expression" dxfId="306" priority="41">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D40:D41">
-    <cfRule type="expression" dxfId="304" priority="40">
+    <cfRule type="expression" dxfId="305" priority="40">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D39">
-    <cfRule type="expression" dxfId="303" priority="39">
+    <cfRule type="expression" dxfId="304" priority="39">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D42">
-    <cfRule type="expression" dxfId="302" priority="38">
+    <cfRule type="expression" dxfId="303" priority="38">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D43">
-    <cfRule type="expression" dxfId="301" priority="37">
+    <cfRule type="expression" dxfId="302" priority="37">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D44">
-    <cfRule type="expression" dxfId="300" priority="36">
+    <cfRule type="expression" dxfId="301" priority="36">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D46">
-    <cfRule type="expression" dxfId="299" priority="35">
+    <cfRule type="expression" dxfId="300" priority="35">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D57">
-    <cfRule type="expression" dxfId="298" priority="34">
+    <cfRule type="expression" dxfId="299" priority="34">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D54">
-    <cfRule type="expression" dxfId="297" priority="32">
+    <cfRule type="expression" dxfId="298" priority="32">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A22:F22">
-    <cfRule type="expression" dxfId="296" priority="30">
+    <cfRule type="expression" dxfId="297" priority="30">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M22:N22">
-    <cfRule type="expression" dxfId="295" priority="29">
+    <cfRule type="expression" dxfId="296" priority="29">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N22">
-    <cfRule type="expression" dxfId="294" priority="26">
+    <cfRule type="expression" dxfId="295" priority="26">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M22:N22">
-    <cfRule type="expression" dxfId="293" priority="25">
+    <cfRule type="expression" dxfId="294" priority="25">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A60:F60">
-    <cfRule type="expression" dxfId="292" priority="18">
+    <cfRule type="expression" dxfId="293" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G60:H60 K60:N60">
-    <cfRule type="expression" dxfId="291" priority="17">
+    <cfRule type="expression" dxfId="292" priority="17">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A50:B50">
-    <cfRule type="expression" dxfId="290" priority="16">
+    <cfRule type="expression" dxfId="291" priority="16">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G50:H50 K50:N50">
-    <cfRule type="expression" dxfId="289" priority="15">
+    <cfRule type="expression" dxfId="290" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A38:F38">
-    <cfRule type="expression" dxfId="288" priority="14">
+    <cfRule type="expression" dxfId="289" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G38:H38 K38:N38">
-    <cfRule type="expression" dxfId="287" priority="13">
+    <cfRule type="expression" dxfId="288" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A45:F45">
-    <cfRule type="expression" dxfId="286" priority="12">
+    <cfRule type="expression" dxfId="287" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14:F14">
-    <cfRule type="expression" dxfId="285" priority="11">
+    <cfRule type="expression" dxfId="286" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G14:H14 K14:N14">
-    <cfRule type="expression" dxfId="284" priority="10">
+    <cfRule type="expression" dxfId="285" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B19:F20">
-    <cfRule type="expression" dxfId="283" priority="9">
+    <cfRule type="expression" dxfId="284" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G19:H20 K19:N20">
-    <cfRule type="expression" dxfId="282" priority="8">
+    <cfRule type="expression" dxfId="283" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G25:H25 K25:N25">
-    <cfRule type="expression" dxfId="281" priority="4">
+    <cfRule type="expression" dxfId="282" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A25:F25">
-    <cfRule type="expression" dxfId="280" priority="7">
+    <cfRule type="expression" dxfId="281" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A48:F48">
-    <cfRule type="expression" dxfId="279" priority="6">
+    <cfRule type="expression" dxfId="280" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A59:F59">
-    <cfRule type="expression" dxfId="278" priority="5">
+    <cfRule type="expression" dxfId="279" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A66:E66">
-    <cfRule type="expression" dxfId="277" priority="3">
+    <cfRule type="expression" dxfId="278" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A53:E53">
-    <cfRule type="expression" dxfId="276" priority="1">
+    <cfRule type="expression" dxfId="277" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -23736,42 +25519,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2 A48:A49 AE58 AD56:AE57 AE43:AE55 AD42:AD55 A3:G4 AD6:AE9 AD12:AE19 AD21:AD40 AE21:AE39 H2:AE4 A10:AE11 C48:AC49 A5:AC9 A50:AC57 A12:AC47 A59:AE63">
-    <cfRule type="expression" dxfId="275" priority="13">
+    <cfRule type="expression" dxfId="276" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE40">
-    <cfRule type="expression" dxfId="274" priority="12">
+    <cfRule type="expression" dxfId="275" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE42">
-    <cfRule type="expression" dxfId="273" priority="11">
+    <cfRule type="expression" dxfId="274" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48:B49">
-    <cfRule type="expression" dxfId="272" priority="5">
+    <cfRule type="expression" dxfId="273" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD5:AE5">
-    <cfRule type="expression" dxfId="271" priority="4">
+    <cfRule type="expression" dxfId="272" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD41">
-    <cfRule type="expression" dxfId="270" priority="3">
+    <cfRule type="expression" dxfId="271" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE41">
-    <cfRule type="expression" dxfId="269" priority="2">
+    <cfRule type="expression" dxfId="270" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD20:AE20">
-    <cfRule type="expression" dxfId="268" priority="1">
+    <cfRule type="expression" dxfId="269" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29809,112 +31592,112 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G30 G14:G15 G2 A57:G57 G58 A55:A56 H2:AC4 A17:G27 H57:AA62 AC67 AC50:AC64 AB5:AC5 A53:G53 H49:AA54 AB49:AB64 A37:AA40 H5:AA15 AB7:AC15 A16:AC16 A31:G36 H17:AA36 AB65:AC66 AC17:AC46 AB17:AB47 A68:AC71 A54:B54 D54:G54 C55:AA56 A3:G5 A7:G8 A6:C6 E6:G6 A10:G13 A9:C9 E9:G9 A29:G29 A28:C28 E28:G28 A42:AA45 A41:C41 E41:AA41 A47:AA48 A46:C46 E46:AA46 A49:C52 E49:G52 A64:AA66 A59:C63 E63:AA63 E59:G62">
-    <cfRule type="expression" dxfId="267" priority="28">
+    <cfRule type="expression" dxfId="268" priority="28">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC47">
-    <cfRule type="expression" dxfId="266" priority="27">
+    <cfRule type="expression" dxfId="267" priority="27">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC49">
-    <cfRule type="expression" dxfId="265" priority="26">
+    <cfRule type="expression" dxfId="266" priority="26">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A30:C30 F30">
-    <cfRule type="expression" dxfId="264" priority="25">
+    <cfRule type="expression" dxfId="265" priority="25">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14:F14 A15:C15 E15:F15">
-    <cfRule type="expression" dxfId="263" priority="23">
+    <cfRule type="expression" dxfId="264" priority="23">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D30:E30">
-    <cfRule type="expression" dxfId="262" priority="22">
+    <cfRule type="expression" dxfId="263" priority="22">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58:F58">
-    <cfRule type="expression" dxfId="261" priority="20">
+    <cfRule type="expression" dxfId="262" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55:B56">
-    <cfRule type="expression" dxfId="260" priority="19">
+    <cfRule type="expression" dxfId="261" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB6:AC6">
-    <cfRule type="expression" dxfId="259" priority="15">
+    <cfRule type="expression" dxfId="260" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB48">
-    <cfRule type="expression" dxfId="258" priority="14">
+    <cfRule type="expression" dxfId="259" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC48">
-    <cfRule type="expression" dxfId="257" priority="13">
+    <cfRule type="expression" dxfId="258" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6">
-    <cfRule type="expression" dxfId="256" priority="12">
+    <cfRule type="expression" dxfId="257" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9">
-    <cfRule type="expression" dxfId="255" priority="11">
+    <cfRule type="expression" dxfId="256" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D15">
-    <cfRule type="expression" dxfId="254" priority="10">
+    <cfRule type="expression" dxfId="255" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D28">
-    <cfRule type="expression" dxfId="253" priority="9">
+    <cfRule type="expression" dxfId="254" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D41">
-    <cfRule type="expression" dxfId="252" priority="8">
+    <cfRule type="expression" dxfId="253" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D46">
-    <cfRule type="expression" dxfId="251" priority="7">
+    <cfRule type="expression" dxfId="252" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D49">
-    <cfRule type="expression" dxfId="250" priority="6">
+    <cfRule type="expression" dxfId="251" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D60:D63">
-    <cfRule type="expression" dxfId="249" priority="1">
+    <cfRule type="expression" dxfId="250" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D50:D51">
-    <cfRule type="expression" dxfId="248" priority="5">
+    <cfRule type="expression" dxfId="249" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D52">
-    <cfRule type="expression" dxfId="247" priority="4">
+    <cfRule type="expression" dxfId="248" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D59">
-    <cfRule type="expression" dxfId="246" priority="2">
+    <cfRule type="expression" dxfId="247" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -35829,107 +37612,107 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G29 G13:G14 G2 A30:G36 A39:G40 G53 A58:C61 G57 H39:AA53 H56:AA59 A54:A55 F54:AA55 A37:AA38 H2:AC4 A15:G26 H5:AA36 AC49:AC58 AC60:AC64 AC5:AC46 AB5:AB61 A62:AB63 A65:AC68 A3:G7 A9:G12 A8:C8 E8:G8 A28:G28 A27:C27 E27:G27 A42:G45 A41:C41 E41:G41 A52:G52 A46:C51 E46:G51 A56:G56 E58:G59 E60:AA61">
-    <cfRule type="expression" dxfId="245" priority="24">
+    <cfRule type="expression" dxfId="246" priority="24">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC47">
-    <cfRule type="expression" dxfId="244" priority="23">
+    <cfRule type="expression" dxfId="245" priority="23">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC48">
-    <cfRule type="expression" dxfId="243" priority="22">
+    <cfRule type="expression" dxfId="244" priority="22">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A29:C29 F29">
-    <cfRule type="expression" dxfId="242" priority="21">
+    <cfRule type="expression" dxfId="243" priority="21">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC59">
-    <cfRule type="expression" dxfId="241" priority="20">
+    <cfRule type="expression" dxfId="242" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:F13 A14:C14 E14:F14">
-    <cfRule type="expression" dxfId="240" priority="19">
+    <cfRule type="expression" dxfId="241" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D29:E29">
-    <cfRule type="expression" dxfId="239" priority="18">
+    <cfRule type="expression" dxfId="240" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A53:B53 F53">
-    <cfRule type="expression" dxfId="238" priority="15">
+    <cfRule type="expression" dxfId="239" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A57:F57">
-    <cfRule type="expression" dxfId="237" priority="14">
+    <cfRule type="expression" dxfId="238" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54:B55">
-    <cfRule type="expression" dxfId="236" priority="13">
+    <cfRule type="expression" dxfId="237" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D53:E53 C54:E55">
-    <cfRule type="expression" dxfId="235" priority="12">
+    <cfRule type="expression" dxfId="236" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D58:D61">
-    <cfRule type="expression" dxfId="234" priority="1">
+    <cfRule type="expression" dxfId="235" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="233" priority="10">
+    <cfRule type="expression" dxfId="234" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="232" priority="9">
+    <cfRule type="expression" dxfId="233" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D27">
-    <cfRule type="expression" dxfId="231" priority="8">
+    <cfRule type="expression" dxfId="232" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D41">
-    <cfRule type="expression" dxfId="230" priority="7">
+    <cfRule type="expression" dxfId="231" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D47:D48">
-    <cfRule type="expression" dxfId="229" priority="6">
+    <cfRule type="expression" dxfId="230" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D46">
-    <cfRule type="expression" dxfId="228" priority="5">
+    <cfRule type="expression" dxfId="229" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D49">
-    <cfRule type="expression" dxfId="227" priority="4">
+    <cfRule type="expression" dxfId="228" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D50">
-    <cfRule type="expression" dxfId="226" priority="3">
+    <cfRule type="expression" dxfId="227" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D51">
-    <cfRule type="expression" dxfId="225" priority="2">
+    <cfRule type="expression" dxfId="226" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -36281,11 +38064,11 @@
       <c r="O6" s="215"/>
       <c r="P6" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-28323</v>
+        <v>-32219</v>
       </c>
       <c r="Q6" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.56645999999999996</v>
+        <v>-0.64437999999999995</v>
       </c>
       <c r="R6" s="159"/>
       <c r="S6" s="153">
@@ -36302,11 +38085,11 @@
       <c r="X6" s="132"/>
       <c r="Y6" s="154">
         <f t="shared" si="0"/>
-        <v>-76659</v>
+        <v>-80555</v>
       </c>
       <c r="Z6" s="168">
         <f t="shared" si="1"/>
-        <v>-1.53318</v>
+        <v>-1.6111</v>
       </c>
     </row>
     <row r="7" spans="1:26" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -36363,11 +38146,11 @@
       <c r="O7" s="215"/>
       <c r="P7" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-65303</v>
+        <v>-162634</v>
       </c>
       <c r="Q7" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.21767666666666657</v>
+        <v>-0.54211333333333322</v>
       </c>
       <c r="R7" s="159"/>
       <c r="S7" s="88">
@@ -36384,11 +38167,11 @@
       <c r="X7"/>
       <c r="Y7" s="154">
         <f t="shared" si="0"/>
-        <v>1268971</v>
+        <v>1171640</v>
       </c>
       <c r="Z7" s="168">
         <f t="shared" si="1"/>
-        <v>4.2299033333333336</v>
+        <v>3.9054666666666673</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -36527,11 +38310,11 @@
       <c r="O9" s="215"/>
       <c r="P9" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>53780</v>
+        <v>-198885</v>
       </c>
       <c r="Q9" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.17926666666666666</v>
+        <v>-0.66294999999999993</v>
       </c>
       <c r="R9" s="159"/>
       <c r="S9" s="88">
@@ -36547,11 +38330,11 @@
       <c r="W9" s="72"/>
       <c r="Y9" s="154">
         <f t="shared" si="0"/>
-        <v>-305129</v>
+        <v>-557794</v>
       </c>
       <c r="Z9" s="168">
         <f t="shared" si="1"/>
-        <v>-2.4614133333333337</v>
+        <v>-3.3036300000000001</v>
       </c>
     </row>
     <row r="10" spans="1:26" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -36608,11 +38391,11 @@
       <c r="O10" s="215"/>
       <c r="P10" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-284947</v>
+        <v>-336921</v>
       </c>
       <c r="Q10" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1.8996466666666669</v>
+        <v>-2.2461400000000005</v>
       </c>
       <c r="R10" s="159"/>
       <c r="S10" s="153">
@@ -36628,11 +38411,11 @@
       <c r="W10" s="150"/>
       <c r="Y10" s="154">
         <f t="shared" si="0"/>
-        <v>-459909</v>
+        <v>-511883</v>
       </c>
       <c r="Z10" s="168">
         <f t="shared" si="1"/>
-        <v>-3.0660600000000002</v>
+        <v>-3.4125533333333338</v>
       </c>
     </row>
     <row r="11" spans="1:26" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -36689,11 +38472,11 @@
       <c r="O11" s="215"/>
       <c r="P11" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1521776</v>
+        <v>1700999</v>
       </c>
       <c r="Q11" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1.0145173333333335</v>
+        <v>1.1339993333333334</v>
       </c>
       <c r="R11" s="159"/>
       <c r="S11" s="88">
@@ -36710,11 +38493,11 @@
       <c r="X11"/>
       <c r="Y11" s="154">
         <f t="shared" si="0"/>
-        <v>153577</v>
+        <v>332800</v>
       </c>
       <c r="Z11" s="168">
         <f t="shared" si="1"/>
-        <v>0.10238466666666679</v>
+        <v>0.22186666666666666</v>
       </c>
     </row>
     <row r="12" spans="1:26" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -37098,11 +38881,11 @@
       <c r="O16" s="215"/>
       <c r="P16" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>491857</v>
+        <v>582476</v>
       </c>
       <c r="Q16" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.81976166666666672</v>
+        <v>0.9707933333333334</v>
       </c>
       <c r="R16" s="159"/>
       <c r="S16" s="88">
@@ -37118,11 +38901,11 @@
       <c r="W16" s="72"/>
       <c r="Y16" s="154">
         <f t="shared" si="0"/>
-        <v>296523</v>
+        <v>387142</v>
       </c>
       <c r="Z16" s="168">
         <f t="shared" si="1"/>
-        <v>-2.5978583333333329</v>
+        <v>-2.4468266666666665</v>
       </c>
     </row>
     <row r="17" spans="1:34" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -37179,11 +38962,11 @@
       <c r="O17" s="215"/>
       <c r="P17" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>5756</v>
+        <v>12877</v>
       </c>
       <c r="Q17" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>5.756E-2</v>
+        <v>0.12877</v>
       </c>
       <c r="R17" s="159"/>
       <c r="S17" s="153">
@@ -37199,11 +38982,11 @@
       <c r="W17" s="150"/>
       <c r="Y17" s="154">
         <f t="shared" si="0"/>
-        <v>9435</v>
+        <v>16556</v>
       </c>
       <c r="Z17" s="168">
         <f t="shared" si="1"/>
-        <v>9.4350000000000003E-2</v>
+        <v>0.16555999999999998</v>
       </c>
     </row>
     <row r="18" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -37350,11 +39133,11 @@
       <c r="O19" s="215"/>
       <c r="P19" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>123361</v>
+        <v>136037</v>
       </c>
       <c r="Q19" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.49344399999999999</v>
+        <v>0.54414800000000008</v>
       </c>
       <c r="R19" s="159"/>
       <c r="S19" s="88">
@@ -37370,11 +39153,11 @@
       <c r="W19" s="72"/>
       <c r="Y19" s="154">
         <f t="shared" si="0"/>
-        <v>-144055</v>
+        <v>-131379</v>
       </c>
       <c r="Z19" s="168">
         <f t="shared" si="1"/>
-        <v>-2.1807160000000003</v>
+        <v>-2.1300119999999998</v>
       </c>
     </row>
     <row r="20" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -37431,11 +39214,11 @@
       <c r="O20" s="215"/>
       <c r="P20" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-49206</v>
+        <v>-49838</v>
       </c>
       <c r="Q20" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.22366363636363637</v>
+        <v>-0.22653636363636362</v>
       </c>
       <c r="R20" s="159"/>
       <c r="S20" s="88">
@@ -37451,11 +39234,11 @@
       <c r="W20" s="72"/>
       <c r="Y20" s="154">
         <f t="shared" si="0"/>
-        <v>-138106</v>
+        <v>-138738</v>
       </c>
       <c r="Z20" s="168">
         <f t="shared" si="1"/>
-        <v>-1.1126636363636364</v>
+        <v>-1.1155363636363635</v>
       </c>
     </row>
     <row r="21" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -37593,11 +39376,11 @@
       <c r="O22" s="215"/>
       <c r="P22" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>63311</v>
+        <v>72469</v>
       </c>
       <c r="Q22" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.63310999999999995</v>
+        <v>0.72469000000000006</v>
       </c>
       <c r="R22" s="159"/>
       <c r="S22" s="88">
@@ -37613,11 +39396,11 @@
       <c r="W22" s="72"/>
       <c r="Y22" s="154">
         <f t="shared" si="0"/>
-        <v>1778656</v>
+        <v>1787814</v>
       </c>
       <c r="Z22" s="168">
         <f t="shared" si="1"/>
-        <v>17.786559999999998</v>
+        <v>17.878139999999998</v>
       </c>
     </row>
     <row r="23" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -37915,11 +39698,11 @@
       <c r="O26" s="215"/>
       <c r="P26" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-58699</v>
+        <v>-60653</v>
       </c>
       <c r="Q26" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.234796</v>
+        <v>-0.24261200000000005</v>
       </c>
       <c r="R26" s="159"/>
       <c r="S26" s="88">
@@ -37935,11 +39718,11 @@
       <c r="W26" s="72"/>
       <c r="Y26" s="154">
         <f t="shared" si="0"/>
-        <v>299514</v>
+        <v>297560</v>
       </c>
       <c r="Z26" s="168">
         <f t="shared" si="1"/>
-        <v>1.198056</v>
+        <v>1.19024</v>
       </c>
     </row>
     <row r="27" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -37996,11 +39779,11 @@
       <c r="O27" s="215"/>
       <c r="P27" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>357842</v>
+        <v>350234</v>
       </c>
       <c r="Q27" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.89460499999999998</v>
+        <v>0.87558499999999995</v>
       </c>
       <c r="R27" s="159"/>
       <c r="S27" s="88">
@@ -38017,11 +39800,11 @@
       <c r="X27" s="1"/>
       <c r="Y27" s="154">
         <f t="shared" si="0"/>
-        <v>1028305</v>
+        <v>1020697</v>
       </c>
       <c r="Z27" s="168">
         <f t="shared" si="1"/>
-        <v>2.5707624999999998</v>
+        <v>2.5517425</v>
       </c>
     </row>
     <row r="28" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -38078,11 +39861,11 @@
       <c r="O28" s="215"/>
       <c r="P28" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>2450</v>
+        <v>105966</v>
       </c>
       <c r="Q28" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>2.2272727272727222E-2</v>
+        <v>0.9633272727272727</v>
       </c>
       <c r="R28" s="159"/>
       <c r="S28" s="88">
@@ -38099,11 +39882,11 @@
       <c r="X28" s="1"/>
       <c r="Y28" s="154">
         <f t="shared" si="0"/>
-        <v>2168</v>
+        <v>105684</v>
       </c>
       <c r="Z28" s="168">
         <f t="shared" si="1"/>
-        <v>1.9709090909090898E-2</v>
+        <v>0.96076363636363638</v>
       </c>
     </row>
     <row r="29" spans="1:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -38276,11 +40059,11 @@
       <c r="O31" s="215"/>
       <c r="P31" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>22829</v>
+        <v>179772</v>
       </c>
       <c r="Q31" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.15219333333333329</v>
+        <v>1.19848</v>
       </c>
       <c r="R31" s="159"/>
       <c r="S31" s="88">
@@ -38297,11 +40080,11 @@
       <c r="X31"/>
       <c r="Y31" s="154">
         <f t="shared" si="0"/>
-        <v>-482240</v>
+        <v>-325297</v>
       </c>
       <c r="Z31" s="168">
         <f t="shared" si="1"/>
-        <v>-3.2149333333333341</v>
+        <v>-2.1686466666666675</v>
       </c>
     </row>
     <row r="32" spans="1:34" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -38439,11 +40222,11 @@
       <c r="O33" s="215"/>
       <c r="P33" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>221852</v>
+        <v>318230</v>
       </c>
       <c r="Q33" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>2.0168363636363629</v>
+        <v>2.8929999999999993</v>
       </c>
       <c r="R33" s="159"/>
       <c r="S33" s="88">
@@ -38459,11 +40242,11 @@
       <c r="W33" s="72"/>
       <c r="Y33" s="154">
         <f t="shared" si="0"/>
-        <v>-97088</v>
+        <v>-710</v>
       </c>
       <c r="Z33" s="168">
         <f t="shared" si="1"/>
-        <v>-0.88261818181818219</v>
+        <v>-6.4545454545457126E-3</v>
       </c>
       <c r="AB33" s="1"/>
       <c r="AC33" s="1"/>
@@ -38608,11 +40391,11 @@
       <c r="O35" s="215"/>
       <c r="P35" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1124698</v>
+        <v>658668</v>
       </c>
       <c r="Q35" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>4.8899913043478254</v>
+        <v>2.8637739130434778</v>
       </c>
       <c r="R35" s="159"/>
       <c r="S35" s="88">
@@ -38628,11 +40411,11 @@
       <c r="W35" s="72"/>
       <c r="Y35" s="154">
         <f t="shared" si="0"/>
-        <v>5285801</v>
+        <v>4819771</v>
       </c>
       <c r="Z35" s="168">
         <f t="shared" si="1"/>
-        <v>22.981743478260867</v>
+        <v>20.955526086956521</v>
       </c>
     </row>
     <row r="36" spans="1:34" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -38687,11 +40470,11 @@
       <c r="O36" s="215"/>
       <c r="P36" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>135</v>
+        <v>-10990</v>
       </c>
       <c r="Q36" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>6.750000000000006E-3</v>
+        <v>-0.54949999999999999</v>
       </c>
       <c r="R36" s="159"/>
       <c r="S36" s="153">
@@ -38707,11 +40490,11 @@
       <c r="W36" s="150"/>
       <c r="Y36" s="154">
         <f t="shared" ref="Y36" si="16">M36+P36+S36+V36</f>
-        <v>135</v>
+        <v>-10990</v>
       </c>
       <c r="Z36" s="168">
         <f t="shared" ref="Z36" si="17">(N36+Q36+T36+W36)</f>
-        <v>6.750000000000006E-3</v>
+        <v>-0.54949999999999999</v>
       </c>
     </row>
     <row r="37" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -38768,11 +40551,11 @@
       <c r="O37" s="215"/>
       <c r="P37" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-184640</v>
+        <v>-180050</v>
       </c>
       <c r="Q37" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.36928</v>
+        <v>-0.36009999999999998</v>
       </c>
       <c r="R37" s="159"/>
       <c r="S37" s="88">
@@ -38788,11 +40571,11 @@
       <c r="W37" s="72"/>
       <c r="Y37" s="154">
         <f t="shared" si="0"/>
-        <v>2881766</v>
+        <v>2886356</v>
       </c>
       <c r="Z37" s="168">
         <f t="shared" si="1"/>
-        <v>5.7635319999999997</v>
+        <v>5.7727119999999994</v>
       </c>
     </row>
     <row r="38" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -38849,11 +40632,11 @@
       <c r="O38" s="215"/>
       <c r="P38" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>2710166</v>
+        <v>2885461</v>
       </c>
       <c r="Q38" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>2.7101660000000001</v>
+        <v>2.8854610000000003</v>
       </c>
       <c r="R38" s="159"/>
       <c r="S38" s="88">
@@ -38870,11 +40653,11 @@
       <c r="X38" s="132"/>
       <c r="Y38" s="154">
         <f t="shared" ref="Y38:Y71" si="18">M38+P38+S38+V38</f>
-        <v>6303572</v>
+        <v>6478867</v>
       </c>
       <c r="Z38" s="168">
         <f t="shared" ref="Z38:Z71" si="19">(N38+Q38+T38+W38)</f>
-        <v>6.3035720000000008</v>
+        <v>6.478867000000001</v>
       </c>
       <c r="AB38" s="131"/>
     </row>
@@ -39365,11 +41148,11 @@
       <c r="O44" s="215"/>
       <c r="P44" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>719285</v>
+        <v>839303</v>
       </c>
       <c r="Q44" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1.4385699999999999</v>
+        <v>1.6786059999999998</v>
       </c>
       <c r="R44" s="159"/>
       <c r="S44" s="88">
@@ -39385,11 +41168,11 @@
       <c r="W44" s="72"/>
       <c r="Y44" s="154">
         <f t="shared" si="18"/>
-        <v>1936603</v>
+        <v>2056621</v>
       </c>
       <c r="Z44" s="168">
         <f t="shared" si="19"/>
-        <v>3.8732059999999997</v>
+        <v>4.1132419999999996</v>
       </c>
     </row>
     <row r="45" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -39446,11 +41229,11 @@
       <c r="O45" s="215"/>
       <c r="P45" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>335307</v>
+        <v>1060369</v>
       </c>
       <c r="Q45" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.67061399999999993</v>
+        <v>2.1207380000000002</v>
       </c>
       <c r="R45" s="159"/>
       <c r="S45" s="88">
@@ -39467,11 +41250,11 @@
       <c r="X45" s="1"/>
       <c r="Y45" s="154">
         <f t="shared" si="18"/>
-        <v>287569</v>
+        <v>1012631</v>
       </c>
       <c r="Z45" s="168">
         <f t="shared" si="19"/>
-        <v>0.57513799999999971</v>
+        <v>2.0252620000000001</v>
       </c>
       <c r="AA45" s="1"/>
     </row>
@@ -39529,11 +41312,11 @@
       <c r="O46" s="215"/>
       <c r="P46" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-31238</v>
+        <v>-43366</v>
       </c>
       <c r="Q46" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.62475999999999998</v>
+        <v>-0.86731999999999998</v>
       </c>
       <c r="R46" s="159"/>
       <c r="S46" s="88">
@@ -39549,11 +41332,11 @@
       <c r="W46" s="72"/>
       <c r="Y46" s="154">
         <f t="shared" si="18"/>
-        <v>85657</v>
+        <v>73529</v>
       </c>
       <c r="Z46" s="168">
         <f t="shared" si="19"/>
-        <v>1.7131399999999999</v>
+        <v>1.47058</v>
       </c>
       <c r="AD46" s="1"/>
       <c r="AE46" s="1"/>
@@ -39698,11 +41481,11 @@
       <c r="O48" s="215"/>
       <c r="P48" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-135077</v>
+        <v>-32152</v>
       </c>
       <c r="Q48" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-3.376925</v>
+        <v>-0.80379999999999985</v>
       </c>
       <c r="R48" s="159"/>
       <c r="S48" s="88">
@@ -39718,11 +41501,11 @@
       <c r="W48" s="72"/>
       <c r="Y48" s="154">
         <f t="shared" si="18"/>
-        <v>-146905</v>
+        <v>-43980</v>
       </c>
       <c r="Z48" s="168">
         <f t="shared" si="19"/>
-        <v>-3.672625</v>
+        <v>-1.0994999999999999</v>
       </c>
       <c r="AD48"/>
       <c r="AE48"/>
@@ -39953,11 +41736,11 @@
       <c r="O51" s="215"/>
       <c r="P51" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>298056</v>
+        <v>546417</v>
       </c>
       <c r="Q51" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.74514000000000002</v>
+        <v>1.3660425</v>
       </c>
       <c r="R51" s="159"/>
       <c r="S51" s="88">
@@ -39973,11 +41756,11 @@
       <c r="W51" s="72"/>
       <c r="Y51" s="154">
         <f t="shared" si="18"/>
-        <v>-102243</v>
+        <v>146118</v>
       </c>
       <c r="Z51" s="168">
         <f t="shared" si="19"/>
-        <v>-0.2556075000000001</v>
+        <v>0.36529499999999993</v>
       </c>
     </row>
     <row r="52" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40034,11 +41817,11 @@
       <c r="O52" s="215"/>
       <c r="P52" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>224915</v>
+        <v>214785</v>
       </c>
       <c r="Q52" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>2.2491500000000002</v>
+        <v>2.14785</v>
       </c>
       <c r="R52" s="159"/>
       <c r="S52" s="88">
@@ -40054,11 +41837,11 @@
       <c r="W52" s="72"/>
       <c r="Y52" s="154">
         <f t="shared" si="18"/>
-        <v>970708</v>
+        <v>960578</v>
       </c>
       <c r="Z52" s="168">
         <f t="shared" si="19"/>
-        <v>9.7070800000000013</v>
+        <v>9.6057800000000011</v>
       </c>
     </row>
     <row r="53" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40115,11 +41898,11 @@
       <c r="O53" s="215"/>
       <c r="P53" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-75385</v>
+        <v>-74894</v>
       </c>
       <c r="Q53" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1.5076999999999998</v>
+        <v>-1.4978799999999999</v>
       </c>
       <c r="R53" s="159"/>
       <c r="S53" s="153">
@@ -40136,11 +41919,11 @@
       <c r="X53" s="132"/>
       <c r="Y53" s="154">
         <f t="shared" si="18"/>
-        <v>-321163</v>
+        <v>-320672</v>
       </c>
       <c r="Z53" s="168">
         <f t="shared" si="19"/>
-        <v>-6.42326</v>
+        <v>-6.4134399999999996</v>
       </c>
       <c r="AA53" s="132"/>
     </row>
@@ -40198,11 +41981,11 @@
       <c r="O54" s="215"/>
       <c r="P54" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>10809</v>
+        <v>-56793</v>
       </c>
       <c r="Q54" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>3.6030000000000006E-2</v>
+        <v>-0.18931000000000009</v>
       </c>
       <c r="R54" s="159"/>
       <c r="S54" s="88">
@@ -40218,11 +42001,11 @@
       <c r="W54" s="72"/>
       <c r="Y54" s="154">
         <f t="shared" si="18"/>
-        <v>-4688166</v>
+        <v>-4755768</v>
       </c>
       <c r="Z54" s="168">
         <f t="shared" si="19"/>
-        <v>-15.627220000000003</v>
+        <v>-15.852560000000004</v>
       </c>
       <c r="AB54" s="132"/>
       <c r="AC54" s="132"/>
@@ -40281,11 +42064,11 @@
       <c r="O55" s="215"/>
       <c r="P55" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-4835</v>
+        <v>-39847</v>
       </c>
       <c r="Q55" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1.6116666666666696E-2</v>
+        <v>-0.13282333333333335</v>
       </c>
       <c r="R55" s="159"/>
       <c r="S55" s="153">
@@ -40302,11 +42085,11 @@
       <c r="X55" s="132"/>
       <c r="Y55" s="154">
         <f t="shared" si="18"/>
-        <v>-294281</v>
+        <v>-329293</v>
       </c>
       <c r="Z55" s="168">
         <f t="shared" si="19"/>
-        <v>-0.98093666666666668</v>
+        <v>-1.0976433333333333</v>
       </c>
     </row>
     <row r="56" spans="1:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40363,11 +42146,11 @@
       <c r="O56" s="215"/>
       <c r="P56" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>55136</v>
+        <v>40506</v>
       </c>
       <c r="Q56" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.1837866666666666</v>
+        <v>0.13501999999999992</v>
       </c>
       <c r="R56" s="159"/>
       <c r="S56" s="88">
@@ -40384,11 +42167,11 @@
       <c r="X56"/>
       <c r="Y56" s="154">
         <f t="shared" si="18"/>
-        <v>150930</v>
+        <v>136300</v>
       </c>
       <c r="Z56" s="168">
         <f t="shared" si="19"/>
-        <v>0.50309999999999988</v>
+        <v>0.4543333333333332</v>
       </c>
       <c r="AB56"/>
       <c r="AC56"/>
@@ -40541,11 +42324,11 @@
       <c r="O58" s="215"/>
       <c r="P58" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>459273</v>
+        <v>694995</v>
       </c>
       <c r="Q58" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>4.5927300000000004</v>
+        <v>6.9499500000000003</v>
       </c>
       <c r="R58" s="159"/>
       <c r="S58" s="88">
@@ -40561,11 +42344,11 @@
       <c r="W58" s="72"/>
       <c r="Y58" s="154">
         <f t="shared" si="18"/>
-        <v>4009342</v>
+        <v>4245064</v>
       </c>
       <c r="Z58" s="168">
         <f t="shared" si="19"/>
-        <v>40.093420000000002</v>
+        <v>42.45064</v>
       </c>
       <c r="AB58" s="132"/>
       <c r="AC58" s="132"/>
@@ -40627,11 +42410,11 @@
       <c r="O59" s="215"/>
       <c r="P59" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-4826</v>
+        <v>-3104</v>
       </c>
       <c r="Q59" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.48260000000000003</v>
+        <v>-0.31040000000000001</v>
       </c>
       <c r="R59" s="159"/>
       <c r="S59" s="153">
@@ -40647,11 +42430,11 @@
       <c r="W59" s="150"/>
       <c r="Y59" s="154">
         <f t="shared" ref="Y59" si="29">M59+P59+S59+V59</f>
-        <v>-4826</v>
+        <v>-3104</v>
       </c>
       <c r="Z59" s="168">
         <f t="shared" ref="Z59" si="30">(N59+Q59+T59+W59)</f>
-        <v>-0.48260000000000003</v>
+        <v>-0.31040000000000001</v>
       </c>
     </row>
     <row r="60" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40708,11 +42491,11 @@
       <c r="O60" s="215"/>
       <c r="P60" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>77351</v>
+        <v>326369</v>
       </c>
       <c r="Q60" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.25783666666666638</v>
+        <v>1.0878966666666665</v>
       </c>
       <c r="R60" s="159"/>
       <c r="S60" s="88">
@@ -40728,11 +42511,11 @@
       <c r="W60" s="72"/>
       <c r="Y60" s="154">
         <f t="shared" si="18"/>
-        <v>750200</v>
+        <v>999218</v>
       </c>
       <c r="Z60" s="168">
         <f t="shared" si="19"/>
-        <v>2.5006666666666661</v>
+        <v>3.3307266666666662</v>
       </c>
       <c r="AB60" s="1"/>
       <c r="AC60" s="1"/>
@@ -40796,11 +42579,11 @@
       <c r="O61" s="215"/>
       <c r="P61" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>414410</v>
+        <v>517102</v>
       </c>
       <c r="Q61" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1.036025</v>
+        <v>1.2927550000000001</v>
       </c>
       <c r="R61" s="159"/>
       <c r="S61" s="88">
@@ -40816,11 +42599,11 @@
       <c r="W61" s="72"/>
       <c r="Y61" s="154">
         <f t="shared" si="18"/>
-        <v>1089410</v>
+        <v>1192102</v>
       </c>
       <c r="Z61" s="168">
         <f t="shared" si="19"/>
-        <v>2.723525</v>
+        <v>2.9802550000000001</v>
       </c>
     </row>
     <row r="62" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40959,11 +42742,11 @@
       <c r="O63" s="215"/>
       <c r="P63" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>300390</v>
+        <v>342074</v>
       </c>
       <c r="Q63" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.75097499999999995</v>
+        <v>0.85518499999999986</v>
       </c>
       <c r="R63" s="159"/>
       <c r="S63" s="153">
@@ -40980,11 +42763,11 @@
       <c r="X63" s="132"/>
       <c r="Y63" s="154">
         <f t="shared" si="18"/>
-        <v>824802</v>
+        <v>866486</v>
       </c>
       <c r="Z63" s="168">
         <f t="shared" si="19"/>
-        <v>2.0620050000000001</v>
+        <v>2.1662150000000002</v>
       </c>
     </row>
     <row r="64" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -41121,11 +42904,11 @@
       <c r="O65" s="215"/>
       <c r="P65" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-464997</v>
+        <v>148388</v>
       </c>
       <c r="Q65" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.93019399999999997</v>
+        <v>0.148288</v>
       </c>
       <c r="R65" s="159"/>
       <c r="S65" s="153">
@@ -41141,11 +42924,11 @@
       <c r="W65" s="150"/>
       <c r="Y65" s="154">
         <f t="shared" ref="Y65" si="35">M65+P65+S65+V65</f>
-        <v>-464997</v>
+        <v>148388</v>
       </c>
       <c r="Z65" s="168">
         <f t="shared" ref="Z65" si="36">(N65+Q65+T65+W65)</f>
-        <v>-0.93019399999999997</v>
+        <v>0.148288</v>
       </c>
     </row>
     <row r="66" spans="1:27" x14ac:dyDescent="0.25">
@@ -41202,11 +42985,11 @@
       <c r="O66" s="215"/>
       <c r="P66" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-30142</v>
+        <v>-14245</v>
       </c>
       <c r="Q66" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.60284000000000004</v>
+        <v>-0.28489999999999999</v>
       </c>
       <c r="R66" s="159"/>
       <c r="S66" s="153">
@@ -41222,11 +43005,11 @@
       <c r="W66" s="150"/>
       <c r="Y66" s="154">
         <f t="shared" si="18"/>
-        <v>-76796</v>
+        <v>-60899</v>
       </c>
       <c r="Z66" s="168">
         <f t="shared" si="19"/>
-        <v>-1.53592</v>
+        <v>-1.2179800000000001</v>
       </c>
     </row>
     <row r="67" spans="1:27" x14ac:dyDescent="0.25">
@@ -41283,11 +43066,11 @@
       <c r="O67" s="215"/>
       <c r="P67" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>799439</v>
+        <v>1139620</v>
       </c>
       <c r="Q67" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1.9985975</v>
+        <v>2.8490500000000001</v>
       </c>
       <c r="R67" s="159"/>
       <c r="S67" s="153">
@@ -41303,11 +43086,11 @@
       <c r="W67" s="150"/>
       <c r="Y67" s="154">
         <f t="shared" si="18"/>
-        <v>391487</v>
+        <v>731668</v>
       </c>
       <c r="Z67" s="168">
         <f t="shared" si="19"/>
-        <v>0.97871749999999991</v>
+        <v>1.82917</v>
       </c>
     </row>
     <row r="68" spans="1:27" x14ac:dyDescent="0.25">
@@ -41364,11 +43147,11 @@
       <c r="O68" s="215"/>
       <c r="P68" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>208394</v>
+        <v>183258</v>
       </c>
       <c r="Q68" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1.6671520000000002</v>
+        <v>1.466064</v>
       </c>
       <c r="R68" s="159"/>
       <c r="S68" s="153">
@@ -41384,11 +43167,11 @@
       <c r="W68" s="150"/>
       <c r="Y68" s="154">
         <f t="shared" si="18"/>
-        <v>185112</v>
+        <v>159976</v>
       </c>
       <c r="Z68" s="168">
         <f t="shared" si="19"/>
-        <v>1.4343320000000002</v>
+        <v>1.233244</v>
       </c>
     </row>
     <row r="69" spans="1:27" x14ac:dyDescent="0.25">
@@ -41526,11 +43309,11 @@
       <c r="O70" s="215"/>
       <c r="P70" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>723115</v>
+        <v>820640</v>
       </c>
       <c r="Q70" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>2.4103833333333338</v>
+        <v>2.7354666666666669</v>
       </c>
       <c r="R70" s="159"/>
       <c r="S70" s="88">
@@ -41546,11 +43329,11 @@
       <c r="W70" s="72"/>
       <c r="Y70" s="154">
         <f t="shared" si="18"/>
-        <v>555733</v>
+        <v>653258</v>
       </c>
       <c r="Z70" s="168">
         <f t="shared" si="19"/>
-        <v>1.8524433333333339</v>
+        <v>2.1775266666666671</v>
       </c>
     </row>
     <row r="71" spans="1:27" x14ac:dyDescent="0.25">
@@ -41607,11 +43390,11 @@
       <c r="O71" s="215"/>
       <c r="P71" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-42961</v>
+        <v>-109640</v>
       </c>
       <c r="Q71" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.171844</v>
+        <v>-0.43856000000000001</v>
       </c>
       <c r="R71" s="159"/>
       <c r="S71" s="88">
@@ -41627,11 +43410,11 @@
       <c r="W71" s="72"/>
       <c r="Y71" s="154">
         <f t="shared" si="18"/>
-        <v>-314713</v>
+        <v>-381392</v>
       </c>
       <c r="Z71" s="168">
         <f t="shared" si="19"/>
-        <v>-1.2588520000000001</v>
+        <v>-1.5255680000000003</v>
       </c>
     </row>
     <row r="72" spans="1:27" s="132" customFormat="1" x14ac:dyDescent="0.25">
@@ -41686,11 +43469,11 @@
       <c r="O72" s="215"/>
       <c r="P72" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-6157</v>
+        <v>46776</v>
       </c>
       <c r="Q72" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.24628</v>
+        <v>1.8710399999999998</v>
       </c>
       <c r="R72" s="159"/>
       <c r="S72" s="153">
@@ -41706,11 +43489,11 @@
       <c r="W72" s="150"/>
       <c r="Y72" s="154">
         <f t="shared" ref="Y72:Y73" si="41">M72+P72+S72+V72</f>
-        <v>-6157</v>
+        <v>46776</v>
       </c>
       <c r="Z72" s="168">
         <f t="shared" ref="Z72:Z73" si="42">(N72+Q72+T72+W72)</f>
-        <v>-0.24628</v>
+        <v>1.8710399999999998</v>
       </c>
     </row>
     <row r="73" spans="1:27" s="132" customFormat="1" x14ac:dyDescent="0.25">
@@ -41765,11 +43548,11 @@
       <c r="O73" s="215"/>
       <c r="P73" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>203148</v>
+        <v>459559</v>
       </c>
       <c r="Q73" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$136,'FY-(26-27)Q2'!$A$4:$ABW$120,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.40629599999999993</v>
+        <v>0.91911799999999988</v>
       </c>
       <c r="R73" s="159"/>
       <c r="S73" s="153">
@@ -41785,11 +43568,11 @@
       <c r="W73" s="150"/>
       <c r="Y73" s="154">
         <f t="shared" si="41"/>
-        <v>203148</v>
+        <v>459559</v>
       </c>
       <c r="Z73" s="168">
         <f t="shared" si="42"/>
-        <v>0.40629599999999993</v>
+        <v>0.91911799999999988</v>
       </c>
     </row>
     <row r="74" spans="1:27" x14ac:dyDescent="0.25">
@@ -41819,7 +43602,7 @@
       <c r="O74" s="122"/>
       <c r="P74" s="109">
         <f>SUM(P4:P71)</f>
-        <v>12568331</v>
+        <v>15174001</v>
       </c>
       <c r="Q74" s="122"/>
       <c r="R74" s="122"/>
@@ -41830,7 +43613,7 @@
       <c r="W74" s="50"/>
       <c r="Y74" s="154">
         <f>SUM(Y4:Y73)</f>
-        <v>32122857</v>
+        <v>35037871</v>
       </c>
       <c r="Z74" s="161"/>
     </row>
@@ -42285,1122 +44068,1122 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A54:C54 V4:W4 A25:F27 V18:W19 A11:C11 W47:W48 A3:F4 L2:L3 A47:F48 A51:C51 W20:W28 A77:F78 C14 A7:F8 W44:W45 W41 A41:H41 G40:H40 F14 F11 F67:F68 W56:W58 G56:J58 A64:J64 Y56:Y58 Y74:Z74 G11:H12 G7:J10 F52 F54:J54 Y54 W51:W54 H4:O4 M5:O5 G14:H16 I11:J16 Y4:Z16 K5:L16 A18:F22 D5:J5 F69:J71 A43:J43 Y64 Z54:Z58 G44:J53 Y18:Z31 K43:L58 A70:C70 A71:E71 A44:F45 E51:F51 A58:F58 Y33:Z35 G18:O31 M77:O79 M7:O16 A33:O35 R43:W43 R69:W71 R7:W8 R11:W14 R33:W35 R44:U45 R15:U15 R20:U28 R47:U58 U77:U79 A74:E74 A37:H38 A60:F60 K60:O64 Z60:Z64 Y60:Y61 G60:J61 R37:U42 M37:O58 I37:L42 Y37:Z53 W37:W38 G74:W75 G81:W81 K66:O71 G66:J66 W64:W65 R60:U68 G65:O65 Y65:Z71">
-    <cfRule type="expression" dxfId="224" priority="427">
+    <cfRule type="expression" dxfId="225" priority="427">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V37:V38 V21:V22 V57 V47:V48 V54 V44:V45 V25:V27 G2:I3 V51 G4:H4">
-    <cfRule type="expression" dxfId="223" priority="426">
+    <cfRule type="expression" dxfId="224" priority="426">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J3">
-    <cfRule type="expression" dxfId="222" priority="423">
+    <cfRule type="expression" dxfId="223" priority="423">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V77:W78">
-    <cfRule type="expression" dxfId="221" priority="420">
+    <cfRule type="expression" dxfId="222" priority="420">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K3">
-    <cfRule type="expression" dxfId="220" priority="421">
+    <cfRule type="expression" dxfId="221" priority="421">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V58">
-    <cfRule type="expression" dxfId="219" priority="411">
+    <cfRule type="expression" dxfId="220" priority="411">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V20">
-    <cfRule type="expression" dxfId="218" priority="412">
+    <cfRule type="expression" dxfId="219" priority="412">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A52:C52 E52">
-    <cfRule type="expression" dxfId="217" priority="401">
+    <cfRule type="expression" dxfId="218" priority="401">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V52:V53">
-    <cfRule type="expression" dxfId="216" priority="399">
+    <cfRule type="expression" dxfId="217" priority="399">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E54">
-    <cfRule type="expression" dxfId="215" priority="397">
+    <cfRule type="expression" dxfId="216" priority="397">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V41">
-    <cfRule type="expression" dxfId="214" priority="388">
+    <cfRule type="expression" dxfId="215" priority="388">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A28:F28 A29:A31">
-    <cfRule type="expression" dxfId="213" priority="387">
+    <cfRule type="expression" dxfId="214" priority="387">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B69:C69">
-    <cfRule type="expression" dxfId="212" priority="359">
+    <cfRule type="expression" dxfId="213" priority="359">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V28">
-    <cfRule type="expression" dxfId="211" priority="385">
+    <cfRule type="expression" dxfId="212" priority="385">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:E24">
-    <cfRule type="expression" dxfId="210" priority="384">
+    <cfRule type="expression" dxfId="211" priority="384">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V24">
-    <cfRule type="expression" dxfId="209" priority="382">
+    <cfRule type="expression" dxfId="210" priority="382">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A23:E23">
-    <cfRule type="expression" dxfId="208" priority="381">
+    <cfRule type="expression" dxfId="209" priority="381">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V23">
-    <cfRule type="expression" dxfId="207" priority="379">
+    <cfRule type="expression" dxfId="208" priority="379">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A56:C56 E56:F56">
-    <cfRule type="expression" dxfId="206" priority="366">
+    <cfRule type="expression" dxfId="207" priority="366">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T4:U4 T18:U19">
-    <cfRule type="expression" dxfId="205" priority="310">
+    <cfRule type="expression" dxfId="206" priority="310">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A69">
-    <cfRule type="expression" dxfId="204" priority="357">
+    <cfRule type="expression" dxfId="205" priority="357">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S4:U4 S18:U19">
-    <cfRule type="expression" dxfId="203" priority="309">
+    <cfRule type="expression" dxfId="204" priority="309">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V56">
-    <cfRule type="expression" dxfId="202" priority="362">
+    <cfRule type="expression" dxfId="203" priority="362">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F23">
-    <cfRule type="expression" dxfId="201" priority="328">
+    <cfRule type="expression" dxfId="202" priority="328">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M18:O19 M33:O33">
-    <cfRule type="expression" dxfId="200" priority="326">
+    <cfRule type="expression" dxfId="201" priority="326">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:F15 A16:C16 E16:F16">
-    <cfRule type="expression" dxfId="199" priority="334">
+    <cfRule type="expression" dxfId="200" priority="334">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V15:W15">
-    <cfRule type="expression" dxfId="198" priority="333">
+    <cfRule type="expression" dxfId="199" priority="333">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R4 R18:R19">
-    <cfRule type="expression" dxfId="197" priority="318">
+    <cfRule type="expression" dxfId="198" priority="318">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R4 R18:R19">
-    <cfRule type="expression" dxfId="196" priority="317">
+    <cfRule type="expression" dxfId="197" priority="317">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V64:V65">
-    <cfRule type="expression" dxfId="195" priority="348">
+    <cfRule type="expression" dxfId="196" priority="348">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W60">
-    <cfRule type="expression" dxfId="194" priority="308">
+    <cfRule type="expression" dxfId="195" priority="308">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M34:O34">
-    <cfRule type="expression" dxfId="193" priority="319">
+    <cfRule type="expression" dxfId="194" priority="319">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F24">
-    <cfRule type="expression" dxfId="192" priority="329">
+    <cfRule type="expression" dxfId="193" priority="329">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N18:O19 N33:O33">
-    <cfRule type="expression" dxfId="191" priority="327">
+    <cfRule type="expression" dxfId="192" priority="327">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N34:O34">
-    <cfRule type="expression" dxfId="190" priority="320">
+    <cfRule type="expression" dxfId="191" priority="320">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V60">
-    <cfRule type="expression" dxfId="189" priority="307">
+    <cfRule type="expression" dxfId="190" priority="307">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M16:O16">
-    <cfRule type="expression" dxfId="188" priority="265">
+    <cfRule type="expression" dxfId="189" priority="265">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R16">
-    <cfRule type="expression" dxfId="187" priority="264">
+    <cfRule type="expression" dxfId="188" priority="264">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T16:U16">
-    <cfRule type="expression" dxfId="186" priority="262">
+    <cfRule type="expression" dxfId="187" priority="262">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29:F30 B31:C31 E31:F31">
-    <cfRule type="expression" dxfId="185" priority="254">
+    <cfRule type="expression" dxfId="186" priority="254">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W29:W30">
-    <cfRule type="expression" dxfId="184" priority="253">
+    <cfRule type="expression" dxfId="185" priority="253">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V16:W16">
-    <cfRule type="expression" dxfId="183" priority="267">
+    <cfRule type="expression" dxfId="184" priority="267">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N16:O16">
-    <cfRule type="expression" dxfId="182" priority="266">
+    <cfRule type="expression" dxfId="183" priority="266">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R16">
-    <cfRule type="expression" dxfId="181" priority="263">
+    <cfRule type="expression" dxfId="182" priority="263">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S16:U16">
-    <cfRule type="expression" dxfId="180" priority="261">
+    <cfRule type="expression" dxfId="181" priority="261">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V29:V30">
-    <cfRule type="expression" dxfId="179" priority="252">
+    <cfRule type="expression" dxfId="180" priority="252">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S29:U30">
-    <cfRule type="expression" dxfId="178" priority="246">
+    <cfRule type="expression" dxfId="179" priority="246">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N29:O30">
-    <cfRule type="expression" dxfId="177" priority="251">
+    <cfRule type="expression" dxfId="178" priority="251">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M29:O30">
-    <cfRule type="expression" dxfId="176" priority="250">
+    <cfRule type="expression" dxfId="177" priority="250">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T29:U30">
-    <cfRule type="expression" dxfId="175" priority="247">
+    <cfRule type="expression" dxfId="176" priority="247">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R29:R30">
-    <cfRule type="expression" dxfId="174" priority="249">
+    <cfRule type="expression" dxfId="175" priority="249">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R29:R30">
-    <cfRule type="expression" dxfId="173" priority="248">
+    <cfRule type="expression" dxfId="174" priority="248">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A10:F10 A9:C9 E9:F9">
-    <cfRule type="expression" dxfId="172" priority="239">
+    <cfRule type="expression" dxfId="173" priority="239">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V9:W10">
-    <cfRule type="expression" dxfId="171" priority="238">
+    <cfRule type="expression" dxfId="172" priority="238">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R9:R10">
-    <cfRule type="expression" dxfId="170" priority="235">
+    <cfRule type="expression" dxfId="171" priority="235">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R9:R10">
-    <cfRule type="expression" dxfId="169" priority="234">
+    <cfRule type="expression" dxfId="170" priority="234">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S9:U10">
-    <cfRule type="expression" dxfId="168" priority="232">
+    <cfRule type="expression" dxfId="169" priority="232">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N9:O10">
-    <cfRule type="expression" dxfId="167" priority="237">
+    <cfRule type="expression" dxfId="168" priority="237">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M9:O10">
-    <cfRule type="expression" dxfId="166" priority="236">
+    <cfRule type="expression" dxfId="167" priority="236">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T9:U10">
-    <cfRule type="expression" dxfId="165" priority="233">
+    <cfRule type="expression" dxfId="166" priority="233">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A46:C46 E46:F46">
-    <cfRule type="expression" dxfId="164" priority="225">
+    <cfRule type="expression" dxfId="165" priority="225">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W46">
-    <cfRule type="expression" dxfId="163" priority="224">
+    <cfRule type="expression" dxfId="164" priority="224">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V46">
-    <cfRule type="expression" dxfId="162" priority="223">
+    <cfRule type="expression" dxfId="163" priority="223">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T46:U46">
-    <cfRule type="expression" dxfId="161" priority="218">
+    <cfRule type="expression" dxfId="162" priority="218">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S46:U46">
-    <cfRule type="expression" dxfId="160" priority="217">
+    <cfRule type="expression" dxfId="161" priority="217">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M46:O46">
-    <cfRule type="expression" dxfId="159" priority="221">
+    <cfRule type="expression" dxfId="160" priority="221">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R46">
-    <cfRule type="expression" dxfId="158" priority="220">
+    <cfRule type="expression" dxfId="159" priority="220">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R46">
-    <cfRule type="expression" dxfId="157" priority="219">
+    <cfRule type="expression" dxfId="158" priority="219">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N46:O46">
-    <cfRule type="expression" dxfId="156" priority="222">
+    <cfRule type="expression" dxfId="157" priority="222">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A57:C57 E57:F57">
-    <cfRule type="expression" dxfId="155" priority="210">
+    <cfRule type="expression" dxfId="156" priority="210">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:C5">
-    <cfRule type="expression" dxfId="154" priority="206">
+    <cfRule type="expression" dxfId="155" priority="206">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V5:W5">
-    <cfRule type="expression" dxfId="153" priority="205">
+    <cfRule type="expression" dxfId="154" priority="205">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T5:U5">
-    <cfRule type="expression" dxfId="152" priority="199">
+    <cfRule type="expression" dxfId="153" priority="199">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S5:U5">
-    <cfRule type="expression" dxfId="151" priority="198">
+    <cfRule type="expression" dxfId="152" priority="198">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5:O5">
-    <cfRule type="expression" dxfId="150" priority="202">
+    <cfRule type="expression" dxfId="151" priority="202">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R5">
-    <cfRule type="expression" dxfId="149" priority="201">
+    <cfRule type="expression" dxfId="150" priority="201">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R5">
-    <cfRule type="expression" dxfId="148" priority="200">
+    <cfRule type="expression" dxfId="149" priority="200">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N5:O5">
-    <cfRule type="expression" dxfId="147" priority="203">
+    <cfRule type="expression" dxfId="148" priority="203">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A49:F50">
-    <cfRule type="expression" dxfId="146" priority="187">
+    <cfRule type="expression" dxfId="147" priority="187">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W49:W50">
-    <cfRule type="expression" dxfId="145" priority="186">
+    <cfRule type="expression" dxfId="146" priority="186">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V49:V50">
-    <cfRule type="expression" dxfId="144" priority="185">
+    <cfRule type="expression" dxfId="145" priority="185">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W31">
-    <cfRule type="expression" dxfId="143" priority="179">
+    <cfRule type="expression" dxfId="144" priority="179">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V31">
-    <cfRule type="expression" dxfId="142" priority="178">
+    <cfRule type="expression" dxfId="143" priority="178">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S31:U31">
-    <cfRule type="expression" dxfId="141" priority="172">
+    <cfRule type="expression" dxfId="142" priority="172">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N31:O31">
-    <cfRule type="expression" dxfId="140" priority="177">
+    <cfRule type="expression" dxfId="141" priority="177">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M31:O31">
-    <cfRule type="expression" dxfId="139" priority="176">
+    <cfRule type="expression" dxfId="140" priority="176">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T31:U31">
-    <cfRule type="expression" dxfId="138" priority="173">
+    <cfRule type="expression" dxfId="139" priority="173">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R31">
-    <cfRule type="expression" dxfId="137" priority="175">
+    <cfRule type="expression" dxfId="138" priority="175">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R31">
-    <cfRule type="expression" dxfId="136" priority="174">
+    <cfRule type="expression" dxfId="137" priority="174">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W61">
-    <cfRule type="expression" dxfId="135" priority="170">
+    <cfRule type="expression" dxfId="136" priority="170">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V61">
-    <cfRule type="expression" dxfId="134" priority="169">
+    <cfRule type="expression" dxfId="135" priority="169">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12:F12">
-    <cfRule type="expression" dxfId="133" priority="156">
+    <cfRule type="expression" dxfId="134" priority="156">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W40">
-    <cfRule type="expression" dxfId="132" priority="165">
+    <cfRule type="expression" dxfId="133" priority="165">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V40">
-    <cfRule type="expression" dxfId="131" priority="164">
+    <cfRule type="expression" dxfId="132" priority="164">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A66:C66 E66:F66">
-    <cfRule type="expression" dxfId="130" priority="154">
+    <cfRule type="expression" dxfId="131" priority="154">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W66">
-    <cfRule type="expression" dxfId="129" priority="153">
+    <cfRule type="expression" dxfId="130" priority="153">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V66">
-    <cfRule type="expression" dxfId="128" priority="152">
+    <cfRule type="expression" dxfId="129" priority="152">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G77:G78">
-    <cfRule type="expression" dxfId="127" priority="147">
+    <cfRule type="expression" dxfId="128" priority="147">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H77">
-    <cfRule type="expression" dxfId="126" priority="144">
+    <cfRule type="expression" dxfId="127" priority="144">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H78">
-    <cfRule type="expression" dxfId="125" priority="143">
+    <cfRule type="expression" dxfId="126" priority="143">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L76">
-    <cfRule type="expression" dxfId="124" priority="142">
+    <cfRule type="expression" dxfId="125" priority="142">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G76:I76">
-    <cfRule type="expression" dxfId="123" priority="141">
+    <cfRule type="expression" dxfId="124" priority="141">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J76">
-    <cfRule type="expression" dxfId="122" priority="140">
+    <cfRule type="expression" dxfId="123" priority="140">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K76">
-    <cfRule type="expression" dxfId="121" priority="139">
+    <cfRule type="expression" dxfId="122" priority="139">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y77:Z78">
-    <cfRule type="expression" dxfId="120" priority="126">
+    <cfRule type="expression" dxfId="121" priority="126">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A39:F39">
-    <cfRule type="expression" dxfId="119" priority="136">
+    <cfRule type="expression" dxfId="120" priority="136">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40:F40">
-    <cfRule type="expression" dxfId="118" priority="135">
+    <cfRule type="expression" dxfId="119" priority="135">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A42:F42">
-    <cfRule type="expression" dxfId="117" priority="134">
+    <cfRule type="expression" dxfId="118" priority="134">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W42 G42:H42">
-    <cfRule type="expression" dxfId="116" priority="133">
+    <cfRule type="expression" dxfId="117" priority="133">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V42">
-    <cfRule type="expression" dxfId="115" priority="132">
+    <cfRule type="expression" dxfId="116" priority="132">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W39 G39:H39">
-    <cfRule type="expression" dxfId="114" priority="131">
+    <cfRule type="expression" dxfId="115" priority="131">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V39">
-    <cfRule type="expression" dxfId="113" priority="130">
+    <cfRule type="expression" dxfId="114" priority="130">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D11:E11">
-    <cfRule type="expression" dxfId="112" priority="121">
+    <cfRule type="expression" dxfId="113" priority="121">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y81:Z81">
-    <cfRule type="expression" dxfId="111" priority="127">
+    <cfRule type="expression" dxfId="112" priority="127">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:B14">
-    <cfRule type="expression" dxfId="110" priority="125">
+    <cfRule type="expression" dxfId="111" priority="125">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13">
-    <cfRule type="expression" dxfId="109" priority="124">
+    <cfRule type="expression" dxfId="110" priority="124">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F13">
-    <cfRule type="expression" dxfId="108" priority="123">
+    <cfRule type="expression" dxfId="109" priority="123">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D13:E14">
-    <cfRule type="expression" dxfId="107" priority="122">
+    <cfRule type="expression" dxfId="108" priority="122">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G13:H13">
-    <cfRule type="expression" dxfId="106" priority="120">
+    <cfRule type="expression" dxfId="107" priority="120">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J77:J78">
-    <cfRule type="expression" dxfId="105" priority="117">
+    <cfRule type="expression" dxfId="106" priority="117">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I77:J78">
-    <cfRule type="expression" dxfId="104" priority="116">
+    <cfRule type="expression" dxfId="105" priority="116">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A67:C68 E67:E68">
-    <cfRule type="expression" dxfId="103" priority="115">
+    <cfRule type="expression" dxfId="104" priority="115">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G67:J68 M67:O68">
-    <cfRule type="expression" dxfId="102" priority="114">
+    <cfRule type="expression" dxfId="103" priority="114">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W67:W68">
-    <cfRule type="expression" dxfId="101" priority="113">
+    <cfRule type="expression" dxfId="102" priority="113">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V67:V68">
-    <cfRule type="expression" dxfId="100" priority="112">
+    <cfRule type="expression" dxfId="101" priority="112">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V55">
-    <cfRule type="expression" dxfId="99" priority="109">
+    <cfRule type="expression" dxfId="100" priority="109">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A55:C55 E55:F55">
-    <cfRule type="expression" dxfId="98" priority="111">
+    <cfRule type="expression" dxfId="99" priority="111">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W55 Y55 G55:J55">
-    <cfRule type="expression" dxfId="97" priority="110">
+    <cfRule type="expression" dxfId="98" priority="110">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A62:A63">
-    <cfRule type="expression" dxfId="96" priority="108">
+    <cfRule type="expression" dxfId="97" priority="108">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61:B61">
-    <cfRule type="expression" dxfId="95" priority="107">
+    <cfRule type="expression" dxfId="96" priority="107">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B62:B63">
-    <cfRule type="expression" dxfId="94" priority="106">
+    <cfRule type="expression" dxfId="95" priority="106">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M62:O63 G62:J63 Y62:Y63">
-    <cfRule type="expression" dxfId="93" priority="105">
+    <cfRule type="expression" dxfId="94" priority="105">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W62:W63">
-    <cfRule type="expression" dxfId="92" priority="103">
+    <cfRule type="expression" dxfId="93" priority="103">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V62:V63">
-    <cfRule type="expression" dxfId="91" priority="102">
+    <cfRule type="expression" dxfId="92" priority="102">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A6:C6 E6:F6">
-    <cfRule type="expression" dxfId="90" priority="101">
+    <cfRule type="expression" dxfId="91" priority="101">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G6:J6 M6:O6">
-    <cfRule type="expression" dxfId="89" priority="100">
+    <cfRule type="expression" dxfId="90" priority="100">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V6:W6">
-    <cfRule type="expression" dxfId="88" priority="99">
+    <cfRule type="expression" dxfId="89" priority="99">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T6:U6">
-    <cfRule type="expression" dxfId="87" priority="94">
+    <cfRule type="expression" dxfId="88" priority="94">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S6:U6">
-    <cfRule type="expression" dxfId="86" priority="93">
+    <cfRule type="expression" dxfId="87" priority="93">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M6:O6">
-    <cfRule type="expression" dxfId="85" priority="97">
+    <cfRule type="expression" dxfId="86" priority="97">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R6">
-    <cfRule type="expression" dxfId="84" priority="96">
+    <cfRule type="expression" dxfId="85" priority="96">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R6">
-    <cfRule type="expression" dxfId="83" priority="95">
+    <cfRule type="expression" dxfId="84" priority="95">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N6:O6">
-    <cfRule type="expression" dxfId="82" priority="98">
+    <cfRule type="expression" dxfId="83" priority="98">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A53:C53 E53:F53">
-    <cfRule type="expression" dxfId="81" priority="92">
+    <cfRule type="expression" dxfId="82" priority="92">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A79:F79">
-    <cfRule type="expression" dxfId="80" priority="90">
+    <cfRule type="expression" dxfId="81" priority="90">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V79:W79">
-    <cfRule type="expression" dxfId="79" priority="88">
+    <cfRule type="expression" dxfId="80" priority="88">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G79">
-    <cfRule type="expression" dxfId="78" priority="87">
+    <cfRule type="expression" dxfId="79" priority="87">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H79">
-    <cfRule type="expression" dxfId="77" priority="86">
+    <cfRule type="expression" dxfId="78" priority="86">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y79:Z79">
-    <cfRule type="expression" dxfId="76" priority="85">
+    <cfRule type="expression" dxfId="77" priority="85">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J79">
-    <cfRule type="expression" dxfId="75" priority="84">
+    <cfRule type="expression" dxfId="76" priority="84">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I79:J79">
-    <cfRule type="expression" dxfId="74" priority="83">
+    <cfRule type="expression" dxfId="75" priority="83">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K77:L79">
-    <cfRule type="expression" dxfId="73" priority="81">
+    <cfRule type="expression" dxfId="74" priority="81">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S17:U17">
-    <cfRule type="expression" dxfId="72" priority="71">
+    <cfRule type="expression" dxfId="73" priority="71">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:F17">
-    <cfRule type="expression" dxfId="71" priority="79">
+    <cfRule type="expression" dxfId="72" priority="79">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y17:Z17 G17:O17">
-    <cfRule type="expression" dxfId="70" priority="78">
+    <cfRule type="expression" dxfId="71" priority="78">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M17:O17">
-    <cfRule type="expression" dxfId="69" priority="75">
+    <cfRule type="expression" dxfId="70" priority="75">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R17">
-    <cfRule type="expression" dxfId="68" priority="74">
+    <cfRule type="expression" dxfId="69" priority="74">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T17:U17">
-    <cfRule type="expression" dxfId="67" priority="72">
+    <cfRule type="expression" dxfId="68" priority="72">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V17:W17">
-    <cfRule type="expression" dxfId="66" priority="77">
+    <cfRule type="expression" dxfId="67" priority="77">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N17:O17">
-    <cfRule type="expression" dxfId="65" priority="76">
+    <cfRule type="expression" dxfId="66" priority="76">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R17">
-    <cfRule type="expression" dxfId="64" priority="73">
+    <cfRule type="expression" dxfId="65" priority="73">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E69:E70">
-    <cfRule type="expression" dxfId="63" priority="70">
+    <cfRule type="expression" dxfId="64" priority="70">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F62:F63">
-    <cfRule type="expression" dxfId="62" priority="69">
+    <cfRule type="expression" dxfId="63" priority="69">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F61">
-    <cfRule type="expression" dxfId="61" priority="68">
+    <cfRule type="expression" dxfId="62" priority="68">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D61:E61 C62:E63">
-    <cfRule type="expression" dxfId="60" priority="67">
+    <cfRule type="expression" dxfId="61" priority="67">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9">
-    <cfRule type="expression" dxfId="59" priority="66">
+    <cfRule type="expression" dxfId="60" priority="66">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6">
-    <cfRule type="expression" dxfId="58" priority="65">
+    <cfRule type="expression" dxfId="59" priority="65">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D16">
-    <cfRule type="expression" dxfId="57" priority="64">
+    <cfRule type="expression" dxfId="58" priority="64">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D31">
-    <cfRule type="expression" dxfId="56" priority="63">
+    <cfRule type="expression" dxfId="57" priority="63">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D67:D68">
-    <cfRule type="expression" dxfId="55" priority="51">
+    <cfRule type="expression" dxfId="56" priority="51">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D46">
-    <cfRule type="expression" dxfId="54" priority="61">
+    <cfRule type="expression" dxfId="55" priority="61">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D52:D53">
-    <cfRule type="expression" dxfId="53" priority="60">
+    <cfRule type="expression" dxfId="54" priority="60">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D51">
-    <cfRule type="expression" dxfId="52" priority="59">
+    <cfRule type="expression" dxfId="53" priority="59">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D54">
-    <cfRule type="expression" dxfId="51" priority="58">
+    <cfRule type="expression" dxfId="52" priority="58">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D55">
-    <cfRule type="expression" dxfId="50" priority="57">
+    <cfRule type="expression" dxfId="51" priority="57">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D56">
-    <cfRule type="expression" dxfId="49" priority="56">
+    <cfRule type="expression" dxfId="50" priority="56">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D57">
-    <cfRule type="expression" dxfId="48" priority="55">
+    <cfRule type="expression" dxfId="49" priority="55">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D70">
-    <cfRule type="expression" dxfId="47" priority="54">
+    <cfRule type="expression" dxfId="48" priority="54">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D69">
-    <cfRule type="expression" dxfId="46" priority="53">
+    <cfRule type="expression" dxfId="47" priority="53">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D66">
-    <cfRule type="expression" dxfId="45" priority="52">
+    <cfRule type="expression" dxfId="46" priority="52">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A32:F32">
-    <cfRule type="expression" dxfId="44" priority="50">
+    <cfRule type="expression" dxfId="45" priority="50">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G32:O32 Y32:Z32">
-    <cfRule type="expression" dxfId="43" priority="49">
+    <cfRule type="expression" dxfId="44" priority="49">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W32">
-    <cfRule type="expression" dxfId="42" priority="48">
+    <cfRule type="expression" dxfId="43" priority="48">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V32">
-    <cfRule type="expression" dxfId="41" priority="47">
+    <cfRule type="expression" dxfId="42" priority="47">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S32:U32">
-    <cfRule type="expression" dxfId="40" priority="41">
+    <cfRule type="expression" dxfId="41" priority="41">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N32:O32">
-    <cfRule type="expression" dxfId="39" priority="46">
+    <cfRule type="expression" dxfId="40" priority="46">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M32:O32">
-    <cfRule type="expression" dxfId="38" priority="45">
+    <cfRule type="expression" dxfId="39" priority="45">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T32:U32">
-    <cfRule type="expression" dxfId="37" priority="42">
+    <cfRule type="expression" dxfId="38" priority="42">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R32">
-    <cfRule type="expression" dxfId="36" priority="44">
+    <cfRule type="expression" dxfId="37" priority="44">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R32">
-    <cfRule type="expression" dxfId="35" priority="43">
+    <cfRule type="expression" dxfId="36" priority="43">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q4:Q35 Q37:Q58 Q60:Q71">
-    <cfRule type="expression" dxfId="34" priority="38">
+    <cfRule type="expression" dxfId="35" priority="38">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P4:Q35 P37:Q58 P60:Q71">
-    <cfRule type="expression" dxfId="33" priority="37">
+    <cfRule type="expression" dxfId="34" priority="37">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R77:T79">
-    <cfRule type="expression" dxfId="32" priority="36">
+    <cfRule type="expression" dxfId="33" priority="36">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q77:Q79">
-    <cfRule type="expression" dxfId="31" priority="35">
+    <cfRule type="expression" dxfId="32" priority="35">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P77:Q79">
-    <cfRule type="expression" dxfId="30" priority="34">
+    <cfRule type="expression" dxfId="31" priority="34">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A73:F73">
-    <cfRule type="expression" dxfId="29" priority="33">
+    <cfRule type="expression" dxfId="30" priority="33">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A72:F72">
-    <cfRule type="expression" dxfId="28" priority="32">
+    <cfRule type="expression" dxfId="29" priority="32">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G72:O73 Y72:Z73 R72:W73">
-    <cfRule type="expression" dxfId="27" priority="31">
+    <cfRule type="expression" dxfId="28" priority="31">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q72:Q73">
-    <cfRule type="expression" dxfId="26" priority="30">
+    <cfRule type="expression" dxfId="27" priority="30">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P72:Q73">
-    <cfRule type="expression" dxfId="25" priority="29">
+    <cfRule type="expression" dxfId="26" priority="29">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P36:Q36">
-    <cfRule type="expression" dxfId="24" priority="18">
+    <cfRule type="expression" dxfId="25" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A36:F36">
-    <cfRule type="expression" dxfId="23" priority="27">
+    <cfRule type="expression" dxfId="24" priority="27">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P80:Q80">
-    <cfRule type="expression" dxfId="22" priority="3">
+    <cfRule type="expression" dxfId="23" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A59:F59">
-    <cfRule type="expression" dxfId="21" priority="25">
+    <cfRule type="expression" dxfId="22" priority="25">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W59 Y59:Z59 G59:O59 R59:U59">
-    <cfRule type="expression" dxfId="20" priority="24">
+    <cfRule type="expression" dxfId="21" priority="24">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V59">
-    <cfRule type="expression" dxfId="19" priority="23">
+    <cfRule type="expression" dxfId="20" priority="23">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q59">
-    <cfRule type="expression" dxfId="18" priority="22">
+    <cfRule type="expression" dxfId="19" priority="22">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P59:Q59">
-    <cfRule type="expression" dxfId="17" priority="21">
+    <cfRule type="expression" dxfId="18" priority="21">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y36:Z36 G36:O36 R36:W36">
-    <cfRule type="expression" dxfId="16" priority="20">
+    <cfRule type="expression" dxfId="17" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q36">
-    <cfRule type="expression" dxfId="15" priority="19">
+    <cfRule type="expression" dxfId="16" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q80">
-    <cfRule type="expression" dxfId="14" priority="4">
+    <cfRule type="expression" dxfId="15" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F80">
-    <cfRule type="expression" dxfId="13" priority="15">
+    <cfRule type="expression" dxfId="14" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A80:E80">
-    <cfRule type="expression" dxfId="12" priority="14">
+    <cfRule type="expression" dxfId="13" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M80:O80 U80">
-    <cfRule type="expression" dxfId="11" priority="13">
+    <cfRule type="expression" dxfId="12" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V80:W80">
-    <cfRule type="expression" dxfId="10" priority="12">
+    <cfRule type="expression" dxfId="11" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G80">
-    <cfRule type="expression" dxfId="9" priority="11">
+    <cfRule type="expression" dxfId="10" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H80">
-    <cfRule type="expression" dxfId="8" priority="10">
+    <cfRule type="expression" dxfId="9" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y80:Z80">
-    <cfRule type="expression" dxfId="7" priority="9">
+    <cfRule type="expression" dxfId="8" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J80">
-    <cfRule type="expression" dxfId="6" priority="8">
+    <cfRule type="expression" dxfId="7" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I80:J80">
-    <cfRule type="expression" dxfId="5" priority="7">
+    <cfRule type="expression" dxfId="6" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K80:L80">
-    <cfRule type="expression" dxfId="4" priority="6">
+    <cfRule type="expression" dxfId="5" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R80:T80">
-    <cfRule type="expression" dxfId="3" priority="5">
+    <cfRule type="expression" dxfId="4" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F65">
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A65:E65">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Quant Strategy(2026-27).xlsx
+++ b/Quant Strategy(2026-27).xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21480" windowHeight="6690" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21480" windowHeight="6690"/>
   </bookViews>
   <sheets>
     <sheet name="SEP-2026" sheetId="43" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2645" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2646" uniqueCount="322">
   <si>
     <t>Sudeep</t>
   </si>
@@ -2328,21 +2328,7 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="453">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="451">
     <dxf>
       <fill>
         <patternFill>
@@ -5831,7 +5817,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:V66"/>
+  <dimension ref="A1:W66"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" style="133" customWidth="1" outlineLevel="1"/>
@@ -5841,32 +5827,36 @@
     <col min="5" max="5" width="9.42578125" style="133" customWidth="1"/>
     <col min="6" max="6" width="6.5703125" style="133" customWidth="1"/>
     <col min="7" max="7" width="1.7109375" style="133" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="133" customWidth="1" outlineLevel="1"/>
-    <col min="9" max="9" width="11.28515625" style="133" customWidth="1"/>
-    <col min="10" max="10" width="10.42578125" style="133" customWidth="1" outlineLevel="1"/>
-    <col min="11" max="11" width="10.7109375" style="133" customWidth="1" outlineLevel="1"/>
-    <col min="12" max="17" width="9.140625" style="133"/>
-    <col min="18" max="18" width="14.140625" style="133" customWidth="1"/>
-    <col min="19" max="19" width="12" style="133" customWidth="1"/>
-    <col min="20" max="20" width="15.85546875" style="133" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="133"/>
+    <col min="8" max="9" width="13.42578125" style="133" customWidth="1" outlineLevel="1"/>
+    <col min="10" max="10" width="11.28515625" style="133" customWidth="1"/>
+    <col min="11" max="11" width="10.42578125" style="133" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="12" max="12" width="10.7109375" style="133" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="13" max="13" width="9.140625" style="133" collapsed="1"/>
+    <col min="14" max="18" width="9.140625" style="133"/>
+    <col min="19" max="19" width="14.140625" style="133" customWidth="1"/>
+    <col min="20" max="20" width="12" style="133" customWidth="1"/>
+    <col min="21" max="21" width="15.85546875" style="133" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="133"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G2" s="221"/>
       <c r="H2" s="222">
         <v>46266</v>
       </c>
-      <c r="I2" s="183"/>
-      <c r="J2" s="184" t="s">
+      <c r="I2" s="256">
+        <v>46267</v>
+      </c>
+      <c r="J2" s="183"/>
+      <c r="K2" s="184" t="s">
         <v>281</v>
       </c>
-      <c r="K2" s="185" t="s">
+      <c r="L2" s="185" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="186" t="s">
         <v>54</v>
       </c>
@@ -5889,17 +5879,20 @@
       <c r="H3" s="179" t="s">
         <v>233</v>
       </c>
-      <c r="I3" s="180"/>
-      <c r="J3" s="189"/>
-      <c r="K3" s="180"/>
-      <c r="R3" s="133" t="s">
+      <c r="I3" s="179" t="s">
+        <v>237</v>
+      </c>
+      <c r="J3" s="180"/>
+      <c r="K3" s="189"/>
+      <c r="L3" s="180"/>
+      <c r="S3" s="133" t="s">
         <v>198</v>
       </c>
-      <c r="S3" s="133">
+      <c r="T3" s="133">
         <v>13780</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="142" t="s">
         <v>216</v>
       </c>
@@ -5922,23 +5915,26 @@
       <c r="H4" s="158">
         <v>0</v>
       </c>
-      <c r="I4" s="211"/>
-      <c r="J4" s="171">
-        <f t="shared" ref="J4:J30" si="0">SUM(H4:I4)</f>
-        <v>0</v>
-      </c>
-      <c r="K4" s="149">
-        <f t="shared" ref="K4:K30" si="1">IFERROR(J4/F4*100,0)/10000000</f>
-        <v>0</v>
-      </c>
-      <c r="R4" s="133" t="s">
+      <c r="I4" s="158">
+        <v>-13362</v>
+      </c>
+      <c r="J4" s="211"/>
+      <c r="K4" s="171">
+        <f t="shared" ref="K4:K30" si="0">SUM(H4:J4)</f>
+        <v>-13362</v>
+      </c>
+      <c r="L4" s="149">
+        <f t="shared" ref="L4:L30" si="1">IFERROR(K4/F4*100,0)/10000000</f>
+        <v>-0.26723999999999998</v>
+      </c>
+      <c r="S4" s="133" t="s">
         <v>170</v>
       </c>
-      <c r="S4" s="133">
+      <c r="T4" s="133">
         <v>2865</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="142" t="s">
         <v>30</v>
       </c>
@@ -5961,17 +5957,20 @@
       <c r="H5" s="147">
         <v>-170827</v>
       </c>
-      <c r="I5" s="174"/>
-      <c r="J5" s="171">
+      <c r="I5" s="147">
+        <v>31407</v>
+      </c>
+      <c r="J5" s="174"/>
+      <c r="K5" s="171">
         <f t="shared" si="0"/>
-        <v>-170827</v>
-      </c>
-      <c r="K5" s="149">
+        <v>-139420</v>
+      </c>
+      <c r="L5" s="149">
         <f t="shared" si="1"/>
-        <v>-0.56942333333333339</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+        <v>-0.46473333333333339</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="142" t="s">
         <v>177</v>
       </c>
@@ -5994,17 +5993,20 @@
       <c r="H6" s="147">
         <v>0</v>
       </c>
-      <c r="I6" s="174"/>
-      <c r="J6" s="171">
+      <c r="I6" s="147">
+        <v>0</v>
+      </c>
+      <c r="J6" s="174"/>
+      <c r="K6" s="171">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K6" s="149">
+      <c r="L6" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="142"/>
       <c r="B7" s="141" t="s">
         <v>309</v>
@@ -6025,17 +6027,20 @@
       <c r="H7" s="147">
         <v>-57700</v>
       </c>
-      <c r="I7" s="174"/>
-      <c r="J7" s="171">
+      <c r="I7" s="147">
+        <v>13000</v>
+      </c>
+      <c r="J7" s="174"/>
+      <c r="K7" s="171">
         <f t="shared" si="0"/>
-        <v>-57700</v>
-      </c>
-      <c r="K7" s="149">
+        <v>-44700</v>
+      </c>
+      <c r="L7" s="149">
         <f t="shared" si="1"/>
-        <v>-0.57699999999999996</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+        <v>-0.44700000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="142" t="s">
         <v>134</v>
       </c>
@@ -6058,21 +6063,24 @@
       <c r="H8" s="147">
         <v>179600</v>
       </c>
-      <c r="I8" s="174"/>
-      <c r="J8" s="171">
+      <c r="I8" s="147">
+        <v>-26565</v>
+      </c>
+      <c r="J8" s="174"/>
+      <c r="K8" s="171">
         <f t="shared" si="0"/>
-        <v>179600</v>
-      </c>
-      <c r="K8" s="149">
+        <v>153035</v>
+      </c>
+      <c r="L8" s="149">
         <f t="shared" si="1"/>
-        <v>0.59866666666666657</v>
-      </c>
-      <c r="M8" s="5"/>
-      <c r="N8" s="134">
-        <v>-173831</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+        <v>0.51011666666666655</v>
+      </c>
+      <c r="N8" s="5"/>
+      <c r="O8" s="134">
+        <v>-2106</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="142" t="s">
         <v>217</v>
       </c>
@@ -6095,21 +6103,24 @@
       <c r="H9" s="147">
         <v>59398</v>
       </c>
-      <c r="I9" s="174"/>
-      <c r="J9" s="171">
+      <c r="I9" s="147">
+        <v>-14500</v>
+      </c>
+      <c r="J9" s="174"/>
+      <c r="K9" s="171">
         <f t="shared" si="0"/>
-        <v>59398</v>
-      </c>
-      <c r="K9" s="149">
+        <v>44898</v>
+      </c>
+      <c r="L9" s="149">
         <f t="shared" si="1"/>
-        <v>0.39598666666666665</v>
-      </c>
-      <c r="M9" s="134">
-        <v>1114329</v>
-      </c>
-      <c r="N9" s="134"/>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+        <v>0.29931999999999997</v>
+      </c>
+      <c r="N9" s="134">
+        <v>494669</v>
+      </c>
+      <c r="O9" s="134"/>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="142" t="s">
         <v>313</v>
       </c>
@@ -6130,24 +6141,27 @@
       <c r="H10" s="147">
         <v>8234</v>
       </c>
-      <c r="I10" s="174"/>
-      <c r="J10" s="171">
+      <c r="I10" s="147">
+        <v>-21600</v>
+      </c>
+      <c r="J10" s="174"/>
+      <c r="K10" s="171">
         <f t="shared" si="0"/>
-        <v>8234</v>
-      </c>
-      <c r="K10" s="149">
+        <v>-13366</v>
+      </c>
+      <c r="L10" s="149">
         <f t="shared" si="1"/>
-        <v>0.13723333333333335</v>
-      </c>
-      <c r="M10" s="134">
-        <v>940498</v>
+        <v>-0.2227666666666667</v>
       </c>
       <c r="N10" s="134">
-        <f>(M10+M9)/10000000*13780</f>
-        <v>2831.551606</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+        <v>492563</v>
+      </c>
+      <c r="O10" s="134">
+        <f>(N10+N9)/10000000*13780</f>
+        <v>1360.405696</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" s="143" t="s">
         <v>35</v>
       </c>
@@ -6170,19 +6184,22 @@
       <c r="H11" s="147">
         <v>-413740</v>
       </c>
-      <c r="I11" s="174"/>
-      <c r="J11" s="171">
+      <c r="I11" s="147">
+        <v>0</v>
+      </c>
+      <c r="J11" s="174"/>
+      <c r="K11" s="171">
         <f t="shared" si="0"/>
         <v>-413740</v>
       </c>
-      <c r="K11" s="149">
+      <c r="L11" s="149">
         <f t="shared" si="1"/>
         <v>-0.27582666666666672</v>
       </c>
-      <c r="M11" s="134"/>
       <c r="N11" s="134"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="O11" s="134"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="143" t="s">
         <v>137</v>
       </c>
@@ -6205,19 +6222,22 @@
       <c r="H12" s="147">
         <v>-61243</v>
       </c>
-      <c r="I12" s="174"/>
-      <c r="J12" s="171">
+      <c r="I12" s="147">
+        <v>50</v>
+      </c>
+      <c r="J12" s="174"/>
+      <c r="K12" s="171">
         <f t="shared" si="0"/>
-        <v>-61243</v>
-      </c>
-      <c r="K12" s="149">
+        <v>-61193</v>
+      </c>
+      <c r="L12" s="149">
         <f t="shared" si="1"/>
-        <v>-0.10207166666666666</v>
-      </c>
-      <c r="M12" s="134"/>
+        <v>-0.10198833333333333</v>
+      </c>
       <c r="N12" s="134"/>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="O12" s="134"/>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="143" t="s">
         <v>42</v>
       </c>
@@ -6240,19 +6260,22 @@
       <c r="H13" s="147">
         <v>-4458</v>
       </c>
-      <c r="I13" s="174"/>
-      <c r="J13" s="171">
+      <c r="I13" s="147">
+        <v>-2649</v>
+      </c>
+      <c r="J13" s="174"/>
+      <c r="K13" s="171">
         <f t="shared" si="0"/>
-        <v>-4458</v>
-      </c>
-      <c r="K13" s="149">
+        <v>-7107</v>
+      </c>
+      <c r="L13" s="149">
         <f t="shared" si="1"/>
-        <v>-4.4580000000000002E-2</v>
-      </c>
-      <c r="M13" s="134"/>
+        <v>-7.1069999999999994E-2</v>
+      </c>
       <c r="N13" s="134"/>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="O13" s="134"/>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="142" t="s">
         <v>212</v>
       </c>
@@ -6275,19 +6298,22 @@
       <c r="H14" s="147">
         <v>724</v>
       </c>
-      <c r="I14" s="174"/>
-      <c r="J14" s="171">
+      <c r="I14" s="147">
+        <v>0</v>
+      </c>
+      <c r="J14" s="174"/>
+      <c r="K14" s="171">
         <f t="shared" si="0"/>
         <v>724</v>
       </c>
-      <c r="K14" s="149">
+      <c r="L14" s="149">
         <f t="shared" si="1"/>
         <v>2.8960000000000006E-3</v>
       </c>
-      <c r="M14" s="134"/>
       <c r="N14" s="134"/>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="O14" s="134"/>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" s="142" t="s">
         <v>51</v>
       </c>
@@ -6310,29 +6336,32 @@
       <c r="H15" s="147">
         <v>-4897</v>
       </c>
-      <c r="I15" s="174"/>
-      <c r="J15" s="171">
+      <c r="I15" s="147">
+        <v>0</v>
+      </c>
+      <c r="J15" s="174"/>
+      <c r="K15" s="171">
         <f t="shared" si="0"/>
         <v>-4897</v>
       </c>
-      <c r="K15" s="149">
+      <c r="L15" s="149">
         <f t="shared" si="1"/>
         <v>-2.2259090909090905E-2</v>
       </c>
-      <c r="M15" s="134"/>
-      <c r="N15" s="193">
-        <f>N8-N10</f>
-        <v>-176662.55160599999</v>
-      </c>
-      <c r="Q15" s="133">
+      <c r="N15" s="134"/>
+      <c r="O15" s="193">
+        <f>O8-O10</f>
+        <v>-3466.4056959999998</v>
+      </c>
+      <c r="R15" s="133">
         <v>116185</v>
       </c>
-      <c r="S15" s="133">
-        <f>Q15+N15</f>
-        <v>-60477.551605999994</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T15" s="133">
+        <f>R15+O15</f>
+        <v>112718.594304</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" s="142" t="s">
         <v>43</v>
       </c>
@@ -6355,17 +6384,20 @@
       <c r="H16" s="147">
         <v>-11113</v>
       </c>
-      <c r="I16" s="174"/>
-      <c r="J16" s="171">
+      <c r="I16" s="147">
+        <v>-3245</v>
+      </c>
+      <c r="J16" s="174"/>
+      <c r="K16" s="171">
         <f t="shared" si="0"/>
-        <v>-11113</v>
-      </c>
-      <c r="K16" s="149">
+        <v>-14358</v>
+      </c>
+      <c r="L16" s="149">
         <f t="shared" si="1"/>
-        <v>-0.11113000000000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+        <v>-0.14358000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A17" s="142" t="s">
         <v>24</v>
       </c>
@@ -6388,28 +6420,31 @@
       <c r="H17" s="147">
         <v>0</v>
       </c>
-      <c r="I17" s="174"/>
-      <c r="J17" s="171">
+      <c r="I17" s="147">
+        <v>0</v>
+      </c>
+      <c r="J17" s="174"/>
+      <c r="K17" s="171">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K17" s="149">
+      <c r="L17" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="S17" s="133">
+      <c r="T17" s="133">
         <v>4000000</v>
       </c>
-      <c r="T17" s="133">
-        <f>S17*7/100</f>
+      <c r="U17" s="133">
+        <f>T17*7/100</f>
         <v>280000</v>
       </c>
-      <c r="V17" s="133">
+      <c r="W17" s="133">
         <f>15*12</f>
         <v>180</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A18" s="142" t="s">
         <v>23</v>
       </c>
@@ -6432,21 +6467,24 @@
       <c r="H18" s="147">
         <v>0</v>
       </c>
-      <c r="I18" s="174"/>
-      <c r="J18" s="171">
+      <c r="I18" s="147">
+        <v>0</v>
+      </c>
+      <c r="J18" s="174"/>
+      <c r="K18" s="171">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K18" s="149">
+      <c r="L18" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="T18" s="133">
-        <f>T17/12</f>
+      <c r="U18" s="133">
+        <f>U17/12</f>
         <v>23333.333333333332</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19" s="142" t="s">
         <v>165</v>
       </c>
@@ -6469,17 +6507,20 @@
       <c r="H19" s="147">
         <v>17500</v>
       </c>
-      <c r="I19" s="174"/>
-      <c r="J19" s="171">
+      <c r="I19" s="147">
+        <v>-31966</v>
+      </c>
+      <c r="J19" s="174"/>
+      <c r="K19" s="171">
         <f t="shared" si="0"/>
-        <v>17500</v>
-      </c>
-      <c r="K19" s="149">
+        <v>-14466</v>
+      </c>
+      <c r="L19" s="149">
         <f t="shared" si="1"/>
-        <v>0.11666666666666665</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+        <v>-9.6439999999999998E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20" s="142" t="s">
         <v>110</v>
       </c>
@@ -6502,17 +6543,20 @@
       <c r="H20" s="147">
         <v>9433</v>
       </c>
-      <c r="I20" s="174"/>
-      <c r="J20" s="171">
+      <c r="I20" s="147">
+        <v>0</v>
+      </c>
+      <c r="J20" s="174"/>
+      <c r="K20" s="171">
         <f t="shared" si="0"/>
         <v>9433</v>
       </c>
-      <c r="K20" s="149">
+      <c r="L20" s="149">
         <f t="shared" si="1"/>
         <v>8.5754545454545431E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A21" s="142" t="s">
         <v>319</v>
       </c>
@@ -6535,17 +6579,20 @@
       <c r="H21" s="147">
         <v>4737</v>
       </c>
-      <c r="I21" s="174"/>
-      <c r="J21" s="171">
+      <c r="I21" s="147">
+        <v>-3466</v>
+      </c>
+      <c r="J21" s="174"/>
+      <c r="K21" s="171">
         <f t="shared" si="0"/>
-        <v>4737</v>
-      </c>
-      <c r="K21" s="149">
+        <v>1271</v>
+      </c>
+      <c r="L21" s="149">
         <f t="shared" si="1"/>
-        <v>0.18948000000000001</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+        <v>5.0840000000000003E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A22" s="142" t="s">
         <v>316</v>
       </c>
@@ -6568,17 +6615,20 @@
       <c r="H22" s="147">
         <v>-1048</v>
       </c>
-      <c r="I22" s="174"/>
-      <c r="J22" s="171">
+      <c r="I22" s="147">
+        <v>6953</v>
+      </c>
+      <c r="J22" s="174"/>
+      <c r="K22" s="171">
         <f t="shared" si="0"/>
-        <v>-1048</v>
-      </c>
-      <c r="K22" s="149">
+        <v>5905</v>
+      </c>
+      <c r="L22" s="149">
         <f t="shared" si="1"/>
-        <v>-5.2399999999999999E-3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+        <v>2.9524999999999999E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A23" s="142" t="s">
         <v>317</v>
       </c>
@@ -6599,17 +6649,20 @@
       <c r="H23" s="147">
         <v>0</v>
       </c>
-      <c r="I23" s="174"/>
-      <c r="J23" s="171">
+      <c r="I23" s="147">
+        <v>0</v>
+      </c>
+      <c r="J23" s="174"/>
+      <c r="K23" s="171">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K23" s="149">
+      <c r="L23" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A24" s="142" t="s">
         <v>32</v>
       </c>
@@ -6632,17 +6685,20 @@
       <c r="H24" s="147">
         <v>9208</v>
       </c>
-      <c r="I24" s="174"/>
-      <c r="J24" s="171">
+      <c r="I24" s="147">
+        <v>700</v>
+      </c>
+      <c r="J24" s="174"/>
+      <c r="K24" s="171">
         <f t="shared" si="0"/>
-        <v>9208</v>
-      </c>
-      <c r="K24" s="149">
+        <v>9908</v>
+      </c>
+      <c r="L24" s="149">
         <f t="shared" si="1"/>
-        <v>8.37090909090909E-2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+        <v>9.0072727272727263E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A25" s="142" t="s">
         <v>97</v>
       </c>
@@ -6665,17 +6721,20 @@
       <c r="H25" s="147">
         <v>-244000</v>
       </c>
-      <c r="I25" s="174"/>
-      <c r="J25" s="171">
+      <c r="I25" s="147">
+        <v>-162700</v>
+      </c>
+      <c r="J25" s="174"/>
+      <c r="K25" s="171">
         <f t="shared" si="0"/>
-        <v>-244000</v>
-      </c>
-      <c r="K25" s="149">
+        <v>-406700</v>
+      </c>
+      <c r="L25" s="149">
         <f t="shared" si="1"/>
-        <v>-1.0608695652173914</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+        <v>-1.7682608695652176</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A26" s="142" t="s">
         <v>302</v>
       </c>
@@ -6696,17 +6755,20 @@
       <c r="H26" s="147">
         <v>1765</v>
       </c>
-      <c r="I26" s="174"/>
-      <c r="J26" s="171">
+      <c r="I26" s="147">
+        <v>2038</v>
+      </c>
+      <c r="J26" s="174"/>
+      <c r="K26" s="171">
         <f t="shared" si="0"/>
-        <v>1765</v>
-      </c>
-      <c r="K26" s="149">
+        <v>3803</v>
+      </c>
+      <c r="L26" s="149">
         <f t="shared" si="1"/>
-        <v>8.8249999999999995E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+        <v>0.19015000000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A27" s="142" t="s">
         <v>29</v>
       </c>
@@ -6729,17 +6791,20 @@
       <c r="H27" s="147">
         <v>39000</v>
       </c>
-      <c r="I27" s="174"/>
-      <c r="J27" s="171">
+      <c r="I27" s="147">
+        <v>0</v>
+      </c>
+      <c r="J27" s="174"/>
+      <c r="K27" s="171">
         <f t="shared" si="0"/>
         <v>39000</v>
       </c>
-      <c r="K27" s="149">
+      <c r="L27" s="149">
         <f t="shared" si="1"/>
         <v>7.8E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A28" s="142" t="s">
         <v>28</v>
       </c>
@@ -6762,17 +6827,20 @@
       <c r="H28" s="147">
         <v>-9140</v>
       </c>
-      <c r="I28" s="174"/>
-      <c r="J28" s="171">
+      <c r="I28" s="147">
+        <v>-102505</v>
+      </c>
+      <c r="J28" s="174"/>
+      <c r="K28" s="171">
         <f t="shared" si="0"/>
-        <v>-9140</v>
-      </c>
-      <c r="K28" s="149">
+        <v>-111645</v>
+      </c>
+      <c r="L28" s="149">
         <f t="shared" si="1"/>
-        <v>-9.1400000000000006E-3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
+        <v>-0.11164499999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A29" s="142" t="s">
         <v>65</v>
       </c>
@@ -6795,17 +6863,20 @@
       <c r="H29" s="147">
         <v>-455000</v>
       </c>
-      <c r="I29" s="174"/>
-      <c r="J29" s="171">
+      <c r="I29" s="147">
+        <v>0</v>
+      </c>
+      <c r="J29" s="174"/>
+      <c r="K29" s="171">
         <f t="shared" si="0"/>
         <v>-455000</v>
       </c>
-      <c r="K29" s="149">
+      <c r="L29" s="149">
         <f t="shared" si="1"/>
         <v>-0.91</v>
       </c>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A30" s="141" t="s">
         <v>34</v>
       </c>
@@ -6828,17 +6899,20 @@
       <c r="H30" s="147">
         <v>-176663</v>
       </c>
-      <c r="I30" s="174"/>
-      <c r="J30" s="171">
+      <c r="I30" s="147">
+        <v>3891</v>
+      </c>
+      <c r="J30" s="174"/>
+      <c r="K30" s="171">
         <f t="shared" si="0"/>
-        <v>-176663</v>
-      </c>
-      <c r="K30" s="149">
+        <v>-172772</v>
+      </c>
+      <c r="L30" s="149">
         <f t="shared" si="1"/>
-        <v>-0.35332599999999997</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
+        <v>-0.34554400000000002</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A31" s="141" t="s">
         <v>131</v>
       </c>
@@ -6861,17 +6935,20 @@
       <c r="H31" s="147">
         <v>-37540</v>
       </c>
-      <c r="I31" s="174"/>
-      <c r="J31" s="171">
-        <f t="shared" ref="J31:J56" si="2">SUM(H31:I31)</f>
-        <v>-37540</v>
-      </c>
-      <c r="K31" s="149">
-        <f t="shared" ref="K31:K56" si="3">IFERROR(J31/F31*100,0)/10000000</f>
-        <v>-0.75080000000000002</v>
-      </c>
-    </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="I31" s="147">
+        <v>-42207</v>
+      </c>
+      <c r="J31" s="174"/>
+      <c r="K31" s="171">
+        <f t="shared" ref="K31:K56" si="2">SUM(H31:J31)</f>
+        <v>-79747</v>
+      </c>
+      <c r="L31" s="149">
+        <f t="shared" ref="L31:L56" si="3">IFERROR(K31/F31*100,0)/10000000</f>
+        <v>-1.59494</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A32" s="43" t="s">
         <v>67</v>
       </c>
@@ -6894,18 +6971,21 @@
       <c r="H32" s="147">
         <v>0</v>
       </c>
-      <c r="I32" s="174"/>
-      <c r="J32" s="171">
+      <c r="I32" s="147">
+        <v>9510</v>
+      </c>
+      <c r="J32" s="174"/>
+      <c r="K32" s="171">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K32" s="149">
+        <v>9510</v>
+      </c>
+      <c r="L32" s="149">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N32" s="134"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+        <v>0.23774999999999999</v>
+      </c>
+      <c r="O32" s="134"/>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="43" t="s">
         <v>143</v>
       </c>
@@ -6928,21 +7008,24 @@
       <c r="H33" s="147">
         <v>0</v>
       </c>
-      <c r="I33" s="174"/>
-      <c r="J33" s="171">
+      <c r="I33" s="147">
+        <v>0</v>
+      </c>
+      <c r="J33" s="174"/>
+      <c r="K33" s="171">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K33" s="149">
+      <c r="L33" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M33" s="5"/>
-      <c r="N33" s="134">
-        <v>-32700</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N33" s="5"/>
+      <c r="O33" s="134">
+        <v>-25594</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="43" t="s">
         <v>144</v>
       </c>
@@ -6965,19 +7048,22 @@
       <c r="H34" s="147">
         <v>0</v>
       </c>
-      <c r="I34" s="174"/>
-      <c r="J34" s="171">
+      <c r="I34" s="147">
+        <v>0</v>
+      </c>
+      <c r="J34" s="174"/>
+      <c r="K34" s="171">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K34" s="149">
+      <c r="L34" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M34" s="5"/>
-      <c r="N34" s="134"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N34" s="5"/>
+      <c r="O34" s="134"/>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="142" t="s">
         <v>31</v>
       </c>
@@ -7000,24 +7086,27 @@
       <c r="H35" s="147">
         <v>-45755</v>
       </c>
-      <c r="I35" s="174"/>
-      <c r="J35" s="171">
+      <c r="I35" s="147">
+        <v>-88146</v>
+      </c>
+      <c r="J35" s="174"/>
+      <c r="K35" s="171">
         <f t="shared" si="2"/>
-        <v>-45755</v>
-      </c>
-      <c r="K35" s="149">
+        <v>-133901</v>
+      </c>
+      <c r="L35" s="149">
         <f t="shared" si="3"/>
-        <v>-0.1143875</v>
-      </c>
-      <c r="M35" s="134">
-        <v>498709</v>
+        <v>-0.33475250000000001</v>
       </c>
       <c r="N35" s="134">
-        <f>(M36+M35)/10000000*13780</f>
-        <v>1329.4241220000001</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+        <v>1045608</v>
+      </c>
+      <c r="O35" s="134">
+        <f>(N36+N35)/10000000*13780</f>
+        <v>2846.4271159999998</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="142" t="s">
         <v>104</v>
       </c>
@@ -7040,21 +7129,24 @@
       <c r="H36" s="147">
         <v>-30970</v>
       </c>
-      <c r="I36" s="174"/>
-      <c r="J36" s="171">
+      <c r="I36" s="147">
+        <v>-23605</v>
+      </c>
+      <c r="J36" s="174"/>
+      <c r="K36" s="171">
         <f t="shared" si="2"/>
-        <v>-30970</v>
-      </c>
-      <c r="K36" s="149">
+        <v>-54575</v>
+      </c>
+      <c r="L36" s="149">
         <f t="shared" si="3"/>
-        <v>-0.30969999999999998</v>
-      </c>
-      <c r="M36" s="134">
-        <v>466040</v>
-      </c>
-      <c r="N36" s="134"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+        <v>-0.54574999999999996</v>
+      </c>
+      <c r="N36" s="134">
+        <v>1020014</v>
+      </c>
+      <c r="O36" s="134"/>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="142" t="s">
         <v>314</v>
       </c>
@@ -7075,22 +7167,25 @@
       <c r="H37" s="147">
         <v>0</v>
       </c>
-      <c r="I37" s="174"/>
-      <c r="J37" s="171">
+      <c r="I37" s="147">
+        <v>0</v>
+      </c>
+      <c r="J37" s="174"/>
+      <c r="K37" s="171">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K37" s="149">
+      <c r="L37" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M37" s="134"/>
-      <c r="N37" s="134">
-        <f>+N33-N35</f>
-        <v>-34029.424121999997</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N37" s="134"/>
+      <c r="O37" s="134">
+        <f>+O33-O35</f>
+        <v>-28440.427115999999</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="142" t="s">
         <v>229</v>
       </c>
@@ -7113,19 +7208,22 @@
       <c r="H38" s="147">
         <v>0</v>
       </c>
-      <c r="I38" s="174"/>
-      <c r="J38" s="171">
+      <c r="I38" s="147">
+        <v>-13160</v>
+      </c>
+      <c r="J38" s="174"/>
+      <c r="K38" s="171">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K38" s="149">
+        <v>-13160</v>
+      </c>
+      <c r="L38" s="149">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M38" s="134"/>
+        <v>-0.26319999999999999</v>
+      </c>
       <c r="N38" s="134"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O38" s="134"/>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="142" t="s">
         <v>52</v>
       </c>
@@ -7148,19 +7246,22 @@
       <c r="H39" s="147">
         <v>0</v>
       </c>
-      <c r="I39" s="174"/>
-      <c r="J39" s="171">
+      <c r="I39" s="147">
+        <v>0</v>
+      </c>
+      <c r="J39" s="174"/>
+      <c r="K39" s="171">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K39" s="149">
+      <c r="L39" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M39" s="134"/>
       <c r="N39" s="134"/>
-    </row>
-    <row r="40" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O39" s="134"/>
+    </row>
+    <row r="40" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="142" t="s">
         <v>45</v>
       </c>
@@ -7183,16 +7284,22 @@
       <c r="H40" s="147">
         <v>-71306</v>
       </c>
-      <c r="I40" s="174"/>
-      <c r="J40" s="171">
+      <c r="I40" s="147">
+        <v>12600</v>
+      </c>
+      <c r="J40" s="174"/>
+      <c r="K40" s="171">
         <f t="shared" si="2"/>
-        <v>-71306</v>
-      </c>
-      <c r="K40" s="149"/>
-      <c r="M40" s="134"/>
+        <v>-58706</v>
+      </c>
+      <c r="L40" s="149">
+        <f t="shared" si="3"/>
+        <v>-0.19568666666666668</v>
+      </c>
       <c r="N40" s="134"/>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O40" s="134"/>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="142" t="s">
         <v>292</v>
       </c>
@@ -7213,18 +7320,21 @@
       <c r="H41" s="147">
         <v>30690</v>
       </c>
-      <c r="I41" s="174"/>
-      <c r="J41" s="171">
+      <c r="I41" s="147">
+        <v>-9266</v>
+      </c>
+      <c r="J41" s="174"/>
+      <c r="K41" s="171">
         <f t="shared" si="2"/>
-        <v>30690</v>
-      </c>
-      <c r="K41" s="149">
+        <v>21424</v>
+      </c>
+      <c r="L41" s="149">
         <f t="shared" si="3"/>
-        <v>3.069</v>
-      </c>
-      <c r="M41" s="134"/>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+        <v>2.1423999999999999</v>
+      </c>
+      <c r="N41" s="134"/>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="142" t="s">
         <v>132</v>
       </c>
@@ -7247,17 +7357,20 @@
       <c r="H42" s="147">
         <v>0</v>
       </c>
-      <c r="I42" s="174"/>
-      <c r="J42" s="171">
+      <c r="I42" s="147">
+        <v>-3990</v>
+      </c>
+      <c r="J42" s="174"/>
+      <c r="K42" s="171">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K42" s="149">
+        <v>-3990</v>
+      </c>
+      <c r="L42" s="149">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+        <v>-7.9799999999999996E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="142" t="s">
         <v>48</v>
       </c>
@@ -7280,17 +7393,20 @@
       <c r="H43" s="147">
         <v>-49700</v>
       </c>
-      <c r="I43" s="174"/>
-      <c r="J43" s="171">
+      <c r="I43" s="147">
+        <v>-66367</v>
+      </c>
+      <c r="J43" s="174"/>
+      <c r="K43" s="171">
         <f t="shared" si="2"/>
-        <v>-49700</v>
-      </c>
-      <c r="K43" s="149">
+        <v>-116067</v>
+      </c>
+      <c r="L43" s="149">
         <f t="shared" si="3"/>
-        <v>-0.497</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+        <v>-1.1606700000000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="142" t="s">
         <v>301</v>
       </c>
@@ -7311,17 +7427,20 @@
       <c r="H44" s="147">
         <v>7256</v>
       </c>
-      <c r="I44" s="174"/>
-      <c r="J44" s="171">
+      <c r="I44" s="147">
+        <v>-4040</v>
+      </c>
+      <c r="J44" s="174"/>
+      <c r="K44" s="171">
         <f t="shared" si="2"/>
-        <v>7256</v>
-      </c>
-      <c r="K44" s="149">
+        <v>3216</v>
+      </c>
+      <c r="L44" s="149">
         <f t="shared" si="3"/>
-        <v>0.72560000000000002</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+        <v>0.3216</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="143" t="s">
         <v>168</v>
       </c>
@@ -7344,17 +7463,20 @@
       <c r="H45" s="147">
         <v>0</v>
       </c>
-      <c r="I45" s="174"/>
-      <c r="J45" s="171">
+      <c r="I45" s="147">
+        <v>5133</v>
+      </c>
+      <c r="J45" s="174"/>
+      <c r="K45" s="171">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K45" s="149">
+        <v>5133</v>
+      </c>
+      <c r="L45" s="149">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+        <v>1.28325E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="143" t="s">
         <v>202</v>
       </c>
@@ -7377,17 +7499,20 @@
       <c r="H46" s="147">
         <v>27000</v>
       </c>
-      <c r="I46" s="174"/>
-      <c r="J46" s="171">
+      <c r="I46" s="147">
+        <v>-1041</v>
+      </c>
+      <c r="J46" s="174"/>
+      <c r="K46" s="171">
         <f t="shared" si="2"/>
-        <v>27000</v>
-      </c>
-      <c r="K46" s="149">
+        <v>25959</v>
+      </c>
+      <c r="L46" s="149">
         <f t="shared" si="3"/>
-        <v>6.7500000000000004E-2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+        <v>6.4897499999999997E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="143" t="s">
         <v>33</v>
       </c>
@@ -7410,17 +7535,20 @@
       <c r="H47" s="147">
         <v>15088</v>
       </c>
-      <c r="I47" s="174"/>
-      <c r="J47" s="171">
+      <c r="I47" s="147">
+        <v>-61960</v>
+      </c>
+      <c r="J47" s="174"/>
+      <c r="K47" s="171">
         <f t="shared" si="2"/>
-        <v>15088</v>
-      </c>
-      <c r="K47" s="149">
+        <v>-46872</v>
+      </c>
+      <c r="L47" s="149">
         <f t="shared" si="3"/>
-        <v>5.0293333333333329E-2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+        <v>-0.15623999999999999</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="59" t="s">
         <v>306</v>
       </c>
@@ -7441,17 +7569,20 @@
       <c r="H48" s="151">
         <v>-405100</v>
       </c>
-      <c r="I48" s="174"/>
-      <c r="J48" s="171">
+      <c r="I48" s="151">
+        <v>64400</v>
+      </c>
+      <c r="J48" s="174"/>
+      <c r="K48" s="171">
         <f t="shared" si="2"/>
-        <v>-405100</v>
-      </c>
-      <c r="K48" s="149">
+        <v>-340700</v>
+      </c>
+      <c r="L48" s="149">
         <f t="shared" si="3"/>
-        <v>-0.40510000000000002</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+        <v>-0.3407</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" s="59" t="s">
         <v>320</v>
       </c>
@@ -7470,17 +7601,20 @@
       <c r="H49" s="151">
         <v>0</v>
       </c>
-      <c r="I49" s="174"/>
-      <c r="J49" s="171">
+      <c r="I49" s="151">
+        <v>0</v>
+      </c>
+      <c r="J49" s="174"/>
+      <c r="K49" s="171">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K49" s="149">
+      <c r="L49" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" s="59" t="s">
         <v>197</v>
       </c>
@@ -7503,17 +7637,20 @@
       <c r="H50" s="151">
         <v>12773</v>
       </c>
-      <c r="I50" s="174"/>
-      <c r="J50" s="171">
+      <c r="I50" s="151">
+        <v>1824</v>
+      </c>
+      <c r="J50" s="174"/>
+      <c r="K50" s="171">
         <f t="shared" si="2"/>
-        <v>12773</v>
-      </c>
-      <c r="K50" s="149">
+        <v>14597</v>
+      </c>
+      <c r="L50" s="149">
         <f t="shared" si="3"/>
-        <v>0.25546000000000002</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+        <v>0.29193999999999998</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" s="59" t="s">
         <v>213</v>
       </c>
@@ -7536,17 +7673,20 @@
       <c r="H51" s="151">
         <v>-152273</v>
       </c>
-      <c r="I51" s="174"/>
-      <c r="J51" s="171">
+      <c r="I51" s="151">
+        <v>0</v>
+      </c>
+      <c r="J51" s="174"/>
+      <c r="K51" s="171">
         <f t="shared" si="2"/>
         <v>-152273</v>
       </c>
-      <c r="K51" s="149">
+      <c r="L51" s="149">
         <f t="shared" si="3"/>
         <v>-0.23426615384615385</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A52" s="59" t="s">
         <v>214</v>
       </c>
@@ -7569,17 +7709,20 @@
       <c r="H52" s="151">
         <v>31488</v>
       </c>
-      <c r="I52" s="174"/>
-      <c r="J52" s="171">
+      <c r="I52" s="151">
+        <v>-28440</v>
+      </c>
+      <c r="J52" s="174"/>
+      <c r="K52" s="171">
         <f t="shared" si="2"/>
-        <v>31488</v>
-      </c>
-      <c r="K52" s="149">
+        <v>3048</v>
+      </c>
+      <c r="L52" s="149">
         <f t="shared" si="3"/>
-        <v>0.25190400000000002</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.4383999999999999E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53" s="59" t="s">
         <v>49</v>
       </c>
@@ -7602,17 +7745,20 @@
       <c r="H53" s="151">
         <v>-121091</v>
       </c>
-      <c r="I53" s="174"/>
-      <c r="J53" s="171">
+      <c r="I53" s="151">
+        <v>0</v>
+      </c>
+      <c r="J53" s="174"/>
+      <c r="K53" s="171">
         <f t="shared" si="2"/>
         <v>-121091</v>
       </c>
-      <c r="K53" s="149">
+      <c r="L53" s="149">
         <f t="shared" si="3"/>
         <v>-0.40363666666666664</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54" s="59" t="s">
         <v>300</v>
       </c>
@@ -7633,17 +7779,20 @@
       <c r="H54" s="151">
         <v>-14700</v>
       </c>
-      <c r="I54" s="174"/>
-      <c r="J54" s="171">
+      <c r="I54" s="151">
+        <v>9455</v>
+      </c>
+      <c r="J54" s="174"/>
+      <c r="K54" s="171">
         <f t="shared" si="2"/>
-        <v>-14700</v>
-      </c>
-      <c r="K54" s="149">
+        <v>-5245</v>
+      </c>
+      <c r="L54" s="149">
         <f t="shared" si="3"/>
-        <v>-9.8000000000000004E-2</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>-3.496666666666666E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="59" t="s">
         <v>288</v>
       </c>
@@ -7664,17 +7813,20 @@
       <c r="H55" s="151">
         <v>-34030</v>
       </c>
-      <c r="I55" s="174"/>
-      <c r="J55" s="171">
+      <c r="I55" s="151">
+        <v>32229</v>
+      </c>
+      <c r="J55" s="174"/>
+      <c r="K55" s="171">
         <f t="shared" si="2"/>
-        <v>-34030</v>
-      </c>
-      <c r="K55" s="149">
+        <v>-1801</v>
+      </c>
+      <c r="L55" s="149">
         <f t="shared" si="3"/>
-        <v>-6.8059999999999996E-2</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>-3.6020000000000002E-3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="24"/>
       <c r="B56" s="25"/>
       <c r="C56" s="26"/>
@@ -7688,18 +7840,22 @@
       </c>
       <c r="I56" s="254">
         <f>SUM(I4:I55)</f>
-        <v>0</v>
+        <v>-531590</v>
       </c>
       <c r="J56" s="254">
+        <f>SUM(J4:J55)</f>
+        <v>0</v>
+      </c>
+      <c r="K56" s="254">
         <f t="shared" si="2"/>
-        <v>-2118400</v>
-      </c>
-      <c r="K56" s="255">
+        <v>-2649990</v>
+      </c>
+      <c r="L56" s="255">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:15" s="249" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:16" s="249" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="250"/>
       <c r="B57" s="250"/>
       <c r="C57" s="250"/>
@@ -7710,9 +7866,10 @@
       <c r="H57" s="250"/>
       <c r="I57" s="250"/>
       <c r="J57" s="250"/>
-      <c r="K57" s="252"/>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="K57" s="250"/>
+      <c r="L57" s="252"/>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A58" s="202" t="s">
         <v>241</v>
       </c>
@@ -7735,18 +7892,21 @@
       <c r="H58" s="162">
         <v>-370080</v>
       </c>
-      <c r="I58" s="246"/>
-      <c r="J58" s="247">
-        <f>SUM(H58:I58)</f>
+      <c r="I58" s="162">
+        <v>0</v>
+      </c>
+      <c r="J58" s="246"/>
+      <c r="K58" s="247">
+        <f>SUM(H58:J58)</f>
         <v>-370080</v>
       </c>
-      <c r="K58" s="248">
-        <f>IFERROR(J58/F58*100,0)/10000000</f>
+      <c r="L58" s="248">
+        <f>IFERROR(K58/F58*100,0)/10000000</f>
         <v>-1.2336</v>
       </c>
-      <c r="N58" s="134"/>
-    </row>
-    <row r="59" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O58" s="134"/>
+    </row>
+    <row r="59" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="202" t="s">
         <v>273</v>
       </c>
@@ -7767,18 +7927,21 @@
       <c r="H59" s="162">
         <v>-246000</v>
       </c>
-      <c r="I59" s="174"/>
-      <c r="J59" s="171">
-        <f>SUM(H59:I59)</f>
+      <c r="I59" s="162">
+        <v>0</v>
+      </c>
+      <c r="J59" s="174"/>
+      <c r="K59" s="171">
+        <f>SUM(H59:J59)</f>
         <v>-246000</v>
       </c>
-      <c r="K59" s="149">
-        <f>IFERROR(J59/F59*100,0)/10000000</f>
-        <v>0</v>
-      </c>
-      <c r="M59" s="134"/>
-    </row>
-    <row r="60" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L59" s="149">
+        <f>IFERROR(K59/F59*100,0)/10000000</f>
+        <v>0</v>
+      </c>
+      <c r="N59" s="134"/>
+    </row>
+    <row r="60" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="200"/>
       <c r="B60" s="16"/>
       <c r="C60" s="16"/>
@@ -7794,128 +7957,132 @@
         <f>SUM(I58:I59)</f>
         <v>0</v>
       </c>
-      <c r="J60" s="254">
-        <f>SUM(H60:I60)</f>
+      <c r="J60" s="170">
+        <f>SUM(J58:J59)</f>
+        <v>0</v>
+      </c>
+      <c r="K60" s="254">
+        <f>SUM(H60:J60)</f>
         <v>-616080</v>
       </c>
-      <c r="K60" s="19"/>
-      <c r="M60" s="5"/>
-      <c r="N60" s="134"/>
-      <c r="O60" s="237"/>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="M61" s="134"/>
+      <c r="L60" s="19"/>
+      <c r="N60" s="5"/>
+      <c r="O60" s="134"/>
+      <c r="P60" s="237"/>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
       <c r="N61" s="134"/>
-      <c r="O61" s="237"/>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="M62" s="134"/>
+      <c r="O61" s="134"/>
+      <c r="P61" s="237"/>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
       <c r="N62" s="134"/>
-      <c r="O62" s="237"/>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="M63" s="134"/>
+      <c r="O62" s="134"/>
+      <c r="P62" s="237"/>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
       <c r="N63" s="134"/>
-      <c r="O63" s="237"/>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="M64" s="134"/>
+      <c r="O63" s="134"/>
+      <c r="P63" s="237"/>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
       <c r="N64" s="134"/>
-      <c r="O64" s="237"/>
-    </row>
-    <row r="65" spans="13:15" x14ac:dyDescent="0.25">
-      <c r="M65" s="134"/>
-      <c r="N65" s="237"/>
+      <c r="O64" s="134"/>
+      <c r="P64" s="237"/>
+    </row>
+    <row r="65" spans="14:16" x14ac:dyDescent="0.25">
+      <c r="N65" s="134"/>
       <c r="O65" s="237"/>
-    </row>
-    <row r="66" spans="13:15" x14ac:dyDescent="0.25">
-      <c r="M66" s="237"/>
+      <c r="P65" s="237"/>
+    </row>
+    <row r="66" spans="14:16" x14ac:dyDescent="0.25">
       <c r="N66" s="237"/>
       <c r="O66" s="237"/>
+      <c r="P66" s="237"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G2 A3:G3 K56:K57 J55:K55 K60 J43:K43 J5:K10 J24:K25 H2:K3 A58:K59 A60:I60 A37:J37 K11:K21 J11:J22 J45:K53 J27:J36 K27:K35 A4:I36 J38:J41 A38:I39 A41:I56 G40:I40">
-    <cfRule type="expression" dxfId="448" priority="21">
+  <conditionalFormatting sqref="G2 A3:G3 L56:L57 K55:L55 L60 K43:L43 K5:L10 K24:L25 H2:L3 A58:L59 A37:K37 L11:L21 K11:K22 K45:L53 K27:K36 L27:L35 A4:J36 K38:K41 A38:J39 G40:J40 A41:J56 A60:J60">
+    <cfRule type="expression" dxfId="450" priority="21">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K36">
-    <cfRule type="expression" dxfId="447" priority="20">
+  <conditionalFormatting sqref="L36">
+    <cfRule type="expression" dxfId="449" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K39:K40">
-    <cfRule type="expression" dxfId="446" priority="19">
+  <conditionalFormatting sqref="L39:L40">
+    <cfRule type="expression" dxfId="448" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J4:K4">
-    <cfRule type="expression" dxfId="445" priority="18">
+  <conditionalFormatting sqref="K4:L4">
+    <cfRule type="expression" dxfId="447" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K38">
-    <cfRule type="expression" dxfId="444" priority="17">
+  <conditionalFormatting sqref="L38">
+    <cfRule type="expression" dxfId="446" priority="17">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K22">
-    <cfRule type="expression" dxfId="443" priority="14">
+  <conditionalFormatting sqref="L22">
+    <cfRule type="expression" dxfId="445" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J56">
-    <cfRule type="expression" dxfId="442" priority="13">
+  <conditionalFormatting sqref="K56">
+    <cfRule type="expression" dxfId="444" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K41">
-    <cfRule type="expression" dxfId="441" priority="12">
+  <conditionalFormatting sqref="L41">
+    <cfRule type="expression" dxfId="443" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J26:K26">
-    <cfRule type="expression" dxfId="440" priority="11">
+  <conditionalFormatting sqref="K26:L26">
+    <cfRule type="expression" dxfId="442" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J54:K54">
-    <cfRule type="expression" dxfId="439" priority="10">
+  <conditionalFormatting sqref="K54:L54">
+    <cfRule type="expression" dxfId="441" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J44:K44">
-    <cfRule type="expression" dxfId="438" priority="9">
+  <conditionalFormatting sqref="K44:L44">
+    <cfRule type="expression" dxfId="440" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J60">
-    <cfRule type="expression" dxfId="437" priority="8">
+  <conditionalFormatting sqref="K60">
+    <cfRule type="expression" dxfId="439" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J42:K42">
-    <cfRule type="expression" dxfId="436" priority="6">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J23">
-    <cfRule type="expression" dxfId="435" priority="5">
+  <conditionalFormatting sqref="K42:L42">
+    <cfRule type="expression" dxfId="438" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K23">
-    <cfRule type="expression" dxfId="434" priority="4">
+    <cfRule type="expression" dxfId="437" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K37">
-    <cfRule type="expression" dxfId="433" priority="2">
+  <conditionalFormatting sqref="L23">
+    <cfRule type="expression" dxfId="436" priority="4">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L37">
+    <cfRule type="expression" dxfId="435" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40:F40">
-    <cfRule type="expression" dxfId="432" priority="1">
+    <cfRule type="expression" dxfId="434" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14382,112 +14549,112 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2 A3:G3 AD47:AD48 AD55:AD57 AD68:AD69 AD50 AD11:AD19 AD21:AD23 AC11:AC24 AC29:AC43 AD29:AD42 AC66:AD67 AC54:AC57 AD73 H2:AD3 A68:G68 AC52:AD52 AC5:AD10 AC58:AD64 AC26:AD27 A70:AD72 A4:AB22 A44:S44 A45:AC50 A73:AB73 A26:AB43 B23:AB25 A52:AB67 B51:AB51">
-    <cfRule type="expression" dxfId="431" priority="22">
+    <cfRule type="expression" dxfId="433" priority="22">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD43">
-    <cfRule type="expression" dxfId="430" priority="21">
+    <cfRule type="expression" dxfId="432" priority="21">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD46">
-    <cfRule type="expression" dxfId="429" priority="20">
+    <cfRule type="expression" dxfId="431" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC4:AD4">
-    <cfRule type="expression" dxfId="428" priority="19">
+    <cfRule type="expression" dxfId="430" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD45">
-    <cfRule type="expression" dxfId="427" priority="18">
+    <cfRule type="expression" dxfId="429" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD20">
-    <cfRule type="expression" dxfId="426" priority="17">
+    <cfRule type="expression" dxfId="428" priority="17">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD54">
-    <cfRule type="expression" dxfId="425" priority="16">
+    <cfRule type="expression" dxfId="427" priority="16">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD24">
-    <cfRule type="expression" dxfId="424" priority="15">
+    <cfRule type="expression" dxfId="426" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC68">
-    <cfRule type="expression" dxfId="423" priority="14">
+    <cfRule type="expression" dxfId="425" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD49">
-    <cfRule type="expression" dxfId="422" priority="13">
+    <cfRule type="expression" dxfId="424" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC28:AD28">
-    <cfRule type="expression" dxfId="421" priority="12">
+    <cfRule type="expression" dxfId="423" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC65:AD65">
-    <cfRule type="expression" dxfId="420" priority="11">
+    <cfRule type="expression" dxfId="422" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC53:AD53">
-    <cfRule type="expression" dxfId="419" priority="10">
+    <cfRule type="expression" dxfId="421" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC73">
-    <cfRule type="expression" dxfId="418" priority="9">
+    <cfRule type="expression" dxfId="420" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H68:AB68">
-    <cfRule type="expression" dxfId="417" priority="8">
+    <cfRule type="expression" dxfId="419" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC51:AD51">
-    <cfRule type="expression" dxfId="416" priority="7">
+    <cfRule type="expression" dxfId="418" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC25">
-    <cfRule type="expression" dxfId="415" priority="6">
+    <cfRule type="expression" dxfId="417" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD25">
-    <cfRule type="expression" dxfId="414" priority="5">
+    <cfRule type="expression" dxfId="416" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T44:AC44">
-    <cfRule type="expression" dxfId="413" priority="4">
+    <cfRule type="expression" dxfId="415" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD44">
-    <cfRule type="expression" dxfId="412" priority="3">
+    <cfRule type="expression" dxfId="414" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A23:A25">
-    <cfRule type="expression" dxfId="411" priority="2">
+    <cfRule type="expression" dxfId="413" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A51">
-    <cfRule type="expression" dxfId="410" priority="1">
+    <cfRule type="expression" dxfId="412" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20787,82 +20954,82 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2 A3:G3 AF43:AF44 AF50:AF52 AF62:AF63 H2:AF3 AF46:AF47 AF9:AF17 AF23:AF24 AF19:AF21 AE9:AE24 AE5:AF8 AE26:AE47 AF26:AF39 AE60:AF61 AE49:AE52 A64:AF66 AF67 A67:AD67 AE53:AF58 A4:AD20 A23:AD62 C21:AD21 B22:AD22">
-    <cfRule type="expression" dxfId="409" priority="20">
+    <cfRule type="expression" dxfId="411" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF40">
-    <cfRule type="expression" dxfId="408" priority="19">
+    <cfRule type="expression" dxfId="410" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF42">
-    <cfRule type="expression" dxfId="407" priority="18">
+    <cfRule type="expression" dxfId="409" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE4:AF4">
-    <cfRule type="expression" dxfId="406" priority="16">
+    <cfRule type="expression" dxfId="408" priority="16">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF41">
-    <cfRule type="expression" dxfId="405" priority="14">
+    <cfRule type="expression" dxfId="407" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF18">
-    <cfRule type="expression" dxfId="404" priority="13">
+    <cfRule type="expression" dxfId="406" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF49">
-    <cfRule type="expression" dxfId="403" priority="12">
+    <cfRule type="expression" dxfId="405" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF22">
-    <cfRule type="expression" dxfId="402" priority="11">
+    <cfRule type="expression" dxfId="404" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE62">
-    <cfRule type="expression" dxfId="401" priority="10">
+    <cfRule type="expression" dxfId="403" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF45">
-    <cfRule type="expression" dxfId="400" priority="9">
+    <cfRule type="expression" dxfId="402" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE25:AF25">
-    <cfRule type="expression" dxfId="399" priority="6">
+    <cfRule type="expression" dxfId="401" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE59:AF59">
-    <cfRule type="expression" dxfId="398" priority="5">
+    <cfRule type="expression" dxfId="400" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE48:AF48">
-    <cfRule type="expression" dxfId="397" priority="4">
+    <cfRule type="expression" dxfId="399" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE67">
-    <cfRule type="expression" dxfId="396" priority="3">
+    <cfRule type="expression" dxfId="398" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21">
-    <cfRule type="expression" dxfId="395" priority="2">
+    <cfRule type="expression" dxfId="397" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:A22">
-    <cfRule type="expression" dxfId="394" priority="1">
+    <cfRule type="expression" dxfId="396" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20986,20 +21153,20 @@
         <v>-0.20805999999999999</v>
       </c>
       <c r="K4" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>-13362</v>
       </c>
       <c r="L4" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>-0.26723999999999998</v>
       </c>
       <c r="M4" s="71">
         <f t="shared" ref="M4:N62" si="0">G4+I4+K4</f>
-        <v>-27044</v>
+        <v>-40406</v>
       </c>
       <c r="N4" s="166">
         <f t="shared" si="0"/>
-        <v>-0.54088000000000003</v>
+        <v>-0.80811999999999995</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -21038,20 +21205,20 @@
         <v>-1.2725900000000001</v>
       </c>
       <c r="K5" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>-170827</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>-139420</v>
       </c>
       <c r="L5" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>-0.56942333333333339</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>-0.46473333333333339</v>
       </c>
       <c r="M5" s="71">
         <f t="shared" si="0"/>
-        <v>-421798</v>
+        <v>-390391</v>
       </c>
       <c r="N5" s="166">
         <f t="shared" si="0"/>
-        <v>-1.4059933333333334</v>
+        <v>-1.3013033333333335</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -21090,11 +21257,11 @@
         <v>1.16185</v>
       </c>
       <c r="K6" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L6" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M6" s="71">
@@ -21140,11 +21307,11 @@
         <v>0</v>
       </c>
       <c r="K7" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L7" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M7" s="71">
@@ -21192,20 +21359,20 @@
         <v>-1.6494500000000001</v>
       </c>
       <c r="K8" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>179600</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>153035</v>
       </c>
       <c r="L8" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>0.59866666666666657</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>0.51011666666666655</v>
       </c>
       <c r="M8" s="71">
         <f t="shared" si="0"/>
-        <v>-275497</v>
+        <v>-302062</v>
       </c>
       <c r="N8" s="166">
         <f t="shared" si="0"/>
-        <v>-0.91832333333333349</v>
+        <v>-1.0068733333333335</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -21244,20 +21411,20 @@
         <v>0.16230666666666665</v>
       </c>
       <c r="K9" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>59398</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>44898</v>
       </c>
       <c r="L9" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>0.39598666666666665</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>0.29931999999999997</v>
       </c>
       <c r="M9" s="71">
         <f t="shared" si="0"/>
-        <v>-234738</v>
+        <v>-249238</v>
       </c>
       <c r="N9" s="166">
         <f t="shared" si="0"/>
-        <v>-1.5649200000000003</v>
+        <v>-1.661586666666667</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -21296,20 +21463,20 @@
         <v>-1.1035999999999999</v>
       </c>
       <c r="K10" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>8234</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>-13366</v>
       </c>
       <c r="L10" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>0.13723333333333335</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>-0.2227666666666667</v>
       </c>
       <c r="M10" s="71">
         <f t="shared" ref="M10" si="3">G10+I10+K10</f>
-        <v>-184015</v>
+        <v>-205615</v>
       </c>
       <c r="N10" s="166">
         <f t="shared" ref="N10" si="4">H10+J10+L10</f>
-        <v>-3.0669166666666667</v>
+        <v>-3.4269166666666671</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -21348,11 +21515,11 @@
         <v>-0.91267399999999999</v>
       </c>
       <c r="K11" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
         <v>-413740</v>
       </c>
       <c r="L11" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
         <v>-0.27582666666666672</v>
       </c>
       <c r="M11" s="71">
@@ -21400,20 +21567,20 @@
         <v>3.0566666666666667E-3</v>
       </c>
       <c r="K12" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>-61243</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>-61193</v>
       </c>
       <c r="L12" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>-0.10207166666666666</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>-0.10198833333333333</v>
       </c>
       <c r="M12" s="71">
         <f t="shared" si="0"/>
-        <v>346537</v>
+        <v>346587</v>
       </c>
       <c r="N12" s="166">
         <f t="shared" si="0"/>
-        <v>0.57756166666666675</v>
+        <v>0.57764500000000008</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -21452,20 +21619,20 @@
         <v>0.12322</v>
       </c>
       <c r="K13" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>-4458</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>-7107</v>
       </c>
       <c r="L13" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>-4.4580000000000002E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>-7.1069999999999994E-2</v>
       </c>
       <c r="M13" s="71">
         <f t="shared" si="0"/>
-        <v>8958</v>
+        <v>6309</v>
       </c>
       <c r="N13" s="166">
         <f t="shared" si="0"/>
-        <v>8.9579999999999993E-2</v>
+        <v>6.3090000000000007E-2</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -21504,11 +21671,11 @@
         <v>-0.65036000000000005</v>
       </c>
       <c r="K14" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
         <v>724</v>
       </c>
       <c r="L14" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
         <v>2.8960000000000006E-3</v>
       </c>
       <c r="M14" s="71">
@@ -21556,11 +21723,11 @@
         <v>0</v>
       </c>
       <c r="K15" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L15" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M15" s="71">
@@ -21608,20 +21775,20 @@
         <v>0.33139000000000002</v>
       </c>
       <c r="K16" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>-11113</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>-14358</v>
       </c>
       <c r="L16" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>-0.11113000000000001</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>-0.14358000000000001</v>
       </c>
       <c r="M16" s="71">
         <f t="shared" si="0"/>
-        <v>62294</v>
+        <v>59049</v>
       </c>
       <c r="N16" s="166">
         <f t="shared" si="0"/>
-        <v>0.62294000000000005</v>
+        <v>0.59048999999999996</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -21660,11 +21827,11 @@
         <v>-0.4931636363636363</v>
       </c>
       <c r="K17" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
         <v>-4897</v>
       </c>
       <c r="L17" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
         <v>-2.2259090909090905E-2</v>
       </c>
       <c r="M17" s="71">
@@ -21712,11 +21879,11 @@
         <v>-0.44636399999999998</v>
       </c>
       <c r="K18" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L18" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M18" s="71">
@@ -21764,11 +21931,11 @@
         <v>-0.20675499999999999</v>
       </c>
       <c r="K19" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L19" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M19" s="71">
@@ -21816,11 +21983,11 @@
         <v>0.25088181818181815</v>
       </c>
       <c r="K20" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
         <v>9433</v>
       </c>
       <c r="L20" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
         <v>8.5754545454545431E-2</v>
       </c>
       <c r="M20" s="71">
@@ -21868,20 +22035,20 @@
         <v>-2.8835999999999999</v>
       </c>
       <c r="K21" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>4737</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>1271</v>
       </c>
       <c r="L21" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>0.18948000000000001</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>5.0840000000000003E-2</v>
       </c>
       <c r="M21" s="71">
         <f t="shared" ref="M21:M22" si="7">G21+I21+K21</f>
-        <v>-38809</v>
+        <v>-42275</v>
       </c>
       <c r="N21" s="166">
         <f t="shared" ref="N21:N22" si="8">H21+J21+L21</f>
-        <v>-1.5523599999999997</v>
+        <v>-1.6909999999999998</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
@@ -21920,20 +22087,20 @@
         <v>0.15673999999999999</v>
       </c>
       <c r="K22" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>-1048</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>5905</v>
       </c>
       <c r="L22" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>-5.2399999999999999E-3</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>2.9524999999999999E-2</v>
       </c>
       <c r="M22" s="71">
         <f t="shared" si="7"/>
-        <v>15084</v>
+        <v>22037</v>
       </c>
       <c r="N22" s="166">
         <f t="shared" si="8"/>
-        <v>7.5420000000000001E-2</v>
+        <v>0.11018499999999999</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
@@ -21972,20 +22139,20 @@
         <v>9.7766666666666668E-2</v>
       </c>
       <c r="K23" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>17500</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>-14466</v>
       </c>
       <c r="L23" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>0.11666666666666665</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>-9.6439999999999998E-2</v>
       </c>
       <c r="M23" s="71">
         <f t="shared" si="0"/>
-        <v>132513</v>
+        <v>100547</v>
       </c>
       <c r="N23" s="166">
         <f t="shared" si="0"/>
-        <v>0.88342000000000009</v>
+        <v>0.67031333333333343</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -22024,11 +22191,11 @@
         <v>0</v>
       </c>
       <c r="K24" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L24" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M24" s="71">
@@ -22076,20 +22243,20 @@
         <v>-1.1453363636363634</v>
       </c>
       <c r="K25" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>9208</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>9908</v>
       </c>
       <c r="L25" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>8.37090909090909E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>9.0072727272727263E-2</v>
       </c>
       <c r="M25" s="71">
         <f t="shared" si="0"/>
-        <v>213912</v>
+        <v>214612</v>
       </c>
       <c r="N25" s="166">
         <f t="shared" si="0"/>
-        <v>1.944654545454545</v>
+        <v>1.9510181818181813</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
@@ -22128,20 +22295,20 @@
         <v>-2.2903086956521741</v>
       </c>
       <c r="K26" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>-244000</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>-406700</v>
       </c>
       <c r="L26" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>-1.0608695652173914</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>-1.7682608695652176</v>
       </c>
       <c r="M26" s="71">
         <f t="shared" si="0"/>
-        <v>110061</v>
+        <v>-52639</v>
       </c>
       <c r="N26" s="166">
         <f t="shared" si="0"/>
-        <v>0.4785260869565211</v>
+        <v>-0.22886521739130505</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
@@ -22178,20 +22345,20 @@
         <v>-0.8901</v>
       </c>
       <c r="K27" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>1765</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>3803</v>
       </c>
       <c r="L27" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>8.8249999999999995E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>0.19015000000000001</v>
       </c>
       <c r="M27" s="71">
         <f t="shared" ref="M27" si="9">G27+I27+K27</f>
-        <v>-18531</v>
+        <v>-16493</v>
       </c>
       <c r="N27" s="166">
         <f t="shared" ref="N27" si="10">H27+J27+L27</f>
-        <v>-0.92654999999999998</v>
+        <v>-0.82464999999999988</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
@@ -22230,11 +22397,11 @@
         <v>-0.33289600000000003</v>
       </c>
       <c r="K28" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
         <v>39000</v>
       </c>
       <c r="L28" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
         <v>7.8E-2</v>
       </c>
       <c r="M28" s="71">
@@ -22282,20 +22449,20 @@
         <v>0.19531499999999999</v>
       </c>
       <c r="K29" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>-9140</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>-111645</v>
       </c>
       <c r="L29" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>-9.1400000000000006E-3</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>-0.11164499999999999</v>
       </c>
       <c r="M29" s="71">
         <f t="shared" si="0"/>
-        <v>3458272</v>
+        <v>3355767</v>
       </c>
       <c r="N29" s="166">
         <f t="shared" si="0"/>
-        <v>3.458272</v>
+        <v>3.3557670000000002</v>
       </c>
       <c r="O29" s="131"/>
     </row>
@@ -22335,11 +22502,11 @@
         <v>-0.60594000000000003</v>
       </c>
       <c r="K30" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L30" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M30" s="71">
@@ -22387,11 +22554,11 @@
         <v>-0.58230000000000004</v>
       </c>
       <c r="K31" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L31" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M31" s="71">
@@ -22439,11 +22606,11 @@
         <v>-0.58148999999999995</v>
       </c>
       <c r="K32" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L32" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M32" s="71">
@@ -22491,11 +22658,11 @@
         <v>-0.69791999999999998</v>
       </c>
       <c r="K33" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L33" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M33" s="71">
@@ -22543,11 +22710,11 @@
         <v>-0.58009333333333335</v>
       </c>
       <c r="K34" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L34" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M34" s="71">
@@ -22595,11 +22762,11 @@
         <v>-1.010926</v>
       </c>
       <c r="K35" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
         <v>-455000</v>
       </c>
       <c r="L35" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
         <v>-0.91</v>
       </c>
       <c r="M35" s="71">
@@ -22647,20 +22814,20 @@
         <v>1.1398239999999999</v>
       </c>
       <c r="K36" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>-176663</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>-172772</v>
       </c>
       <c r="L36" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>-0.35332599999999997</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>-0.34554400000000002</v>
       </c>
       <c r="M36" s="71">
         <f t="shared" si="0"/>
-        <v>850744</v>
+        <v>854635</v>
       </c>
       <c r="N36" s="166">
         <f t="shared" si="0"/>
-        <v>1.7014879999999999</v>
+        <v>1.7092699999999998</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
@@ -22699,20 +22866,20 @@
         <v>-1.28678</v>
       </c>
       <c r="K37" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>-37540</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>-79747</v>
       </c>
       <c r="L37" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>-0.75080000000000002</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>-1.59494</v>
       </c>
       <c r="M37" s="71">
         <f t="shared" si="0"/>
-        <v>-116904</v>
+        <v>-159111</v>
       </c>
       <c r="N37" s="166">
         <f t="shared" si="0"/>
-        <v>-2.3380800000000002</v>
+        <v>-3.18222</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
@@ -22751,20 +22918,20 @@
         <v>1.3305</v>
       </c>
       <c r="K38" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>9510</v>
       </c>
       <c r="L38" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>0.23774999999999999</v>
       </c>
       <c r="M38" s="71">
         <f t="shared" si="0"/>
-        <v>-65525</v>
+        <v>-56015</v>
       </c>
       <c r="N38" s="166">
         <f t="shared" si="0"/>
-        <v>-1.6381249999999998</v>
+        <v>-1.4003749999999999</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
@@ -22803,11 +22970,11 @@
         <v>0.12665999999999999</v>
       </c>
       <c r="K39" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L39" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M39" s="71">
@@ -22855,11 +23022,11 @@
         <v>0</v>
       </c>
       <c r="K40" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L40" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M40" s="71">
@@ -22907,20 +23074,20 @@
         <v>0.8756275</v>
       </c>
       <c r="K41" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>-45755</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>-133901</v>
       </c>
       <c r="L41" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>-0.1143875</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>-0.33475250000000001</v>
       </c>
       <c r="M41" s="71">
         <f t="shared" si="0"/>
-        <v>665181</v>
+        <v>577035</v>
       </c>
       <c r="N41" s="166">
         <f t="shared" si="0"/>
-        <v>1.6629525000000001</v>
+        <v>1.4425875000000001</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
@@ -22959,20 +23126,20 @@
         <v>0.53249000000000002</v>
       </c>
       <c r="K42" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>-30970</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>-54575</v>
       </c>
       <c r="L42" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>-0.30969999999999998</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>-0.54574999999999996</v>
       </c>
       <c r="M42" s="71">
         <f t="shared" si="0"/>
-        <v>172662</v>
+        <v>149057</v>
       </c>
       <c r="N42" s="166">
         <f t="shared" si="0"/>
-        <v>1.72662</v>
+        <v>1.49057</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
@@ -23009,11 +23176,11 @@
         <v>0</v>
       </c>
       <c r="K43" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L43" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M43" s="71">
@@ -23061,20 +23228,20 @@
         <v>-0.28554000000000002</v>
       </c>
       <c r="K44" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>-13160</v>
       </c>
       <c r="L44" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>-0.26319999999999999</v>
       </c>
       <c r="M44" s="71">
         <f t="shared" si="0"/>
-        <v>-66383</v>
+        <v>-79543</v>
       </c>
       <c r="N44" s="166">
         <f t="shared" si="0"/>
-        <v>-1.3276599999999998</v>
+        <v>-1.5908599999999997</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
@@ -23113,20 +23280,20 @@
         <v>-0.63329999999999997</v>
       </c>
       <c r="K45" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>-71306</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>-58706</v>
       </c>
       <c r="L45" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>-0.19568666666666668</v>
       </c>
       <c r="M45" s="71">
         <f t="shared" si="0"/>
-        <v>-182098</v>
+        <v>-169498</v>
       </c>
       <c r="N45" s="166">
         <f t="shared" si="0"/>
-        <v>-0.36930666666666667</v>
+        <v>-0.56499333333333335</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
@@ -23165,11 +23332,11 @@
         <v>-0.34641333333333335</v>
       </c>
       <c r="K46" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L46" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M46" s="71">
@@ -23217,11 +23384,11 @@
         <v>-0.37293333333333334</v>
       </c>
       <c r="K47" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L47" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M47" s="71">
@@ -23267,20 +23434,20 @@
         <v>-0.49170000000000003</v>
       </c>
       <c r="K48" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>30690</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>21424</v>
       </c>
       <c r="L48" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>3.069</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>2.1423999999999999</v>
       </c>
       <c r="M48" s="71">
         <f t="shared" ref="M48" si="15">G48+I48+K48</f>
-        <v>13758</v>
+        <v>4492</v>
       </c>
       <c r="N48" s="166">
         <f t="shared" ref="N48" si="16">H48+J48+L48</f>
-        <v>1.3757999999999999</v>
+        <v>0.44919999999999982</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
@@ -23319,20 +23486,20 @@
         <v>4.5359999999999998E-2</v>
       </c>
       <c r="K49" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>-3990</v>
       </c>
       <c r="L49" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>-7.9799999999999996E-2</v>
       </c>
       <c r="M49" s="71">
         <f t="shared" si="0"/>
-        <v>34328</v>
+        <v>30338</v>
       </c>
       <c r="N49" s="166">
         <f t="shared" si="0"/>
-        <v>0.36596000000000001</v>
+        <v>0.28616000000000003</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
@@ -23371,20 +23538,20 @@
         <v>7.0315700000000003</v>
       </c>
       <c r="K50" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>-49700</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>-116067</v>
       </c>
       <c r="L50" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>-0.497</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>-1.1606700000000001</v>
       </c>
       <c r="M50" s="71">
         <f t="shared" si="0"/>
-        <v>837674</v>
+        <v>771307</v>
       </c>
       <c r="N50" s="166">
         <f t="shared" si="0"/>
-        <v>8.3767399999999999</v>
+        <v>7.7130700000000001</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
@@ -23421,20 +23588,20 @@
         <v>9.1899999999999996E-2</v>
       </c>
       <c r="K51" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>7256</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>3216</v>
       </c>
       <c r="L51" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>0.72560000000000002</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>0.3216</v>
       </c>
       <c r="M51" s="71">
         <f t="shared" ref="M51" si="17">G51+I51+K51</f>
-        <v>3710</v>
+        <v>-330</v>
       </c>
       <c r="N51" s="166">
         <f t="shared" ref="N51" si="18">H51+J51+L51</f>
-        <v>0.371</v>
+        <v>-3.3000000000000029E-2</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
@@ -23473,20 +23640,20 @@
         <v>-1.2057033333333331</v>
       </c>
       <c r="K52" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>15088</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>-46872</v>
       </c>
       <c r="L52" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>5.0293333333333329E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>-0.15623999999999999</v>
       </c>
       <c r="M52" s="71">
         <f t="shared" si="0"/>
-        <v>6355</v>
+        <v>-55605</v>
       </c>
       <c r="N52" s="166">
         <f t="shared" si="0"/>
-        <v>2.118333333333336E-2</v>
+        <v>-0.18534999999999996</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
@@ -23519,11 +23686,11 @@
         <v>-9.0149999999999994E-2</v>
       </c>
       <c r="K53" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L53" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M53" s="71">
@@ -23571,20 +23738,20 @@
         <v>0.15198</v>
       </c>
       <c r="K54" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>5133</v>
       </c>
       <c r="L54" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>1.28325E-2</v>
       </c>
       <c r="M54" s="71">
         <f t="shared" si="0"/>
-        <v>475202</v>
+        <v>480335</v>
       </c>
       <c r="N54" s="166">
         <f t="shared" si="0"/>
-        <v>1.188005</v>
+        <v>1.2008375</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
@@ -23623,20 +23790,20 @@
         <v>-0.25410250000000001</v>
       </c>
       <c r="K55" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>27000</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>25959</v>
       </c>
       <c r="L55" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>6.7500000000000004E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>6.4897499999999997E-2</v>
       </c>
       <c r="M55" s="71">
         <f t="shared" si="0"/>
-        <v>369274</v>
+        <v>368233</v>
       </c>
       <c r="N55" s="166">
         <f t="shared" si="0"/>
-        <v>0.92318499999999992</v>
+        <v>0.92058249999999986</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
@@ -23673,20 +23840,20 @@
         <v>-1.03518</v>
       </c>
       <c r="K56" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>-405100</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>-340700</v>
       </c>
       <c r="L56" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>-0.40510000000000002</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <v>-0.3407</v>
       </c>
       <c r="M56" s="71">
         <f t="shared" ref="M56" si="21">G56+I56+K56</f>
-        <v>-1440180</v>
+        <v>-1375780</v>
       </c>
       <c r="N56" s="166">
         <f t="shared" ref="N56" si="22">H56+J56+L56</f>
-        <v>-1.44028</v>
+        <v>-1.37588</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
@@ -23719,11 +23886,11 @@
         <v>0</v>
       </c>
       <c r="K57" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L57" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DM$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M57" s="71">
@@ -24114,12 +24281,12 @@
       <c r="J65" s="100"/>
       <c r="K65" s="109">
         <f>SUM(K4:K62)</f>
-        <v>-1782867</v>
+        <v>-2342525</v>
       </c>
       <c r="L65" s="109"/>
       <c r="M65" s="154">
         <f>SUM(M4:M62)</f>
-        <v>9997170</v>
+        <v>9437512</v>
       </c>
       <c r="N65" s="235"/>
     </row>
@@ -24280,492 +24447,492 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A45:C45 A11:C11 A3:F3 L2:L3 A41:C41 A5 A32:F32 F11 F42:F43 F45 A61:C61 A62:E62 A34:F36 E41:F41 A50:F50 A23 A38:F39 A55:F55 F59:F62 E61 G65:N66 A25:F26 M25:N26 A65:E65 C53:F53 M23:N23 G23:H26 A28:F29 A52:F52 G41:H42 G28:H39 G69:N71 F56:F57 G54:H56 A14:H16 M14:N16 K58:N63 M28:N39 M41:N42 M5:N9 G8:J9 G11:I13 M11:N12 I44:J56 M44:N52 G44:H52 G4:L4 C5:J5 M54:N56 A18:F19 G18:H20 M18:N20 I14:I42 J11:J42 K5:L56 I58:J64 G58:H63">
-    <cfRule type="expression" dxfId="393" priority="228">
+    <cfRule type="expression" dxfId="395" priority="228">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:I3">
-    <cfRule type="expression" dxfId="392" priority="227">
+    <cfRule type="expression" dxfId="394" priority="227">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J3">
-    <cfRule type="expression" dxfId="391" priority="226">
+    <cfRule type="expression" dxfId="393" priority="226">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K3">
-    <cfRule type="expression" dxfId="390" priority="225">
+    <cfRule type="expression" dxfId="392" priority="225">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A42:C42 E42 A43">
-    <cfRule type="expression" dxfId="389" priority="221">
+    <cfRule type="expression" dxfId="391" priority="221">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E45">
-    <cfRule type="expression" dxfId="388" priority="219">
+    <cfRule type="expression" dxfId="390" priority="219">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A20:F20">
-    <cfRule type="expression" dxfId="387" priority="217">
+    <cfRule type="expression" dxfId="389" priority="217">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:C47 E47:F47">
-    <cfRule type="expression" dxfId="386" priority="211">
+    <cfRule type="expression" dxfId="388" priority="211">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M25:N25">
-    <cfRule type="expression" dxfId="385" priority="201">
+    <cfRule type="expression" dxfId="387" priority="201">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12:C12 E12:F12">
-    <cfRule type="expression" dxfId="384" priority="206">
+    <cfRule type="expression" dxfId="386" priority="206">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N25">
-    <cfRule type="expression" dxfId="383" priority="202">
+    <cfRule type="expression" dxfId="385" priority="202">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M12:N12">
-    <cfRule type="expression" dxfId="382" priority="187">
+    <cfRule type="expression" dxfId="384" priority="187">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23:C23 E23:F23">
-    <cfRule type="expression" dxfId="381" priority="182">
+    <cfRule type="expression" dxfId="383" priority="182">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N12">
-    <cfRule type="expression" dxfId="380" priority="188">
+    <cfRule type="expression" dxfId="382" priority="188">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A8:C8 E8:F8 A9:F9 A10:B10 D10:F10">
-    <cfRule type="expression" dxfId="379" priority="173">
+    <cfRule type="expression" dxfId="381" priority="173">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N8:N9">
-    <cfRule type="expression" dxfId="378" priority="171">
+    <cfRule type="expression" dxfId="380" priority="171">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M8:N9">
-    <cfRule type="expression" dxfId="377" priority="170">
+    <cfRule type="expression" dxfId="379" priority="170">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A37:C37 E37:F37">
-    <cfRule type="expression" dxfId="376" priority="165">
+    <cfRule type="expression" dxfId="378" priority="165">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M37:N37">
-    <cfRule type="expression" dxfId="375" priority="161">
+    <cfRule type="expression" dxfId="377" priority="161">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N37">
-    <cfRule type="expression" dxfId="374" priority="162">
+    <cfRule type="expression" dxfId="376" priority="162">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A49:C49 E49:F49">
-    <cfRule type="expression" dxfId="373" priority="156">
+    <cfRule type="expression" dxfId="375" priority="156">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N23">
-    <cfRule type="expression" dxfId="372" priority="142">
+    <cfRule type="expression" dxfId="374" priority="142">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M23:N23">
-    <cfRule type="expression" dxfId="371" priority="141">
+    <cfRule type="expression" dxfId="373" priority="141">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58:C58 E58:F58">
-    <cfRule type="expression" dxfId="370" priority="131">
+    <cfRule type="expression" dxfId="372" priority="131">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L67:L68">
-    <cfRule type="expression" dxfId="369" priority="125">
+    <cfRule type="expression" dxfId="371" priority="125">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G67:I68">
-    <cfRule type="expression" dxfId="368" priority="124">
+    <cfRule type="expression" dxfId="370" priority="124">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J67:J68">
-    <cfRule type="expression" dxfId="367" priority="123">
+    <cfRule type="expression" dxfId="369" priority="123">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K67:K68">
-    <cfRule type="expression" dxfId="366" priority="122">
+    <cfRule type="expression" dxfId="368" priority="122">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A30:F30">
-    <cfRule type="expression" dxfId="365" priority="121">
+    <cfRule type="expression" dxfId="367" priority="121">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A31:F31">
-    <cfRule type="expression" dxfId="364" priority="120">
+    <cfRule type="expression" dxfId="366" priority="120">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A33:F33">
-    <cfRule type="expression" dxfId="363" priority="119">
+    <cfRule type="expression" dxfId="365" priority="119">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D11:E11">
-    <cfRule type="expression" dxfId="362" priority="108">
+    <cfRule type="expression" dxfId="364" priority="108">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A59:C60 E59:E60">
-    <cfRule type="expression" dxfId="361" priority="104">
+    <cfRule type="expression" dxfId="363" priority="104">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M59:N60">
-    <cfRule type="expression" dxfId="360" priority="103">
+    <cfRule type="expression" dxfId="362" priority="103">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A46:C46 E46:F46">
-    <cfRule type="expression" dxfId="359" priority="100">
+    <cfRule type="expression" dxfId="361" priority="100">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A54:B54">
-    <cfRule type="expression" dxfId="358" priority="96">
+    <cfRule type="expression" dxfId="360" priority="96">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4:C4 E4:F4">
-    <cfRule type="expression" dxfId="357" priority="91">
+    <cfRule type="expression" dxfId="359" priority="91">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M4:N4">
-    <cfRule type="expression" dxfId="356" priority="90">
+    <cfRule type="expression" dxfId="358" priority="90">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M4:N4">
-    <cfRule type="expression" dxfId="355" priority="87">
+    <cfRule type="expression" dxfId="357" priority="87">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N4">
-    <cfRule type="expression" dxfId="354" priority="88">
+    <cfRule type="expression" dxfId="356" priority="88">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A44:C44 E44:F44">
-    <cfRule type="expression" dxfId="353" priority="82">
+    <cfRule type="expression" dxfId="355" priority="82">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A69:F69 F70">
-    <cfRule type="expression" dxfId="352" priority="81">
+    <cfRule type="expression" dxfId="354" priority="81">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:F13">
-    <cfRule type="expression" dxfId="351" priority="73">
+    <cfRule type="expression" dxfId="353" priority="73">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M13:N13">
-    <cfRule type="expression" dxfId="350" priority="72">
+    <cfRule type="expression" dxfId="352" priority="72">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M13:N13">
-    <cfRule type="expression" dxfId="349" priority="69">
+    <cfRule type="expression" dxfId="351" priority="69">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N13">
-    <cfRule type="expression" dxfId="348" priority="70">
+    <cfRule type="expression" dxfId="350" priority="70">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F54">
-    <cfRule type="expression" dxfId="347" priority="62">
+    <cfRule type="expression" dxfId="349" priority="62">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D54:E54">
-    <cfRule type="expression" dxfId="346" priority="61">
+    <cfRule type="expression" dxfId="348" priority="61">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="345" priority="60">
+    <cfRule type="expression" dxfId="347" priority="60">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4">
-    <cfRule type="expression" dxfId="344" priority="59">
+    <cfRule type="expression" dxfId="346" priority="59">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D12">
-    <cfRule type="expression" dxfId="343" priority="58">
+    <cfRule type="expression" dxfId="345" priority="58">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D23">
-    <cfRule type="expression" dxfId="342" priority="57">
+    <cfRule type="expression" dxfId="344" priority="57">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D59:D60">
-    <cfRule type="expression" dxfId="341" priority="46">
+    <cfRule type="expression" dxfId="343" priority="46">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D37">
-    <cfRule type="expression" dxfId="340" priority="56">
+    <cfRule type="expression" dxfId="342" priority="56">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D42 D44">
-    <cfRule type="expression" dxfId="339" priority="55">
+    <cfRule type="expression" dxfId="341" priority="55">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D41">
-    <cfRule type="expression" dxfId="338" priority="54">
+    <cfRule type="expression" dxfId="340" priority="54">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D45">
-    <cfRule type="expression" dxfId="337" priority="53">
+    <cfRule type="expression" dxfId="339" priority="53">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D46">
-    <cfRule type="expression" dxfId="336" priority="52">
+    <cfRule type="expression" dxfId="338" priority="52">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D47">
-    <cfRule type="expression" dxfId="335" priority="51">
+    <cfRule type="expression" dxfId="337" priority="51">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D49">
-    <cfRule type="expression" dxfId="334" priority="50">
+    <cfRule type="expression" dxfId="336" priority="50">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D61">
-    <cfRule type="expression" dxfId="333" priority="49">
+    <cfRule type="expression" dxfId="335" priority="49">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D58">
-    <cfRule type="expression" dxfId="332" priority="47">
+    <cfRule type="expression" dxfId="334" priority="47">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:F24">
-    <cfRule type="expression" dxfId="331" priority="45">
+    <cfRule type="expression" dxfId="333" priority="45">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M24:N24">
-    <cfRule type="expression" dxfId="330" priority="44">
+    <cfRule type="expression" dxfId="332" priority="44">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N24">
-    <cfRule type="expression" dxfId="329" priority="41">
+    <cfRule type="expression" dxfId="331" priority="41">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M24:N24">
-    <cfRule type="expression" dxfId="328" priority="40">
+    <cfRule type="expression" dxfId="330" priority="40">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A64:F64">
-    <cfRule type="expression" dxfId="327" priority="33">
+    <cfRule type="expression" dxfId="329" priority="33">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G64:H64 K64:N64">
-    <cfRule type="expression" dxfId="326" priority="32">
+    <cfRule type="expression" dxfId="328" priority="32">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A53:B53">
-    <cfRule type="expression" dxfId="325" priority="31">
+    <cfRule type="expression" dxfId="327" priority="31">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G53:H53 M53:N53">
-    <cfRule type="expression" dxfId="324" priority="30">
+    <cfRule type="expression" dxfId="326" priority="30">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40:F40">
-    <cfRule type="expression" dxfId="323" priority="29">
+    <cfRule type="expression" dxfId="325" priority="29">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G40:H40 M40:N40">
-    <cfRule type="expression" dxfId="322" priority="28">
+    <cfRule type="expression" dxfId="324" priority="28">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A48:F48">
-    <cfRule type="expression" dxfId="321" priority="27">
+    <cfRule type="expression" dxfId="323" priority="27">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:F17">
-    <cfRule type="expression" dxfId="320" priority="26">
+    <cfRule type="expression" dxfId="322" priority="26">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G17:H17 M17:N17">
-    <cfRule type="expression" dxfId="319" priority="25">
+    <cfRule type="expression" dxfId="321" priority="25">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:F22 C21:F21">
-    <cfRule type="expression" dxfId="318" priority="24">
+    <cfRule type="expression" dxfId="320" priority="24">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G21:H22 M21:N22">
-    <cfRule type="expression" dxfId="317" priority="23">
+    <cfRule type="expression" dxfId="319" priority="23">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G27:H27 M27:N27">
-    <cfRule type="expression" dxfId="316" priority="19">
+    <cfRule type="expression" dxfId="318" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27:F27">
-    <cfRule type="expression" dxfId="315" priority="22">
+    <cfRule type="expression" dxfId="317" priority="22">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A51:F51">
-    <cfRule type="expression" dxfId="314" priority="21">
+    <cfRule type="expression" dxfId="316" priority="21">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A63:F63">
-    <cfRule type="expression" dxfId="313" priority="20">
+    <cfRule type="expression" dxfId="315" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A70:E70">
-    <cfRule type="expression" dxfId="312" priority="18">
+    <cfRule type="expression" dxfId="314" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A56:E56 A57">
-    <cfRule type="expression" dxfId="311" priority="16">
+    <cfRule type="expression" dxfId="313" priority="16">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A6:F7">
-    <cfRule type="expression" dxfId="310" priority="15">
+    <cfRule type="expression" dxfId="312" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G6:J7">
-    <cfRule type="expression" dxfId="309" priority="14">
+    <cfRule type="expression" dxfId="311" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B57:E57">
-    <cfRule type="expression" dxfId="308" priority="13">
+    <cfRule type="expression" dxfId="310" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5">
-    <cfRule type="expression" dxfId="307" priority="12">
+    <cfRule type="expression" dxfId="309" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C10">
-    <cfRule type="expression" dxfId="306" priority="11">
+    <cfRule type="expression" dxfId="308" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G10:J10 M10:N10">
-    <cfRule type="expression" dxfId="305" priority="10">
+    <cfRule type="expression" dxfId="307" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N10">
-    <cfRule type="expression" dxfId="304" priority="9">
+    <cfRule type="expression" dxfId="306" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M10:N10">
-    <cfRule type="expression" dxfId="303" priority="8">
+    <cfRule type="expression" dxfId="305" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="expression" dxfId="302" priority="7">
+    <cfRule type="expression" dxfId="304" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C43">
-    <cfRule type="expression" dxfId="301" priority="6">
+    <cfRule type="expression" dxfId="303" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D43:E43">
-    <cfRule type="expression" dxfId="300" priority="5">
+    <cfRule type="expression" dxfId="302" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G43:J43 M43:N43">
-    <cfRule type="expression" dxfId="299" priority="4">
+    <cfRule type="expression" dxfId="301" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21">
-    <cfRule type="expression" dxfId="298" priority="3">
+    <cfRule type="expression" dxfId="300" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:A22">
-    <cfRule type="expression" dxfId="297" priority="2">
+    <cfRule type="expression" dxfId="299" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G57:N57">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="298" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -30456,42 +30623,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2 A48:A49 AE58 AD56:AE57 AE43:AE55 AD42:AD55 A3:G4 AD6:AE9 AD12:AE19 AD21:AD40 AE21:AE39 H2:AE4 A10:AE11 C48:AC49 A5:AC9 A50:AC57 A12:AC47 A59:AE63">
-    <cfRule type="expression" dxfId="296" priority="13">
+    <cfRule type="expression" dxfId="297" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE40">
-    <cfRule type="expression" dxfId="295" priority="12">
+    <cfRule type="expression" dxfId="296" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE42">
-    <cfRule type="expression" dxfId="294" priority="11">
+    <cfRule type="expression" dxfId="295" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48:B49">
-    <cfRule type="expression" dxfId="293" priority="5">
+    <cfRule type="expression" dxfId="294" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD5:AE5">
-    <cfRule type="expression" dxfId="292" priority="4">
+    <cfRule type="expression" dxfId="293" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD41">
-    <cfRule type="expression" dxfId="291" priority="3">
+    <cfRule type="expression" dxfId="292" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE41">
-    <cfRule type="expression" dxfId="290" priority="2">
+    <cfRule type="expression" dxfId="291" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD20:AE20">
-    <cfRule type="expression" dxfId="289" priority="1">
+    <cfRule type="expression" dxfId="290" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -36529,112 +36696,112 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G30 G14:G15 G2 A57:G57 G58 A55:A56 H2:AC4 A17:G27 H57:AA62 AC67 AC50:AC64 AB5:AC5 A53:G53 H49:AA54 AB49:AB64 A37:AA40 H5:AA15 AB7:AC15 A16:AC16 A31:G36 H17:AA36 AB65:AC66 AC17:AC46 AB17:AB47 A68:AC71 A54:B54 D54:G54 C55:AA56 A3:G5 A7:G8 A6:C6 E6:G6 A10:G13 A9:C9 E9:G9 A29:G29 A28:C28 E28:G28 A42:AA45 A41:C41 E41:AA41 A47:AA48 A46:C46 E46:AA46 A49:C52 E49:G52 A64:AA66 A59:C63 E63:AA63 E59:G62">
-    <cfRule type="expression" dxfId="288" priority="28">
+    <cfRule type="expression" dxfId="289" priority="28">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC47">
-    <cfRule type="expression" dxfId="287" priority="27">
+    <cfRule type="expression" dxfId="288" priority="27">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC49">
-    <cfRule type="expression" dxfId="286" priority="26">
+    <cfRule type="expression" dxfId="287" priority="26">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A30:C30 F30">
-    <cfRule type="expression" dxfId="285" priority="25">
+    <cfRule type="expression" dxfId="286" priority="25">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14:F14 A15:C15 E15:F15">
-    <cfRule type="expression" dxfId="284" priority="23">
+    <cfRule type="expression" dxfId="285" priority="23">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D30:E30">
-    <cfRule type="expression" dxfId="283" priority="22">
+    <cfRule type="expression" dxfId="284" priority="22">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58:F58">
-    <cfRule type="expression" dxfId="282" priority="20">
+    <cfRule type="expression" dxfId="283" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55:B56">
-    <cfRule type="expression" dxfId="281" priority="19">
+    <cfRule type="expression" dxfId="282" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB6:AC6">
-    <cfRule type="expression" dxfId="280" priority="15">
+    <cfRule type="expression" dxfId="281" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB48">
-    <cfRule type="expression" dxfId="279" priority="14">
+    <cfRule type="expression" dxfId="280" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC48">
-    <cfRule type="expression" dxfId="278" priority="13">
+    <cfRule type="expression" dxfId="279" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6">
-    <cfRule type="expression" dxfId="277" priority="12">
+    <cfRule type="expression" dxfId="278" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9">
-    <cfRule type="expression" dxfId="276" priority="11">
+    <cfRule type="expression" dxfId="277" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D15">
-    <cfRule type="expression" dxfId="275" priority="10">
+    <cfRule type="expression" dxfId="276" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D28">
-    <cfRule type="expression" dxfId="274" priority="9">
+    <cfRule type="expression" dxfId="275" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D41">
-    <cfRule type="expression" dxfId="273" priority="8">
+    <cfRule type="expression" dxfId="274" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D46">
-    <cfRule type="expression" dxfId="272" priority="7">
+    <cfRule type="expression" dxfId="273" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D49">
-    <cfRule type="expression" dxfId="271" priority="6">
+    <cfRule type="expression" dxfId="272" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D60:D63">
-    <cfRule type="expression" dxfId="270" priority="1">
+    <cfRule type="expression" dxfId="271" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D50:D51">
-    <cfRule type="expression" dxfId="269" priority="5">
+    <cfRule type="expression" dxfId="270" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D52">
-    <cfRule type="expression" dxfId="268" priority="4">
+    <cfRule type="expression" dxfId="269" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D59">
-    <cfRule type="expression" dxfId="267" priority="2">
+    <cfRule type="expression" dxfId="268" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -42549,107 +42716,107 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G29 G13:G14 G2 A30:G36 A39:G40 G53 A58:C61 G57 H39:AA53 H56:AA59 A54:A55 F54:AA55 A37:AA38 H2:AC4 A15:G26 H5:AA36 AC49:AC58 AC60:AC64 AC5:AC46 AB5:AB61 A62:AB63 A65:AC68 A3:G7 A9:G12 A8:C8 E8:G8 A28:G28 A27:C27 E27:G27 A42:G45 A41:C41 E41:G41 A52:G52 A46:C51 E46:G51 A56:G56 E58:G59 E60:AA61">
-    <cfRule type="expression" dxfId="266" priority="24">
+    <cfRule type="expression" dxfId="267" priority="24">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC47">
-    <cfRule type="expression" dxfId="265" priority="23">
+    <cfRule type="expression" dxfId="266" priority="23">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC48">
-    <cfRule type="expression" dxfId="264" priority="22">
+    <cfRule type="expression" dxfId="265" priority="22">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A29:C29 F29">
-    <cfRule type="expression" dxfId="263" priority="21">
+    <cfRule type="expression" dxfId="264" priority="21">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC59">
-    <cfRule type="expression" dxfId="262" priority="20">
+    <cfRule type="expression" dxfId="263" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:F13 A14:C14 E14:F14">
-    <cfRule type="expression" dxfId="261" priority="19">
+    <cfRule type="expression" dxfId="262" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D29:E29">
-    <cfRule type="expression" dxfId="260" priority="18">
+    <cfRule type="expression" dxfId="261" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A53:B53 F53">
-    <cfRule type="expression" dxfId="259" priority="15">
+    <cfRule type="expression" dxfId="260" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A57:F57">
-    <cfRule type="expression" dxfId="258" priority="14">
+    <cfRule type="expression" dxfId="259" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54:B55">
-    <cfRule type="expression" dxfId="257" priority="13">
+    <cfRule type="expression" dxfId="258" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D53:E53 C54:E55">
-    <cfRule type="expression" dxfId="256" priority="12">
+    <cfRule type="expression" dxfId="257" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D58:D61">
-    <cfRule type="expression" dxfId="255" priority="1">
+    <cfRule type="expression" dxfId="256" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="254" priority="10">
+    <cfRule type="expression" dxfId="255" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="253" priority="9">
+    <cfRule type="expression" dxfId="254" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D27">
-    <cfRule type="expression" dxfId="252" priority="8">
+    <cfRule type="expression" dxfId="253" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D41">
-    <cfRule type="expression" dxfId="251" priority="7">
+    <cfRule type="expression" dxfId="252" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D47:D48">
-    <cfRule type="expression" dxfId="250" priority="6">
+    <cfRule type="expression" dxfId="251" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D46">
-    <cfRule type="expression" dxfId="249" priority="5">
+    <cfRule type="expression" dxfId="250" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D49">
-    <cfRule type="expression" dxfId="248" priority="4">
+    <cfRule type="expression" dxfId="249" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D50">
-    <cfRule type="expression" dxfId="247" priority="3">
+    <cfRule type="expression" dxfId="248" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D51">
-    <cfRule type="expression" dxfId="246" priority="2">
+    <cfRule type="expression" dxfId="247" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -43001,11 +43168,11 @@
       <c r="O6" s="215"/>
       <c r="P6" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-27044</v>
+        <v>-40406</v>
       </c>
       <c r="Q6" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.54088000000000003</v>
+        <v>-0.80811999999999995</v>
       </c>
       <c r="R6" s="159"/>
       <c r="S6" s="153">
@@ -43022,11 +43189,11 @@
       <c r="X6" s="132"/>
       <c r="Y6" s="154">
         <f t="shared" si="0"/>
-        <v>-75380</v>
+        <v>-88742</v>
       </c>
       <c r="Z6" s="168">
         <f t="shared" si="1"/>
-        <v>-1.5076000000000001</v>
+        <v>-1.77484</v>
       </c>
     </row>
     <row r="7" spans="1:26" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -43083,11 +43250,11 @@
       <c r="O7" s="215"/>
       <c r="P7" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-421798</v>
+        <v>-390391</v>
       </c>
       <c r="Q7" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1.4059933333333334</v>
+        <v>-1.3013033333333335</v>
       </c>
       <c r="R7" s="159"/>
       <c r="S7" s="88">
@@ -43104,11 +43271,11 @@
       <c r="X7"/>
       <c r="Y7" s="154">
         <f t="shared" si="0"/>
-        <v>912476</v>
+        <v>943883</v>
       </c>
       <c r="Z7" s="168">
         <f t="shared" si="1"/>
-        <v>3.0415866666666669</v>
+        <v>3.1462766666666671</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -43280,11 +43447,11 @@
       <c r="O10" s="215"/>
       <c r="P10" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-275497</v>
+        <v>-302062</v>
       </c>
       <c r="Q10" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.91832333333333349</v>
+        <v>-1.0068733333333335</v>
       </c>
       <c r="R10" s="159"/>
       <c r="S10" s="88">
@@ -43300,11 +43467,11 @@
       <c r="W10" s="72"/>
       <c r="Y10" s="154">
         <f t="shared" si="0"/>
-        <v>-634406</v>
+        <v>-660971</v>
       </c>
       <c r="Z10" s="168">
         <f t="shared" si="1"/>
-        <v>-3.5590033333333335</v>
+        <v>-3.6475533333333336</v>
       </c>
     </row>
     <row r="11" spans="1:26" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -43361,11 +43528,11 @@
       <c r="O11" s="215"/>
       <c r="P11" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-234738</v>
+        <v>-249238</v>
       </c>
       <c r="Q11" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1.5649200000000003</v>
+        <v>-1.661586666666667</v>
       </c>
       <c r="R11" s="159"/>
       <c r="S11" s="153">
@@ -43381,11 +43548,11 @@
       <c r="W11" s="150"/>
       <c r="Y11" s="154">
         <f t="shared" si="0"/>
-        <v>-409700</v>
+        <v>-424200</v>
       </c>
       <c r="Z11" s="168">
         <f t="shared" si="1"/>
-        <v>-2.7313333333333336</v>
+        <v>-2.8280000000000003</v>
       </c>
     </row>
     <row r="12" spans="1:26" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -43442,11 +43609,11 @@
       <c r="O12" s="215"/>
       <c r="P12" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-184015</v>
+        <v>-205615</v>
       </c>
       <c r="Q12" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-3.0669166666666667</v>
+        <v>-3.4269166666666671</v>
       </c>
       <c r="R12" s="159"/>
       <c r="S12" s="153">
@@ -43462,11 +43629,11 @@
       <c r="W12" s="150"/>
       <c r="Y12" s="154">
         <f t="shared" ref="Y12" si="10">M12+P12+S12+V12</f>
-        <v>-184015</v>
+        <v>-205615</v>
       </c>
       <c r="Z12" s="168">
         <f t="shared" ref="Z12" si="11">(N12+Q12+T12+W12)</f>
-        <v>-3.0669166666666667</v>
+        <v>-3.4269166666666671</v>
       </c>
     </row>
     <row r="13" spans="1:26" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -43932,11 +44099,11 @@
       <c r="O18" s="215"/>
       <c r="P18" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>346537</v>
+        <v>346587</v>
       </c>
       <c r="Q18" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.57756166666666675</v>
+        <v>0.57764500000000008</v>
       </c>
       <c r="R18" s="159"/>
       <c r="S18" s="88">
@@ -43952,11 +44119,11 @@
       <c r="W18" s="72"/>
       <c r="Y18" s="154">
         <f t="shared" si="0"/>
-        <v>151203</v>
+        <v>151253</v>
       </c>
       <c r="Z18" s="168">
         <f t="shared" si="1"/>
-        <v>-2.8400583333333334</v>
+        <v>-2.8399749999999999</v>
       </c>
     </row>
     <row r="19" spans="1:34" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -44013,11 +44180,11 @@
       <c r="O19" s="215"/>
       <c r="P19" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>8958</v>
+        <v>6309</v>
       </c>
       <c r="Q19" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>8.9579999999999993E-2</v>
+        <v>6.3090000000000007E-2</v>
       </c>
       <c r="R19" s="159"/>
       <c r="S19" s="153">
@@ -44033,11 +44200,11 @@
       <c r="W19" s="150"/>
       <c r="Y19" s="154">
         <f t="shared" si="0"/>
-        <v>12637</v>
+        <v>9988</v>
       </c>
       <c r="Z19" s="168">
         <f t="shared" si="1"/>
-        <v>0.12636999999999998</v>
+        <v>9.988000000000001E-2</v>
       </c>
     </row>
     <row r="20" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -44427,11 +44594,11 @@
       <c r="O24" s="215"/>
       <c r="P24" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>62294</v>
+        <v>59049</v>
       </c>
       <c r="Q24" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.62294000000000005</v>
+        <v>0.59048999999999996</v>
       </c>
       <c r="R24" s="159"/>
       <c r="S24" s="88">
@@ -44447,11 +44614,11 @@
       <c r="W24" s="72"/>
       <c r="Y24" s="154">
         <f t="shared" si="0"/>
-        <v>1777639</v>
+        <v>1774394</v>
       </c>
       <c r="Z24" s="168">
         <f t="shared" si="1"/>
-        <v>17.776389999999999</v>
+        <v>17.743939999999998</v>
       </c>
     </row>
     <row r="25" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45083,11 +45250,11 @@
       <c r="O32" s="215"/>
       <c r="P32" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>132513</v>
+        <v>100547</v>
       </c>
       <c r="Q32" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.88342000000000009</v>
+        <v>0.67031333333333343</v>
       </c>
       <c r="R32" s="159"/>
       <c r="S32" s="88">
@@ -45104,11 +45271,11 @@
       <c r="X32"/>
       <c r="Y32" s="154">
         <f t="shared" si="0"/>
-        <v>-372556</v>
+        <v>-404522</v>
       </c>
       <c r="Z32" s="168">
         <f t="shared" si="1"/>
-        <v>-2.4837066666666674</v>
+        <v>-2.696813333333334</v>
       </c>
     </row>
     <row r="33" spans="1:34" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45246,11 +45413,11 @@
       <c r="O34" s="215"/>
       <c r="P34" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>213912</v>
+        <v>214612</v>
       </c>
       <c r="Q34" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1.944654545454545</v>
+        <v>1.9510181818181813</v>
       </c>
       <c r="R34" s="159"/>
       <c r="S34" s="88">
@@ -45266,11 +45433,11 @@
       <c r="W34" s="72"/>
       <c r="Y34" s="154">
         <f t="shared" si="0"/>
-        <v>-105028</v>
+        <v>-104328</v>
       </c>
       <c r="Z34" s="168">
         <f t="shared" si="1"/>
-        <v>-0.95480000000000009</v>
+        <v>-0.94843636363636374</v>
       </c>
       <c r="AB34" s="1"/>
       <c r="AC34" s="1"/>
@@ -45415,11 +45582,11 @@
       <c r="O36" s="215"/>
       <c r="P36" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>110061</v>
+        <v>-52639</v>
       </c>
       <c r="Q36" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.4785260869565211</v>
+        <v>-0.22886521739130505</v>
       </c>
       <c r="R36" s="159"/>
       <c r="S36" s="88">
@@ -45435,11 +45602,11 @@
       <c r="W36" s="72"/>
       <c r="Y36" s="154">
         <f t="shared" si="0"/>
-        <v>4271164</v>
+        <v>4108464</v>
       </c>
       <c r="Z36" s="168">
         <f t="shared" si="1"/>
-        <v>18.570278260869564</v>
+        <v>17.862886956521738</v>
       </c>
     </row>
     <row r="37" spans="1:34" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45494,11 +45661,11 @@
       <c r="O37" s="215"/>
       <c r="P37" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-18531</v>
+        <v>-16493</v>
       </c>
       <c r="Q37" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.92654999999999998</v>
+        <v>-0.82464999999999988</v>
       </c>
       <c r="R37" s="159"/>
       <c r="S37" s="153">
@@ -45514,11 +45681,11 @@
       <c r="W37" s="150"/>
       <c r="Y37" s="154">
         <f t="shared" ref="Y37" si="20">M37+P37+S37+V37</f>
-        <v>-18531</v>
+        <v>-16493</v>
       </c>
       <c r="Z37" s="168">
         <f t="shared" ref="Z37" si="21">(N37+Q37+T37+W37)</f>
-        <v>-0.92654999999999998</v>
+        <v>-0.82464999999999988</v>
       </c>
     </row>
     <row r="38" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45656,11 +45823,11 @@
       <c r="O39" s="215"/>
       <c r="P39" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>3458272</v>
+        <v>3355767</v>
       </c>
       <c r="Q39" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>3.458272</v>
+        <v>3.3557670000000002</v>
       </c>
       <c r="R39" s="159"/>
       <c r="S39" s="88">
@@ -45677,11 +45844,11 @@
       <c r="X39" s="132"/>
       <c r="Y39" s="154">
         <f t="shared" ref="Y39:Y74" si="22">M39+P39+S39+V39</f>
-        <v>7051678</v>
+        <v>6949173</v>
       </c>
       <c r="Z39" s="168">
         <f t="shared" ref="Z39:Z74" si="23">(N39+Q39+T39+W39)</f>
-        <v>7.0516780000000008</v>
+        <v>6.949173</v>
       </c>
       <c r="AB39" s="131"/>
     </row>
@@ -46253,11 +46420,11 @@
       <c r="O46" s="215"/>
       <c r="P46" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>850744</v>
+        <v>854635</v>
       </c>
       <c r="Q46" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1.7014879999999999</v>
+        <v>1.7092699999999998</v>
       </c>
       <c r="R46" s="159"/>
       <c r="S46" s="88">
@@ -46274,11 +46441,11 @@
       <c r="X46" s="1"/>
       <c r="Y46" s="154">
         <f t="shared" si="22"/>
-        <v>803006</v>
+        <v>806897</v>
       </c>
       <c r="Z46" s="168">
         <f t="shared" si="23"/>
-        <v>1.6060119999999998</v>
+        <v>1.6137939999999997</v>
       </c>
       <c r="AA46" s="1"/>
     </row>
@@ -46336,11 +46503,11 @@
       <c r="O47" s="215"/>
       <c r="P47" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-116904</v>
+        <v>-159111</v>
       </c>
       <c r="Q47" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-2.3380800000000002</v>
+        <v>-3.18222</v>
       </c>
       <c r="R47" s="159"/>
       <c r="S47" s="88">
@@ -46356,11 +46523,11 @@
       <c r="W47" s="72"/>
       <c r="Y47" s="154">
         <f t="shared" si="22"/>
-        <v>-9</v>
+        <v>-42216</v>
       </c>
       <c r="Z47" s="168">
         <f t="shared" si="23"/>
-        <v>-1.8000000000029104E-4</v>
+        <v>-0.84432000000000018</v>
       </c>
       <c r="AD47" s="1"/>
       <c r="AE47" s="1"/>
@@ -46505,11 +46672,11 @@
       <c r="O49" s="215"/>
       <c r="P49" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-65525</v>
+        <v>-56015</v>
       </c>
       <c r="Q49" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1.6381249999999998</v>
+        <v>-1.4003749999999999</v>
       </c>
       <c r="R49" s="159"/>
       <c r="S49" s="88">
@@ -46525,11 +46692,11 @@
       <c r="W49" s="72"/>
       <c r="Y49" s="154">
         <f t="shared" si="22"/>
-        <v>-77353</v>
+        <v>-67843</v>
       </c>
       <c r="Z49" s="168">
         <f t="shared" si="23"/>
-        <v>-1.9338249999999999</v>
+        <v>-1.696075</v>
       </c>
       <c r="AD49"/>
       <c r="AE49"/>
@@ -46760,11 +46927,11 @@
       <c r="O52" s="215"/>
       <c r="P52" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>665181</v>
+        <v>577035</v>
       </c>
       <c r="Q52" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1.6629525000000001</v>
+        <v>1.4425875000000001</v>
       </c>
       <c r="R52" s="159"/>
       <c r="S52" s="88">
@@ -46780,11 +46947,11 @@
       <c r="W52" s="72"/>
       <c r="Y52" s="154">
         <f t="shared" si="22"/>
-        <v>264882</v>
+        <v>176736</v>
       </c>
       <c r="Z52" s="168">
         <f t="shared" si="23"/>
-        <v>0.66220499999999993</v>
+        <v>0.44184000000000001</v>
       </c>
     </row>
     <row r="53" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -46841,11 +47008,11 @@
       <c r="O53" s="215"/>
       <c r="P53" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>172662</v>
+        <v>149057</v>
       </c>
       <c r="Q53" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1.72662</v>
+        <v>1.49057</v>
       </c>
       <c r="R53" s="159"/>
       <c r="S53" s="88">
@@ -46861,11 +47028,11 @@
       <c r="W53" s="72"/>
       <c r="Y53" s="154">
         <f t="shared" si="22"/>
-        <v>918455</v>
+        <v>894850</v>
       </c>
       <c r="Z53" s="168">
         <f t="shared" si="23"/>
-        <v>9.1845500000000015</v>
+        <v>8.948500000000001</v>
       </c>
     </row>
     <row r="54" spans="1:34" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -47003,11 +47170,11 @@
       <c r="O55" s="215"/>
       <c r="P55" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-66383</v>
+        <v>-79543</v>
       </c>
       <c r="Q55" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1.3276599999999998</v>
+        <v>-1.5908599999999997</v>
       </c>
       <c r="R55" s="159"/>
       <c r="S55" s="153">
@@ -47024,11 +47191,11 @@
       <c r="X55" s="132"/>
       <c r="Y55" s="154">
         <f t="shared" si="22"/>
-        <v>-312161</v>
+        <v>-325321</v>
       </c>
       <c r="Z55" s="168">
         <f t="shared" si="23"/>
-        <v>-6.24322</v>
+        <v>-6.5064200000000003</v>
       </c>
       <c r="AA55" s="132"/>
     </row>
@@ -47086,11 +47253,11 @@
       <c r="O56" s="215"/>
       <c r="P56" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-182098</v>
+        <v>-169498</v>
       </c>
       <c r="Q56" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.36930666666666667</v>
+        <v>-0.56499333333333335</v>
       </c>
       <c r="R56" s="159"/>
       <c r="S56" s="88">
@@ -47106,11 +47273,11 @@
       <c r="W56" s="72"/>
       <c r="Y56" s="154">
         <f t="shared" si="22"/>
-        <v>-4881073</v>
+        <v>-4868473</v>
       </c>
       <c r="Z56" s="168">
         <f t="shared" si="23"/>
-        <v>-16.032556666666672</v>
+        <v>-16.228243333333335</v>
       </c>
       <c r="AB56" s="132"/>
       <c r="AC56" s="132"/>
@@ -47340,11 +47507,11 @@
       <c r="O59" s="215"/>
       <c r="P59" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>34328</v>
+        <v>30338</v>
       </c>
       <c r="Q59" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.36596000000000001</v>
+        <v>0.28616000000000003</v>
       </c>
       <c r="R59" s="159"/>
       <c r="S59" s="88">
@@ -47361,11 +47528,11 @@
       <c r="X59" s="1"/>
       <c r="Y59" s="154">
         <f t="shared" si="22"/>
-        <v>71051</v>
+        <v>67061</v>
       </c>
       <c r="Z59" s="168">
         <f t="shared" si="23"/>
-        <v>0.69479333333333337</v>
+        <v>0.61499333333333328</v>
       </c>
       <c r="AB59" s="1"/>
       <c r="AC59" s="1"/>
@@ -47429,11 +47596,11 @@
       <c r="O60" s="215"/>
       <c r="P60" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>837674</v>
+        <v>771307</v>
       </c>
       <c r="Q60" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>8.3767399999999999</v>
+        <v>7.7130700000000001</v>
       </c>
       <c r="R60" s="159"/>
       <c r="S60" s="88">
@@ -47449,11 +47616,11 @@
       <c r="W60" s="72"/>
       <c r="Y60" s="154">
         <f t="shared" si="22"/>
-        <v>4387743</v>
+        <v>4321376</v>
       </c>
       <c r="Z60" s="168">
         <f t="shared" si="23"/>
-        <v>43.877429999999997</v>
+        <v>43.213760000000001</v>
       </c>
       <c r="AB60" s="132"/>
       <c r="AC60" s="132"/>
@@ -47515,11 +47682,11 @@
       <c r="O61" s="215"/>
       <c r="P61" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>3710</v>
+        <v>-330</v>
       </c>
       <c r="Q61" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.371</v>
+        <v>-3.3000000000000029E-2</v>
       </c>
       <c r="R61" s="159"/>
       <c r="S61" s="153">
@@ -47535,11 +47702,11 @@
       <c r="W61" s="150"/>
       <c r="Y61" s="154">
         <f t="shared" ref="Y61" si="37">M61+P61+S61+V61</f>
-        <v>3710</v>
+        <v>-330</v>
       </c>
       <c r="Z61" s="168">
         <f t="shared" ref="Z61" si="38">(N61+Q61+T61+W61)</f>
-        <v>0.371</v>
+        <v>-3.3000000000000029E-2</v>
       </c>
     </row>
     <row r="62" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -47596,11 +47763,11 @@
       <c r="O62" s="215"/>
       <c r="P62" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>6355</v>
+        <v>-55605</v>
       </c>
       <c r="Q62" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>2.118333333333336E-2</v>
+        <v>-0.18534999999999996</v>
       </c>
       <c r="R62" s="159"/>
       <c r="S62" s="88">
@@ -47616,11 +47783,11 @@
       <c r="W62" s="72"/>
       <c r="Y62" s="154">
         <f t="shared" si="22"/>
-        <v>679204</v>
+        <v>617244</v>
       </c>
       <c r="Z62" s="168">
         <f t="shared" si="23"/>
-        <v>2.2640133333333332</v>
+        <v>2.0574799999999995</v>
       </c>
       <c r="AB62" s="1"/>
       <c r="AC62" s="1"/>
@@ -47684,11 +47851,11 @@
       <c r="O63" s="215"/>
       <c r="P63" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>475202</v>
+        <v>480335</v>
       </c>
       <c r="Q63" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1.188005</v>
+        <v>1.2008375</v>
       </c>
       <c r="R63" s="159"/>
       <c r="S63" s="88">
@@ -47704,11 +47871,11 @@
       <c r="W63" s="72"/>
       <c r="Y63" s="154">
         <f t="shared" si="22"/>
-        <v>1150202</v>
+        <v>1155335</v>
       </c>
       <c r="Z63" s="168">
         <f t="shared" si="23"/>
-        <v>2.875505</v>
+        <v>2.8883375</v>
       </c>
     </row>
     <row r="64" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -47847,11 +48014,11 @@
       <c r="O65" s="215"/>
       <c r="P65" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>369274</v>
+        <v>368233</v>
       </c>
       <c r="Q65" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.92318499999999992</v>
+        <v>0.92058249999999986</v>
       </c>
       <c r="R65" s="159"/>
       <c r="S65" s="153">
@@ -47868,11 +48035,11 @@
       <c r="X65" s="132"/>
       <c r="Y65" s="154">
         <f t="shared" si="22"/>
-        <v>893686</v>
+        <v>892645</v>
       </c>
       <c r="Z65" s="168">
         <f t="shared" si="23"/>
-        <v>2.2342149999999998</v>
+        <v>2.2316124999999998</v>
       </c>
     </row>
     <row r="66" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -48009,11 +48176,11 @@
       <c r="O67" s="215"/>
       <c r="P67" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1440180</v>
+        <v>-1375780</v>
       </c>
       <c r="Q67" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1.44028</v>
+        <v>-1.37588</v>
       </c>
       <c r="R67" s="159"/>
       <c r="S67" s="153">
@@ -48029,11 +48196,11 @@
       <c r="W67" s="150"/>
       <c r="Y67" s="154">
         <f t="shared" ref="Y67" si="43">M67+P67+S67+V67</f>
-        <v>-1440180</v>
+        <v>-1375780</v>
       </c>
       <c r="Z67" s="168">
         <f t="shared" ref="Z67" si="44">(N67+Q67+T67+W67)</f>
-        <v>-1.44028</v>
+        <v>-1.37588</v>
       </c>
     </row>
     <row r="68" spans="1:26" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -48764,7 +48931,7 @@
       <c r="O77" s="122"/>
       <c r="P77" s="109">
         <f>SUM(P4:P74)</f>
-        <v>10007137</v>
+        <v>9453258</v>
       </c>
       <c r="Q77" s="122"/>
       <c r="R77" s="122"/>
@@ -48775,7 +48942,7 @@
       <c r="W77" s="50"/>
       <c r="Y77" s="154">
         <f>SUM(Y4:Y76)</f>
-        <v>29934242</v>
+        <v>29380363</v>
       </c>
       <c r="Z77" s="161"/>
     </row>
@@ -49230,1222 +49397,1222 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A56:C56 V4:W4 A27:F29 V20:W21 A13:C13 W48:W49 A3:F4 L2:L3 A48:F49 A52:C52 W22:W30 A80:F81 C16 W45:W46 W42 A42:H42 G41:H41 F16 F13 F70:F71 W58:W60 G58:J60 A66:J66 Y58:Y60 Y77:Z77 G13:H14 G7:J11 F53 F56:J56 Y56 W52:W53 H4:O4 M5:O5 G16:H18 Y4:Z11 K5:L11 A20:F24 D5:J5 F72:J74 A44:J44 Y66 Z56:Z60 G45:J53 K44:L53 A73:C73 A74:E74 A45:F46 E52:F52 A60:F60 Y34:Z36 M80:O82 M7:O11 A34:O36 R44:W44 R72:W74 R7:W9 R13:W16 R34:W36 R45:U46 R17:U17 R22:U30 R48:U53 U80:U82 A77:E77 A38:H39 A62:F62 K62:O66 Z62:Z66 Y62:Y63 G62:J63 R38:U43 M38:O53 I38:L43 Y38:Z53 W38:W39 G77:W78 G84:W84 K69:O74 G69:J69 W66:W68 R62:U71 G67:O68 Y67:Z74 A9 F9 I13:O18 Y13:Z18 Y55:Z55 R55:U60 K55:O60 G55:J55 W55:W56 Y20:Z32 G20:O32 A31:A32 P13:Q36 A7:F8">
-    <cfRule type="expression" dxfId="245" priority="448">
+    <cfRule type="expression" dxfId="246" priority="448">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V38:V39 V23:V24 V59 V48:V49 V56 V45:V46 V27:V29 G2:I3 V52 G4:H4">
-    <cfRule type="expression" dxfId="244" priority="447">
+    <cfRule type="expression" dxfId="245" priority="447">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J3">
-    <cfRule type="expression" dxfId="243" priority="444">
+    <cfRule type="expression" dxfId="244" priority="444">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V80:W81">
-    <cfRule type="expression" dxfId="242" priority="441">
+    <cfRule type="expression" dxfId="243" priority="441">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K3">
-    <cfRule type="expression" dxfId="241" priority="442">
+    <cfRule type="expression" dxfId="242" priority="442">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V60">
-    <cfRule type="expression" dxfId="240" priority="432">
+    <cfRule type="expression" dxfId="241" priority="432">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V22">
-    <cfRule type="expression" dxfId="239" priority="433">
+    <cfRule type="expression" dxfId="240" priority="433">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A53:C53 E53">
-    <cfRule type="expression" dxfId="238" priority="422">
+    <cfRule type="expression" dxfId="239" priority="422">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V53 V55">
-    <cfRule type="expression" dxfId="237" priority="420">
+    <cfRule type="expression" dxfId="238" priority="420">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E56">
-    <cfRule type="expression" dxfId="236" priority="418">
+    <cfRule type="expression" dxfId="237" priority="418">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V42">
-    <cfRule type="expression" dxfId="235" priority="409">
+    <cfRule type="expression" dxfId="236" priority="409">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A30:F30">
-    <cfRule type="expression" dxfId="234" priority="408">
+    <cfRule type="expression" dxfId="235" priority="408">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B72:C72">
-    <cfRule type="expression" dxfId="233" priority="380">
+    <cfRule type="expression" dxfId="234" priority="380">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V30">
-    <cfRule type="expression" dxfId="232" priority="406">
+    <cfRule type="expression" dxfId="233" priority="406">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26:E26">
-    <cfRule type="expression" dxfId="231" priority="405">
+    <cfRule type="expression" dxfId="232" priority="405">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V26">
-    <cfRule type="expression" dxfId="230" priority="403">
+    <cfRule type="expression" dxfId="231" priority="403">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A25:E25">
-    <cfRule type="expression" dxfId="229" priority="402">
+    <cfRule type="expression" dxfId="230" priority="402">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V25">
-    <cfRule type="expression" dxfId="228" priority="400">
+    <cfRule type="expression" dxfId="229" priority="400">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58:C58 E58:F58">
-    <cfRule type="expression" dxfId="227" priority="387">
+    <cfRule type="expression" dxfId="228" priority="387">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T4:U4 T20:U21">
-    <cfRule type="expression" dxfId="226" priority="331">
+    <cfRule type="expression" dxfId="227" priority="331">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A72">
-    <cfRule type="expression" dxfId="225" priority="378">
+    <cfRule type="expression" dxfId="226" priority="378">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S4:U4 S20:U21">
-    <cfRule type="expression" dxfId="224" priority="330">
+    <cfRule type="expression" dxfId="225" priority="330">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V58">
-    <cfRule type="expression" dxfId="223" priority="383">
+    <cfRule type="expression" dxfId="224" priority="383">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F25">
-    <cfRule type="expression" dxfId="222" priority="349">
+    <cfRule type="expression" dxfId="223" priority="349">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M20:O21 M34:O34">
-    <cfRule type="expression" dxfId="221" priority="347">
+    <cfRule type="expression" dxfId="222" priority="347">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:F17 A18:C18 E18:F18">
-    <cfRule type="expression" dxfId="220" priority="355">
+    <cfRule type="expression" dxfId="221" priority="355">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V17:W17">
-    <cfRule type="expression" dxfId="219" priority="354">
+    <cfRule type="expression" dxfId="220" priority="354">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R4 R20:R21">
-    <cfRule type="expression" dxfId="218" priority="339">
+    <cfRule type="expression" dxfId="219" priority="339">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R4 R20:R21">
-    <cfRule type="expression" dxfId="217" priority="338">
+    <cfRule type="expression" dxfId="218" priority="338">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V66:V68">
-    <cfRule type="expression" dxfId="216" priority="369">
+    <cfRule type="expression" dxfId="217" priority="369">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W62">
-    <cfRule type="expression" dxfId="215" priority="329">
+    <cfRule type="expression" dxfId="216" priority="329">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M35:O35">
-    <cfRule type="expression" dxfId="214" priority="340">
+    <cfRule type="expression" dxfId="215" priority="340">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F26">
-    <cfRule type="expression" dxfId="213" priority="350">
+    <cfRule type="expression" dxfId="214" priority="350">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N20:O21 N34:O34">
-    <cfRule type="expression" dxfId="212" priority="348">
+    <cfRule type="expression" dxfId="213" priority="348">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N35:O35">
-    <cfRule type="expression" dxfId="211" priority="341">
+    <cfRule type="expression" dxfId="212" priority="341">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V62">
-    <cfRule type="expression" dxfId="210" priority="328">
+    <cfRule type="expression" dxfId="211" priority="328">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M18:O18">
-    <cfRule type="expression" dxfId="209" priority="286">
+    <cfRule type="expression" dxfId="210" priority="286">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R18">
-    <cfRule type="expression" dxfId="208" priority="285">
+    <cfRule type="expression" dxfId="209" priority="285">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T18:U18">
-    <cfRule type="expression" dxfId="207" priority="283">
+    <cfRule type="expression" dxfId="208" priority="283">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31:F31 B32:C32 E32:F32">
-    <cfRule type="expression" dxfId="206" priority="275">
+    <cfRule type="expression" dxfId="207" priority="275">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W31">
-    <cfRule type="expression" dxfId="205" priority="274">
+    <cfRule type="expression" dxfId="206" priority="274">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V18:W18">
-    <cfRule type="expression" dxfId="204" priority="288">
+    <cfRule type="expression" dxfId="205" priority="288">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N18:O18">
-    <cfRule type="expression" dxfId="203" priority="287">
+    <cfRule type="expression" dxfId="204" priority="287">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R18">
-    <cfRule type="expression" dxfId="202" priority="284">
+    <cfRule type="expression" dxfId="203" priority="284">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S18:U18">
-    <cfRule type="expression" dxfId="201" priority="282">
+    <cfRule type="expression" dxfId="202" priority="282">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V31">
-    <cfRule type="expression" dxfId="200" priority="273">
+    <cfRule type="expression" dxfId="201" priority="273">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S31:U31">
-    <cfRule type="expression" dxfId="199" priority="267">
+    <cfRule type="expression" dxfId="200" priority="267">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N31:O31">
-    <cfRule type="expression" dxfId="198" priority="272">
+    <cfRule type="expression" dxfId="199" priority="272">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M31:O31">
-    <cfRule type="expression" dxfId="197" priority="271">
+    <cfRule type="expression" dxfId="198" priority="271">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T31:U31">
-    <cfRule type="expression" dxfId="196" priority="268">
+    <cfRule type="expression" dxfId="197" priority="268">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R31">
-    <cfRule type="expression" dxfId="195" priority="270">
+    <cfRule type="expression" dxfId="196" priority="270">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R31">
-    <cfRule type="expression" dxfId="194" priority="269">
+    <cfRule type="expression" dxfId="195" priority="269">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11:F11 A10:C10 E10:F10 F12">
-    <cfRule type="expression" dxfId="193" priority="260">
+    <cfRule type="expression" dxfId="194" priority="260">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V10:W11">
-    <cfRule type="expression" dxfId="192" priority="259">
+    <cfRule type="expression" dxfId="193" priority="259">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R10:R11">
-    <cfRule type="expression" dxfId="191" priority="256">
+    <cfRule type="expression" dxfId="192" priority="256">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R10:R11">
-    <cfRule type="expression" dxfId="190" priority="255">
+    <cfRule type="expression" dxfId="191" priority="255">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S10:U11">
-    <cfRule type="expression" dxfId="189" priority="253">
+    <cfRule type="expression" dxfId="190" priority="253">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N10:O11">
-    <cfRule type="expression" dxfId="188" priority="258">
+    <cfRule type="expression" dxfId="189" priority="258">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M10:O11">
-    <cfRule type="expression" dxfId="187" priority="257">
+    <cfRule type="expression" dxfId="188" priority="257">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T10:U11">
-    <cfRule type="expression" dxfId="186" priority="254">
+    <cfRule type="expression" dxfId="187" priority="254">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:C47 E47:F47">
-    <cfRule type="expression" dxfId="185" priority="246">
+    <cfRule type="expression" dxfId="186" priority="246">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W47">
-    <cfRule type="expression" dxfId="184" priority="245">
+    <cfRule type="expression" dxfId="185" priority="245">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V47">
-    <cfRule type="expression" dxfId="183" priority="244">
+    <cfRule type="expression" dxfId="184" priority="244">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T47:U47">
-    <cfRule type="expression" dxfId="182" priority="239">
+    <cfRule type="expression" dxfId="183" priority="239">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S47:U47">
-    <cfRule type="expression" dxfId="181" priority="238">
+    <cfRule type="expression" dxfId="182" priority="238">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M47:O47">
-    <cfRule type="expression" dxfId="180" priority="242">
+    <cfRule type="expression" dxfId="181" priority="242">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R47">
-    <cfRule type="expression" dxfId="179" priority="241">
+    <cfRule type="expression" dxfId="180" priority="241">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R47">
-    <cfRule type="expression" dxfId="178" priority="240">
+    <cfRule type="expression" dxfId="179" priority="240">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N47:O47">
-    <cfRule type="expression" dxfId="177" priority="243">
+    <cfRule type="expression" dxfId="178" priority="243">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A59:C59 E59:F59">
-    <cfRule type="expression" dxfId="176" priority="231">
+    <cfRule type="expression" dxfId="177" priority="231">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:C5">
-    <cfRule type="expression" dxfId="175" priority="227">
+    <cfRule type="expression" dxfId="176" priority="227">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V5:W5">
-    <cfRule type="expression" dxfId="174" priority="226">
+    <cfRule type="expression" dxfId="175" priority="226">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T5:U5">
-    <cfRule type="expression" dxfId="173" priority="220">
+    <cfRule type="expression" dxfId="174" priority="220">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S5:U5">
-    <cfRule type="expression" dxfId="172" priority="219">
+    <cfRule type="expression" dxfId="173" priority="219">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5:O5">
-    <cfRule type="expression" dxfId="171" priority="223">
+    <cfRule type="expression" dxfId="172" priority="223">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R5">
-    <cfRule type="expression" dxfId="170" priority="222">
+    <cfRule type="expression" dxfId="171" priority="222">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R5">
-    <cfRule type="expression" dxfId="169" priority="221">
+    <cfRule type="expression" dxfId="170" priority="221">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N5:O5">
-    <cfRule type="expression" dxfId="168" priority="224">
+    <cfRule type="expression" dxfId="169" priority="224">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A50:F51">
-    <cfRule type="expression" dxfId="167" priority="208">
+    <cfRule type="expression" dxfId="168" priority="208">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W50:W51">
-    <cfRule type="expression" dxfId="166" priority="207">
+    <cfRule type="expression" dxfId="167" priority="207">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V50:V51">
-    <cfRule type="expression" dxfId="165" priority="206">
+    <cfRule type="expression" dxfId="166" priority="206">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W32">
-    <cfRule type="expression" dxfId="164" priority="200">
+    <cfRule type="expression" dxfId="165" priority="200">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V32">
-    <cfRule type="expression" dxfId="163" priority="199">
+    <cfRule type="expression" dxfId="164" priority="199">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S32:U32">
-    <cfRule type="expression" dxfId="162" priority="193">
+    <cfRule type="expression" dxfId="163" priority="193">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N32:O32">
-    <cfRule type="expression" dxfId="161" priority="198">
+    <cfRule type="expression" dxfId="162" priority="198">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M32:O32">
-    <cfRule type="expression" dxfId="160" priority="197">
+    <cfRule type="expression" dxfId="161" priority="197">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T32:U32">
-    <cfRule type="expression" dxfId="159" priority="194">
+    <cfRule type="expression" dxfId="160" priority="194">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R32">
-    <cfRule type="expression" dxfId="158" priority="196">
+    <cfRule type="expression" dxfId="159" priority="196">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R32">
-    <cfRule type="expression" dxfId="157" priority="195">
+    <cfRule type="expression" dxfId="158" priority="195">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W63">
-    <cfRule type="expression" dxfId="156" priority="191">
+    <cfRule type="expression" dxfId="157" priority="191">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V63">
-    <cfRule type="expression" dxfId="155" priority="190">
+    <cfRule type="expression" dxfId="156" priority="190">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14:F14">
-    <cfRule type="expression" dxfId="154" priority="177">
+    <cfRule type="expression" dxfId="155" priority="177">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W41">
-    <cfRule type="expression" dxfId="153" priority="186">
+    <cfRule type="expression" dxfId="154" priority="186">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V41">
-    <cfRule type="expression" dxfId="152" priority="185">
+    <cfRule type="expression" dxfId="153" priority="185">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A69:C69 E69:F69">
-    <cfRule type="expression" dxfId="151" priority="175">
+    <cfRule type="expression" dxfId="152" priority="175">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W69">
-    <cfRule type="expression" dxfId="150" priority="174">
+    <cfRule type="expression" dxfId="151" priority="174">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V69">
-    <cfRule type="expression" dxfId="149" priority="173">
+    <cfRule type="expression" dxfId="150" priority="173">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G80:G81">
-    <cfRule type="expression" dxfId="148" priority="168">
+    <cfRule type="expression" dxfId="149" priority="168">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H80">
-    <cfRule type="expression" dxfId="147" priority="165">
+    <cfRule type="expression" dxfId="148" priority="165">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H81">
-    <cfRule type="expression" dxfId="146" priority="164">
+    <cfRule type="expression" dxfId="147" priority="164">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L79">
-    <cfRule type="expression" dxfId="145" priority="163">
+    <cfRule type="expression" dxfId="146" priority="163">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G79:I79">
-    <cfRule type="expression" dxfId="144" priority="162">
+    <cfRule type="expression" dxfId="145" priority="162">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J79">
-    <cfRule type="expression" dxfId="143" priority="161">
+    <cfRule type="expression" dxfId="144" priority="161">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K79">
-    <cfRule type="expression" dxfId="142" priority="160">
+    <cfRule type="expression" dxfId="143" priority="160">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y80:Z81">
-    <cfRule type="expression" dxfId="141" priority="147">
+    <cfRule type="expression" dxfId="142" priority="147">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40:F40">
-    <cfRule type="expression" dxfId="140" priority="157">
+    <cfRule type="expression" dxfId="141" priority="157">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A41:F41">
-    <cfRule type="expression" dxfId="139" priority="156">
+    <cfRule type="expression" dxfId="140" priority="156">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A43:F43">
-    <cfRule type="expression" dxfId="138" priority="155">
+    <cfRule type="expression" dxfId="139" priority="155">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W43 G43:H43">
-    <cfRule type="expression" dxfId="137" priority="154">
+    <cfRule type="expression" dxfId="138" priority="154">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V43">
-    <cfRule type="expression" dxfId="136" priority="153">
+    <cfRule type="expression" dxfId="137" priority="153">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W40 G40:H40">
-    <cfRule type="expression" dxfId="135" priority="152">
+    <cfRule type="expression" dxfId="136" priority="152">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V40">
-    <cfRule type="expression" dxfId="134" priority="151">
+    <cfRule type="expression" dxfId="135" priority="151">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D13:E13">
-    <cfRule type="expression" dxfId="133" priority="142">
+    <cfRule type="expression" dxfId="134" priority="142">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y84:Z84">
-    <cfRule type="expression" dxfId="132" priority="148">
+    <cfRule type="expression" dxfId="133" priority="148">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:B16">
-    <cfRule type="expression" dxfId="131" priority="146">
+    <cfRule type="expression" dxfId="132" priority="146">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15">
-    <cfRule type="expression" dxfId="130" priority="145">
+    <cfRule type="expression" dxfId="131" priority="145">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15">
-    <cfRule type="expression" dxfId="129" priority="144">
+    <cfRule type="expression" dxfId="130" priority="144">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D15:E16">
-    <cfRule type="expression" dxfId="128" priority="143">
+    <cfRule type="expression" dxfId="129" priority="143">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G15:H15">
-    <cfRule type="expression" dxfId="127" priority="141">
+    <cfRule type="expression" dxfId="128" priority="141">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J80:J81">
-    <cfRule type="expression" dxfId="126" priority="138">
+    <cfRule type="expression" dxfId="127" priority="138">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I80:J81">
-    <cfRule type="expression" dxfId="125" priority="137">
+    <cfRule type="expression" dxfId="126" priority="137">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A70:C71 E70:E71">
-    <cfRule type="expression" dxfId="124" priority="136">
+    <cfRule type="expression" dxfId="125" priority="136">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G70:J71 M70:O71">
-    <cfRule type="expression" dxfId="123" priority="135">
+    <cfRule type="expression" dxfId="124" priority="135">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W70:W71">
-    <cfRule type="expression" dxfId="122" priority="134">
+    <cfRule type="expression" dxfId="123" priority="134">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V70:V71">
-    <cfRule type="expression" dxfId="121" priority="133">
+    <cfRule type="expression" dxfId="122" priority="133">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V57">
-    <cfRule type="expression" dxfId="120" priority="130">
+    <cfRule type="expression" dxfId="121" priority="130">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A57:C57 E57:F57">
-    <cfRule type="expression" dxfId="119" priority="132">
+    <cfRule type="expression" dxfId="120" priority="132">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W57 Y57 G57:J57">
-    <cfRule type="expression" dxfId="118" priority="131">
+    <cfRule type="expression" dxfId="119" priority="131">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A64:A65">
-    <cfRule type="expression" dxfId="117" priority="129">
+    <cfRule type="expression" dxfId="118" priority="129">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A63:B63">
-    <cfRule type="expression" dxfId="116" priority="128">
+    <cfRule type="expression" dxfId="117" priority="128">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B64:B65">
-    <cfRule type="expression" dxfId="115" priority="127">
+    <cfRule type="expression" dxfId="116" priority="127">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M64:O65 G64:J65 Y64:Y65">
-    <cfRule type="expression" dxfId="114" priority="126">
+    <cfRule type="expression" dxfId="115" priority="126">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W64:W65">
-    <cfRule type="expression" dxfId="113" priority="124">
+    <cfRule type="expression" dxfId="114" priority="124">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V64:V65">
-    <cfRule type="expression" dxfId="112" priority="123">
+    <cfRule type="expression" dxfId="113" priority="123">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A6:C6 E6:F6">
-    <cfRule type="expression" dxfId="111" priority="122">
+    <cfRule type="expression" dxfId="112" priority="122">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G6:J6 M6:O6">
-    <cfRule type="expression" dxfId="110" priority="121">
+    <cfRule type="expression" dxfId="111" priority="121">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V6:W6">
-    <cfRule type="expression" dxfId="109" priority="120">
+    <cfRule type="expression" dxfId="110" priority="120">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T6:U6">
-    <cfRule type="expression" dxfId="108" priority="115">
+    <cfRule type="expression" dxfId="109" priority="115">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S6:U6">
-    <cfRule type="expression" dxfId="107" priority="114">
+    <cfRule type="expression" dxfId="108" priority="114">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M6:O6">
-    <cfRule type="expression" dxfId="106" priority="118">
+    <cfRule type="expression" dxfId="107" priority="118">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R6">
-    <cfRule type="expression" dxfId="105" priority="117">
+    <cfRule type="expression" dxfId="106" priority="117">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R6">
-    <cfRule type="expression" dxfId="104" priority="116">
+    <cfRule type="expression" dxfId="105" priority="116">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N6:O6">
-    <cfRule type="expression" dxfId="103" priority="119">
+    <cfRule type="expression" dxfId="104" priority="119">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A55:C55 E55:F55">
-    <cfRule type="expression" dxfId="102" priority="113">
+    <cfRule type="expression" dxfId="103" priority="113">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A82:F82">
-    <cfRule type="expression" dxfId="101" priority="111">
+    <cfRule type="expression" dxfId="102" priority="111">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V82:W82">
-    <cfRule type="expression" dxfId="100" priority="109">
+    <cfRule type="expression" dxfId="101" priority="109">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G82">
-    <cfRule type="expression" dxfId="99" priority="108">
+    <cfRule type="expression" dxfId="100" priority="108">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H82">
-    <cfRule type="expression" dxfId="98" priority="107">
+    <cfRule type="expression" dxfId="99" priority="107">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y82:Z82">
-    <cfRule type="expression" dxfId="97" priority="106">
+    <cfRule type="expression" dxfId="98" priority="106">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J82">
-    <cfRule type="expression" dxfId="96" priority="105">
+    <cfRule type="expression" dxfId="97" priority="105">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I82:J82">
-    <cfRule type="expression" dxfId="95" priority="104">
+    <cfRule type="expression" dxfId="96" priority="104">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K80:L82">
-    <cfRule type="expression" dxfId="94" priority="102">
+    <cfRule type="expression" dxfId="95" priority="102">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S19:U19">
-    <cfRule type="expression" dxfId="93" priority="92">
+    <cfRule type="expression" dxfId="94" priority="92">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19:F19">
-    <cfRule type="expression" dxfId="92" priority="100">
+    <cfRule type="expression" dxfId="93" priority="100">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y19:Z19 G19:O19">
-    <cfRule type="expression" dxfId="91" priority="99">
+    <cfRule type="expression" dxfId="92" priority="99">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M19:O19">
-    <cfRule type="expression" dxfId="90" priority="96">
+    <cfRule type="expression" dxfId="91" priority="96">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R19">
-    <cfRule type="expression" dxfId="89" priority="95">
+    <cfRule type="expression" dxfId="90" priority="95">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T19:U19">
-    <cfRule type="expression" dxfId="88" priority="93">
+    <cfRule type="expression" dxfId="89" priority="93">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V19:W19">
-    <cfRule type="expression" dxfId="87" priority="98">
+    <cfRule type="expression" dxfId="88" priority="98">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N19:O19">
-    <cfRule type="expression" dxfId="86" priority="97">
+    <cfRule type="expression" dxfId="87" priority="97">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R19">
-    <cfRule type="expression" dxfId="85" priority="94">
+    <cfRule type="expression" dxfId="86" priority="94">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E72:E73">
-    <cfRule type="expression" dxfId="84" priority="91">
+    <cfRule type="expression" dxfId="85" priority="91">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F64:F65">
-    <cfRule type="expression" dxfId="83" priority="90">
+    <cfRule type="expression" dxfId="84" priority="90">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F63">
-    <cfRule type="expression" dxfId="82" priority="89">
+    <cfRule type="expression" dxfId="83" priority="89">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D63:E63 C64:E65">
-    <cfRule type="expression" dxfId="81" priority="88">
+    <cfRule type="expression" dxfId="82" priority="88">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D10">
-    <cfRule type="expression" dxfId="80" priority="87">
+    <cfRule type="expression" dxfId="81" priority="87">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6">
-    <cfRule type="expression" dxfId="79" priority="86">
+    <cfRule type="expression" dxfId="80" priority="86">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D18">
-    <cfRule type="expression" dxfId="78" priority="85">
+    <cfRule type="expression" dxfId="79" priority="85">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D32">
-    <cfRule type="expression" dxfId="77" priority="84">
+    <cfRule type="expression" dxfId="78" priority="84">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D70:D71">
-    <cfRule type="expression" dxfId="76" priority="72">
+    <cfRule type="expression" dxfId="77" priority="72">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D47">
-    <cfRule type="expression" dxfId="75" priority="82">
+    <cfRule type="expression" dxfId="76" priority="82">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D53 D55">
-    <cfRule type="expression" dxfId="74" priority="81">
+    <cfRule type="expression" dxfId="75" priority="81">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D52">
-    <cfRule type="expression" dxfId="73" priority="80">
+    <cfRule type="expression" dxfId="74" priority="80">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D56">
-    <cfRule type="expression" dxfId="72" priority="79">
+    <cfRule type="expression" dxfId="73" priority="79">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D57">
-    <cfRule type="expression" dxfId="71" priority="78">
+    <cfRule type="expression" dxfId="72" priority="78">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D58">
-    <cfRule type="expression" dxfId="70" priority="77">
+    <cfRule type="expression" dxfId="71" priority="77">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D59">
-    <cfRule type="expression" dxfId="69" priority="76">
+    <cfRule type="expression" dxfId="70" priority="76">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D73">
-    <cfRule type="expression" dxfId="68" priority="75">
+    <cfRule type="expression" dxfId="69" priority="75">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D72">
-    <cfRule type="expression" dxfId="67" priority="74">
+    <cfRule type="expression" dxfId="68" priority="74">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D69">
-    <cfRule type="expression" dxfId="66" priority="73">
+    <cfRule type="expression" dxfId="67" priority="73">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A33:F33">
-    <cfRule type="expression" dxfId="65" priority="71">
+    <cfRule type="expression" dxfId="66" priority="71">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G33:O33 Y33:Z33">
-    <cfRule type="expression" dxfId="64" priority="70">
+    <cfRule type="expression" dxfId="65" priority="70">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W33">
-    <cfRule type="expression" dxfId="63" priority="69">
+    <cfRule type="expression" dxfId="64" priority="69">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V33">
-    <cfRule type="expression" dxfId="62" priority="68">
+    <cfRule type="expression" dxfId="63" priority="68">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S33:U33">
-    <cfRule type="expression" dxfId="61" priority="62">
+    <cfRule type="expression" dxfId="62" priority="62">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N33:O33">
-    <cfRule type="expression" dxfId="60" priority="67">
+    <cfRule type="expression" dxfId="61" priority="67">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M33:O33">
-    <cfRule type="expression" dxfId="59" priority="66">
+    <cfRule type="expression" dxfId="60" priority="66">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T33:U33">
-    <cfRule type="expression" dxfId="58" priority="63">
+    <cfRule type="expression" dxfId="59" priority="63">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R33">
-    <cfRule type="expression" dxfId="57" priority="65">
+    <cfRule type="expression" dxfId="58" priority="65">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R33">
-    <cfRule type="expression" dxfId="56" priority="64">
+    <cfRule type="expression" dxfId="57" priority="64">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q4:Q11 Q38:Q53 Q62:Q74 Q55:Q60">
-    <cfRule type="expression" dxfId="55" priority="59">
+    <cfRule type="expression" dxfId="56" priority="59">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P4:Q11 P38:Q53 P62:Q74 P55:Q60">
-    <cfRule type="expression" dxfId="54" priority="58">
+    <cfRule type="expression" dxfId="55" priority="58">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R80:T82">
-    <cfRule type="expression" dxfId="53" priority="57">
+    <cfRule type="expression" dxfId="54" priority="57">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q80:Q82">
-    <cfRule type="expression" dxfId="52" priority="56">
+    <cfRule type="expression" dxfId="53" priority="56">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P80:Q82">
-    <cfRule type="expression" dxfId="51" priority="55">
+    <cfRule type="expression" dxfId="52" priority="55">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A76:F76">
-    <cfRule type="expression" dxfId="50" priority="54">
+    <cfRule type="expression" dxfId="51" priority="54">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A75:F75">
-    <cfRule type="expression" dxfId="49" priority="53">
+    <cfRule type="expression" dxfId="50" priority="53">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G75:O76 Y75:Z76 R75:W76">
-    <cfRule type="expression" dxfId="48" priority="52">
+    <cfRule type="expression" dxfId="49" priority="52">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q75:Q76">
-    <cfRule type="expression" dxfId="47" priority="51">
+    <cfRule type="expression" dxfId="48" priority="51">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P75:Q76">
-    <cfRule type="expression" dxfId="46" priority="50">
+    <cfRule type="expression" dxfId="47" priority="50">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P37:Q37">
-    <cfRule type="expression" dxfId="45" priority="39">
+    <cfRule type="expression" dxfId="46" priority="39">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A37:F37">
-    <cfRule type="expression" dxfId="44" priority="48">
+    <cfRule type="expression" dxfId="45" priority="48">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P83:Q83">
-    <cfRule type="expression" dxfId="43" priority="24">
+    <cfRule type="expression" dxfId="44" priority="24">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61:F61">
-    <cfRule type="expression" dxfId="42" priority="46">
+    <cfRule type="expression" dxfId="43" priority="46">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W61 Y61:Z61 G61:O61 R61:U61">
-    <cfRule type="expression" dxfId="41" priority="45">
+    <cfRule type="expression" dxfId="42" priority="45">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V61">
-    <cfRule type="expression" dxfId="40" priority="44">
+    <cfRule type="expression" dxfId="41" priority="44">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q61">
-    <cfRule type="expression" dxfId="39" priority="43">
+    <cfRule type="expression" dxfId="40" priority="43">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P61:Q61">
-    <cfRule type="expression" dxfId="38" priority="42">
+    <cfRule type="expression" dxfId="39" priority="42">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y37:Z37 G37:O37 R37:W37">
-    <cfRule type="expression" dxfId="37" priority="41">
+    <cfRule type="expression" dxfId="38" priority="41">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q37">
-    <cfRule type="expression" dxfId="36" priority="40">
+    <cfRule type="expression" dxfId="37" priority="40">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q83">
-    <cfRule type="expression" dxfId="35" priority="25">
+    <cfRule type="expression" dxfId="36" priority="25">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F83">
-    <cfRule type="expression" dxfId="34" priority="36">
+    <cfRule type="expression" dxfId="35" priority="36">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A83:E83">
-    <cfRule type="expression" dxfId="33" priority="35">
+    <cfRule type="expression" dxfId="34" priority="35">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M83:O83 U83">
-    <cfRule type="expression" dxfId="32" priority="34">
+    <cfRule type="expression" dxfId="33" priority="34">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V83:W83">
-    <cfRule type="expression" dxfId="31" priority="33">
+    <cfRule type="expression" dxfId="32" priority="33">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G83">
-    <cfRule type="expression" dxfId="30" priority="32">
+    <cfRule type="expression" dxfId="31" priority="32">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H83">
-    <cfRule type="expression" dxfId="29" priority="31">
+    <cfRule type="expression" dxfId="30" priority="31">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y83:Z83">
-    <cfRule type="expression" dxfId="28" priority="30">
+    <cfRule type="expression" dxfId="29" priority="30">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J83">
-    <cfRule type="expression" dxfId="27" priority="29">
+    <cfRule type="expression" dxfId="28" priority="29">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I83:J83">
-    <cfRule type="expression" dxfId="26" priority="28">
+    <cfRule type="expression" dxfId="27" priority="28">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K83:L83">
-    <cfRule type="expression" dxfId="25" priority="27">
+    <cfRule type="expression" dxfId="26" priority="27">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R83:T83">
-    <cfRule type="expression" dxfId="24" priority="26">
+    <cfRule type="expression" dxfId="25" priority="26">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F67:F68">
-    <cfRule type="expression" dxfId="23" priority="23">
+    <cfRule type="expression" dxfId="24" priority="23">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A67:E67 A68">
-    <cfRule type="expression" dxfId="22" priority="22">
+    <cfRule type="expression" dxfId="23" priority="22">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68:E68">
-    <cfRule type="expression" dxfId="21" priority="21">
+    <cfRule type="expression" dxfId="22" priority="21">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9:E9">
-    <cfRule type="expression" dxfId="20" priority="20">
+    <cfRule type="expression" dxfId="21" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12:B12 D12:E12">
-    <cfRule type="expression" dxfId="19" priority="19">
+    <cfRule type="expression" dxfId="20" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C12">
-    <cfRule type="expression" dxfId="18" priority="18">
+    <cfRule type="expression" dxfId="19" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y12:Z12 G12:O12">
-    <cfRule type="expression" dxfId="17" priority="17">
+    <cfRule type="expression" dxfId="18" priority="17">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V12:W12">
-    <cfRule type="expression" dxfId="16" priority="16">
+    <cfRule type="expression" dxfId="17" priority="16">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R12">
-    <cfRule type="expression" dxfId="15" priority="13">
+    <cfRule type="expression" dxfId="16" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R12">
-    <cfRule type="expression" dxfId="14" priority="12">
+    <cfRule type="expression" dxfId="15" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S12:U12">
-    <cfRule type="expression" dxfId="13" priority="10">
+    <cfRule type="expression" dxfId="14" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N12:O12">
-    <cfRule type="expression" dxfId="12" priority="15">
+    <cfRule type="expression" dxfId="13" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M12:O12">
-    <cfRule type="expression" dxfId="11" priority="14">
+    <cfRule type="expression" dxfId="12" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T12:U12">
-    <cfRule type="expression" dxfId="10" priority="11">
+    <cfRule type="expression" dxfId="11" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q12">
-    <cfRule type="expression" dxfId="9" priority="9">
+    <cfRule type="expression" dxfId="10" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P12:Q12">
-    <cfRule type="expression" dxfId="8" priority="8">
+    <cfRule type="expression" dxfId="9" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A54:C54 E54:F54">
-    <cfRule type="expression" dxfId="7" priority="7">
+    <cfRule type="expression" dxfId="8" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P54:Q54">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D54">
-    <cfRule type="expression" dxfId="5" priority="5">
+    <cfRule type="expression" dxfId="6" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W54 R54:U54 G54:O54 Y54:Z54">
-    <cfRule type="expression" dxfId="4" priority="4">
+    <cfRule type="expression" dxfId="5" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V54">
-    <cfRule type="expression" dxfId="3" priority="3">
+    <cfRule type="expression" dxfId="4" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q54">
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Quant Strategy(2026-27).xlsx
+++ b/Quant Strategy(2026-27).xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2646" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2647" uniqueCount="322">
   <si>
     <t>Sudeep</t>
   </si>
@@ -2328,14 +2328,7 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="451">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="450">
     <dxf>
       <fill>
         <patternFill>
@@ -5817,7 +5810,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:W66"/>
+  <dimension ref="A1:X66"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" style="133" customWidth="1" outlineLevel="1"/>
@@ -5827,20 +5820,19 @@
     <col min="5" max="5" width="9.42578125" style="133" customWidth="1"/>
     <col min="6" max="6" width="6.5703125" style="133" customWidth="1"/>
     <col min="7" max="7" width="1.7109375" style="133" customWidth="1"/>
-    <col min="8" max="9" width="13.42578125" style="133" customWidth="1" outlineLevel="1"/>
-    <col min="10" max="10" width="11.28515625" style="133" customWidth="1"/>
-    <col min="11" max="11" width="10.42578125" style="133" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="12" max="12" width="10.7109375" style="133" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="13" max="13" width="9.140625" style="133" collapsed="1"/>
-    <col min="14" max="18" width="9.140625" style="133"/>
-    <col min="19" max="19" width="14.140625" style="133" customWidth="1"/>
-    <col min="20" max="20" width="12" style="133" customWidth="1"/>
-    <col min="21" max="21" width="15.85546875" style="133" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="133"/>
+    <col min="8" max="10" width="13.42578125" style="133" customWidth="1" outlineLevel="1"/>
+    <col min="11" max="11" width="11.28515625" style="133" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" style="133" customWidth="1" outlineLevel="1"/>
+    <col min="13" max="13" width="10.7109375" style="133" customWidth="1" outlineLevel="1"/>
+    <col min="14" max="19" width="9.140625" style="133"/>
+    <col min="20" max="20" width="14.140625" style="133" customWidth="1"/>
+    <col min="21" max="21" width="12" style="133" customWidth="1"/>
+    <col min="22" max="22" width="15.85546875" style="133" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="133"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G2" s="221"/>
       <c r="H2" s="222">
         <v>46266</v>
@@ -5848,15 +5840,18 @@
       <c r="I2" s="256">
         <v>46267</v>
       </c>
-      <c r="J2" s="183"/>
-      <c r="K2" s="184" t="s">
+      <c r="J2" s="256">
+        <v>46268</v>
+      </c>
+      <c r="K2" s="183"/>
+      <c r="L2" s="184" t="s">
         <v>281</v>
       </c>
-      <c r="L2" s="185" t="s">
+      <c r="M2" s="185" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="186" t="s">
         <v>54</v>
       </c>
@@ -5882,17 +5877,20 @@
       <c r="I3" s="179" t="s">
         <v>237</v>
       </c>
-      <c r="J3" s="180"/>
-      <c r="K3" s="189"/>
-      <c r="L3" s="180"/>
-      <c r="S3" s="133" t="s">
+      <c r="J3" s="179" t="s">
+        <v>236</v>
+      </c>
+      <c r="K3" s="180"/>
+      <c r="L3" s="189"/>
+      <c r="M3" s="180"/>
+      <c r="T3" s="133" t="s">
         <v>198</v>
       </c>
-      <c r="T3" s="133">
+      <c r="U3" s="133">
         <v>13780</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="142" t="s">
         <v>216</v>
       </c>
@@ -5918,23 +5916,26 @@
       <c r="I4" s="158">
         <v>-13362</v>
       </c>
-      <c r="J4" s="211"/>
-      <c r="K4" s="171">
-        <f t="shared" ref="K4:K30" si="0">SUM(H4:J4)</f>
-        <v>-13362</v>
-      </c>
-      <c r="L4" s="149">
-        <f t="shared" ref="L4:L30" si="1">IFERROR(K4/F4*100,0)/10000000</f>
-        <v>-0.26723999999999998</v>
-      </c>
-      <c r="S4" s="133" t="s">
+      <c r="J4" s="158">
+        <v>1600</v>
+      </c>
+      <c r="K4" s="211"/>
+      <c r="L4" s="171">
+        <f t="shared" ref="L4:L30" si="0">SUM(H4:K4)</f>
+        <v>-11762</v>
+      </c>
+      <c r="M4" s="149">
+        <f t="shared" ref="M4:M30" si="1">IFERROR(L4/F4*100,0)/10000000</f>
+        <v>-0.23524</v>
+      </c>
+      <c r="T4" s="133" t="s">
         <v>170</v>
       </c>
-      <c r="T4" s="133">
+      <c r="U4" s="133">
         <v>2865</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="142" t="s">
         <v>30</v>
       </c>
@@ -5960,17 +5961,20 @@
       <c r="I5" s="147">
         <v>31407</v>
       </c>
-      <c r="J5" s="174"/>
-      <c r="K5" s="171">
+      <c r="J5" s="147">
+        <v>31240</v>
+      </c>
+      <c r="K5" s="174"/>
+      <c r="L5" s="171">
         <f t="shared" si="0"/>
-        <v>-139420</v>
-      </c>
-      <c r="L5" s="149">
+        <v>-108180</v>
+      </c>
+      <c r="M5" s="149">
         <f t="shared" si="1"/>
-        <v>-0.46473333333333339</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+        <v>-0.36059999999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="142" t="s">
         <v>177</v>
       </c>
@@ -5996,17 +6000,20 @@
       <c r="I6" s="147">
         <v>0</v>
       </c>
-      <c r="J6" s="174"/>
-      <c r="K6" s="171">
+      <c r="J6" s="147">
+        <v>0</v>
+      </c>
+      <c r="K6" s="174"/>
+      <c r="L6" s="171">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L6" s="149">
+      <c r="M6" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="142"/>
       <c r="B7" s="141" t="s">
         <v>309</v>
@@ -6030,17 +6037,20 @@
       <c r="I7" s="147">
         <v>13000</v>
       </c>
-      <c r="J7" s="174"/>
-      <c r="K7" s="171">
+      <c r="J7" s="147">
+        <v>0</v>
+      </c>
+      <c r="K7" s="174"/>
+      <c r="L7" s="171">
         <f t="shared" si="0"/>
         <v>-44700</v>
       </c>
-      <c r="L7" s="149">
+      <c r="M7" s="149">
         <f t="shared" si="1"/>
         <v>-0.44700000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="142" t="s">
         <v>134</v>
       </c>
@@ -6066,21 +6076,24 @@
       <c r="I8" s="147">
         <v>-26565</v>
       </c>
-      <c r="J8" s="174"/>
-      <c r="K8" s="171">
+      <c r="J8" s="147">
+        <v>-45278</v>
+      </c>
+      <c r="K8" s="174"/>
+      <c r="L8" s="171">
         <f t="shared" si="0"/>
-        <v>153035</v>
-      </c>
-      <c r="L8" s="149">
+        <v>107757</v>
+      </c>
+      <c r="M8" s="149">
         <f t="shared" si="1"/>
-        <v>0.51011666666666655</v>
-      </c>
-      <c r="N8" s="5"/>
-      <c r="O8" s="134">
-        <v>-2106</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+        <v>0.35919000000000001</v>
+      </c>
+      <c r="O8" s="5"/>
+      <c r="P8" s="134">
+        <v>-153157</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="142" t="s">
         <v>217</v>
       </c>
@@ -6106,21 +6119,24 @@
       <c r="I9" s="147">
         <v>-14500</v>
       </c>
-      <c r="J9" s="174"/>
-      <c r="K9" s="171">
+      <c r="J9" s="147">
+        <v>36650</v>
+      </c>
+      <c r="K9" s="174"/>
+      <c r="L9" s="171">
         <f t="shared" si="0"/>
-        <v>44898</v>
-      </c>
-      <c r="L9" s="149">
+        <v>81548</v>
+      </c>
+      <c r="M9" s="149">
         <f t="shared" si="1"/>
-        <v>0.29931999999999997</v>
-      </c>
-      <c r="N9" s="134">
-        <v>494669</v>
-      </c>
-      <c r="O9" s="134"/>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+        <v>0.54365333333333343</v>
+      </c>
+      <c r="O9" s="134">
+        <v>2843927</v>
+      </c>
+      <c r="P9" s="134"/>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="142" t="s">
         <v>313</v>
       </c>
@@ -6144,24 +6160,27 @@
       <c r="I10" s="147">
         <v>-21600</v>
       </c>
-      <c r="J10" s="174"/>
-      <c r="K10" s="171">
+      <c r="J10" s="147">
+        <v>21640</v>
+      </c>
+      <c r="K10" s="174"/>
+      <c r="L10" s="171">
         <f t="shared" si="0"/>
-        <v>-13366</v>
-      </c>
-      <c r="L10" s="149">
+        <v>8274</v>
+      </c>
+      <c r="M10" s="149">
         <f t="shared" si="1"/>
-        <v>-0.2227666666666667</v>
-      </c>
-      <c r="N10" s="134">
-        <v>492563</v>
+        <v>0.13789999999999999</v>
       </c>
       <c r="O10" s="134">
-        <f>(N10+N9)/10000000*13780</f>
-        <v>1360.405696</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+        <v>2690770</v>
+      </c>
+      <c r="P10" s="134">
+        <f>(O10+O9)/10000000*13780</f>
+        <v>7626.8124659999994</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="143" t="s">
         <v>35</v>
       </c>
@@ -6187,19 +6206,22 @@
       <c r="I11" s="147">
         <v>0</v>
       </c>
-      <c r="J11" s="174"/>
-      <c r="K11" s="171">
+      <c r="J11" s="147">
+        <v>0</v>
+      </c>
+      <c r="K11" s="174"/>
+      <c r="L11" s="171">
         <f t="shared" si="0"/>
         <v>-413740</v>
       </c>
-      <c r="L11" s="149">
+      <c r="M11" s="149">
         <f t="shared" si="1"/>
         <v>-0.27582666666666672</v>
       </c>
-      <c r="N11" s="134"/>
       <c r="O11" s="134"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="P11" s="134"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="143" t="s">
         <v>137</v>
       </c>
@@ -6225,19 +6247,22 @@
       <c r="I12" s="147">
         <v>50</v>
       </c>
-      <c r="J12" s="174"/>
-      <c r="K12" s="171">
+      <c r="J12" s="147">
+        <v>-50942</v>
+      </c>
+      <c r="K12" s="174"/>
+      <c r="L12" s="171">
         <f t="shared" si="0"/>
-        <v>-61193</v>
-      </c>
-      <c r="L12" s="149">
+        <v>-112135</v>
+      </c>
+      <c r="M12" s="149">
         <f t="shared" si="1"/>
-        <v>-0.10198833333333333</v>
-      </c>
-      <c r="N12" s="134"/>
+        <v>-0.18689166666666668</v>
+      </c>
       <c r="O12" s="134"/>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="P12" s="134"/>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="143" t="s">
         <v>42</v>
       </c>
@@ -6263,19 +6288,22 @@
       <c r="I13" s="147">
         <v>-2649</v>
       </c>
-      <c r="J13" s="174"/>
-      <c r="K13" s="171">
+      <c r="J13" s="147">
+        <v>3000</v>
+      </c>
+      <c r="K13" s="174"/>
+      <c r="L13" s="171">
         <f t="shared" si="0"/>
-        <v>-7107</v>
-      </c>
-      <c r="L13" s="149">
+        <v>-4107</v>
+      </c>
+      <c r="M13" s="149">
         <f t="shared" si="1"/>
-        <v>-7.1069999999999994E-2</v>
-      </c>
-      <c r="N13" s="134"/>
+        <v>-4.1070000000000002E-2</v>
+      </c>
       <c r="O13" s="134"/>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="P13" s="134"/>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="142" t="s">
         <v>212</v>
       </c>
@@ -6301,19 +6329,22 @@
       <c r="I14" s="147">
         <v>0</v>
       </c>
-      <c r="J14" s="174"/>
-      <c r="K14" s="171">
+      <c r="J14" s="147">
+        <v>-3828</v>
+      </c>
+      <c r="K14" s="174"/>
+      <c r="L14" s="171">
         <f t="shared" si="0"/>
-        <v>724</v>
-      </c>
-      <c r="L14" s="149">
+        <v>-3104</v>
+      </c>
+      <c r="M14" s="149">
         <f t="shared" si="1"/>
-        <v>2.8960000000000006E-3</v>
-      </c>
-      <c r="N14" s="134"/>
+        <v>-1.2415999999999998E-2</v>
+      </c>
       <c r="O14" s="134"/>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="P14" s="134"/>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="142" t="s">
         <v>51</v>
       </c>
@@ -6339,29 +6370,32 @@
       <c r="I15" s="147">
         <v>0</v>
       </c>
-      <c r="J15" s="174"/>
-      <c r="K15" s="171">
+      <c r="J15" s="147">
+        <v>-100</v>
+      </c>
+      <c r="K15" s="174"/>
+      <c r="L15" s="171">
         <f t="shared" si="0"/>
-        <v>-4897</v>
-      </c>
-      <c r="L15" s="149">
+        <v>-4997</v>
+      </c>
+      <c r="M15" s="149">
         <f t="shared" si="1"/>
-        <v>-2.2259090909090905E-2</v>
-      </c>
-      <c r="N15" s="134"/>
-      <c r="O15" s="193">
-        <f>O8-O10</f>
-        <v>-3466.4056959999998</v>
-      </c>
-      <c r="R15" s="133">
+        <v>-2.2713636363636359E-2</v>
+      </c>
+      <c r="O15" s="134"/>
+      <c r="P15" s="193">
+        <f>P8-P10</f>
+        <v>-160783.812466</v>
+      </c>
+      <c r="S15" s="133">
         <v>116185</v>
       </c>
-      <c r="T15" s="133">
-        <f>R15+O15</f>
-        <v>112718.594304</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U15" s="133">
+        <f>S15+P15</f>
+        <v>-44598.812466000003</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="142" t="s">
         <v>43</v>
       </c>
@@ -6387,17 +6421,20 @@
       <c r="I16" s="147">
         <v>-3245</v>
       </c>
-      <c r="J16" s="174"/>
-      <c r="K16" s="171">
+      <c r="J16" s="147">
+        <v>7937</v>
+      </c>
+      <c r="K16" s="174"/>
+      <c r="L16" s="171">
         <f t="shared" si="0"/>
-        <v>-14358</v>
-      </c>
-      <c r="L16" s="149">
+        <v>-6421</v>
+      </c>
+      <c r="M16" s="149">
         <f t="shared" si="1"/>
-        <v>-0.14358000000000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+        <v>-6.4210000000000003E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" s="142" t="s">
         <v>24</v>
       </c>
@@ -6423,28 +6460,31 @@
       <c r="I17" s="147">
         <v>0</v>
       </c>
-      <c r="J17" s="174"/>
-      <c r="K17" s="171">
+      <c r="J17" s="147">
+        <v>0</v>
+      </c>
+      <c r="K17" s="174"/>
+      <c r="L17" s="171">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L17" s="149">
+      <c r="M17" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="T17" s="133">
+      <c r="U17" s="133">
         <v>4000000</v>
       </c>
-      <c r="U17" s="133">
-        <f>T17*7/100</f>
+      <c r="V17" s="133">
+        <f>U17*7/100</f>
         <v>280000</v>
       </c>
-      <c r="W17" s="133">
+      <c r="X17" s="133">
         <f>15*12</f>
         <v>180</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" s="142" t="s">
         <v>23</v>
       </c>
@@ -6470,21 +6510,24 @@
       <c r="I18" s="147">
         <v>0</v>
       </c>
-      <c r="J18" s="174"/>
-      <c r="K18" s="171">
+      <c r="J18" s="147">
+        <v>0</v>
+      </c>
+      <c r="K18" s="174"/>
+      <c r="L18" s="171">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L18" s="149">
+      <c r="M18" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="U18" s="133">
-        <f>U17/12</f>
+      <c r="V18" s="133">
+        <f>V17/12</f>
         <v>23333.333333333332</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" s="142" t="s">
         <v>165</v>
       </c>
@@ -6510,17 +6553,20 @@
       <c r="I19" s="147">
         <v>-31966</v>
       </c>
-      <c r="J19" s="174"/>
-      <c r="K19" s="171">
+      <c r="J19" s="147">
+        <v>17400</v>
+      </c>
+      <c r="K19" s="174"/>
+      <c r="L19" s="171">
         <f t="shared" si="0"/>
-        <v>-14466</v>
-      </c>
-      <c r="L19" s="149">
+        <v>2934</v>
+      </c>
+      <c r="M19" s="149">
         <f t="shared" si="1"/>
-        <v>-9.6439999999999998E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+        <v>1.9560000000000001E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" s="142" t="s">
         <v>110</v>
       </c>
@@ -6546,17 +6592,20 @@
       <c r="I20" s="147">
         <v>0</v>
       </c>
-      <c r="J20" s="174"/>
-      <c r="K20" s="171">
+      <c r="J20" s="147">
+        <v>-11491</v>
+      </c>
+      <c r="K20" s="174"/>
+      <c r="L20" s="171">
         <f t="shared" si="0"/>
-        <v>9433</v>
-      </c>
-      <c r="L20" s="149">
+        <v>-2058</v>
+      </c>
+      <c r="M20" s="149">
         <f t="shared" si="1"/>
-        <v>8.5754545454545431E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
+        <v>-1.8709090909090908E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" s="142" t="s">
         <v>319</v>
       </c>
@@ -6582,17 +6631,20 @@
       <c r="I21" s="147">
         <v>-3466</v>
       </c>
-      <c r="J21" s="174"/>
-      <c r="K21" s="171">
+      <c r="J21" s="147">
+        <v>2500</v>
+      </c>
+      <c r="K21" s="174"/>
+      <c r="L21" s="171">
         <f t="shared" si="0"/>
-        <v>1271</v>
-      </c>
-      <c r="L21" s="149">
+        <v>3771</v>
+      </c>
+      <c r="M21" s="149">
         <f t="shared" si="1"/>
-        <v>5.0840000000000003E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
+        <v>0.15084</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" s="142" t="s">
         <v>316</v>
       </c>
@@ -6618,17 +6670,20 @@
       <c r="I22" s="147">
         <v>6953</v>
       </c>
-      <c r="J22" s="174"/>
-      <c r="K22" s="171">
+      <c r="J22" s="147">
+        <v>2574</v>
+      </c>
+      <c r="K22" s="174"/>
+      <c r="L22" s="171">
         <f t="shared" si="0"/>
-        <v>5905</v>
-      </c>
-      <c r="L22" s="149">
+        <v>8479</v>
+      </c>
+      <c r="M22" s="149">
         <f t="shared" si="1"/>
-        <v>2.9524999999999999E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
+        <v>4.2395000000000002E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" s="142" t="s">
         <v>317</v>
       </c>
@@ -6652,17 +6707,20 @@
       <c r="I23" s="147">
         <v>0</v>
       </c>
-      <c r="J23" s="174"/>
-      <c r="K23" s="171">
+      <c r="J23" s="147">
+        <v>0</v>
+      </c>
+      <c r="K23" s="174"/>
+      <c r="L23" s="171">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L23" s="149">
+      <c r="M23" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" s="142" t="s">
         <v>32</v>
       </c>
@@ -6688,17 +6746,20 @@
       <c r="I24" s="147">
         <v>700</v>
       </c>
-      <c r="J24" s="174"/>
-      <c r="K24" s="171">
+      <c r="J24" s="147">
+        <v>6060</v>
+      </c>
+      <c r="K24" s="174"/>
+      <c r="L24" s="171">
         <f t="shared" si="0"/>
-        <v>9908</v>
-      </c>
-      <c r="L24" s="149">
+        <v>15968</v>
+      </c>
+      <c r="M24" s="149">
         <f t="shared" si="1"/>
-        <v>9.0072727272727263E-2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
+        <v>0.14516363636363636</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" s="142" t="s">
         <v>97</v>
       </c>
@@ -6724,17 +6785,20 @@
       <c r="I25" s="147">
         <v>-162700</v>
       </c>
-      <c r="J25" s="174"/>
-      <c r="K25" s="171">
+      <c r="J25" s="147">
+        <v>-200</v>
+      </c>
+      <c r="K25" s="174"/>
+      <c r="L25" s="171">
         <f t="shared" si="0"/>
-        <v>-406700</v>
-      </c>
-      <c r="L25" s="149">
+        <v>-406900</v>
+      </c>
+      <c r="M25" s="149">
         <f t="shared" si="1"/>
-        <v>-1.7682608695652176</v>
-      </c>
-    </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
+        <v>-1.7691304347826089</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" s="142" t="s">
         <v>302</v>
       </c>
@@ -6758,17 +6822,20 @@
       <c r="I26" s="147">
         <v>2038</v>
       </c>
-      <c r="J26" s="174"/>
-      <c r="K26" s="171">
+      <c r="J26" s="147">
+        <v>1257</v>
+      </c>
+      <c r="K26" s="174"/>
+      <c r="L26" s="171">
         <f t="shared" si="0"/>
-        <v>3803</v>
-      </c>
-      <c r="L26" s="149">
+        <v>5060</v>
+      </c>
+      <c r="M26" s="149">
         <f t="shared" si="1"/>
-        <v>0.19015000000000001</v>
-      </c>
-    </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
+        <v>0.253</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" s="142" t="s">
         <v>29</v>
       </c>
@@ -6794,17 +6861,20 @@
       <c r="I27" s="147">
         <v>0</v>
       </c>
-      <c r="J27" s="174"/>
-      <c r="K27" s="171">
+      <c r="J27" s="147">
+        <v>0</v>
+      </c>
+      <c r="K27" s="174"/>
+      <c r="L27" s="171">
         <f t="shared" si="0"/>
         <v>39000</v>
       </c>
-      <c r="L27" s="149">
+      <c r="M27" s="149">
         <f t="shared" si="1"/>
         <v>7.8E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" s="142" t="s">
         <v>28</v>
       </c>
@@ -6830,17 +6900,20 @@
       <c r="I28" s="147">
         <v>-102505</v>
       </c>
-      <c r="J28" s="174"/>
-      <c r="K28" s="171">
+      <c r="J28" s="147">
+        <v>184400</v>
+      </c>
+      <c r="K28" s="174"/>
+      <c r="L28" s="171">
         <f t="shared" si="0"/>
-        <v>-111645</v>
-      </c>
-      <c r="L28" s="149">
+        <v>72755</v>
+      </c>
+      <c r="M28" s="149">
         <f t="shared" si="1"/>
-        <v>-0.11164499999999999</v>
-      </c>
-    </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
+        <v>7.2755E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" s="142" t="s">
         <v>65</v>
       </c>
@@ -6866,17 +6939,20 @@
       <c r="I29" s="147">
         <v>0</v>
       </c>
-      <c r="J29" s="174"/>
-      <c r="K29" s="171">
+      <c r="J29" s="147">
+        <v>-20000</v>
+      </c>
+      <c r="K29" s="174"/>
+      <c r="L29" s="171">
         <f t="shared" si="0"/>
-        <v>-455000</v>
-      </c>
-      <c r="L29" s="149">
+        <v>-475000</v>
+      </c>
+      <c r="M29" s="149">
         <f t="shared" si="1"/>
-        <v>-0.91</v>
-      </c>
-    </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
+        <v>-0.95</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" s="141" t="s">
         <v>34</v>
       </c>
@@ -6902,17 +6978,20 @@
       <c r="I30" s="147">
         <v>3891</v>
       </c>
-      <c r="J30" s="174"/>
-      <c r="K30" s="171">
+      <c r="J30" s="147">
+        <v>-135</v>
+      </c>
+      <c r="K30" s="174"/>
+      <c r="L30" s="171">
         <f t="shared" si="0"/>
-        <v>-172772</v>
-      </c>
-      <c r="L30" s="149">
+        <v>-172907</v>
+      </c>
+      <c r="M30" s="149">
         <f t="shared" si="1"/>
-        <v>-0.34554400000000002</v>
-      </c>
-    </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
+        <v>-0.34581400000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" s="141" t="s">
         <v>131</v>
       </c>
@@ -6938,17 +7017,20 @@
       <c r="I31" s="147">
         <v>-42207</v>
       </c>
-      <c r="J31" s="174"/>
-      <c r="K31" s="171">
-        <f t="shared" ref="K31:K56" si="2">SUM(H31:J31)</f>
-        <v>-79747</v>
-      </c>
-      <c r="L31" s="149">
-        <f t="shared" ref="L31:L56" si="3">IFERROR(K31/F31*100,0)/10000000</f>
-        <v>-1.59494</v>
-      </c>
-    </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="J31" s="147">
+        <v>-18371</v>
+      </c>
+      <c r="K31" s="174"/>
+      <c r="L31" s="171">
+        <f t="shared" ref="L31:L56" si="2">SUM(H31:K31)</f>
+        <v>-98118</v>
+      </c>
+      <c r="M31" s="149">
+        <f t="shared" ref="M31:M56" si="3">IFERROR(L31/F31*100,0)/10000000</f>
+        <v>-1.9623600000000001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32" s="43" t="s">
         <v>67</v>
       </c>
@@ -6974,18 +7056,21 @@
       <c r="I32" s="147">
         <v>9510</v>
       </c>
-      <c r="J32" s="174"/>
-      <c r="K32" s="171">
+      <c r="J32" s="147">
+        <v>-924</v>
+      </c>
+      <c r="K32" s="174"/>
+      <c r="L32" s="171">
         <f t="shared" si="2"/>
-        <v>9510</v>
-      </c>
-      <c r="L32" s="149">
+        <v>8586</v>
+      </c>
+      <c r="M32" s="149">
         <f t="shared" si="3"/>
-        <v>0.23774999999999999</v>
-      </c>
-      <c r="O32" s="134"/>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+        <v>0.21465000000000001</v>
+      </c>
+      <c r="P32" s="134"/>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="43" t="s">
         <v>143</v>
       </c>
@@ -7011,21 +7096,24 @@
       <c r="I33" s="147">
         <v>0</v>
       </c>
-      <c r="J33" s="174"/>
-      <c r="K33" s="171">
+      <c r="J33" s="147">
+        <v>0</v>
+      </c>
+      <c r="K33" s="174"/>
+      <c r="L33" s="171">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L33" s="149">
+      <c r="M33" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N33" s="5"/>
-      <c r="O33" s="134">
-        <v>-25594</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O33" s="5"/>
+      <c r="P33" s="134">
+        <v>6971</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="43" t="s">
         <v>144</v>
       </c>
@@ -7051,19 +7139,22 @@
       <c r="I34" s="147">
         <v>0</v>
       </c>
-      <c r="J34" s="174"/>
-      <c r="K34" s="171">
+      <c r="J34" s="147">
+        <v>0</v>
+      </c>
+      <c r="K34" s="174"/>
+      <c r="L34" s="171">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L34" s="149">
+      <c r="M34" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N34" s="5"/>
-      <c r="O34" s="134"/>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O34" s="5"/>
+      <c r="P34" s="134"/>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="142" t="s">
         <v>31</v>
       </c>
@@ -7089,24 +7180,27 @@
       <c r="I35" s="147">
         <v>-88146</v>
       </c>
-      <c r="J35" s="174"/>
-      <c r="K35" s="171">
+      <c r="J35" s="147">
+        <v>49649</v>
+      </c>
+      <c r="K35" s="174"/>
+      <c r="L35" s="171">
         <f t="shared" si="2"/>
-        <v>-133901</v>
-      </c>
-      <c r="L35" s="149">
+        <v>-84252</v>
+      </c>
+      <c r="M35" s="149">
         <f t="shared" si="3"/>
-        <v>-0.33475250000000001</v>
-      </c>
-      <c r="N35" s="134">
-        <v>1045608</v>
+        <v>-0.21063000000000001</v>
       </c>
       <c r="O35" s="134">
-        <f>(N36+N35)/10000000*13780</f>
-        <v>2846.4271159999998</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+        <v>327210</v>
+      </c>
+      <c r="P35" s="134">
+        <f>(O36+O35)/10000000*13780</f>
+        <v>911.3967980000001</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="142" t="s">
         <v>104</v>
       </c>
@@ -7132,21 +7226,24 @@
       <c r="I36" s="147">
         <v>-23605</v>
       </c>
-      <c r="J36" s="174"/>
-      <c r="K36" s="171">
+      <c r="J36" s="147">
+        <v>47158</v>
+      </c>
+      <c r="K36" s="174"/>
+      <c r="L36" s="171">
         <f t="shared" si="2"/>
-        <v>-54575</v>
-      </c>
-      <c r="L36" s="149">
+        <v>-7417</v>
+      </c>
+      <c r="M36" s="149">
         <f t="shared" si="3"/>
-        <v>-0.54574999999999996</v>
-      </c>
-      <c r="N36" s="134">
-        <v>1020014</v>
-      </c>
-      <c r="O36" s="134"/>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+        <v>-7.417E-2</v>
+      </c>
+      <c r="O36" s="134">
+        <v>334181</v>
+      </c>
+      <c r="P36" s="134"/>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="142" t="s">
         <v>314</v>
       </c>
@@ -7170,22 +7267,25 @@
       <c r="I37" s="147">
         <v>0</v>
       </c>
-      <c r="J37" s="174"/>
-      <c r="K37" s="171">
+      <c r="J37" s="147">
+        <v>0</v>
+      </c>
+      <c r="K37" s="174"/>
+      <c r="L37" s="171">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L37" s="149">
+      <c r="M37" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N37" s="134"/>
-      <c r="O37" s="134">
-        <f>+O33-O35</f>
-        <v>-28440.427115999999</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O37" s="134"/>
+      <c r="P37" s="134">
+        <f>+P33-P35</f>
+        <v>6059.6032020000002</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" s="142" t="s">
         <v>229</v>
       </c>
@@ -7211,19 +7311,22 @@
       <c r="I38" s="147">
         <v>-13160</v>
       </c>
-      <c r="J38" s="174"/>
-      <c r="K38" s="171">
+      <c r="J38" s="147">
+        <v>-15600</v>
+      </c>
+      <c r="K38" s="174"/>
+      <c r="L38" s="171">
         <f t="shared" si="2"/>
-        <v>-13160</v>
-      </c>
-      <c r="L38" s="149">
+        <v>-28760</v>
+      </c>
+      <c r="M38" s="149">
         <f t="shared" si="3"/>
-        <v>-0.26319999999999999</v>
-      </c>
-      <c r="N38" s="134"/>
+        <v>-0.57520000000000004</v>
+      </c>
       <c r="O38" s="134"/>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P38" s="134"/>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" s="142" t="s">
         <v>52</v>
       </c>
@@ -7249,19 +7352,22 @@
       <c r="I39" s="147">
         <v>0</v>
       </c>
-      <c r="J39" s="174"/>
-      <c r="K39" s="171">
+      <c r="J39" s="147">
+        <v>0</v>
+      </c>
+      <c r="K39" s="174"/>
+      <c r="L39" s="171">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L39" s="149">
+      <c r="M39" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N39" s="134"/>
       <c r="O39" s="134"/>
-    </row>
-    <row r="40" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P39" s="134"/>
+    </row>
+    <row r="40" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="142" t="s">
         <v>45</v>
       </c>
@@ -7287,19 +7393,22 @@
       <c r="I40" s="147">
         <v>12600</v>
       </c>
-      <c r="J40" s="174"/>
-      <c r="K40" s="171">
+      <c r="J40" s="147">
+        <v>2300</v>
+      </c>
+      <c r="K40" s="174"/>
+      <c r="L40" s="171">
         <f t="shared" si="2"/>
-        <v>-58706</v>
-      </c>
-      <c r="L40" s="149">
+        <v>-56406</v>
+      </c>
+      <c r="M40" s="149">
         <f t="shared" si="3"/>
-        <v>-0.19568666666666668</v>
-      </c>
-      <c r="N40" s="134"/>
+        <v>-0.18801999999999999</v>
+      </c>
       <c r="O40" s="134"/>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P40" s="134"/>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" s="142" t="s">
         <v>292</v>
       </c>
@@ -7323,18 +7432,21 @@
       <c r="I41" s="147">
         <v>-9266</v>
       </c>
-      <c r="J41" s="174"/>
-      <c r="K41" s="171">
+      <c r="J41" s="147">
+        <v>-1079</v>
+      </c>
+      <c r="K41" s="174"/>
+      <c r="L41" s="171">
         <f t="shared" si="2"/>
-        <v>21424</v>
-      </c>
-      <c r="L41" s="149">
+        <v>20345</v>
+      </c>
+      <c r="M41" s="149">
         <f t="shared" si="3"/>
-        <v>2.1423999999999999</v>
-      </c>
-      <c r="N41" s="134"/>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.0345</v>
+      </c>
+      <c r="O41" s="134"/>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" s="142" t="s">
         <v>132</v>
       </c>
@@ -7360,17 +7472,20 @@
       <c r="I42" s="147">
         <v>-3990</v>
       </c>
-      <c r="J42" s="174"/>
-      <c r="K42" s="171">
+      <c r="J42" s="147">
+        <v>6275</v>
+      </c>
+      <c r="K42" s="174"/>
+      <c r="L42" s="171">
         <f t="shared" si="2"/>
-        <v>-3990</v>
-      </c>
-      <c r="L42" s="149">
+        <v>2285</v>
+      </c>
+      <c r="M42" s="149">
         <f t="shared" si="3"/>
-        <v>-7.9799999999999996E-2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+        <v>4.5699999999999998E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" s="142" t="s">
         <v>48</v>
       </c>
@@ -7396,17 +7511,20 @@
       <c r="I43" s="147">
         <v>-66367</v>
       </c>
-      <c r="J43" s="174"/>
-      <c r="K43" s="171">
+      <c r="J43" s="147">
+        <v>80500</v>
+      </c>
+      <c r="K43" s="174"/>
+      <c r="L43" s="171">
         <f t="shared" si="2"/>
-        <v>-116067</v>
-      </c>
-      <c r="L43" s="149">
+        <v>-35567</v>
+      </c>
+      <c r="M43" s="149">
         <f t="shared" si="3"/>
-        <v>-1.1606700000000001</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+        <v>-0.35566999999999999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" s="142" t="s">
         <v>301</v>
       </c>
@@ -7430,17 +7548,20 @@
       <c r="I44" s="147">
         <v>-4040</v>
       </c>
-      <c r="J44" s="174"/>
-      <c r="K44" s="171">
+      <c r="J44" s="147">
+        <v>3264</v>
+      </c>
+      <c r="K44" s="174"/>
+      <c r="L44" s="171">
         <f t="shared" si="2"/>
-        <v>3216</v>
-      </c>
-      <c r="L44" s="149">
+        <v>6480</v>
+      </c>
+      <c r="M44" s="149">
         <f t="shared" si="3"/>
-        <v>0.3216</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+        <v>0.64800000000000002</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" s="143" t="s">
         <v>168</v>
       </c>
@@ -7466,17 +7587,20 @@
       <c r="I45" s="147">
         <v>5133</v>
       </c>
-      <c r="J45" s="174"/>
-      <c r="K45" s="171">
+      <c r="J45" s="147">
+        <v>-161258</v>
+      </c>
+      <c r="K45" s="174"/>
+      <c r="L45" s="171">
         <f t="shared" si="2"/>
-        <v>5133</v>
-      </c>
-      <c r="L45" s="149">
+        <v>-156125</v>
+      </c>
+      <c r="M45" s="149">
         <f t="shared" si="3"/>
-        <v>1.28325E-2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+        <v>-0.39031250000000001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" s="143" t="s">
         <v>202</v>
       </c>
@@ -7502,17 +7626,20 @@
       <c r="I46" s="147">
         <v>-1041</v>
       </c>
-      <c r="J46" s="174"/>
-      <c r="K46" s="171">
+      <c r="J46" s="147">
+        <v>5300</v>
+      </c>
+      <c r="K46" s="174"/>
+      <c r="L46" s="171">
         <f t="shared" si="2"/>
-        <v>25959</v>
-      </c>
-      <c r="L46" s="149">
+        <v>31259</v>
+      </c>
+      <c r="M46" s="149">
         <f t="shared" si="3"/>
-        <v>6.4897499999999997E-2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+        <v>7.8147499999999995E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" s="143" t="s">
         <v>33</v>
       </c>
@@ -7538,17 +7665,20 @@
       <c r="I47" s="147">
         <v>-61960</v>
       </c>
-      <c r="J47" s="174"/>
-      <c r="K47" s="171">
+      <c r="J47" s="147">
+        <v>79536</v>
+      </c>
+      <c r="K47" s="174"/>
+      <c r="L47" s="171">
         <f t="shared" si="2"/>
-        <v>-46872</v>
-      </c>
-      <c r="L47" s="149">
+        <v>32664</v>
+      </c>
+      <c r="M47" s="149">
         <f t="shared" si="3"/>
-        <v>-0.15623999999999999</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+        <v>0.10888</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48" s="59" t="s">
         <v>306</v>
       </c>
@@ -7572,17 +7702,20 @@
       <c r="I48" s="151">
         <v>64400</v>
       </c>
-      <c r="J48" s="174"/>
-      <c r="K48" s="171">
+      <c r="J48" s="151">
+        <v>-30800</v>
+      </c>
+      <c r="K48" s="174"/>
+      <c r="L48" s="171">
         <f t="shared" si="2"/>
-        <v>-340700</v>
-      </c>
-      <c r="L48" s="149">
+        <v>-371500</v>
+      </c>
+      <c r="M48" s="149">
         <f t="shared" si="3"/>
-        <v>-0.3407</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+        <v>-0.3715</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="59" t="s">
         <v>320</v>
       </c>
@@ -7604,17 +7737,20 @@
       <c r="I49" s="151">
         <v>0</v>
       </c>
-      <c r="J49" s="174"/>
-      <c r="K49" s="171">
+      <c r="J49" s="151">
+        <v>0</v>
+      </c>
+      <c r="K49" s="174"/>
+      <c r="L49" s="171">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L49" s="149">
+      <c r="M49" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="59" t="s">
         <v>197</v>
       </c>
@@ -7640,17 +7776,20 @@
       <c r="I50" s="151">
         <v>1824</v>
       </c>
-      <c r="J50" s="174"/>
-      <c r="K50" s="171">
+      <c r="J50" s="151">
+        <v>335</v>
+      </c>
+      <c r="K50" s="174"/>
+      <c r="L50" s="171">
         <f t="shared" si="2"/>
-        <v>14597</v>
-      </c>
-      <c r="L50" s="149">
+        <v>14932</v>
+      </c>
+      <c r="M50" s="149">
         <f t="shared" si="3"/>
-        <v>0.29193999999999998</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.29864000000000002</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="59" t="s">
         <v>213</v>
       </c>
@@ -7676,17 +7815,20 @@
       <c r="I51" s="151">
         <v>0</v>
       </c>
-      <c r="J51" s="174"/>
-      <c r="K51" s="171">
+      <c r="J51" s="151">
+        <v>0</v>
+      </c>
+      <c r="K51" s="174"/>
+      <c r="L51" s="171">
         <f t="shared" si="2"/>
         <v>-152273</v>
       </c>
-      <c r="L51" s="149">
+      <c r="M51" s="149">
         <f t="shared" si="3"/>
         <v>-0.23426615384615385</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="59" t="s">
         <v>214</v>
       </c>
@@ -7712,17 +7854,20 @@
       <c r="I52" s="151">
         <v>-28440</v>
       </c>
-      <c r="J52" s="174"/>
-      <c r="K52" s="171">
+      <c r="J52" s="151">
+        <v>-160784</v>
+      </c>
+      <c r="K52" s="174"/>
+      <c r="L52" s="171">
         <f t="shared" si="2"/>
-        <v>3048</v>
-      </c>
-      <c r="L52" s="149">
+        <v>-157736</v>
+      </c>
+      <c r="M52" s="149">
         <f t="shared" si="3"/>
-        <v>2.4383999999999999E-2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+        <v>-1.2618879999999999</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="59" t="s">
         <v>49</v>
       </c>
@@ -7748,17 +7893,20 @@
       <c r="I53" s="151">
         <v>0</v>
       </c>
-      <c r="J53" s="174"/>
-      <c r="K53" s="171">
+      <c r="J53" s="151">
+        <v>14450</v>
+      </c>
+      <c r="K53" s="174"/>
+      <c r="L53" s="171">
         <f t="shared" si="2"/>
-        <v>-121091</v>
-      </c>
-      <c r="L53" s="149">
+        <v>-106641</v>
+      </c>
+      <c r="M53" s="149">
         <f t="shared" si="3"/>
-        <v>-0.40363666666666664</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+        <v>-0.35547000000000001</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" s="59" t="s">
         <v>300</v>
       </c>
@@ -7782,17 +7930,20 @@
       <c r="I54" s="151">
         <v>9455</v>
       </c>
-      <c r="J54" s="174"/>
-      <c r="K54" s="171">
+      <c r="J54" s="151">
+        <v>13380</v>
+      </c>
+      <c r="K54" s="174"/>
+      <c r="L54" s="171">
         <f t="shared" si="2"/>
-        <v>-5245</v>
-      </c>
-      <c r="L54" s="149">
+        <v>8135</v>
+      </c>
+      <c r="M54" s="149">
         <f t="shared" si="3"/>
-        <v>-3.496666666666666E-2</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>5.4233333333333328E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="59" t="s">
         <v>288</v>
       </c>
@@ -7816,17 +7967,20 @@
       <c r="I55" s="151">
         <v>32229</v>
       </c>
-      <c r="J55" s="174"/>
-      <c r="K55" s="171">
+      <c r="J55" s="151">
+        <v>43947</v>
+      </c>
+      <c r="K55" s="174"/>
+      <c r="L55" s="171">
         <f t="shared" si="2"/>
-        <v>-1801</v>
-      </c>
-      <c r="L55" s="149">
+        <v>42146</v>
+      </c>
+      <c r="M55" s="149">
         <f t="shared" si="3"/>
-        <v>-3.6020000000000002E-3</v>
-      </c>
-    </row>
-    <row r="56" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>8.4292000000000006E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="24"/>
       <c r="B56" s="25"/>
       <c r="C56" s="26"/>
@@ -7844,18 +7998,22 @@
       </c>
       <c r="J56" s="254">
         <f>SUM(J4:J55)</f>
-        <v>0</v>
+        <v>141562</v>
       </c>
       <c r="K56" s="254">
+        <f>SUM(K4:K55)</f>
+        <v>0</v>
+      </c>
+      <c r="L56" s="254">
         <f t="shared" si="2"/>
-        <v>-2649990</v>
-      </c>
-      <c r="L56" s="255">
+        <v>-2508428</v>
+      </c>
+      <c r="M56" s="255">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:16" s="249" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:17" s="249" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="250"/>
       <c r="B57" s="250"/>
       <c r="C57" s="250"/>
@@ -7867,9 +8025,10 @@
       <c r="I57" s="250"/>
       <c r="J57" s="250"/>
       <c r="K57" s="250"/>
-      <c r="L57" s="252"/>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L57" s="250"/>
+      <c r="M57" s="252"/>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="202" t="s">
         <v>241</v>
       </c>
@@ -7895,18 +8054,21 @@
       <c r="I58" s="162">
         <v>0</v>
       </c>
-      <c r="J58" s="246"/>
-      <c r="K58" s="247">
-        <f>SUM(H58:J58)</f>
-        <v>-370080</v>
-      </c>
-      <c r="L58" s="248">
-        <f>IFERROR(K58/F58*100,0)/10000000</f>
-        <v>-1.2336</v>
-      </c>
-      <c r="O58" s="134"/>
-    </row>
-    <row r="59" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J58" s="162">
+        <v>-17480</v>
+      </c>
+      <c r="K58" s="246"/>
+      <c r="L58" s="247">
+        <f>SUM(H58:K58)</f>
+        <v>-387560</v>
+      </c>
+      <c r="M58" s="248">
+        <f>IFERROR(L58/F58*100,0)/10000000</f>
+        <v>-1.2918666666666667</v>
+      </c>
+      <c r="P58" s="134"/>
+    </row>
+    <row r="59" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="202" t="s">
         <v>273</v>
       </c>
@@ -7930,18 +8092,21 @@
       <c r="I59" s="162">
         <v>0</v>
       </c>
-      <c r="J59" s="174"/>
-      <c r="K59" s="171">
-        <f>SUM(H59:J59)</f>
+      <c r="J59" s="162">
+        <v>0</v>
+      </c>
+      <c r="K59" s="174"/>
+      <c r="L59" s="171">
+        <f>SUM(H59:K59)</f>
         <v>-246000</v>
       </c>
-      <c r="L59" s="149">
-        <f>IFERROR(K59/F59*100,0)/10000000</f>
-        <v>0</v>
-      </c>
-      <c r="N59" s="134"/>
-    </row>
-    <row r="60" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M59" s="149">
+        <f>IFERROR(L59/F59*100,0)/10000000</f>
+        <v>0</v>
+      </c>
+      <c r="O59" s="134"/>
+    </row>
+    <row r="60" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="200"/>
       <c r="B60" s="16"/>
       <c r="C60" s="16"/>
@@ -7959,130 +8124,134 @@
       </c>
       <c r="J60" s="170">
         <f>SUM(J58:J59)</f>
-        <v>0</v>
-      </c>
-      <c r="K60" s="254">
-        <f>SUM(H60:J60)</f>
-        <v>-616080</v>
-      </c>
-      <c r="L60" s="19"/>
-      <c r="N60" s="5"/>
-      <c r="O60" s="134"/>
-      <c r="P60" s="237"/>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="N61" s="134"/>
+        <v>-17480</v>
+      </c>
+      <c r="K60" s="170">
+        <f>SUM(K58:K59)</f>
+        <v>0</v>
+      </c>
+      <c r="L60" s="254">
+        <f>SUM(H60:K60)</f>
+        <v>-633560</v>
+      </c>
+      <c r="M60" s="19"/>
+      <c r="O60" s="5"/>
+      <c r="P60" s="134"/>
+      <c r="Q60" s="237"/>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="O61" s="134"/>
-      <c r="P61" s="237"/>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="N62" s="134"/>
+      <c r="P61" s="134"/>
+      <c r="Q61" s="237"/>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="O62" s="134"/>
-      <c r="P62" s="237"/>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="N63" s="134"/>
+      <c r="P62" s="134"/>
+      <c r="Q62" s="237"/>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="O63" s="134"/>
-      <c r="P63" s="237"/>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="N64" s="134"/>
+      <c r="P63" s="134"/>
+      <c r="Q63" s="237"/>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="O64" s="134"/>
-      <c r="P64" s="237"/>
-    </row>
-    <row r="65" spans="14:16" x14ac:dyDescent="0.25">
-      <c r="N65" s="134"/>
-      <c r="O65" s="237"/>
+      <c r="P64" s="134"/>
+      <c r="Q64" s="237"/>
+    </row>
+    <row r="65" spans="15:17" x14ac:dyDescent="0.25">
+      <c r="O65" s="134"/>
       <c r="P65" s="237"/>
-    </row>
-    <row r="66" spans="14:16" x14ac:dyDescent="0.25">
-      <c r="N66" s="237"/>
+      <c r="Q65" s="237"/>
+    </row>
+    <row r="66" spans="15:17" x14ac:dyDescent="0.25">
       <c r="O66" s="237"/>
       <c r="P66" s="237"/>
+      <c r="Q66" s="237"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G2 A3:G3 L56:L57 K55:L55 L60 K43:L43 K5:L10 K24:L25 H2:L3 A58:L59 A37:K37 L11:L21 K11:K22 K45:L53 K27:K36 L27:L35 A4:J36 K38:K41 A38:J39 G40:J40 A41:J56 A60:J60">
-    <cfRule type="expression" dxfId="450" priority="21">
+  <conditionalFormatting sqref="G2 A3:G3 M56:M57 L55:M55 M60 L43:M43 L5:M10 L24:M25 H2:M3 A58:M59 A37:L37 M11:M21 L11:L22 L45:M53 L27:L36 M27:M35 A4:K36 L38:L41 A38:K39 G40:K40 A41:K56 A60:K60">
+    <cfRule type="expression" dxfId="449" priority="21">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L36">
-    <cfRule type="expression" dxfId="449" priority="20">
+  <conditionalFormatting sqref="M36">
+    <cfRule type="expression" dxfId="448" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L39:L40">
-    <cfRule type="expression" dxfId="448" priority="19">
+  <conditionalFormatting sqref="M39:M40">
+    <cfRule type="expression" dxfId="447" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K4:L4">
-    <cfRule type="expression" dxfId="447" priority="18">
+  <conditionalFormatting sqref="L4:M4">
+    <cfRule type="expression" dxfId="446" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L38">
-    <cfRule type="expression" dxfId="446" priority="17">
+  <conditionalFormatting sqref="M38">
+    <cfRule type="expression" dxfId="445" priority="17">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L22">
-    <cfRule type="expression" dxfId="445" priority="14">
+  <conditionalFormatting sqref="M22">
+    <cfRule type="expression" dxfId="444" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K56">
-    <cfRule type="expression" dxfId="444" priority="13">
+  <conditionalFormatting sqref="L56">
+    <cfRule type="expression" dxfId="443" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L41">
-    <cfRule type="expression" dxfId="443" priority="12">
+  <conditionalFormatting sqref="M41">
+    <cfRule type="expression" dxfId="442" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K26:L26">
-    <cfRule type="expression" dxfId="442" priority="11">
+  <conditionalFormatting sqref="L26:M26">
+    <cfRule type="expression" dxfId="441" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K54:L54">
-    <cfRule type="expression" dxfId="441" priority="10">
+  <conditionalFormatting sqref="L54:M54">
+    <cfRule type="expression" dxfId="440" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K44:L44">
-    <cfRule type="expression" dxfId="440" priority="9">
+  <conditionalFormatting sqref="L44:M44">
+    <cfRule type="expression" dxfId="439" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K60">
-    <cfRule type="expression" dxfId="439" priority="8">
+  <conditionalFormatting sqref="L60">
+    <cfRule type="expression" dxfId="438" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K42:L42">
-    <cfRule type="expression" dxfId="438" priority="6">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K23">
-    <cfRule type="expression" dxfId="437" priority="5">
+  <conditionalFormatting sqref="L42:M42">
+    <cfRule type="expression" dxfId="437" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L23">
-    <cfRule type="expression" dxfId="436" priority="4">
+    <cfRule type="expression" dxfId="436" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L37">
-    <cfRule type="expression" dxfId="435" priority="2">
+  <conditionalFormatting sqref="M23">
+    <cfRule type="expression" dxfId="435" priority="4">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M37">
+    <cfRule type="expression" dxfId="434" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40:F40">
-    <cfRule type="expression" dxfId="434" priority="1">
+    <cfRule type="expression" dxfId="433" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14549,112 +14718,112 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2 A3:G3 AD47:AD48 AD55:AD57 AD68:AD69 AD50 AD11:AD19 AD21:AD23 AC11:AC24 AC29:AC43 AD29:AD42 AC66:AD67 AC54:AC57 AD73 H2:AD3 A68:G68 AC52:AD52 AC5:AD10 AC58:AD64 AC26:AD27 A70:AD72 A4:AB22 A44:S44 A45:AC50 A73:AB73 A26:AB43 B23:AB25 A52:AB67 B51:AB51">
-    <cfRule type="expression" dxfId="433" priority="22">
+    <cfRule type="expression" dxfId="432" priority="22">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD43">
-    <cfRule type="expression" dxfId="432" priority="21">
+    <cfRule type="expression" dxfId="431" priority="21">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD46">
-    <cfRule type="expression" dxfId="431" priority="20">
+    <cfRule type="expression" dxfId="430" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC4:AD4">
-    <cfRule type="expression" dxfId="430" priority="19">
+    <cfRule type="expression" dxfId="429" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD45">
-    <cfRule type="expression" dxfId="429" priority="18">
+    <cfRule type="expression" dxfId="428" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD20">
-    <cfRule type="expression" dxfId="428" priority="17">
+    <cfRule type="expression" dxfId="427" priority="17">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD54">
-    <cfRule type="expression" dxfId="427" priority="16">
+    <cfRule type="expression" dxfId="426" priority="16">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD24">
-    <cfRule type="expression" dxfId="426" priority="15">
+    <cfRule type="expression" dxfId="425" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC68">
-    <cfRule type="expression" dxfId="425" priority="14">
+    <cfRule type="expression" dxfId="424" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD49">
-    <cfRule type="expression" dxfId="424" priority="13">
+    <cfRule type="expression" dxfId="423" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC28:AD28">
-    <cfRule type="expression" dxfId="423" priority="12">
+    <cfRule type="expression" dxfId="422" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC65:AD65">
-    <cfRule type="expression" dxfId="422" priority="11">
+    <cfRule type="expression" dxfId="421" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC53:AD53">
-    <cfRule type="expression" dxfId="421" priority="10">
+    <cfRule type="expression" dxfId="420" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC73">
-    <cfRule type="expression" dxfId="420" priority="9">
+    <cfRule type="expression" dxfId="419" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H68:AB68">
-    <cfRule type="expression" dxfId="419" priority="8">
+    <cfRule type="expression" dxfId="418" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC51:AD51">
-    <cfRule type="expression" dxfId="418" priority="7">
+    <cfRule type="expression" dxfId="417" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC25">
-    <cfRule type="expression" dxfId="417" priority="6">
+    <cfRule type="expression" dxfId="416" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD25">
-    <cfRule type="expression" dxfId="416" priority="5">
+    <cfRule type="expression" dxfId="415" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T44:AC44">
-    <cfRule type="expression" dxfId="415" priority="4">
+    <cfRule type="expression" dxfId="414" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD44">
-    <cfRule type="expression" dxfId="414" priority="3">
+    <cfRule type="expression" dxfId="413" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A23:A25">
-    <cfRule type="expression" dxfId="413" priority="2">
+    <cfRule type="expression" dxfId="412" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A51">
-    <cfRule type="expression" dxfId="412" priority="1">
+    <cfRule type="expression" dxfId="411" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20954,82 +21123,82 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2 A3:G3 AF43:AF44 AF50:AF52 AF62:AF63 H2:AF3 AF46:AF47 AF9:AF17 AF23:AF24 AF19:AF21 AE9:AE24 AE5:AF8 AE26:AE47 AF26:AF39 AE60:AF61 AE49:AE52 A64:AF66 AF67 A67:AD67 AE53:AF58 A4:AD20 A23:AD62 C21:AD21 B22:AD22">
-    <cfRule type="expression" dxfId="411" priority="20">
+    <cfRule type="expression" dxfId="410" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF40">
-    <cfRule type="expression" dxfId="410" priority="19">
+    <cfRule type="expression" dxfId="409" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF42">
-    <cfRule type="expression" dxfId="409" priority="18">
+    <cfRule type="expression" dxfId="408" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE4:AF4">
-    <cfRule type="expression" dxfId="408" priority="16">
+    <cfRule type="expression" dxfId="407" priority="16">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF41">
-    <cfRule type="expression" dxfId="407" priority="14">
+    <cfRule type="expression" dxfId="406" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF18">
-    <cfRule type="expression" dxfId="406" priority="13">
+    <cfRule type="expression" dxfId="405" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF49">
-    <cfRule type="expression" dxfId="405" priority="12">
+    <cfRule type="expression" dxfId="404" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF22">
-    <cfRule type="expression" dxfId="404" priority="11">
+    <cfRule type="expression" dxfId="403" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE62">
-    <cfRule type="expression" dxfId="403" priority="10">
+    <cfRule type="expression" dxfId="402" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF45">
-    <cfRule type="expression" dxfId="402" priority="9">
+    <cfRule type="expression" dxfId="401" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE25:AF25">
-    <cfRule type="expression" dxfId="401" priority="6">
+    <cfRule type="expression" dxfId="400" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE59:AF59">
-    <cfRule type="expression" dxfId="400" priority="5">
+    <cfRule type="expression" dxfId="399" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE48:AF48">
-    <cfRule type="expression" dxfId="399" priority="4">
+    <cfRule type="expression" dxfId="398" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE67">
-    <cfRule type="expression" dxfId="398" priority="3">
+    <cfRule type="expression" dxfId="397" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21">
-    <cfRule type="expression" dxfId="397" priority="2">
+    <cfRule type="expression" dxfId="396" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:A22">
-    <cfRule type="expression" dxfId="396" priority="1">
+    <cfRule type="expression" dxfId="395" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21153,20 +21322,20 @@
         <v>-0.20805999999999999</v>
       </c>
       <c r="K4" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>-13362</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>-11762</v>
       </c>
       <c r="L4" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>-0.26723999999999998</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>-0.23524</v>
       </c>
       <c r="M4" s="71">
         <f t="shared" ref="M4:N62" si="0">G4+I4+K4</f>
-        <v>-40406</v>
+        <v>-38806</v>
       </c>
       <c r="N4" s="166">
         <f t="shared" si="0"/>
-        <v>-0.80811999999999995</v>
+        <v>-0.77612000000000003</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -21205,20 +21374,20 @@
         <v>-1.2725900000000001</v>
       </c>
       <c r="K5" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>-139420</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>-108180</v>
       </c>
       <c r="L5" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>-0.46473333333333339</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>-0.36059999999999998</v>
       </c>
       <c r="M5" s="71">
         <f t="shared" si="0"/>
-        <v>-390391</v>
+        <v>-359151</v>
       </c>
       <c r="N5" s="166">
         <f t="shared" si="0"/>
-        <v>-1.3013033333333335</v>
+        <v>-1.1971700000000001</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -21257,11 +21426,11 @@
         <v>1.16185</v>
       </c>
       <c r="K6" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L6" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M6" s="71">
@@ -21307,11 +21476,11 @@
         <v>0</v>
       </c>
       <c r="K7" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L7" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M7" s="71">
@@ -21359,20 +21528,20 @@
         <v>-1.6494500000000001</v>
       </c>
       <c r="K8" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>153035</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>107757</v>
       </c>
       <c r="L8" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>0.51011666666666655</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>0.35919000000000001</v>
       </c>
       <c r="M8" s="71">
         <f t="shared" si="0"/>
-        <v>-302062</v>
+        <v>-347340</v>
       </c>
       <c r="N8" s="166">
         <f t="shared" si="0"/>
-        <v>-1.0068733333333335</v>
+        <v>-1.1577999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -21411,20 +21580,20 @@
         <v>0.16230666666666665</v>
       </c>
       <c r="K9" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>44898</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>81548</v>
       </c>
       <c r="L9" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>0.29931999999999997</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>0.54365333333333343</v>
       </c>
       <c r="M9" s="71">
         <f t="shared" si="0"/>
-        <v>-249238</v>
+        <v>-212588</v>
       </c>
       <c r="N9" s="166">
         <f t="shared" si="0"/>
-        <v>-1.661586666666667</v>
+        <v>-1.4172533333333335</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -21463,20 +21632,20 @@
         <v>-1.1035999999999999</v>
       </c>
       <c r="K10" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>-13366</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>8274</v>
       </c>
       <c r="L10" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>-0.2227666666666667</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>0.13789999999999999</v>
       </c>
       <c r="M10" s="71">
         <f t="shared" ref="M10" si="3">G10+I10+K10</f>
-        <v>-205615</v>
+        <v>-183975</v>
       </c>
       <c r="N10" s="166">
         <f t="shared" ref="N10" si="4">H10+J10+L10</f>
-        <v>-3.4269166666666671</v>
+        <v>-3.0662500000000001</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -21515,11 +21684,11 @@
         <v>-0.91267399999999999</v>
       </c>
       <c r="K11" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
         <v>-413740</v>
       </c>
       <c r="L11" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
         <v>-0.27582666666666672</v>
       </c>
       <c r="M11" s="71">
@@ -21567,20 +21736,20 @@
         <v>3.0566666666666667E-3</v>
       </c>
       <c r="K12" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>-61193</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>-112135</v>
       </c>
       <c r="L12" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>-0.10198833333333333</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>-0.18689166666666668</v>
       </c>
       <c r="M12" s="71">
         <f t="shared" si="0"/>
-        <v>346587</v>
+        <v>295645</v>
       </c>
       <c r="N12" s="166">
         <f t="shared" si="0"/>
-        <v>0.57764500000000008</v>
+        <v>0.49274166666666674</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -21619,20 +21788,20 @@
         <v>0.12322</v>
       </c>
       <c r="K13" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>-7107</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>-4107</v>
       </c>
       <c r="L13" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>-7.1069999999999994E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>-4.1070000000000002E-2</v>
       </c>
       <c r="M13" s="71">
         <f t="shared" si="0"/>
-        <v>6309</v>
+        <v>9309</v>
       </c>
       <c r="N13" s="166">
         <f t="shared" si="0"/>
-        <v>6.3090000000000007E-2</v>
+        <v>9.3090000000000006E-2</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -21671,20 +21840,20 @@
         <v>-0.65036000000000005</v>
       </c>
       <c r="K14" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>724</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>-3104</v>
       </c>
       <c r="L14" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>2.8960000000000006E-3</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>-1.2415999999999998E-2</v>
       </c>
       <c r="M14" s="71">
         <f t="shared" si="0"/>
-        <v>45644</v>
+        <v>41816</v>
       </c>
       <c r="N14" s="166">
         <f t="shared" si="0"/>
-        <v>0.18257599999999996</v>
+        <v>0.16726399999999994</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
@@ -21723,11 +21892,11 @@
         <v>0</v>
       </c>
       <c r="K15" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L15" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M15" s="71">
@@ -21775,20 +21944,20 @@
         <v>0.33139000000000002</v>
       </c>
       <c r="K16" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>-14358</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>-6421</v>
       </c>
       <c r="L16" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>-0.14358000000000001</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>-6.4210000000000003E-2</v>
       </c>
       <c r="M16" s="71">
         <f t="shared" si="0"/>
-        <v>59049</v>
+        <v>66986</v>
       </c>
       <c r="N16" s="166">
         <f t="shared" si="0"/>
-        <v>0.59048999999999996</v>
+        <v>0.66986000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -21827,20 +21996,20 @@
         <v>-0.4931636363636363</v>
       </c>
       <c r="K17" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>-4897</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>-4997</v>
       </c>
       <c r="L17" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>-2.2259090909090905E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>-2.2713636363636359E-2</v>
       </c>
       <c r="M17" s="71">
         <f t="shared" ref="M17" si="5">G17+I17+K17</f>
-        <v>-92805</v>
+        <v>-92905</v>
       </c>
       <c r="N17" s="166">
         <f t="shared" ref="N17" si="6">H17+J17+L17</f>
-        <v>-0.42184090909090904</v>
+        <v>-0.42229545454545453</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
@@ -21879,11 +22048,11 @@
         <v>-0.44636399999999998</v>
       </c>
       <c r="K18" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L18" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M18" s="71">
@@ -21931,11 +22100,11 @@
         <v>-0.20675499999999999</v>
       </c>
       <c r="K19" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L19" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M19" s="71">
@@ -21983,20 +22152,20 @@
         <v>0.25088181818181815</v>
       </c>
       <c r="K20" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>9433</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>-2058</v>
       </c>
       <c r="L20" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>8.5754545454545431E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>-1.8709090909090908E-2</v>
       </c>
       <c r="M20" s="71">
         <f t="shared" si="0"/>
-        <v>97115</v>
+        <v>85624</v>
       </c>
       <c r="N20" s="166">
         <f t="shared" si="0"/>
-        <v>0.88286363636363618</v>
+        <v>0.77839999999999987</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -22035,20 +22204,20 @@
         <v>-2.8835999999999999</v>
       </c>
       <c r="K21" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>1271</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>3771</v>
       </c>
       <c r="L21" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>5.0840000000000003E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>0.15084</v>
       </c>
       <c r="M21" s="71">
         <f t="shared" ref="M21:M22" si="7">G21+I21+K21</f>
-        <v>-42275</v>
+        <v>-39775</v>
       </c>
       <c r="N21" s="166">
         <f t="shared" ref="N21:N22" si="8">H21+J21+L21</f>
-        <v>-1.6909999999999998</v>
+        <v>-1.5909999999999997</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
@@ -22087,20 +22256,20 @@
         <v>0.15673999999999999</v>
       </c>
       <c r="K22" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>5905</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>8479</v>
       </c>
       <c r="L22" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>2.9524999999999999E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>4.2395000000000002E-2</v>
       </c>
       <c r="M22" s="71">
         <f t="shared" si="7"/>
-        <v>22037</v>
+        <v>24611</v>
       </c>
       <c r="N22" s="166">
         <f t="shared" si="8"/>
-        <v>0.11018499999999999</v>
+        <v>0.123055</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
@@ -22139,20 +22308,20 @@
         <v>9.7766666666666668E-2</v>
       </c>
       <c r="K23" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>-14466</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>2934</v>
       </c>
       <c r="L23" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>-9.6439999999999998E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>1.9560000000000001E-2</v>
       </c>
       <c r="M23" s="71">
         <f t="shared" si="0"/>
-        <v>100547</v>
+        <v>117947</v>
       </c>
       <c r="N23" s="166">
         <f t="shared" si="0"/>
-        <v>0.67031333333333343</v>
+        <v>0.78631333333333342</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -22191,11 +22360,11 @@
         <v>0</v>
       </c>
       <c r="K24" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L24" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M24" s="71">
@@ -22243,20 +22412,20 @@
         <v>-1.1453363636363634</v>
       </c>
       <c r="K25" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>9908</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>15968</v>
       </c>
       <c r="L25" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>9.0072727272727263E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>0.14516363636363636</v>
       </c>
       <c r="M25" s="71">
         <f t="shared" si="0"/>
-        <v>214612</v>
+        <v>220672</v>
       </c>
       <c r="N25" s="166">
         <f t="shared" si="0"/>
-        <v>1.9510181818181813</v>
+        <v>2.0061090909090904</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
@@ -22295,20 +22464,20 @@
         <v>-2.2903086956521741</v>
       </c>
       <c r="K26" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>-406700</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>-406900</v>
       </c>
       <c r="L26" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>-1.7682608695652176</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>-1.7691304347826089</v>
       </c>
       <c r="M26" s="71">
         <f t="shared" si="0"/>
-        <v>-52639</v>
+        <v>-52839</v>
       </c>
       <c r="N26" s="166">
         <f t="shared" si="0"/>
-        <v>-0.22886521739130505</v>
+        <v>-0.2297347826086964</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
@@ -22345,20 +22514,20 @@
         <v>-0.8901</v>
       </c>
       <c r="K27" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>3803</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>5060</v>
       </c>
       <c r="L27" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>0.19015000000000001</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>0.253</v>
       </c>
       <c r="M27" s="71">
         <f t="shared" ref="M27" si="9">G27+I27+K27</f>
-        <v>-16493</v>
+        <v>-15236</v>
       </c>
       <c r="N27" s="166">
         <f t="shared" ref="N27" si="10">H27+J27+L27</f>
-        <v>-0.82464999999999988</v>
+        <v>-0.76179999999999992</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
@@ -22397,11 +22566,11 @@
         <v>-0.33289600000000003</v>
       </c>
       <c r="K28" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
         <v>39000</v>
       </c>
       <c r="L28" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
         <v>7.8E-2</v>
       </c>
       <c r="M28" s="71">
@@ -22449,20 +22618,20 @@
         <v>0.19531499999999999</v>
       </c>
       <c r="K29" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>-111645</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>72755</v>
       </c>
       <c r="L29" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>-0.11164499999999999</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>7.2755E-2</v>
       </c>
       <c r="M29" s="71">
         <f t="shared" si="0"/>
-        <v>3355767</v>
+        <v>3540167</v>
       </c>
       <c r="N29" s="166">
         <f t="shared" si="0"/>
-        <v>3.3557670000000002</v>
+        <v>3.5401669999999998</v>
       </c>
       <c r="O29" s="131"/>
     </row>
@@ -22502,11 +22671,11 @@
         <v>-0.60594000000000003</v>
       </c>
       <c r="K30" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L30" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M30" s="71">
@@ -22554,11 +22723,11 @@
         <v>-0.58230000000000004</v>
       </c>
       <c r="K31" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L31" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M31" s="71">
@@ -22606,11 +22775,11 @@
         <v>-0.58148999999999995</v>
       </c>
       <c r="K32" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L32" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M32" s="71">
@@ -22658,11 +22827,11 @@
         <v>-0.69791999999999998</v>
       </c>
       <c r="K33" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L33" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M33" s="71">
@@ -22710,11 +22879,11 @@
         <v>-0.58009333333333335</v>
       </c>
       <c r="K34" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L34" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M34" s="71">
@@ -22762,20 +22931,20 @@
         <v>-1.010926</v>
       </c>
       <c r="K35" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>-455000</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>-475000</v>
       </c>
       <c r="L35" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>-0.91</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>-0.95</v>
       </c>
       <c r="M35" s="71">
         <f t="shared" si="0"/>
-        <v>244852</v>
+        <v>224852</v>
       </c>
       <c r="N35" s="166">
         <f t="shared" si="0"/>
-        <v>0.48970399999999981</v>
+        <v>0.44970399999999988</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
@@ -22814,20 +22983,20 @@
         <v>1.1398239999999999</v>
       </c>
       <c r="K36" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>-172772</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>-172907</v>
       </c>
       <c r="L36" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>-0.34554400000000002</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>-0.34581400000000001</v>
       </c>
       <c r="M36" s="71">
         <f t="shared" si="0"/>
-        <v>854635</v>
+        <v>854500</v>
       </c>
       <c r="N36" s="166">
         <f t="shared" si="0"/>
-        <v>1.7092699999999998</v>
+        <v>1.7089999999999999</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
@@ -22866,20 +23035,20 @@
         <v>-1.28678</v>
       </c>
       <c r="K37" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>-79747</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>-98118</v>
       </c>
       <c r="L37" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>-1.59494</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>-1.9623600000000001</v>
       </c>
       <c r="M37" s="71">
         <f t="shared" si="0"/>
-        <v>-159111</v>
+        <v>-177482</v>
       </c>
       <c r="N37" s="166">
         <f t="shared" si="0"/>
-        <v>-3.18222</v>
+        <v>-3.5496400000000001</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
@@ -22918,20 +23087,20 @@
         <v>1.3305</v>
       </c>
       <c r="K38" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>9510</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>8586</v>
       </c>
       <c r="L38" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>0.23774999999999999</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>0.21465000000000001</v>
       </c>
       <c r="M38" s="71">
         <f t="shared" si="0"/>
-        <v>-56015</v>
+        <v>-56939</v>
       </c>
       <c r="N38" s="166">
         <f t="shared" si="0"/>
-        <v>-1.4003749999999999</v>
+        <v>-1.4234749999999998</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
@@ -22970,11 +23139,11 @@
         <v>0.12665999999999999</v>
       </c>
       <c r="K39" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L39" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M39" s="71">
@@ -23022,11 +23191,11 @@
         <v>0</v>
       </c>
       <c r="K40" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L40" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M40" s="71">
@@ -23074,20 +23243,20 @@
         <v>0.8756275</v>
       </c>
       <c r="K41" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>-133901</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>-84252</v>
       </c>
       <c r="L41" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>-0.33475250000000001</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>-0.21063000000000001</v>
       </c>
       <c r="M41" s="71">
         <f t="shared" si="0"/>
-        <v>577035</v>
+        <v>626684</v>
       </c>
       <c r="N41" s="166">
         <f t="shared" si="0"/>
-        <v>1.4425875000000001</v>
+        <v>1.56671</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
@@ -23126,20 +23295,20 @@
         <v>0.53249000000000002</v>
       </c>
       <c r="K42" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>-54575</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>-7417</v>
       </c>
       <c r="L42" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>-0.54574999999999996</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>-7.417E-2</v>
       </c>
       <c r="M42" s="71">
         <f t="shared" si="0"/>
-        <v>149057</v>
+        <v>196215</v>
       </c>
       <c r="N42" s="166">
         <f t="shared" si="0"/>
-        <v>1.49057</v>
+        <v>1.9621499999999998</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
@@ -23176,11 +23345,11 @@
         <v>0</v>
       </c>
       <c r="K43" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L43" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M43" s="71">
@@ -23228,20 +23397,20 @@
         <v>-0.28554000000000002</v>
       </c>
       <c r="K44" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>-13160</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>-28760</v>
       </c>
       <c r="L44" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>-0.26319999999999999</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>-0.57520000000000004</v>
       </c>
       <c r="M44" s="71">
         <f t="shared" si="0"/>
-        <v>-79543</v>
+        <v>-95143</v>
       </c>
       <c r="N44" s="166">
         <f t="shared" si="0"/>
-        <v>-1.5908599999999997</v>
+        <v>-1.90286</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
@@ -23280,20 +23449,20 @@
         <v>-0.63329999999999997</v>
       </c>
       <c r="K45" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>-58706</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>-56406</v>
       </c>
       <c r="L45" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>-0.19568666666666668</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>-0.18801999999999999</v>
       </c>
       <c r="M45" s="71">
         <f t="shared" si="0"/>
-        <v>-169498</v>
+        <v>-167198</v>
       </c>
       <c r="N45" s="166">
         <f t="shared" si="0"/>
-        <v>-0.56499333333333335</v>
+        <v>-0.55732666666666664</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
@@ -23332,11 +23501,11 @@
         <v>-0.34641333333333335</v>
       </c>
       <c r="K46" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L46" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M46" s="71">
@@ -23384,11 +23553,11 @@
         <v>-0.37293333333333334</v>
       </c>
       <c r="K47" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L47" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M47" s="71">
@@ -23434,20 +23603,20 @@
         <v>-0.49170000000000003</v>
       </c>
       <c r="K48" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>21424</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>20345</v>
       </c>
       <c r="L48" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>2.1423999999999999</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>2.0345</v>
       </c>
       <c r="M48" s="71">
         <f t="shared" ref="M48" si="15">G48+I48+K48</f>
-        <v>4492</v>
+        <v>3413</v>
       </c>
       <c r="N48" s="166">
         <f t="shared" ref="N48" si="16">H48+J48+L48</f>
-        <v>0.44919999999999982</v>
+        <v>0.34129999999999994</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
@@ -23486,20 +23655,20 @@
         <v>4.5359999999999998E-2</v>
       </c>
       <c r="K49" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>-3990</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>2285</v>
       </c>
       <c r="L49" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>-7.9799999999999996E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>4.5699999999999998E-2</v>
       </c>
       <c r="M49" s="71">
         <f t="shared" si="0"/>
-        <v>30338</v>
+        <v>36613</v>
       </c>
       <c r="N49" s="166">
         <f t="shared" si="0"/>
-        <v>0.28616000000000003</v>
+        <v>0.41166000000000003</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
@@ -23538,20 +23707,20 @@
         <v>7.0315700000000003</v>
       </c>
       <c r="K50" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>-116067</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>-35567</v>
       </c>
       <c r="L50" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>-1.1606700000000001</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>-0.35566999999999999</v>
       </c>
       <c r="M50" s="71">
         <f t="shared" si="0"/>
-        <v>771307</v>
+        <v>851807</v>
       </c>
       <c r="N50" s="166">
         <f t="shared" si="0"/>
-        <v>7.7130700000000001</v>
+        <v>8.5180699999999998</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
@@ -23588,20 +23757,20 @@
         <v>9.1899999999999996E-2</v>
       </c>
       <c r="K51" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>3216</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>6480</v>
       </c>
       <c r="L51" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>0.3216</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>0.64800000000000002</v>
       </c>
       <c r="M51" s="71">
         <f t="shared" ref="M51" si="17">G51+I51+K51</f>
-        <v>-330</v>
+        <v>2934</v>
       </c>
       <c r="N51" s="166">
         <f t="shared" ref="N51" si="18">H51+J51+L51</f>
-        <v>-3.3000000000000029E-2</v>
+        <v>0.29339999999999999</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
@@ -23640,20 +23809,20 @@
         <v>-1.2057033333333331</v>
       </c>
       <c r="K52" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>-46872</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>32664</v>
       </c>
       <c r="L52" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>-0.15623999999999999</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>0.10888</v>
       </c>
       <c r="M52" s="71">
         <f t="shared" si="0"/>
-        <v>-55605</v>
+        <v>23931</v>
       </c>
       <c r="N52" s="166">
         <f t="shared" si="0"/>
-        <v>-0.18534999999999996</v>
+        <v>7.9770000000000035E-2</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
@@ -23686,11 +23855,11 @@
         <v>-9.0149999999999994E-2</v>
       </c>
       <c r="K53" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L53" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M53" s="71">
@@ -23738,20 +23907,20 @@
         <v>0.15198</v>
       </c>
       <c r="K54" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>5133</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>-156125</v>
       </c>
       <c r="L54" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>1.28325E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>-0.39031250000000001</v>
       </c>
       <c r="M54" s="71">
         <f t="shared" si="0"/>
-        <v>480335</v>
+        <v>319077</v>
       </c>
       <c r="N54" s="166">
         <f t="shared" si="0"/>
-        <v>1.2008375</v>
+        <v>0.79769249999999992</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
@@ -23790,20 +23959,20 @@
         <v>-0.25410250000000001</v>
       </c>
       <c r="K55" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>25959</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>31259</v>
       </c>
       <c r="L55" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>6.4897499999999997E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>7.8147499999999995E-2</v>
       </c>
       <c r="M55" s="71">
         <f t="shared" si="0"/>
-        <v>368233</v>
+        <v>373533</v>
       </c>
       <c r="N55" s="166">
         <f t="shared" si="0"/>
-        <v>0.92058249999999986</v>
+        <v>0.93383249999999995</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
@@ -23840,20 +24009,20 @@
         <v>-1.03518</v>
       </c>
       <c r="K56" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>-340700</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>-371500</v>
       </c>
       <c r="L56" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
-        <v>-0.3407</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <v>-0.3715</v>
       </c>
       <c r="M56" s="71">
         <f t="shared" ref="M56" si="21">G56+I56+K56</f>
-        <v>-1375780</v>
+        <v>-1406580</v>
       </c>
       <c r="N56" s="166">
         <f t="shared" ref="N56" si="22">H56+J56+L56</f>
-        <v>-1.37588</v>
+        <v>-1.4066799999999999</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
@@ -23886,11 +24055,11 @@
         <v>0</v>
       </c>
       <c r="K57" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L57" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADM$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DN$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M57" s="71">
@@ -24281,12 +24450,12 @@
       <c r="J65" s="100"/>
       <c r="K65" s="109">
         <f>SUM(K4:K62)</f>
-        <v>-2342525</v>
+        <v>-2112291</v>
       </c>
       <c r="L65" s="109"/>
       <c r="M65" s="154">
         <f>SUM(M4:M62)</f>
-        <v>9437512</v>
+        <v>9667746</v>
       </c>
       <c r="N65" s="235"/>
     </row>
@@ -24447,492 +24616,492 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A45:C45 A11:C11 A3:F3 L2:L3 A41:C41 A5 A32:F32 F11 F42:F43 F45 A61:C61 A62:E62 A34:F36 E41:F41 A50:F50 A23 A38:F39 A55:F55 F59:F62 E61 G65:N66 A25:F26 M25:N26 A65:E65 C53:F53 M23:N23 G23:H26 A28:F29 A52:F52 G41:H42 G28:H39 G69:N71 F56:F57 G54:H56 A14:H16 M14:N16 K58:N63 M28:N39 M41:N42 M5:N9 G8:J9 G11:I13 M11:N12 I44:J56 M44:N52 G44:H52 G4:L4 C5:J5 M54:N56 A18:F19 G18:H20 M18:N20 I14:I42 J11:J42 K5:L56 I58:J64 G58:H63">
-    <cfRule type="expression" dxfId="395" priority="228">
+    <cfRule type="expression" dxfId="394" priority="228">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:I3">
-    <cfRule type="expression" dxfId="394" priority="227">
+    <cfRule type="expression" dxfId="393" priority="227">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J3">
-    <cfRule type="expression" dxfId="393" priority="226">
+    <cfRule type="expression" dxfId="392" priority="226">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K3">
-    <cfRule type="expression" dxfId="392" priority="225">
+    <cfRule type="expression" dxfId="391" priority="225">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A42:C42 E42 A43">
-    <cfRule type="expression" dxfId="391" priority="221">
+    <cfRule type="expression" dxfId="390" priority="221">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E45">
-    <cfRule type="expression" dxfId="390" priority="219">
+    <cfRule type="expression" dxfId="389" priority="219">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A20:F20">
-    <cfRule type="expression" dxfId="389" priority="217">
+    <cfRule type="expression" dxfId="388" priority="217">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:C47 E47:F47">
-    <cfRule type="expression" dxfId="388" priority="211">
+    <cfRule type="expression" dxfId="387" priority="211">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M25:N25">
-    <cfRule type="expression" dxfId="387" priority="201">
+    <cfRule type="expression" dxfId="386" priority="201">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12:C12 E12:F12">
-    <cfRule type="expression" dxfId="386" priority="206">
+    <cfRule type="expression" dxfId="385" priority="206">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N25">
-    <cfRule type="expression" dxfId="385" priority="202">
+    <cfRule type="expression" dxfId="384" priority="202">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M12:N12">
-    <cfRule type="expression" dxfId="384" priority="187">
+    <cfRule type="expression" dxfId="383" priority="187">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23:C23 E23:F23">
-    <cfRule type="expression" dxfId="383" priority="182">
+    <cfRule type="expression" dxfId="382" priority="182">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N12">
-    <cfRule type="expression" dxfId="382" priority="188">
+    <cfRule type="expression" dxfId="381" priority="188">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A8:C8 E8:F8 A9:F9 A10:B10 D10:F10">
-    <cfRule type="expression" dxfId="381" priority="173">
+    <cfRule type="expression" dxfId="380" priority="173">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N8:N9">
-    <cfRule type="expression" dxfId="380" priority="171">
+    <cfRule type="expression" dxfId="379" priority="171">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M8:N9">
-    <cfRule type="expression" dxfId="379" priority="170">
+    <cfRule type="expression" dxfId="378" priority="170">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A37:C37 E37:F37">
-    <cfRule type="expression" dxfId="378" priority="165">
+    <cfRule type="expression" dxfId="377" priority="165">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M37:N37">
-    <cfRule type="expression" dxfId="377" priority="161">
+    <cfRule type="expression" dxfId="376" priority="161">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N37">
-    <cfRule type="expression" dxfId="376" priority="162">
+    <cfRule type="expression" dxfId="375" priority="162">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A49:C49 E49:F49">
-    <cfRule type="expression" dxfId="375" priority="156">
+    <cfRule type="expression" dxfId="374" priority="156">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N23">
-    <cfRule type="expression" dxfId="374" priority="142">
+    <cfRule type="expression" dxfId="373" priority="142">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M23:N23">
-    <cfRule type="expression" dxfId="373" priority="141">
+    <cfRule type="expression" dxfId="372" priority="141">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58:C58 E58:F58">
-    <cfRule type="expression" dxfId="372" priority="131">
+    <cfRule type="expression" dxfId="371" priority="131">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L67:L68">
-    <cfRule type="expression" dxfId="371" priority="125">
+    <cfRule type="expression" dxfId="370" priority="125">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G67:I68">
-    <cfRule type="expression" dxfId="370" priority="124">
+    <cfRule type="expression" dxfId="369" priority="124">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J67:J68">
-    <cfRule type="expression" dxfId="369" priority="123">
+    <cfRule type="expression" dxfId="368" priority="123">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K67:K68">
-    <cfRule type="expression" dxfId="368" priority="122">
+    <cfRule type="expression" dxfId="367" priority="122">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A30:F30">
-    <cfRule type="expression" dxfId="367" priority="121">
+    <cfRule type="expression" dxfId="366" priority="121">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A31:F31">
-    <cfRule type="expression" dxfId="366" priority="120">
+    <cfRule type="expression" dxfId="365" priority="120">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A33:F33">
-    <cfRule type="expression" dxfId="365" priority="119">
+    <cfRule type="expression" dxfId="364" priority="119">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D11:E11">
-    <cfRule type="expression" dxfId="364" priority="108">
+    <cfRule type="expression" dxfId="363" priority="108">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A59:C60 E59:E60">
-    <cfRule type="expression" dxfId="363" priority="104">
+    <cfRule type="expression" dxfId="362" priority="104">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M59:N60">
-    <cfRule type="expression" dxfId="362" priority="103">
+    <cfRule type="expression" dxfId="361" priority="103">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A46:C46 E46:F46">
-    <cfRule type="expression" dxfId="361" priority="100">
+    <cfRule type="expression" dxfId="360" priority="100">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A54:B54">
-    <cfRule type="expression" dxfId="360" priority="96">
+    <cfRule type="expression" dxfId="359" priority="96">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4:C4 E4:F4">
-    <cfRule type="expression" dxfId="359" priority="91">
+    <cfRule type="expression" dxfId="358" priority="91">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M4:N4">
-    <cfRule type="expression" dxfId="358" priority="90">
+    <cfRule type="expression" dxfId="357" priority="90">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M4:N4">
-    <cfRule type="expression" dxfId="357" priority="87">
+    <cfRule type="expression" dxfId="356" priority="87">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N4">
-    <cfRule type="expression" dxfId="356" priority="88">
+    <cfRule type="expression" dxfId="355" priority="88">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A44:C44 E44:F44">
-    <cfRule type="expression" dxfId="355" priority="82">
+    <cfRule type="expression" dxfId="354" priority="82">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A69:F69 F70">
-    <cfRule type="expression" dxfId="354" priority="81">
+    <cfRule type="expression" dxfId="353" priority="81">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:F13">
-    <cfRule type="expression" dxfId="353" priority="73">
+    <cfRule type="expression" dxfId="352" priority="73">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M13:N13">
-    <cfRule type="expression" dxfId="352" priority="72">
+    <cfRule type="expression" dxfId="351" priority="72">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M13:N13">
-    <cfRule type="expression" dxfId="351" priority="69">
+    <cfRule type="expression" dxfId="350" priority="69">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N13">
-    <cfRule type="expression" dxfId="350" priority="70">
+    <cfRule type="expression" dxfId="349" priority="70">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F54">
-    <cfRule type="expression" dxfId="349" priority="62">
+    <cfRule type="expression" dxfId="348" priority="62">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D54:E54">
-    <cfRule type="expression" dxfId="348" priority="61">
+    <cfRule type="expression" dxfId="347" priority="61">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="347" priority="60">
+    <cfRule type="expression" dxfId="346" priority="60">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4">
-    <cfRule type="expression" dxfId="346" priority="59">
+    <cfRule type="expression" dxfId="345" priority="59">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D12">
-    <cfRule type="expression" dxfId="345" priority="58">
+    <cfRule type="expression" dxfId="344" priority="58">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D23">
-    <cfRule type="expression" dxfId="344" priority="57">
+    <cfRule type="expression" dxfId="343" priority="57">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D59:D60">
-    <cfRule type="expression" dxfId="343" priority="46">
+    <cfRule type="expression" dxfId="342" priority="46">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D37">
-    <cfRule type="expression" dxfId="342" priority="56">
+    <cfRule type="expression" dxfId="341" priority="56">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D42 D44">
-    <cfRule type="expression" dxfId="341" priority="55">
+    <cfRule type="expression" dxfId="340" priority="55">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D41">
-    <cfRule type="expression" dxfId="340" priority="54">
+    <cfRule type="expression" dxfId="339" priority="54">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D45">
-    <cfRule type="expression" dxfId="339" priority="53">
+    <cfRule type="expression" dxfId="338" priority="53">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D46">
-    <cfRule type="expression" dxfId="338" priority="52">
+    <cfRule type="expression" dxfId="337" priority="52">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D47">
-    <cfRule type="expression" dxfId="337" priority="51">
+    <cfRule type="expression" dxfId="336" priority="51">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D49">
-    <cfRule type="expression" dxfId="336" priority="50">
+    <cfRule type="expression" dxfId="335" priority="50">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D61">
-    <cfRule type="expression" dxfId="335" priority="49">
+    <cfRule type="expression" dxfId="334" priority="49">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D58">
-    <cfRule type="expression" dxfId="334" priority="47">
+    <cfRule type="expression" dxfId="333" priority="47">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:F24">
-    <cfRule type="expression" dxfId="333" priority="45">
+    <cfRule type="expression" dxfId="332" priority="45">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M24:N24">
-    <cfRule type="expression" dxfId="332" priority="44">
+    <cfRule type="expression" dxfId="331" priority="44">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N24">
-    <cfRule type="expression" dxfId="331" priority="41">
+    <cfRule type="expression" dxfId="330" priority="41">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M24:N24">
-    <cfRule type="expression" dxfId="330" priority="40">
+    <cfRule type="expression" dxfId="329" priority="40">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A64:F64">
-    <cfRule type="expression" dxfId="329" priority="33">
+    <cfRule type="expression" dxfId="328" priority="33">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G64:H64 K64:N64">
-    <cfRule type="expression" dxfId="328" priority="32">
+    <cfRule type="expression" dxfId="327" priority="32">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A53:B53">
-    <cfRule type="expression" dxfId="327" priority="31">
+    <cfRule type="expression" dxfId="326" priority="31">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G53:H53 M53:N53">
-    <cfRule type="expression" dxfId="326" priority="30">
+    <cfRule type="expression" dxfId="325" priority="30">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40:F40">
-    <cfRule type="expression" dxfId="325" priority="29">
+    <cfRule type="expression" dxfId="324" priority="29">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G40:H40 M40:N40">
-    <cfRule type="expression" dxfId="324" priority="28">
+    <cfRule type="expression" dxfId="323" priority="28">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A48:F48">
-    <cfRule type="expression" dxfId="323" priority="27">
+    <cfRule type="expression" dxfId="322" priority="27">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:F17">
-    <cfRule type="expression" dxfId="322" priority="26">
+    <cfRule type="expression" dxfId="321" priority="26">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G17:H17 M17:N17">
-    <cfRule type="expression" dxfId="321" priority="25">
+    <cfRule type="expression" dxfId="320" priority="25">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:F22 C21:F21">
-    <cfRule type="expression" dxfId="320" priority="24">
+    <cfRule type="expression" dxfId="319" priority="24">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G21:H22 M21:N22">
-    <cfRule type="expression" dxfId="319" priority="23">
+    <cfRule type="expression" dxfId="318" priority="23">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G27:H27 M27:N27">
-    <cfRule type="expression" dxfId="318" priority="19">
+    <cfRule type="expression" dxfId="317" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27:F27">
-    <cfRule type="expression" dxfId="317" priority="22">
+    <cfRule type="expression" dxfId="316" priority="22">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A51:F51">
-    <cfRule type="expression" dxfId="316" priority="21">
+    <cfRule type="expression" dxfId="315" priority="21">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A63:F63">
-    <cfRule type="expression" dxfId="315" priority="20">
+    <cfRule type="expression" dxfId="314" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A70:E70">
-    <cfRule type="expression" dxfId="314" priority="18">
+    <cfRule type="expression" dxfId="313" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A56:E56 A57">
-    <cfRule type="expression" dxfId="313" priority="16">
+    <cfRule type="expression" dxfId="312" priority="16">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A6:F7">
-    <cfRule type="expression" dxfId="312" priority="15">
+    <cfRule type="expression" dxfId="311" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G6:J7">
-    <cfRule type="expression" dxfId="311" priority="14">
+    <cfRule type="expression" dxfId="310" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B57:E57">
-    <cfRule type="expression" dxfId="310" priority="13">
+    <cfRule type="expression" dxfId="309" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5">
-    <cfRule type="expression" dxfId="309" priority="12">
+    <cfRule type="expression" dxfId="308" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C10">
-    <cfRule type="expression" dxfId="308" priority="11">
+    <cfRule type="expression" dxfId="307" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G10:J10 M10:N10">
-    <cfRule type="expression" dxfId="307" priority="10">
+    <cfRule type="expression" dxfId="306" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N10">
-    <cfRule type="expression" dxfId="306" priority="9">
+    <cfRule type="expression" dxfId="305" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M10:N10">
-    <cfRule type="expression" dxfId="305" priority="8">
+    <cfRule type="expression" dxfId="304" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="expression" dxfId="304" priority="7">
+    <cfRule type="expression" dxfId="303" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C43">
-    <cfRule type="expression" dxfId="303" priority="6">
+    <cfRule type="expression" dxfId="302" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D43:E43">
-    <cfRule type="expression" dxfId="302" priority="5">
+    <cfRule type="expression" dxfId="301" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G43:J43 M43:N43">
-    <cfRule type="expression" dxfId="301" priority="4">
+    <cfRule type="expression" dxfId="300" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21">
-    <cfRule type="expression" dxfId="300" priority="3">
+    <cfRule type="expression" dxfId="299" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:A22">
-    <cfRule type="expression" dxfId="299" priority="2">
+    <cfRule type="expression" dxfId="298" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G57:N57">
-    <cfRule type="expression" dxfId="298" priority="1">
+    <cfRule type="expression" dxfId="297" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -30623,42 +30792,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2 A48:A49 AE58 AD56:AE57 AE43:AE55 AD42:AD55 A3:G4 AD6:AE9 AD12:AE19 AD21:AD40 AE21:AE39 H2:AE4 A10:AE11 C48:AC49 A5:AC9 A50:AC57 A12:AC47 A59:AE63">
-    <cfRule type="expression" dxfId="297" priority="13">
+    <cfRule type="expression" dxfId="296" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE40">
-    <cfRule type="expression" dxfId="296" priority="12">
+    <cfRule type="expression" dxfId="295" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE42">
-    <cfRule type="expression" dxfId="295" priority="11">
+    <cfRule type="expression" dxfId="294" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48:B49">
-    <cfRule type="expression" dxfId="294" priority="5">
+    <cfRule type="expression" dxfId="293" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD5:AE5">
-    <cfRule type="expression" dxfId="293" priority="4">
+    <cfRule type="expression" dxfId="292" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD41">
-    <cfRule type="expression" dxfId="292" priority="3">
+    <cfRule type="expression" dxfId="291" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE41">
-    <cfRule type="expression" dxfId="291" priority="2">
+    <cfRule type="expression" dxfId="290" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD20:AE20">
-    <cfRule type="expression" dxfId="290" priority="1">
+    <cfRule type="expression" dxfId="289" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -36696,112 +36865,112 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G30 G14:G15 G2 A57:G57 G58 A55:A56 H2:AC4 A17:G27 H57:AA62 AC67 AC50:AC64 AB5:AC5 A53:G53 H49:AA54 AB49:AB64 A37:AA40 H5:AA15 AB7:AC15 A16:AC16 A31:G36 H17:AA36 AB65:AC66 AC17:AC46 AB17:AB47 A68:AC71 A54:B54 D54:G54 C55:AA56 A3:G5 A7:G8 A6:C6 E6:G6 A10:G13 A9:C9 E9:G9 A29:G29 A28:C28 E28:G28 A42:AA45 A41:C41 E41:AA41 A47:AA48 A46:C46 E46:AA46 A49:C52 E49:G52 A64:AA66 A59:C63 E63:AA63 E59:G62">
-    <cfRule type="expression" dxfId="289" priority="28">
+    <cfRule type="expression" dxfId="288" priority="28">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC47">
-    <cfRule type="expression" dxfId="288" priority="27">
+    <cfRule type="expression" dxfId="287" priority="27">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC49">
-    <cfRule type="expression" dxfId="287" priority="26">
+    <cfRule type="expression" dxfId="286" priority="26">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A30:C30 F30">
-    <cfRule type="expression" dxfId="286" priority="25">
+    <cfRule type="expression" dxfId="285" priority="25">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14:F14 A15:C15 E15:F15">
-    <cfRule type="expression" dxfId="285" priority="23">
+    <cfRule type="expression" dxfId="284" priority="23">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D30:E30">
-    <cfRule type="expression" dxfId="284" priority="22">
+    <cfRule type="expression" dxfId="283" priority="22">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58:F58">
-    <cfRule type="expression" dxfId="283" priority="20">
+    <cfRule type="expression" dxfId="282" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55:B56">
-    <cfRule type="expression" dxfId="282" priority="19">
+    <cfRule type="expression" dxfId="281" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB6:AC6">
-    <cfRule type="expression" dxfId="281" priority="15">
+    <cfRule type="expression" dxfId="280" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB48">
-    <cfRule type="expression" dxfId="280" priority="14">
+    <cfRule type="expression" dxfId="279" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC48">
-    <cfRule type="expression" dxfId="279" priority="13">
+    <cfRule type="expression" dxfId="278" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6">
-    <cfRule type="expression" dxfId="278" priority="12">
+    <cfRule type="expression" dxfId="277" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9">
-    <cfRule type="expression" dxfId="277" priority="11">
+    <cfRule type="expression" dxfId="276" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D15">
-    <cfRule type="expression" dxfId="276" priority="10">
+    <cfRule type="expression" dxfId="275" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D28">
-    <cfRule type="expression" dxfId="275" priority="9">
+    <cfRule type="expression" dxfId="274" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D41">
-    <cfRule type="expression" dxfId="274" priority="8">
+    <cfRule type="expression" dxfId="273" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D46">
-    <cfRule type="expression" dxfId="273" priority="7">
+    <cfRule type="expression" dxfId="272" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D49">
-    <cfRule type="expression" dxfId="272" priority="6">
+    <cfRule type="expression" dxfId="271" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D60:D63">
-    <cfRule type="expression" dxfId="271" priority="1">
+    <cfRule type="expression" dxfId="270" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D50:D51">
-    <cfRule type="expression" dxfId="270" priority="5">
+    <cfRule type="expression" dxfId="269" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D52">
-    <cfRule type="expression" dxfId="269" priority="4">
+    <cfRule type="expression" dxfId="268" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D59">
-    <cfRule type="expression" dxfId="268" priority="2">
+    <cfRule type="expression" dxfId="267" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -42716,107 +42885,107 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G29 G13:G14 G2 A30:G36 A39:G40 G53 A58:C61 G57 H39:AA53 H56:AA59 A54:A55 F54:AA55 A37:AA38 H2:AC4 A15:G26 H5:AA36 AC49:AC58 AC60:AC64 AC5:AC46 AB5:AB61 A62:AB63 A65:AC68 A3:G7 A9:G12 A8:C8 E8:G8 A28:G28 A27:C27 E27:G27 A42:G45 A41:C41 E41:G41 A52:G52 A46:C51 E46:G51 A56:G56 E58:G59 E60:AA61">
-    <cfRule type="expression" dxfId="267" priority="24">
+    <cfRule type="expression" dxfId="266" priority="24">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC47">
-    <cfRule type="expression" dxfId="266" priority="23">
+    <cfRule type="expression" dxfId="265" priority="23">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC48">
-    <cfRule type="expression" dxfId="265" priority="22">
+    <cfRule type="expression" dxfId="264" priority="22">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A29:C29 F29">
-    <cfRule type="expression" dxfId="264" priority="21">
+    <cfRule type="expression" dxfId="263" priority="21">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC59">
-    <cfRule type="expression" dxfId="263" priority="20">
+    <cfRule type="expression" dxfId="262" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:F13 A14:C14 E14:F14">
-    <cfRule type="expression" dxfId="262" priority="19">
+    <cfRule type="expression" dxfId="261" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D29:E29">
-    <cfRule type="expression" dxfId="261" priority="18">
+    <cfRule type="expression" dxfId="260" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A53:B53 F53">
-    <cfRule type="expression" dxfId="260" priority="15">
+    <cfRule type="expression" dxfId="259" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A57:F57">
-    <cfRule type="expression" dxfId="259" priority="14">
+    <cfRule type="expression" dxfId="258" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54:B55">
-    <cfRule type="expression" dxfId="258" priority="13">
+    <cfRule type="expression" dxfId="257" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D53:E53 C54:E55">
-    <cfRule type="expression" dxfId="257" priority="12">
+    <cfRule type="expression" dxfId="256" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D58:D61">
-    <cfRule type="expression" dxfId="256" priority="1">
+    <cfRule type="expression" dxfId="255" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="255" priority="10">
+    <cfRule type="expression" dxfId="254" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="254" priority="9">
+    <cfRule type="expression" dxfId="253" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D27">
-    <cfRule type="expression" dxfId="253" priority="8">
+    <cfRule type="expression" dxfId="252" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D41">
-    <cfRule type="expression" dxfId="252" priority="7">
+    <cfRule type="expression" dxfId="251" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D47:D48">
-    <cfRule type="expression" dxfId="251" priority="6">
+    <cfRule type="expression" dxfId="250" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D46">
-    <cfRule type="expression" dxfId="250" priority="5">
+    <cfRule type="expression" dxfId="249" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D49">
-    <cfRule type="expression" dxfId="249" priority="4">
+    <cfRule type="expression" dxfId="248" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D50">
-    <cfRule type="expression" dxfId="248" priority="3">
+    <cfRule type="expression" dxfId="247" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D51">
-    <cfRule type="expression" dxfId="247" priority="2">
+    <cfRule type="expression" dxfId="246" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -43168,11 +43337,11 @@
       <c r="O6" s="215"/>
       <c r="P6" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-40406</v>
+        <v>-38806</v>
       </c>
       <c r="Q6" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.80811999999999995</v>
+        <v>-0.77612000000000003</v>
       </c>
       <c r="R6" s="159"/>
       <c r="S6" s="153">
@@ -43189,11 +43358,11 @@
       <c r="X6" s="132"/>
       <c r="Y6" s="154">
         <f t="shared" si="0"/>
-        <v>-88742</v>
+        <v>-87142</v>
       </c>
       <c r="Z6" s="168">
         <f t="shared" si="1"/>
-        <v>-1.77484</v>
+        <v>-1.7428400000000002</v>
       </c>
     </row>
     <row r="7" spans="1:26" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -43250,11 +43419,11 @@
       <c r="O7" s="215"/>
       <c r="P7" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-390391</v>
+        <v>-359151</v>
       </c>
       <c r="Q7" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1.3013033333333335</v>
+        <v>-1.1971700000000001</v>
       </c>
       <c r="R7" s="159"/>
       <c r="S7" s="88">
@@ -43271,11 +43440,11 @@
       <c r="X7"/>
       <c r="Y7" s="154">
         <f t="shared" si="0"/>
-        <v>943883</v>
+        <v>975123</v>
       </c>
       <c r="Z7" s="168">
         <f t="shared" si="1"/>
-        <v>3.1462766666666671</v>
+        <v>3.2504100000000005</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -43447,11 +43616,11 @@
       <c r="O10" s="215"/>
       <c r="P10" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-302062</v>
+        <v>-347340</v>
       </c>
       <c r="Q10" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1.0068733333333335</v>
+        <v>-1.1577999999999999</v>
       </c>
       <c r="R10" s="159"/>
       <c r="S10" s="88">
@@ -43467,11 +43636,11 @@
       <c r="W10" s="72"/>
       <c r="Y10" s="154">
         <f t="shared" si="0"/>
-        <v>-660971</v>
+        <v>-706249</v>
       </c>
       <c r="Z10" s="168">
         <f t="shared" si="1"/>
-        <v>-3.6475533333333336</v>
+        <v>-3.7984800000000001</v>
       </c>
     </row>
     <row r="11" spans="1:26" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -43528,11 +43697,11 @@
       <c r="O11" s="215"/>
       <c r="P11" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-249238</v>
+        <v>-212588</v>
       </c>
       <c r="Q11" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1.661586666666667</v>
+        <v>-1.4172533333333335</v>
       </c>
       <c r="R11" s="159"/>
       <c r="S11" s="153">
@@ -43548,11 +43717,11 @@
       <c r="W11" s="150"/>
       <c r="Y11" s="154">
         <f t="shared" si="0"/>
-        <v>-424200</v>
+        <v>-387550</v>
       </c>
       <c r="Z11" s="168">
         <f t="shared" si="1"/>
-        <v>-2.8280000000000003</v>
+        <v>-2.5836666666666668</v>
       </c>
     </row>
     <row r="12" spans="1:26" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -43609,11 +43778,11 @@
       <c r="O12" s="215"/>
       <c r="P12" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-205615</v>
+        <v>-183975</v>
       </c>
       <c r="Q12" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-3.4269166666666671</v>
+        <v>-3.0662500000000001</v>
       </c>
       <c r="R12" s="159"/>
       <c r="S12" s="153">
@@ -43629,11 +43798,11 @@
       <c r="W12" s="150"/>
       <c r="Y12" s="154">
         <f t="shared" ref="Y12" si="10">M12+P12+S12+V12</f>
-        <v>-205615</v>
+        <v>-183975</v>
       </c>
       <c r="Z12" s="168">
         <f t="shared" ref="Z12" si="11">(N12+Q12+T12+W12)</f>
-        <v>-3.4269166666666671</v>
+        <v>-3.0662500000000001</v>
       </c>
     </row>
     <row r="13" spans="1:26" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -44099,11 +44268,11 @@
       <c r="O18" s="215"/>
       <c r="P18" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>346587</v>
+        <v>295645</v>
       </c>
       <c r="Q18" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.57764500000000008</v>
+        <v>0.49274166666666674</v>
       </c>
       <c r="R18" s="159"/>
       <c r="S18" s="88">
@@ -44119,11 +44288,11 @@
       <c r="W18" s="72"/>
       <c r="Y18" s="154">
         <f t="shared" si="0"/>
-        <v>151253</v>
+        <v>100311</v>
       </c>
       <c r="Z18" s="168">
         <f t="shared" si="1"/>
-        <v>-2.8399749999999999</v>
+        <v>-2.924878333333333</v>
       </c>
     </row>
     <row r="19" spans="1:34" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -44180,11 +44349,11 @@
       <c r="O19" s="215"/>
       <c r="P19" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>6309</v>
+        <v>9309</v>
       </c>
       <c r="Q19" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>6.3090000000000007E-2</v>
+        <v>9.3090000000000006E-2</v>
       </c>
       <c r="R19" s="159"/>
       <c r="S19" s="153">
@@ -44200,11 +44369,11 @@
       <c r="W19" s="150"/>
       <c r="Y19" s="154">
         <f t="shared" si="0"/>
-        <v>9988</v>
+        <v>12988</v>
       </c>
       <c r="Z19" s="168">
         <f t="shared" si="1"/>
-        <v>9.988000000000001E-2</v>
+        <v>0.12988</v>
       </c>
     </row>
     <row r="20" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -44351,11 +44520,11 @@
       <c r="O21" s="215"/>
       <c r="P21" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>45644</v>
+        <v>41816</v>
       </c>
       <c r="Q21" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.18257599999999996</v>
+        <v>0.16726399999999994</v>
       </c>
       <c r="R21" s="159"/>
       <c r="S21" s="88">
@@ -44371,11 +44540,11 @@
       <c r="W21" s="72"/>
       <c r="Y21" s="154">
         <f t="shared" si="0"/>
-        <v>-221772</v>
+        <v>-225600</v>
       </c>
       <c r="Z21" s="168">
         <f t="shared" si="1"/>
-        <v>-2.491584</v>
+        <v>-2.5068960000000002</v>
       </c>
     </row>
     <row r="22" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -44432,11 +44601,11 @@
       <c r="O22" s="215"/>
       <c r="P22" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-92805</v>
+        <v>-92905</v>
       </c>
       <c r="Q22" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.42184090909090904</v>
+        <v>-0.42229545454545453</v>
       </c>
       <c r="R22" s="159"/>
       <c r="S22" s="88">
@@ -44452,11 +44621,11 @@
       <c r="W22" s="72"/>
       <c r="Y22" s="154">
         <f t="shared" si="0"/>
-        <v>-181705</v>
+        <v>-181805</v>
       </c>
       <c r="Z22" s="168">
         <f t="shared" si="1"/>
-        <v>-1.310840909090909</v>
+        <v>-1.3112954545454545</v>
       </c>
     </row>
     <row r="23" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -44594,11 +44763,11 @@
       <c r="O24" s="215"/>
       <c r="P24" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>59049</v>
+        <v>66986</v>
       </c>
       <c r="Q24" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.59048999999999996</v>
+        <v>0.66986000000000001</v>
       </c>
       <c r="R24" s="159"/>
       <c r="S24" s="88">
@@ -44614,11 +44783,11 @@
       <c r="W24" s="72"/>
       <c r="Y24" s="154">
         <f t="shared" si="0"/>
-        <v>1774394</v>
+        <v>1782331</v>
       </c>
       <c r="Z24" s="168">
         <f t="shared" si="1"/>
-        <v>17.743939999999998</v>
+        <v>17.823309999999999</v>
       </c>
     </row>
     <row r="25" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45079,11 +45248,11 @@
       <c r="O30" s="215"/>
       <c r="P30" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>97115</v>
+        <v>85624</v>
       </c>
       <c r="Q30" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.88286363636363618</v>
+        <v>0.77839999999999987</v>
       </c>
       <c r="R30" s="159"/>
       <c r="S30" s="88">
@@ -45100,11 +45269,11 @@
       <c r="X30" s="1"/>
       <c r="Y30" s="154">
         <f t="shared" si="0"/>
-        <v>96833</v>
+        <v>85342</v>
       </c>
       <c r="Z30" s="168">
         <f t="shared" si="1"/>
-        <v>0.88029999999999986</v>
+        <v>0.77583636363636355</v>
       </c>
     </row>
     <row r="31" spans="1:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45250,11 +45419,11 @@
       <c r="O32" s="215"/>
       <c r="P32" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>100547</v>
+        <v>117947</v>
       </c>
       <c r="Q32" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.67031333333333343</v>
+        <v>0.78631333333333342</v>
       </c>
       <c r="R32" s="159"/>
       <c r="S32" s="88">
@@ -45271,11 +45440,11 @@
       <c r="X32"/>
       <c r="Y32" s="154">
         <f t="shared" si="0"/>
-        <v>-404522</v>
+        <v>-387122</v>
       </c>
       <c r="Z32" s="168">
         <f t="shared" si="1"/>
-        <v>-2.696813333333334</v>
+        <v>-2.5808133333333343</v>
       </c>
     </row>
     <row r="33" spans="1:34" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45413,11 +45582,11 @@
       <c r="O34" s="215"/>
       <c r="P34" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>214612</v>
+        <v>220672</v>
       </c>
       <c r="Q34" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1.9510181818181813</v>
+        <v>2.0061090909090904</v>
       </c>
       <c r="R34" s="159"/>
       <c r="S34" s="88">
@@ -45433,11 +45602,11 @@
       <c r="W34" s="72"/>
       <c r="Y34" s="154">
         <f t="shared" si="0"/>
-        <v>-104328</v>
+        <v>-98268</v>
       </c>
       <c r="Z34" s="168">
         <f t="shared" si="1"/>
-        <v>-0.94843636363636374</v>
+        <v>-0.89334545454545466</v>
       </c>
       <c r="AB34" s="1"/>
       <c r="AC34" s="1"/>
@@ -45582,11 +45751,11 @@
       <c r="O36" s="215"/>
       <c r="P36" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-52639</v>
+        <v>-52839</v>
       </c>
       <c r="Q36" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.22886521739130505</v>
+        <v>-0.2297347826086964</v>
       </c>
       <c r="R36" s="159"/>
       <c r="S36" s="88">
@@ -45602,11 +45771,11 @@
       <c r="W36" s="72"/>
       <c r="Y36" s="154">
         <f t="shared" si="0"/>
-        <v>4108464</v>
+        <v>4108264</v>
       </c>
       <c r="Z36" s="168">
         <f t="shared" si="1"/>
-        <v>17.862886956521738</v>
+        <v>17.862017391304349</v>
       </c>
     </row>
     <row r="37" spans="1:34" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45661,11 +45830,11 @@
       <c r="O37" s="215"/>
       <c r="P37" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-16493</v>
+        <v>-15236</v>
       </c>
       <c r="Q37" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.82464999999999988</v>
+        <v>-0.76179999999999992</v>
       </c>
       <c r="R37" s="159"/>
       <c r="S37" s="153">
@@ -45681,11 +45850,11 @@
       <c r="W37" s="150"/>
       <c r="Y37" s="154">
         <f t="shared" ref="Y37" si="20">M37+P37+S37+V37</f>
-        <v>-16493</v>
+        <v>-15236</v>
       </c>
       <c r="Z37" s="168">
         <f t="shared" ref="Z37" si="21">(N37+Q37+T37+W37)</f>
-        <v>-0.82464999999999988</v>
+        <v>-0.76179999999999992</v>
       </c>
     </row>
     <row r="38" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45823,11 +45992,11 @@
       <c r="O39" s="215"/>
       <c r="P39" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>3355767</v>
+        <v>3540167</v>
       </c>
       <c r="Q39" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>3.3557670000000002</v>
+        <v>3.5401669999999998</v>
       </c>
       <c r="R39" s="159"/>
       <c r="S39" s="88">
@@ -45844,11 +46013,11 @@
       <c r="X39" s="132"/>
       <c r="Y39" s="154">
         <f t="shared" ref="Y39:Y74" si="22">M39+P39+S39+V39</f>
-        <v>6949173</v>
+        <v>7133573</v>
       </c>
       <c r="Z39" s="168">
         <f t="shared" ref="Z39:Z74" si="23">(N39+Q39+T39+W39)</f>
-        <v>6.949173</v>
+        <v>7.1335730000000002</v>
       </c>
       <c r="AB39" s="131"/>
     </row>
@@ -46339,11 +46508,11 @@
       <c r="O45" s="215"/>
       <c r="P45" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>244852</v>
+        <v>224852</v>
       </c>
       <c r="Q45" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.48970399999999981</v>
+        <v>0.44970399999999988</v>
       </c>
       <c r="R45" s="159"/>
       <c r="S45" s="88">
@@ -46359,11 +46528,11 @@
       <c r="W45" s="72"/>
       <c r="Y45" s="154">
         <f t="shared" si="22"/>
-        <v>1462170</v>
+        <v>1442170</v>
       </c>
       <c r="Z45" s="168">
         <f t="shared" si="23"/>
-        <v>2.9243399999999995</v>
+        <v>2.8843399999999999</v>
       </c>
     </row>
     <row r="46" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -46420,11 +46589,11 @@
       <c r="O46" s="215"/>
       <c r="P46" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>854635</v>
+        <v>854500</v>
       </c>
       <c r="Q46" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1.7092699999999998</v>
+        <v>1.7089999999999999</v>
       </c>
       <c r="R46" s="159"/>
       <c r="S46" s="88">
@@ -46441,11 +46610,11 @@
       <c r="X46" s="1"/>
       <c r="Y46" s="154">
         <f t="shared" si="22"/>
-        <v>806897</v>
+        <v>806762</v>
       </c>
       <c r="Z46" s="168">
         <f t="shared" si="23"/>
-        <v>1.6137939999999997</v>
+        <v>1.6135239999999997</v>
       </c>
       <c r="AA46" s="1"/>
     </row>
@@ -46503,11 +46672,11 @@
       <c r="O47" s="215"/>
       <c r="P47" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-159111</v>
+        <v>-177482</v>
       </c>
       <c r="Q47" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-3.18222</v>
+        <v>-3.5496400000000001</v>
       </c>
       <c r="R47" s="159"/>
       <c r="S47" s="88">
@@ -46523,11 +46692,11 @@
       <c r="W47" s="72"/>
       <c r="Y47" s="154">
         <f t="shared" si="22"/>
-        <v>-42216</v>
+        <v>-60587</v>
       </c>
       <c r="Z47" s="168">
         <f t="shared" si="23"/>
-        <v>-0.84432000000000018</v>
+        <v>-1.2117400000000003</v>
       </c>
       <c r="AD47" s="1"/>
       <c r="AE47" s="1"/>
@@ -46672,11 +46841,11 @@
       <c r="O49" s="215"/>
       <c r="P49" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-56015</v>
+        <v>-56939</v>
       </c>
       <c r="Q49" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1.4003749999999999</v>
+        <v>-1.4234749999999998</v>
       </c>
       <c r="R49" s="159"/>
       <c r="S49" s="88">
@@ -46692,11 +46861,11 @@
       <c r="W49" s="72"/>
       <c r="Y49" s="154">
         <f t="shared" si="22"/>
-        <v>-67843</v>
+        <v>-68767</v>
       </c>
       <c r="Z49" s="168">
         <f t="shared" si="23"/>
-        <v>-1.696075</v>
+        <v>-1.7191749999999999</v>
       </c>
       <c r="AD49"/>
       <c r="AE49"/>
@@ -46927,11 +47096,11 @@
       <c r="O52" s="215"/>
       <c r="P52" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>577035</v>
+        <v>626684</v>
       </c>
       <c r="Q52" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1.4425875000000001</v>
+        <v>1.56671</v>
       </c>
       <c r="R52" s="159"/>
       <c r="S52" s="88">
@@ -46947,11 +47116,11 @@
       <c r="W52" s="72"/>
       <c r="Y52" s="154">
         <f t="shared" si="22"/>
-        <v>176736</v>
+        <v>226385</v>
       </c>
       <c r="Z52" s="168">
         <f t="shared" si="23"/>
-        <v>0.44184000000000001</v>
+        <v>0.56596249999999992</v>
       </c>
     </row>
     <row r="53" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -47008,11 +47177,11 @@
       <c r="O53" s="215"/>
       <c r="P53" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>149057</v>
+        <v>196215</v>
       </c>
       <c r="Q53" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1.49057</v>
+        <v>1.9621499999999998</v>
       </c>
       <c r="R53" s="159"/>
       <c r="S53" s="88">
@@ -47028,11 +47197,11 @@
       <c r="W53" s="72"/>
       <c r="Y53" s="154">
         <f t="shared" si="22"/>
-        <v>894850</v>
+        <v>942008</v>
       </c>
       <c r="Z53" s="168">
         <f t="shared" si="23"/>
-        <v>8.948500000000001</v>
+        <v>9.4200800000000005</v>
       </c>
     </row>
     <row r="54" spans="1:34" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -47170,11 +47339,11 @@
       <c r="O55" s="215"/>
       <c r="P55" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-79543</v>
+        <v>-95143</v>
       </c>
       <c r="Q55" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1.5908599999999997</v>
+        <v>-1.90286</v>
       </c>
       <c r="R55" s="159"/>
       <c r="S55" s="153">
@@ -47191,11 +47360,11 @@
       <c r="X55" s="132"/>
       <c r="Y55" s="154">
         <f t="shared" si="22"/>
-        <v>-325321</v>
+        <v>-340921</v>
       </c>
       <c r="Z55" s="168">
         <f t="shared" si="23"/>
-        <v>-6.5064200000000003</v>
+        <v>-6.8184199999999997</v>
       </c>
       <c r="AA55" s="132"/>
     </row>
@@ -47253,11 +47422,11 @@
       <c r="O56" s="215"/>
       <c r="P56" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-169498</v>
+        <v>-167198</v>
       </c>
       <c r="Q56" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.56499333333333335</v>
+        <v>-0.55732666666666664</v>
       </c>
       <c r="R56" s="159"/>
       <c r="S56" s="88">
@@ -47273,11 +47442,11 @@
       <c r="W56" s="72"/>
       <c r="Y56" s="154">
         <f t="shared" si="22"/>
-        <v>-4868473</v>
+        <v>-4866173</v>
       </c>
       <c r="Z56" s="168">
         <f t="shared" si="23"/>
-        <v>-16.228243333333335</v>
+        <v>-16.22057666666667</v>
       </c>
       <c r="AB56" s="132"/>
       <c r="AC56" s="132"/>
@@ -47507,11 +47676,11 @@
       <c r="O59" s="215"/>
       <c r="P59" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>30338</v>
+        <v>36613</v>
       </c>
       <c r="Q59" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.28616000000000003</v>
+        <v>0.41166000000000003</v>
       </c>
       <c r="R59" s="159"/>
       <c r="S59" s="88">
@@ -47528,11 +47697,11 @@
       <c r="X59" s="1"/>
       <c r="Y59" s="154">
         <f t="shared" si="22"/>
-        <v>67061</v>
+        <v>73336</v>
       </c>
       <c r="Z59" s="168">
         <f t="shared" si="23"/>
-        <v>0.61499333333333328</v>
+        <v>0.74049333333333334</v>
       </c>
       <c r="AB59" s="1"/>
       <c r="AC59" s="1"/>
@@ -47596,11 +47765,11 @@
       <c r="O60" s="215"/>
       <c r="P60" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>771307</v>
+        <v>851807</v>
       </c>
       <c r="Q60" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>7.7130700000000001</v>
+        <v>8.5180699999999998</v>
       </c>
       <c r="R60" s="159"/>
       <c r="S60" s="88">
@@ -47616,11 +47785,11 @@
       <c r="W60" s="72"/>
       <c r="Y60" s="154">
         <f t="shared" si="22"/>
-        <v>4321376</v>
+        <v>4401876</v>
       </c>
       <c r="Z60" s="168">
         <f t="shared" si="23"/>
-        <v>43.213760000000001</v>
+        <v>44.01876</v>
       </c>
       <c r="AB60" s="132"/>
       <c r="AC60" s="132"/>
@@ -47682,11 +47851,11 @@
       <c r="O61" s="215"/>
       <c r="P61" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-330</v>
+        <v>2934</v>
       </c>
       <c r="Q61" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-3.3000000000000029E-2</v>
+        <v>0.29339999999999999</v>
       </c>
       <c r="R61" s="159"/>
       <c r="S61" s="153">
@@ -47702,11 +47871,11 @@
       <c r="W61" s="150"/>
       <c r="Y61" s="154">
         <f t="shared" ref="Y61" si="37">M61+P61+S61+V61</f>
-        <v>-330</v>
+        <v>2934</v>
       </c>
       <c r="Z61" s="168">
         <f t="shared" ref="Z61" si="38">(N61+Q61+T61+W61)</f>
-        <v>-3.3000000000000029E-2</v>
+        <v>0.29339999999999999</v>
       </c>
     </row>
     <row r="62" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -47763,11 +47932,11 @@
       <c r="O62" s="215"/>
       <c r="P62" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-55605</v>
+        <v>23931</v>
       </c>
       <c r="Q62" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.18534999999999996</v>
+        <v>7.9770000000000035E-2</v>
       </c>
       <c r="R62" s="159"/>
       <c r="S62" s="88">
@@ -47783,11 +47952,11 @@
       <c r="W62" s="72"/>
       <c r="Y62" s="154">
         <f t="shared" si="22"/>
-        <v>617244</v>
+        <v>696780</v>
       </c>
       <c r="Z62" s="168">
         <f t="shared" si="23"/>
-        <v>2.0574799999999995</v>
+        <v>2.3225999999999996</v>
       </c>
       <c r="AB62" s="1"/>
       <c r="AC62" s="1"/>
@@ -47851,11 +48020,11 @@
       <c r="O63" s="215"/>
       <c r="P63" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>480335</v>
+        <v>319077</v>
       </c>
       <c r="Q63" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1.2008375</v>
+        <v>0.79769249999999992</v>
       </c>
       <c r="R63" s="159"/>
       <c r="S63" s="88">
@@ -47871,11 +48040,11 @@
       <c r="W63" s="72"/>
       <c r="Y63" s="154">
         <f t="shared" si="22"/>
-        <v>1155335</v>
+        <v>994077</v>
       </c>
       <c r="Z63" s="168">
         <f t="shared" si="23"/>
-        <v>2.8883375</v>
+        <v>2.4851925000000001</v>
       </c>
     </row>
     <row r="64" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -48014,11 +48183,11 @@
       <c r="O65" s="215"/>
       <c r="P65" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>368233</v>
+        <v>373533</v>
       </c>
       <c r="Q65" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.92058249999999986</v>
+        <v>0.93383249999999995</v>
       </c>
       <c r="R65" s="159"/>
       <c r="S65" s="153">
@@ -48035,11 +48204,11 @@
       <c r="X65" s="132"/>
       <c r="Y65" s="154">
         <f t="shared" si="22"/>
-        <v>892645</v>
+        <v>897945</v>
       </c>
       <c r="Z65" s="168">
         <f t="shared" si="23"/>
-        <v>2.2316124999999998</v>
+        <v>2.2448625</v>
       </c>
     </row>
     <row r="66" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -48176,11 +48345,11 @@
       <c r="O67" s="215"/>
       <c r="P67" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1375780</v>
+        <v>-1406580</v>
       </c>
       <c r="Q67" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1.37588</v>
+        <v>-1.4066799999999999</v>
       </c>
       <c r="R67" s="159"/>
       <c r="S67" s="153">
@@ -48196,11 +48365,11 @@
       <c r="W67" s="150"/>
       <c r="Y67" s="154">
         <f t="shared" ref="Y67" si="43">M67+P67+S67+V67</f>
-        <v>-1375780</v>
+        <v>-1406580</v>
       </c>
       <c r="Z67" s="168">
         <f t="shared" ref="Z67" si="44">(N67+Q67+T67+W67)</f>
-        <v>-1.37588</v>
+        <v>-1.4066799999999999</v>
       </c>
     </row>
     <row r="68" spans="1:26" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -48931,7 +49100,7 @@
       <c r="O77" s="122"/>
       <c r="P77" s="109">
         <f>SUM(P4:P74)</f>
-        <v>9453258</v>
+        <v>9679497</v>
       </c>
       <c r="Q77" s="122"/>
       <c r="R77" s="122"/>
@@ -48942,7 +49111,7 @@
       <c r="W77" s="50"/>
       <c r="Y77" s="154">
         <f>SUM(Y4:Y76)</f>
-        <v>29380363</v>
+        <v>29606602</v>
       </c>
       <c r="Z77" s="161"/>
     </row>
@@ -49397,1222 +49566,1222 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A56:C56 V4:W4 A27:F29 V20:W21 A13:C13 W48:W49 A3:F4 L2:L3 A48:F49 A52:C52 W22:W30 A80:F81 C16 W45:W46 W42 A42:H42 G41:H41 F16 F13 F70:F71 W58:W60 G58:J60 A66:J66 Y58:Y60 Y77:Z77 G13:H14 G7:J11 F53 F56:J56 Y56 W52:W53 H4:O4 M5:O5 G16:H18 Y4:Z11 K5:L11 A20:F24 D5:J5 F72:J74 A44:J44 Y66 Z56:Z60 G45:J53 K44:L53 A73:C73 A74:E74 A45:F46 E52:F52 A60:F60 Y34:Z36 M80:O82 M7:O11 A34:O36 R44:W44 R72:W74 R7:W9 R13:W16 R34:W36 R45:U46 R17:U17 R22:U30 R48:U53 U80:U82 A77:E77 A38:H39 A62:F62 K62:O66 Z62:Z66 Y62:Y63 G62:J63 R38:U43 M38:O53 I38:L43 Y38:Z53 W38:W39 G77:W78 G84:W84 K69:O74 G69:J69 W66:W68 R62:U71 G67:O68 Y67:Z74 A9 F9 I13:O18 Y13:Z18 Y55:Z55 R55:U60 K55:O60 G55:J55 W55:W56 Y20:Z32 G20:O32 A31:A32 P13:Q36 A7:F8">
-    <cfRule type="expression" dxfId="246" priority="448">
+    <cfRule type="expression" dxfId="245" priority="448">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V38:V39 V23:V24 V59 V48:V49 V56 V45:V46 V27:V29 G2:I3 V52 G4:H4">
-    <cfRule type="expression" dxfId="245" priority="447">
+    <cfRule type="expression" dxfId="244" priority="447">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J3">
-    <cfRule type="expression" dxfId="244" priority="444">
+    <cfRule type="expression" dxfId="243" priority="444">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V80:W81">
-    <cfRule type="expression" dxfId="243" priority="441">
+    <cfRule type="expression" dxfId="242" priority="441">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K3">
-    <cfRule type="expression" dxfId="242" priority="442">
+    <cfRule type="expression" dxfId="241" priority="442">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V60">
-    <cfRule type="expression" dxfId="241" priority="432">
+    <cfRule type="expression" dxfId="240" priority="432">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V22">
-    <cfRule type="expression" dxfId="240" priority="433">
+    <cfRule type="expression" dxfId="239" priority="433">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A53:C53 E53">
-    <cfRule type="expression" dxfId="239" priority="422">
+    <cfRule type="expression" dxfId="238" priority="422">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V53 V55">
-    <cfRule type="expression" dxfId="238" priority="420">
+    <cfRule type="expression" dxfId="237" priority="420">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E56">
-    <cfRule type="expression" dxfId="237" priority="418">
+    <cfRule type="expression" dxfId="236" priority="418">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V42">
-    <cfRule type="expression" dxfId="236" priority="409">
+    <cfRule type="expression" dxfId="235" priority="409">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A30:F30">
-    <cfRule type="expression" dxfId="235" priority="408">
+    <cfRule type="expression" dxfId="234" priority="408">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B72:C72">
-    <cfRule type="expression" dxfId="234" priority="380">
+    <cfRule type="expression" dxfId="233" priority="380">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V30">
-    <cfRule type="expression" dxfId="233" priority="406">
+    <cfRule type="expression" dxfId="232" priority="406">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26:E26">
-    <cfRule type="expression" dxfId="232" priority="405">
+    <cfRule type="expression" dxfId="231" priority="405">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V26">
-    <cfRule type="expression" dxfId="231" priority="403">
+    <cfRule type="expression" dxfId="230" priority="403">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A25:E25">
-    <cfRule type="expression" dxfId="230" priority="402">
+    <cfRule type="expression" dxfId="229" priority="402">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V25">
-    <cfRule type="expression" dxfId="229" priority="400">
+    <cfRule type="expression" dxfId="228" priority="400">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58:C58 E58:F58">
-    <cfRule type="expression" dxfId="228" priority="387">
+    <cfRule type="expression" dxfId="227" priority="387">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T4:U4 T20:U21">
-    <cfRule type="expression" dxfId="227" priority="331">
+    <cfRule type="expression" dxfId="226" priority="331">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A72">
-    <cfRule type="expression" dxfId="226" priority="378">
+    <cfRule type="expression" dxfId="225" priority="378">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S4:U4 S20:U21">
-    <cfRule type="expression" dxfId="225" priority="330">
+    <cfRule type="expression" dxfId="224" priority="330">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V58">
-    <cfRule type="expression" dxfId="224" priority="383">
+    <cfRule type="expression" dxfId="223" priority="383">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F25">
-    <cfRule type="expression" dxfId="223" priority="349">
+    <cfRule type="expression" dxfId="222" priority="349">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M20:O21 M34:O34">
-    <cfRule type="expression" dxfId="222" priority="347">
+    <cfRule type="expression" dxfId="221" priority="347">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:F17 A18:C18 E18:F18">
-    <cfRule type="expression" dxfId="221" priority="355">
+    <cfRule type="expression" dxfId="220" priority="355">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V17:W17">
-    <cfRule type="expression" dxfId="220" priority="354">
+    <cfRule type="expression" dxfId="219" priority="354">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R4 R20:R21">
-    <cfRule type="expression" dxfId="219" priority="339">
+    <cfRule type="expression" dxfId="218" priority="339">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R4 R20:R21">
-    <cfRule type="expression" dxfId="218" priority="338">
+    <cfRule type="expression" dxfId="217" priority="338">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V66:V68">
-    <cfRule type="expression" dxfId="217" priority="369">
+    <cfRule type="expression" dxfId="216" priority="369">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W62">
-    <cfRule type="expression" dxfId="216" priority="329">
+    <cfRule type="expression" dxfId="215" priority="329">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M35:O35">
-    <cfRule type="expression" dxfId="215" priority="340">
+    <cfRule type="expression" dxfId="214" priority="340">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F26">
-    <cfRule type="expression" dxfId="214" priority="350">
+    <cfRule type="expression" dxfId="213" priority="350">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N20:O21 N34:O34">
-    <cfRule type="expression" dxfId="213" priority="348">
+    <cfRule type="expression" dxfId="212" priority="348">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N35:O35">
-    <cfRule type="expression" dxfId="212" priority="341">
+    <cfRule type="expression" dxfId="211" priority="341">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V62">
-    <cfRule type="expression" dxfId="211" priority="328">
+    <cfRule type="expression" dxfId="210" priority="328">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M18:O18">
-    <cfRule type="expression" dxfId="210" priority="286">
+    <cfRule type="expression" dxfId="209" priority="286">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R18">
-    <cfRule type="expression" dxfId="209" priority="285">
+    <cfRule type="expression" dxfId="208" priority="285">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T18:U18">
-    <cfRule type="expression" dxfId="208" priority="283">
+    <cfRule type="expression" dxfId="207" priority="283">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31:F31 B32:C32 E32:F32">
-    <cfRule type="expression" dxfId="207" priority="275">
+    <cfRule type="expression" dxfId="206" priority="275">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W31">
-    <cfRule type="expression" dxfId="206" priority="274">
+    <cfRule type="expression" dxfId="205" priority="274">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V18:W18">
-    <cfRule type="expression" dxfId="205" priority="288">
+    <cfRule type="expression" dxfId="204" priority="288">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N18:O18">
-    <cfRule type="expression" dxfId="204" priority="287">
+    <cfRule type="expression" dxfId="203" priority="287">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R18">
-    <cfRule type="expression" dxfId="203" priority="284">
+    <cfRule type="expression" dxfId="202" priority="284">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S18:U18">
-    <cfRule type="expression" dxfId="202" priority="282">
+    <cfRule type="expression" dxfId="201" priority="282">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V31">
-    <cfRule type="expression" dxfId="201" priority="273">
+    <cfRule type="expression" dxfId="200" priority="273">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S31:U31">
-    <cfRule type="expression" dxfId="200" priority="267">
+    <cfRule type="expression" dxfId="199" priority="267">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N31:O31">
-    <cfRule type="expression" dxfId="199" priority="272">
+    <cfRule type="expression" dxfId="198" priority="272">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M31:O31">
-    <cfRule type="expression" dxfId="198" priority="271">
+    <cfRule type="expression" dxfId="197" priority="271">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T31:U31">
-    <cfRule type="expression" dxfId="197" priority="268">
+    <cfRule type="expression" dxfId="196" priority="268">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R31">
-    <cfRule type="expression" dxfId="196" priority="270">
+    <cfRule type="expression" dxfId="195" priority="270">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R31">
-    <cfRule type="expression" dxfId="195" priority="269">
+    <cfRule type="expression" dxfId="194" priority="269">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11:F11 A10:C10 E10:F10 F12">
-    <cfRule type="expression" dxfId="194" priority="260">
+    <cfRule type="expression" dxfId="193" priority="260">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V10:W11">
-    <cfRule type="expression" dxfId="193" priority="259">
+    <cfRule type="expression" dxfId="192" priority="259">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R10:R11">
-    <cfRule type="expression" dxfId="192" priority="256">
+    <cfRule type="expression" dxfId="191" priority="256">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R10:R11">
-    <cfRule type="expression" dxfId="191" priority="255">
+    <cfRule type="expression" dxfId="190" priority="255">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S10:U11">
-    <cfRule type="expression" dxfId="190" priority="253">
+    <cfRule type="expression" dxfId="189" priority="253">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N10:O11">
-    <cfRule type="expression" dxfId="189" priority="258">
+    <cfRule type="expression" dxfId="188" priority="258">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M10:O11">
-    <cfRule type="expression" dxfId="188" priority="257">
+    <cfRule type="expression" dxfId="187" priority="257">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T10:U11">
-    <cfRule type="expression" dxfId="187" priority="254">
+    <cfRule type="expression" dxfId="186" priority="254">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:C47 E47:F47">
-    <cfRule type="expression" dxfId="186" priority="246">
+    <cfRule type="expression" dxfId="185" priority="246">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W47">
-    <cfRule type="expression" dxfId="185" priority="245">
+    <cfRule type="expression" dxfId="184" priority="245">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V47">
-    <cfRule type="expression" dxfId="184" priority="244">
+    <cfRule type="expression" dxfId="183" priority="244">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T47:U47">
-    <cfRule type="expression" dxfId="183" priority="239">
+    <cfRule type="expression" dxfId="182" priority="239">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S47:U47">
-    <cfRule type="expression" dxfId="182" priority="238">
+    <cfRule type="expression" dxfId="181" priority="238">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M47:O47">
-    <cfRule type="expression" dxfId="181" priority="242">
+    <cfRule type="expression" dxfId="180" priority="242">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R47">
-    <cfRule type="expression" dxfId="180" priority="241">
+    <cfRule type="expression" dxfId="179" priority="241">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R47">
-    <cfRule type="expression" dxfId="179" priority="240">
+    <cfRule type="expression" dxfId="178" priority="240">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N47:O47">
-    <cfRule type="expression" dxfId="178" priority="243">
+    <cfRule type="expression" dxfId="177" priority="243">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A59:C59 E59:F59">
-    <cfRule type="expression" dxfId="177" priority="231">
+    <cfRule type="expression" dxfId="176" priority="231">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:C5">
-    <cfRule type="expression" dxfId="176" priority="227">
+    <cfRule type="expression" dxfId="175" priority="227">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V5:W5">
-    <cfRule type="expression" dxfId="175" priority="226">
+    <cfRule type="expression" dxfId="174" priority="226">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T5:U5">
-    <cfRule type="expression" dxfId="174" priority="220">
+    <cfRule type="expression" dxfId="173" priority="220">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S5:U5">
-    <cfRule type="expression" dxfId="173" priority="219">
+    <cfRule type="expression" dxfId="172" priority="219">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5:O5">
-    <cfRule type="expression" dxfId="172" priority="223">
+    <cfRule type="expression" dxfId="171" priority="223">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R5">
-    <cfRule type="expression" dxfId="171" priority="222">
+    <cfRule type="expression" dxfId="170" priority="222">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R5">
-    <cfRule type="expression" dxfId="170" priority="221">
+    <cfRule type="expression" dxfId="169" priority="221">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N5:O5">
-    <cfRule type="expression" dxfId="169" priority="224">
+    <cfRule type="expression" dxfId="168" priority="224">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A50:F51">
-    <cfRule type="expression" dxfId="168" priority="208">
+    <cfRule type="expression" dxfId="167" priority="208">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W50:W51">
-    <cfRule type="expression" dxfId="167" priority="207">
+    <cfRule type="expression" dxfId="166" priority="207">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V50:V51">
-    <cfRule type="expression" dxfId="166" priority="206">
+    <cfRule type="expression" dxfId="165" priority="206">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W32">
-    <cfRule type="expression" dxfId="165" priority="200">
+    <cfRule type="expression" dxfId="164" priority="200">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V32">
-    <cfRule type="expression" dxfId="164" priority="199">
+    <cfRule type="expression" dxfId="163" priority="199">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S32:U32">
-    <cfRule type="expression" dxfId="163" priority="193">
+    <cfRule type="expression" dxfId="162" priority="193">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N32:O32">
-    <cfRule type="expression" dxfId="162" priority="198">
+    <cfRule type="expression" dxfId="161" priority="198">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M32:O32">
-    <cfRule type="expression" dxfId="161" priority="197">
+    <cfRule type="expression" dxfId="160" priority="197">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T32:U32">
-    <cfRule type="expression" dxfId="160" priority="194">
+    <cfRule type="expression" dxfId="159" priority="194">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R32">
-    <cfRule type="expression" dxfId="159" priority="196">
+    <cfRule type="expression" dxfId="158" priority="196">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R32">
-    <cfRule type="expression" dxfId="158" priority="195">
+    <cfRule type="expression" dxfId="157" priority="195">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W63">
-    <cfRule type="expression" dxfId="157" priority="191">
+    <cfRule type="expression" dxfId="156" priority="191">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V63">
-    <cfRule type="expression" dxfId="156" priority="190">
+    <cfRule type="expression" dxfId="155" priority="190">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14:F14">
-    <cfRule type="expression" dxfId="155" priority="177">
+    <cfRule type="expression" dxfId="154" priority="177">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W41">
-    <cfRule type="expression" dxfId="154" priority="186">
+    <cfRule type="expression" dxfId="153" priority="186">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V41">
-    <cfRule type="expression" dxfId="153" priority="185">
+    <cfRule type="expression" dxfId="152" priority="185">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A69:C69 E69:F69">
-    <cfRule type="expression" dxfId="152" priority="175">
+    <cfRule type="expression" dxfId="151" priority="175">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W69">
-    <cfRule type="expression" dxfId="151" priority="174">
+    <cfRule type="expression" dxfId="150" priority="174">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V69">
-    <cfRule type="expression" dxfId="150" priority="173">
+    <cfRule type="expression" dxfId="149" priority="173">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G80:G81">
-    <cfRule type="expression" dxfId="149" priority="168">
+    <cfRule type="expression" dxfId="148" priority="168">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H80">
-    <cfRule type="expression" dxfId="148" priority="165">
+    <cfRule type="expression" dxfId="147" priority="165">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H81">
-    <cfRule type="expression" dxfId="147" priority="164">
+    <cfRule type="expression" dxfId="146" priority="164">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L79">
-    <cfRule type="expression" dxfId="146" priority="163">
+    <cfRule type="expression" dxfId="145" priority="163">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G79:I79">
-    <cfRule type="expression" dxfId="145" priority="162">
+    <cfRule type="expression" dxfId="144" priority="162">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J79">
-    <cfRule type="expression" dxfId="144" priority="161">
+    <cfRule type="expression" dxfId="143" priority="161">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K79">
-    <cfRule type="expression" dxfId="143" priority="160">
+    <cfRule type="expression" dxfId="142" priority="160">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y80:Z81">
-    <cfRule type="expression" dxfId="142" priority="147">
+    <cfRule type="expression" dxfId="141" priority="147">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40:F40">
-    <cfRule type="expression" dxfId="141" priority="157">
+    <cfRule type="expression" dxfId="140" priority="157">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A41:F41">
-    <cfRule type="expression" dxfId="140" priority="156">
+    <cfRule type="expression" dxfId="139" priority="156">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A43:F43">
-    <cfRule type="expression" dxfId="139" priority="155">
+    <cfRule type="expression" dxfId="138" priority="155">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W43 G43:H43">
-    <cfRule type="expression" dxfId="138" priority="154">
+    <cfRule type="expression" dxfId="137" priority="154">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V43">
-    <cfRule type="expression" dxfId="137" priority="153">
+    <cfRule type="expression" dxfId="136" priority="153">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W40 G40:H40">
-    <cfRule type="expression" dxfId="136" priority="152">
+    <cfRule type="expression" dxfId="135" priority="152">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V40">
-    <cfRule type="expression" dxfId="135" priority="151">
+    <cfRule type="expression" dxfId="134" priority="151">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D13:E13">
-    <cfRule type="expression" dxfId="134" priority="142">
+    <cfRule type="expression" dxfId="133" priority="142">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y84:Z84">
-    <cfRule type="expression" dxfId="133" priority="148">
+    <cfRule type="expression" dxfId="132" priority="148">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:B16">
-    <cfRule type="expression" dxfId="132" priority="146">
+    <cfRule type="expression" dxfId="131" priority="146">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15">
-    <cfRule type="expression" dxfId="131" priority="145">
+    <cfRule type="expression" dxfId="130" priority="145">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15">
-    <cfRule type="expression" dxfId="130" priority="144">
+    <cfRule type="expression" dxfId="129" priority="144">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D15:E16">
-    <cfRule type="expression" dxfId="129" priority="143">
+    <cfRule type="expression" dxfId="128" priority="143">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G15:H15">
-    <cfRule type="expression" dxfId="128" priority="141">
+    <cfRule type="expression" dxfId="127" priority="141">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J80:J81">
-    <cfRule type="expression" dxfId="127" priority="138">
+    <cfRule type="expression" dxfId="126" priority="138">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I80:J81">
-    <cfRule type="expression" dxfId="126" priority="137">
+    <cfRule type="expression" dxfId="125" priority="137">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A70:C71 E70:E71">
-    <cfRule type="expression" dxfId="125" priority="136">
+    <cfRule type="expression" dxfId="124" priority="136">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G70:J71 M70:O71">
-    <cfRule type="expression" dxfId="124" priority="135">
+    <cfRule type="expression" dxfId="123" priority="135">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W70:W71">
-    <cfRule type="expression" dxfId="123" priority="134">
+    <cfRule type="expression" dxfId="122" priority="134">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V70:V71">
-    <cfRule type="expression" dxfId="122" priority="133">
+    <cfRule type="expression" dxfId="121" priority="133">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V57">
-    <cfRule type="expression" dxfId="121" priority="130">
+    <cfRule type="expression" dxfId="120" priority="130">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A57:C57 E57:F57">
-    <cfRule type="expression" dxfId="120" priority="132">
+    <cfRule type="expression" dxfId="119" priority="132">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W57 Y57 G57:J57">
-    <cfRule type="expression" dxfId="119" priority="131">
+    <cfRule type="expression" dxfId="118" priority="131">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A64:A65">
-    <cfRule type="expression" dxfId="118" priority="129">
+    <cfRule type="expression" dxfId="117" priority="129">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A63:B63">
-    <cfRule type="expression" dxfId="117" priority="128">
+    <cfRule type="expression" dxfId="116" priority="128">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B64:B65">
-    <cfRule type="expression" dxfId="116" priority="127">
+    <cfRule type="expression" dxfId="115" priority="127">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M64:O65 G64:J65 Y64:Y65">
-    <cfRule type="expression" dxfId="115" priority="126">
+    <cfRule type="expression" dxfId="114" priority="126">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W64:W65">
-    <cfRule type="expression" dxfId="114" priority="124">
+    <cfRule type="expression" dxfId="113" priority="124">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V64:V65">
-    <cfRule type="expression" dxfId="113" priority="123">
+    <cfRule type="expression" dxfId="112" priority="123">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A6:C6 E6:F6">
-    <cfRule type="expression" dxfId="112" priority="122">
+    <cfRule type="expression" dxfId="111" priority="122">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G6:J6 M6:O6">
-    <cfRule type="expression" dxfId="111" priority="121">
+    <cfRule type="expression" dxfId="110" priority="121">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V6:W6">
-    <cfRule type="expression" dxfId="110" priority="120">
+    <cfRule type="expression" dxfId="109" priority="120">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T6:U6">
-    <cfRule type="expression" dxfId="109" priority="115">
+    <cfRule type="expression" dxfId="108" priority="115">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S6:U6">
-    <cfRule type="expression" dxfId="108" priority="114">
+    <cfRule type="expression" dxfId="107" priority="114">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M6:O6">
-    <cfRule type="expression" dxfId="107" priority="118">
+    <cfRule type="expression" dxfId="106" priority="118">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R6">
-    <cfRule type="expression" dxfId="106" priority="117">
+    <cfRule type="expression" dxfId="105" priority="117">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R6">
-    <cfRule type="expression" dxfId="105" priority="116">
+    <cfRule type="expression" dxfId="104" priority="116">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N6:O6">
-    <cfRule type="expression" dxfId="104" priority="119">
+    <cfRule type="expression" dxfId="103" priority="119">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A55:C55 E55:F55">
-    <cfRule type="expression" dxfId="103" priority="113">
+    <cfRule type="expression" dxfId="102" priority="113">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A82:F82">
-    <cfRule type="expression" dxfId="102" priority="111">
+    <cfRule type="expression" dxfId="101" priority="111">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V82:W82">
-    <cfRule type="expression" dxfId="101" priority="109">
+    <cfRule type="expression" dxfId="100" priority="109">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G82">
-    <cfRule type="expression" dxfId="100" priority="108">
+    <cfRule type="expression" dxfId="99" priority="108">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H82">
-    <cfRule type="expression" dxfId="99" priority="107">
+    <cfRule type="expression" dxfId="98" priority="107">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y82:Z82">
-    <cfRule type="expression" dxfId="98" priority="106">
+    <cfRule type="expression" dxfId="97" priority="106">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J82">
-    <cfRule type="expression" dxfId="97" priority="105">
+    <cfRule type="expression" dxfId="96" priority="105">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I82:J82">
-    <cfRule type="expression" dxfId="96" priority="104">
+    <cfRule type="expression" dxfId="95" priority="104">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K80:L82">
-    <cfRule type="expression" dxfId="95" priority="102">
+    <cfRule type="expression" dxfId="94" priority="102">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S19:U19">
-    <cfRule type="expression" dxfId="94" priority="92">
+    <cfRule type="expression" dxfId="93" priority="92">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19:F19">
-    <cfRule type="expression" dxfId="93" priority="100">
+    <cfRule type="expression" dxfId="92" priority="100">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y19:Z19 G19:O19">
-    <cfRule type="expression" dxfId="92" priority="99">
+    <cfRule type="expression" dxfId="91" priority="99">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M19:O19">
-    <cfRule type="expression" dxfId="91" priority="96">
+    <cfRule type="expression" dxfId="90" priority="96">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R19">
-    <cfRule type="expression" dxfId="90" priority="95">
+    <cfRule type="expression" dxfId="89" priority="95">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T19:U19">
-    <cfRule type="expression" dxfId="89" priority="93">
+    <cfRule type="expression" dxfId="88" priority="93">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V19:W19">
-    <cfRule type="expression" dxfId="88" priority="98">
+    <cfRule type="expression" dxfId="87" priority="98">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N19:O19">
-    <cfRule type="expression" dxfId="87" priority="97">
+    <cfRule type="expression" dxfId="86" priority="97">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R19">
-    <cfRule type="expression" dxfId="86" priority="94">
+    <cfRule type="expression" dxfId="85" priority="94">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E72:E73">
-    <cfRule type="expression" dxfId="85" priority="91">
+    <cfRule type="expression" dxfId="84" priority="91">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F64:F65">
-    <cfRule type="expression" dxfId="84" priority="90">
+    <cfRule type="expression" dxfId="83" priority="90">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F63">
-    <cfRule type="expression" dxfId="83" priority="89">
+    <cfRule type="expression" dxfId="82" priority="89">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D63:E63 C64:E65">
-    <cfRule type="expression" dxfId="82" priority="88">
+    <cfRule type="expression" dxfId="81" priority="88">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D10">
-    <cfRule type="expression" dxfId="81" priority="87">
+    <cfRule type="expression" dxfId="80" priority="87">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6">
-    <cfRule type="expression" dxfId="80" priority="86">
+    <cfRule type="expression" dxfId="79" priority="86">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D18">
-    <cfRule type="expression" dxfId="79" priority="85">
+    <cfRule type="expression" dxfId="78" priority="85">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D32">
-    <cfRule type="expression" dxfId="78" priority="84">
+    <cfRule type="expression" dxfId="77" priority="84">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D70:D71">
-    <cfRule type="expression" dxfId="77" priority="72">
+    <cfRule type="expression" dxfId="76" priority="72">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D47">
-    <cfRule type="expression" dxfId="76" priority="82">
+    <cfRule type="expression" dxfId="75" priority="82">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D53 D55">
-    <cfRule type="expression" dxfId="75" priority="81">
+    <cfRule type="expression" dxfId="74" priority="81">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D52">
-    <cfRule type="expression" dxfId="74" priority="80">
+    <cfRule type="expression" dxfId="73" priority="80">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D56">
-    <cfRule type="expression" dxfId="73" priority="79">
+    <cfRule type="expression" dxfId="72" priority="79">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D57">
-    <cfRule type="expression" dxfId="72" priority="78">
+    <cfRule type="expression" dxfId="71" priority="78">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D58">
-    <cfRule type="expression" dxfId="71" priority="77">
+    <cfRule type="expression" dxfId="70" priority="77">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D59">
-    <cfRule type="expression" dxfId="70" priority="76">
+    <cfRule type="expression" dxfId="69" priority="76">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D73">
-    <cfRule type="expression" dxfId="69" priority="75">
+    <cfRule type="expression" dxfId="68" priority="75">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D72">
-    <cfRule type="expression" dxfId="68" priority="74">
+    <cfRule type="expression" dxfId="67" priority="74">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D69">
-    <cfRule type="expression" dxfId="67" priority="73">
+    <cfRule type="expression" dxfId="66" priority="73">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A33:F33">
-    <cfRule type="expression" dxfId="66" priority="71">
+    <cfRule type="expression" dxfId="65" priority="71">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G33:O33 Y33:Z33">
-    <cfRule type="expression" dxfId="65" priority="70">
+    <cfRule type="expression" dxfId="64" priority="70">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W33">
-    <cfRule type="expression" dxfId="64" priority="69">
+    <cfRule type="expression" dxfId="63" priority="69">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V33">
-    <cfRule type="expression" dxfId="63" priority="68">
+    <cfRule type="expression" dxfId="62" priority="68">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S33:U33">
-    <cfRule type="expression" dxfId="62" priority="62">
+    <cfRule type="expression" dxfId="61" priority="62">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N33:O33">
-    <cfRule type="expression" dxfId="61" priority="67">
+    <cfRule type="expression" dxfId="60" priority="67">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M33:O33">
-    <cfRule type="expression" dxfId="60" priority="66">
+    <cfRule type="expression" dxfId="59" priority="66">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T33:U33">
-    <cfRule type="expression" dxfId="59" priority="63">
+    <cfRule type="expression" dxfId="58" priority="63">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R33">
-    <cfRule type="expression" dxfId="58" priority="65">
+    <cfRule type="expression" dxfId="57" priority="65">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R33">
-    <cfRule type="expression" dxfId="57" priority="64">
+    <cfRule type="expression" dxfId="56" priority="64">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q4:Q11 Q38:Q53 Q62:Q74 Q55:Q60">
-    <cfRule type="expression" dxfId="56" priority="59">
+    <cfRule type="expression" dxfId="55" priority="59">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P4:Q11 P38:Q53 P62:Q74 P55:Q60">
-    <cfRule type="expression" dxfId="55" priority="58">
+    <cfRule type="expression" dxfId="54" priority="58">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R80:T82">
-    <cfRule type="expression" dxfId="54" priority="57">
+    <cfRule type="expression" dxfId="53" priority="57">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q80:Q82">
-    <cfRule type="expression" dxfId="53" priority="56">
+    <cfRule type="expression" dxfId="52" priority="56">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P80:Q82">
-    <cfRule type="expression" dxfId="52" priority="55">
+    <cfRule type="expression" dxfId="51" priority="55">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A76:F76">
-    <cfRule type="expression" dxfId="51" priority="54">
+    <cfRule type="expression" dxfId="50" priority="54">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A75:F75">
-    <cfRule type="expression" dxfId="50" priority="53">
+    <cfRule type="expression" dxfId="49" priority="53">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G75:O76 Y75:Z76 R75:W76">
-    <cfRule type="expression" dxfId="49" priority="52">
+    <cfRule type="expression" dxfId="48" priority="52">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q75:Q76">
-    <cfRule type="expression" dxfId="48" priority="51">
+    <cfRule type="expression" dxfId="47" priority="51">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P75:Q76">
-    <cfRule type="expression" dxfId="47" priority="50">
+    <cfRule type="expression" dxfId="46" priority="50">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P37:Q37">
-    <cfRule type="expression" dxfId="46" priority="39">
+    <cfRule type="expression" dxfId="45" priority="39">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A37:F37">
-    <cfRule type="expression" dxfId="45" priority="48">
+    <cfRule type="expression" dxfId="44" priority="48">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P83:Q83">
-    <cfRule type="expression" dxfId="44" priority="24">
+    <cfRule type="expression" dxfId="43" priority="24">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61:F61">
-    <cfRule type="expression" dxfId="43" priority="46">
+    <cfRule type="expression" dxfId="42" priority="46">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W61 Y61:Z61 G61:O61 R61:U61">
-    <cfRule type="expression" dxfId="42" priority="45">
+    <cfRule type="expression" dxfId="41" priority="45">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V61">
-    <cfRule type="expression" dxfId="41" priority="44">
+    <cfRule type="expression" dxfId="40" priority="44">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q61">
-    <cfRule type="expression" dxfId="40" priority="43">
+    <cfRule type="expression" dxfId="39" priority="43">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P61:Q61">
-    <cfRule type="expression" dxfId="39" priority="42">
+    <cfRule type="expression" dxfId="38" priority="42">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y37:Z37 G37:O37 R37:W37">
-    <cfRule type="expression" dxfId="38" priority="41">
+    <cfRule type="expression" dxfId="37" priority="41">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q37">
-    <cfRule type="expression" dxfId="37" priority="40">
+    <cfRule type="expression" dxfId="36" priority="40">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q83">
-    <cfRule type="expression" dxfId="36" priority="25">
+    <cfRule type="expression" dxfId="35" priority="25">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F83">
-    <cfRule type="expression" dxfId="35" priority="36">
+    <cfRule type="expression" dxfId="34" priority="36">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A83:E83">
-    <cfRule type="expression" dxfId="34" priority="35">
+    <cfRule type="expression" dxfId="33" priority="35">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M83:O83 U83">
-    <cfRule type="expression" dxfId="33" priority="34">
+    <cfRule type="expression" dxfId="32" priority="34">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V83:W83">
-    <cfRule type="expression" dxfId="32" priority="33">
+    <cfRule type="expression" dxfId="31" priority="33">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G83">
-    <cfRule type="expression" dxfId="31" priority="32">
+    <cfRule type="expression" dxfId="30" priority="32">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H83">
-    <cfRule type="expression" dxfId="30" priority="31">
+    <cfRule type="expression" dxfId="29" priority="31">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y83:Z83">
-    <cfRule type="expression" dxfId="29" priority="30">
+    <cfRule type="expression" dxfId="28" priority="30">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J83">
-    <cfRule type="expression" dxfId="28" priority="29">
+    <cfRule type="expression" dxfId="27" priority="29">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I83:J83">
-    <cfRule type="expression" dxfId="27" priority="28">
+    <cfRule type="expression" dxfId="26" priority="28">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K83:L83">
-    <cfRule type="expression" dxfId="26" priority="27">
+    <cfRule type="expression" dxfId="25" priority="27">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R83:T83">
-    <cfRule type="expression" dxfId="25" priority="26">
+    <cfRule type="expression" dxfId="24" priority="26">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F67:F68">
-    <cfRule type="expression" dxfId="24" priority="23">
+    <cfRule type="expression" dxfId="23" priority="23">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A67:E67 A68">
-    <cfRule type="expression" dxfId="23" priority="22">
+    <cfRule type="expression" dxfId="22" priority="22">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68:E68">
-    <cfRule type="expression" dxfId="22" priority="21">
+    <cfRule type="expression" dxfId="21" priority="21">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9:E9">
-    <cfRule type="expression" dxfId="21" priority="20">
+    <cfRule type="expression" dxfId="20" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12:B12 D12:E12">
-    <cfRule type="expression" dxfId="20" priority="19">
+    <cfRule type="expression" dxfId="19" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C12">
-    <cfRule type="expression" dxfId="19" priority="18">
+    <cfRule type="expression" dxfId="18" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y12:Z12 G12:O12">
-    <cfRule type="expression" dxfId="18" priority="17">
+    <cfRule type="expression" dxfId="17" priority="17">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V12:W12">
-    <cfRule type="expression" dxfId="17" priority="16">
+    <cfRule type="expression" dxfId="16" priority="16">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R12">
-    <cfRule type="expression" dxfId="16" priority="13">
+    <cfRule type="expression" dxfId="15" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R12">
-    <cfRule type="expression" dxfId="15" priority="12">
+    <cfRule type="expression" dxfId="14" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S12:U12">
-    <cfRule type="expression" dxfId="14" priority="10">
+    <cfRule type="expression" dxfId="13" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N12:O12">
-    <cfRule type="expression" dxfId="13" priority="15">
+    <cfRule type="expression" dxfId="12" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M12:O12">
-    <cfRule type="expression" dxfId="12" priority="14">
+    <cfRule type="expression" dxfId="11" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T12:U12">
-    <cfRule type="expression" dxfId="11" priority="11">
+    <cfRule type="expression" dxfId="10" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q12">
-    <cfRule type="expression" dxfId="10" priority="9">
+    <cfRule type="expression" dxfId="9" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P12:Q12">
-    <cfRule type="expression" dxfId="9" priority="8">
+    <cfRule type="expression" dxfId="8" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A54:C54 E54:F54">
-    <cfRule type="expression" dxfId="8" priority="7">
+    <cfRule type="expression" dxfId="7" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P54:Q54">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D54">
-    <cfRule type="expression" dxfId="6" priority="5">
+    <cfRule type="expression" dxfId="5" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W54 R54:U54 G54:O54 Y54:Z54">
-    <cfRule type="expression" dxfId="5" priority="4">
+    <cfRule type="expression" dxfId="4" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V54">
-    <cfRule type="expression" dxfId="4" priority="3">
+    <cfRule type="expression" dxfId="3" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q54">
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="2" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Quant Strategy(2026-27).xlsx
+++ b/Quant Strategy(2026-27).xlsx
@@ -16,16 +16,12 @@
     <sheet name="APR-2026" sheetId="36" r:id="rId7"/>
     <sheet name="FY-(26-27)Q1" sheetId="32" r:id="rId8"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId9"/>
-    <externalReference r:id="rId10"/>
-  </externalReferences>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2647" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2648" uniqueCount="322">
   <si>
     <t>Sudeep</t>
   </si>
@@ -2328,28 +2324,7 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="450">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="447">
     <dxf>
       <fill>
         <patternFill>
@@ -5497,32 +5472,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="SEP-2026"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="AUG-2026"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -5810,7 +5759,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X66"/>
+  <dimension ref="A1:Y66"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" style="133" customWidth="1" outlineLevel="1"/>
@@ -5820,19 +5769,19 @@
     <col min="5" max="5" width="9.42578125" style="133" customWidth="1"/>
     <col min="6" max="6" width="6.5703125" style="133" customWidth="1"/>
     <col min="7" max="7" width="1.7109375" style="133" customWidth="1"/>
-    <col min="8" max="10" width="13.42578125" style="133" customWidth="1" outlineLevel="1"/>
-    <col min="11" max="11" width="11.28515625" style="133" customWidth="1"/>
-    <col min="12" max="12" width="10.42578125" style="133" customWidth="1" outlineLevel="1"/>
-    <col min="13" max="13" width="10.7109375" style="133" customWidth="1" outlineLevel="1"/>
-    <col min="14" max="19" width="9.140625" style="133"/>
-    <col min="20" max="20" width="14.140625" style="133" customWidth="1"/>
-    <col min="21" max="21" width="12" style="133" customWidth="1"/>
-    <col min="22" max="22" width="15.85546875" style="133" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="133"/>
+    <col min="8" max="11" width="13.42578125" style="133" customWidth="1" outlineLevel="1"/>
+    <col min="12" max="12" width="11.28515625" style="133" customWidth="1"/>
+    <col min="13" max="13" width="10.42578125" style="133" customWidth="1" outlineLevel="1"/>
+    <col min="14" max="14" width="10.7109375" style="133" customWidth="1" outlineLevel="1"/>
+    <col min="15" max="20" width="9.140625" style="133"/>
+    <col min="21" max="21" width="14.140625" style="133" customWidth="1"/>
+    <col min="22" max="22" width="12" style="133" customWidth="1"/>
+    <col min="23" max="23" width="15.85546875" style="133" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="133"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G2" s="221"/>
       <c r="H2" s="222">
         <v>46266</v>
@@ -5843,15 +5792,18 @@
       <c r="J2" s="256">
         <v>46268</v>
       </c>
-      <c r="K2" s="183"/>
-      <c r="L2" s="184" t="s">
+      <c r="K2" s="256">
+        <v>46269</v>
+      </c>
+      <c r="L2" s="183"/>
+      <c r="M2" s="184" t="s">
         <v>281</v>
       </c>
-      <c r="M2" s="185" t="s">
+      <c r="N2" s="185" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="186" t="s">
         <v>54</v>
       </c>
@@ -5880,17 +5832,20 @@
       <c r="J3" s="179" t="s">
         <v>236</v>
       </c>
-      <c r="K3" s="180"/>
-      <c r="L3" s="189"/>
-      <c r="M3" s="180"/>
-      <c r="T3" s="133" t="s">
+      <c r="K3" s="179" t="s">
+        <v>235</v>
+      </c>
+      <c r="L3" s="180"/>
+      <c r="M3" s="189"/>
+      <c r="N3" s="180"/>
+      <c r="U3" s="133" t="s">
         <v>198</v>
       </c>
-      <c r="U3" s="133">
+      <c r="V3" s="133">
         <v>13780</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="142" t="s">
         <v>216</v>
       </c>
@@ -5919,23 +5874,26 @@
       <c r="J4" s="158">
         <v>1600</v>
       </c>
-      <c r="K4" s="211"/>
-      <c r="L4" s="171">
-        <f t="shared" ref="L4:L30" si="0">SUM(H4:K4)</f>
-        <v>-11762</v>
-      </c>
-      <c r="M4" s="149">
-        <f t="shared" ref="M4:M30" si="1">IFERROR(L4/F4*100,0)/10000000</f>
-        <v>-0.23524</v>
-      </c>
-      <c r="T4" s="133" t="s">
+      <c r="K4" s="158">
+        <v>-649</v>
+      </c>
+      <c r="L4" s="211"/>
+      <c r="M4" s="171">
+        <f t="shared" ref="M4:M30" si="0">SUM(H4:L4)</f>
+        <v>-12411</v>
+      </c>
+      <c r="N4" s="149">
+        <f t="shared" ref="N4:N30" si="1">IFERROR(M4/F4*100,0)/10000000</f>
+        <v>-0.24822</v>
+      </c>
+      <c r="U4" s="133" t="s">
         <v>170</v>
       </c>
-      <c r="U4" s="133">
+      <c r="V4" s="133">
         <v>2865</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="142" t="s">
         <v>30</v>
       </c>
@@ -5964,17 +5922,20 @@
       <c r="J5" s="147">
         <v>31240</v>
       </c>
-      <c r="K5" s="174"/>
-      <c r="L5" s="171">
+      <c r="K5" s="147">
+        <v>73349</v>
+      </c>
+      <c r="L5" s="174"/>
+      <c r="M5" s="171">
         <f t="shared" si="0"/>
-        <v>-108180</v>
-      </c>
-      <c r="M5" s="149">
+        <v>-34831</v>
+      </c>
+      <c r="N5" s="149">
         <f t="shared" si="1"/>
-        <v>-0.36059999999999998</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+        <v>-0.11610333333333335</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="142" t="s">
         <v>177</v>
       </c>
@@ -6003,17 +5964,20 @@
       <c r="J6" s="147">
         <v>0</v>
       </c>
-      <c r="K6" s="174"/>
-      <c r="L6" s="171">
+      <c r="K6" s="147">
+        <v>0</v>
+      </c>
+      <c r="L6" s="174"/>
+      <c r="M6" s="171">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M6" s="149">
+      <c r="N6" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" s="142"/>
       <c r="B7" s="141" t="s">
         <v>309</v>
@@ -6040,17 +6004,20 @@
       <c r="J7" s="147">
         <v>0</v>
       </c>
-      <c r="K7" s="174"/>
-      <c r="L7" s="171">
+      <c r="K7" s="147">
+        <v>37000</v>
+      </c>
+      <c r="L7" s="174"/>
+      <c r="M7" s="171">
         <f t="shared" si="0"/>
-        <v>-44700</v>
-      </c>
-      <c r="M7" s="149">
+        <v>-7700</v>
+      </c>
+      <c r="N7" s="149">
         <f t="shared" si="1"/>
-        <v>-0.44700000000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>-7.6999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="142" t="s">
         <v>134</v>
       </c>
@@ -6079,21 +6046,24 @@
       <c r="J8" s="147">
         <v>-45278</v>
       </c>
-      <c r="K8" s="174"/>
-      <c r="L8" s="171">
+      <c r="K8" s="147">
+        <v>-46000</v>
+      </c>
+      <c r="L8" s="174"/>
+      <c r="M8" s="171">
         <f t="shared" si="0"/>
-        <v>107757</v>
-      </c>
-      <c r="M8" s="149">
+        <v>61757</v>
+      </c>
+      <c r="N8" s="149">
         <f t="shared" si="1"/>
-        <v>0.35919000000000001</v>
-      </c>
-      <c r="O8" s="5"/>
-      <c r="P8" s="134">
-        <v>-153157</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+        <v>0.20585666666666669</v>
+      </c>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="134">
+        <v>-7168</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" s="142" t="s">
         <v>217</v>
       </c>
@@ -6122,21 +6092,24 @@
       <c r="J9" s="147">
         <v>36650</v>
       </c>
-      <c r="K9" s="174"/>
-      <c r="L9" s="171">
+      <c r="K9" s="147">
+        <v>-5025</v>
+      </c>
+      <c r="L9" s="174"/>
+      <c r="M9" s="171">
         <f t="shared" si="0"/>
-        <v>81548</v>
-      </c>
-      <c r="M9" s="149">
+        <v>76523</v>
+      </c>
+      <c r="N9" s="149">
         <f t="shared" si="1"/>
-        <v>0.54365333333333343</v>
-      </c>
-      <c r="O9" s="134">
-        <v>2843927</v>
-      </c>
-      <c r="P9" s="134"/>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+        <v>0.51015333333333335</v>
+      </c>
+      <c r="P9" s="134">
+        <v>512493</v>
+      </c>
+      <c r="Q9" s="134"/>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" s="142" t="s">
         <v>313</v>
       </c>
@@ -6163,24 +6136,27 @@
       <c r="J10" s="147">
         <v>21640</v>
       </c>
-      <c r="K10" s="174"/>
-      <c r="L10" s="171">
+      <c r="K10" s="147">
+        <v>2000</v>
+      </c>
+      <c r="L10" s="174"/>
+      <c r="M10" s="171">
         <f t="shared" si="0"/>
-        <v>8274</v>
-      </c>
-      <c r="M10" s="149">
+        <v>10274</v>
+      </c>
+      <c r="N10" s="149">
         <f t="shared" si="1"/>
-        <v>0.13789999999999999</v>
-      </c>
-      <c r="O10" s="134">
-        <v>2690770</v>
+        <v>0.17123333333333335</v>
       </c>
       <c r="P10" s="134">
-        <f>(O10+O9)/10000000*13780</f>
-        <v>7626.8124659999994</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+        <v>505325</v>
+      </c>
+      <c r="Q10" s="134">
+        <f>(P10+P9)/10000000*13780</f>
+        <v>1402.5532040000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" s="143" t="s">
         <v>35</v>
       </c>
@@ -6209,19 +6185,22 @@
       <c r="J11" s="147">
         <v>0</v>
       </c>
-      <c r="K11" s="174"/>
-      <c r="L11" s="171">
+      <c r="K11" s="147">
+        <v>27700</v>
+      </c>
+      <c r="L11" s="174"/>
+      <c r="M11" s="171">
         <f t="shared" si="0"/>
-        <v>-413740</v>
-      </c>
-      <c r="M11" s="149">
+        <v>-386040</v>
+      </c>
+      <c r="N11" s="149">
         <f t="shared" si="1"/>
-        <v>-0.27582666666666672</v>
-      </c>
-      <c r="O11" s="134"/>
+        <v>-0.25735999999999998</v>
+      </c>
       <c r="P11" s="134"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="Q11" s="134"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="143" t="s">
         <v>137</v>
       </c>
@@ -6250,19 +6229,22 @@
       <c r="J12" s="147">
         <v>-50942</v>
       </c>
-      <c r="K12" s="174"/>
-      <c r="L12" s="171">
+      <c r="K12" s="147">
+        <v>0</v>
+      </c>
+      <c r="L12" s="174"/>
+      <c r="M12" s="171">
         <f t="shared" si="0"/>
         <v>-112135</v>
       </c>
-      <c r="M12" s="149">
+      <c r="N12" s="149">
         <f t="shared" si="1"/>
         <v>-0.18689166666666668</v>
       </c>
-      <c r="O12" s="134"/>
       <c r="P12" s="134"/>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="Q12" s="134"/>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="143" t="s">
         <v>42</v>
       </c>
@@ -6291,19 +6273,22 @@
       <c r="J13" s="147">
         <v>3000</v>
       </c>
-      <c r="K13" s="174"/>
-      <c r="L13" s="171">
+      <c r="K13" s="147">
+        <v>1467</v>
+      </c>
+      <c r="L13" s="174"/>
+      <c r="M13" s="171">
         <f t="shared" si="0"/>
-        <v>-4107</v>
-      </c>
-      <c r="M13" s="149">
+        <v>-2640</v>
+      </c>
+      <c r="N13" s="149">
         <f t="shared" si="1"/>
-        <v>-4.1070000000000002E-2</v>
-      </c>
-      <c r="O13" s="134"/>
+        <v>-2.64E-2</v>
+      </c>
       <c r="P13" s="134"/>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="Q13" s="134"/>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="142" t="s">
         <v>212</v>
       </c>
@@ -6332,19 +6317,22 @@
       <c r="J14" s="147">
         <v>-3828</v>
       </c>
-      <c r="K14" s="174"/>
-      <c r="L14" s="171">
+      <c r="K14" s="147">
+        <v>8298</v>
+      </c>
+      <c r="L14" s="174"/>
+      <c r="M14" s="171">
         <f t="shared" si="0"/>
-        <v>-3104</v>
-      </c>
-      <c r="M14" s="149">
+        <v>5194</v>
+      </c>
+      <c r="N14" s="149">
         <f t="shared" si="1"/>
-        <v>-1.2415999999999998E-2</v>
-      </c>
-      <c r="O14" s="134"/>
+        <v>2.0775999999999999E-2</v>
+      </c>
       <c r="P14" s="134"/>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="Q14" s="134"/>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="142" t="s">
         <v>51</v>
       </c>
@@ -6373,29 +6361,32 @@
       <c r="J15" s="147">
         <v>-100</v>
       </c>
-      <c r="K15" s="174"/>
-      <c r="L15" s="171">
+      <c r="K15" s="147">
+        <v>11194</v>
+      </c>
+      <c r="L15" s="174"/>
+      <c r="M15" s="171">
         <f t="shared" si="0"/>
-        <v>-4997</v>
-      </c>
-      <c r="M15" s="149">
+        <v>6197</v>
+      </c>
+      <c r="N15" s="149">
         <f t="shared" si="1"/>
-        <v>-2.2713636363636359E-2</v>
-      </c>
-      <c r="O15" s="134"/>
-      <c r="P15" s="193">
-        <f>P8-P10</f>
-        <v>-160783.812466</v>
-      </c>
-      <c r="S15" s="133">
+        <v>2.8168181818181818E-2</v>
+      </c>
+      <c r="P15" s="134"/>
+      <c r="Q15" s="193">
+        <f>Q8-Q10</f>
+        <v>-8570.5532039999998</v>
+      </c>
+      <c r="T15" s="133">
         <v>116185</v>
       </c>
-      <c r="U15" s="133">
-        <f>S15+P15</f>
-        <v>-44598.812466000003</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V15" s="133">
+        <f>T15+Q15</f>
+        <v>107614.446796</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" s="142" t="s">
         <v>43</v>
       </c>
@@ -6424,17 +6415,20 @@
       <c r="J16" s="147">
         <v>7937</v>
       </c>
-      <c r="K16" s="174"/>
-      <c r="L16" s="171">
+      <c r="K16" s="147">
+        <v>5065</v>
+      </c>
+      <c r="L16" s="174"/>
+      <c r="M16" s="171">
         <f t="shared" si="0"/>
-        <v>-6421</v>
-      </c>
-      <c r="M16" s="149">
+        <v>-1356</v>
+      </c>
+      <c r="N16" s="149">
         <f t="shared" si="1"/>
-        <v>-6.4210000000000003E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+        <v>-1.3559999999999999E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17" s="142" t="s">
         <v>24</v>
       </c>
@@ -6463,28 +6457,31 @@
       <c r="J17" s="147">
         <v>0</v>
       </c>
-      <c r="K17" s="174"/>
-      <c r="L17" s="171">
+      <c r="K17" s="147">
+        <v>0</v>
+      </c>
+      <c r="L17" s="174"/>
+      <c r="M17" s="171">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M17" s="149">
+      <c r="N17" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="U17" s="133">
+      <c r="V17" s="133">
         <v>4000000</v>
       </c>
-      <c r="V17" s="133">
-        <f>U17*7/100</f>
+      <c r="W17" s="133">
+        <f>V17*7/100</f>
         <v>280000</v>
       </c>
-      <c r="X17" s="133">
+      <c r="Y17" s="133">
         <f>15*12</f>
         <v>180</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" s="142" t="s">
         <v>23</v>
       </c>
@@ -6513,21 +6510,24 @@
       <c r="J18" s="147">
         <v>0</v>
       </c>
-      <c r="K18" s="174"/>
-      <c r="L18" s="171">
+      <c r="K18" s="147">
+        <v>0</v>
+      </c>
+      <c r="L18" s="174"/>
+      <c r="M18" s="171">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M18" s="149">
+      <c r="N18" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="V18" s="133">
-        <f>V17/12</f>
+      <c r="W18" s="133">
+        <f>W17/12</f>
         <v>23333.333333333332</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19" s="142" t="s">
         <v>165</v>
       </c>
@@ -6556,17 +6556,20 @@
       <c r="J19" s="147">
         <v>17400</v>
       </c>
-      <c r="K19" s="174"/>
-      <c r="L19" s="171">
+      <c r="K19" s="147">
+        <v>7586</v>
+      </c>
+      <c r="L19" s="174"/>
+      <c r="M19" s="171">
         <f t="shared" si="0"/>
-        <v>2934</v>
-      </c>
-      <c r="M19" s="149">
+        <v>10520</v>
+      </c>
+      <c r="N19" s="149">
         <f t="shared" si="1"/>
-        <v>1.9560000000000001E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+        <v>7.0133333333333325E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20" s="142" t="s">
         <v>110</v>
       </c>
@@ -6595,17 +6598,20 @@
       <c r="J20" s="147">
         <v>-11491</v>
       </c>
-      <c r="K20" s="174"/>
-      <c r="L20" s="171">
+      <c r="K20" s="147">
+        <v>0</v>
+      </c>
+      <c r="L20" s="174"/>
+      <c r="M20" s="171">
         <f t="shared" si="0"/>
         <v>-2058</v>
       </c>
-      <c r="M20" s="149">
+      <c r="N20" s="149">
         <f t="shared" si="1"/>
         <v>-1.8709090909090908E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" s="142" t="s">
         <v>319</v>
       </c>
@@ -6634,17 +6640,20 @@
       <c r="J21" s="147">
         <v>2500</v>
       </c>
-      <c r="K21" s="174"/>
-      <c r="L21" s="171">
+      <c r="K21" s="147">
+        <v>-8570</v>
+      </c>
+      <c r="L21" s="174"/>
+      <c r="M21" s="171">
         <f t="shared" si="0"/>
-        <v>3771</v>
-      </c>
-      <c r="M21" s="149">
+        <v>-4799</v>
+      </c>
+      <c r="N21" s="149">
         <f t="shared" si="1"/>
-        <v>0.15084</v>
-      </c>
-    </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+        <v>-0.19195999999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22" s="142" t="s">
         <v>316</v>
       </c>
@@ -6673,17 +6682,20 @@
       <c r="J22" s="147">
         <v>2574</v>
       </c>
-      <c r="K22" s="174"/>
-      <c r="L22" s="171">
+      <c r="K22" s="147">
+        <v>-1344</v>
+      </c>
+      <c r="L22" s="174"/>
+      <c r="M22" s="171">
         <f t="shared" si="0"/>
-        <v>8479</v>
-      </c>
-      <c r="M22" s="149">
+        <v>7135</v>
+      </c>
+      <c r="N22" s="149">
         <f t="shared" si="1"/>
-        <v>4.2395000000000002E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+        <v>3.5674999999999998E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23" s="142" t="s">
         <v>317</v>
       </c>
@@ -6710,17 +6722,20 @@
       <c r="J23" s="147">
         <v>0</v>
       </c>
-      <c r="K23" s="174"/>
-      <c r="L23" s="171">
+      <c r="K23" s="147">
+        <v>260</v>
+      </c>
+      <c r="L23" s="174"/>
+      <c r="M23" s="171">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M23" s="149">
+        <v>260</v>
+      </c>
+      <c r="N23" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24" s="142" t="s">
         <v>32</v>
       </c>
@@ -6749,17 +6764,20 @@
       <c r="J24" s="147">
         <v>6060</v>
       </c>
-      <c r="K24" s="174"/>
-      <c r="L24" s="171">
+      <c r="K24" s="147">
+        <v>8477</v>
+      </c>
+      <c r="L24" s="174"/>
+      <c r="M24" s="171">
         <f t="shared" si="0"/>
-        <v>15968</v>
-      </c>
-      <c r="M24" s="149">
+        <v>24445</v>
+      </c>
+      <c r="N24" s="149">
         <f t="shared" si="1"/>
-        <v>0.14516363636363636</v>
-      </c>
-    </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+        <v>0.22222727272727272</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25" s="142" t="s">
         <v>97</v>
       </c>
@@ -6788,17 +6806,20 @@
       <c r="J25" s="147">
         <v>-200</v>
       </c>
-      <c r="K25" s="174"/>
-      <c r="L25" s="171">
+      <c r="K25" s="147">
+        <v>-105800</v>
+      </c>
+      <c r="L25" s="174"/>
+      <c r="M25" s="171">
         <f t="shared" si="0"/>
-        <v>-406900</v>
-      </c>
-      <c r="M25" s="149">
+        <v>-512700</v>
+      </c>
+      <c r="N25" s="149">
         <f t="shared" si="1"/>
-        <v>-1.7691304347826089</v>
-      </c>
-    </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+        <v>-2.2291304347826091</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26" s="142" t="s">
         <v>302</v>
       </c>
@@ -6825,17 +6846,20 @@
       <c r="J26" s="147">
         <v>1257</v>
       </c>
-      <c r="K26" s="174"/>
-      <c r="L26" s="171">
+      <c r="K26" s="147">
+        <v>-1640</v>
+      </c>
+      <c r="L26" s="174"/>
+      <c r="M26" s="171">
         <f t="shared" si="0"/>
-        <v>5060</v>
-      </c>
-      <c r="M26" s="149">
+        <v>3420</v>
+      </c>
+      <c r="N26" s="149">
         <f t="shared" si="1"/>
-        <v>0.253</v>
-      </c>
-    </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+        <v>0.17100000000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A27" s="142" t="s">
         <v>29</v>
       </c>
@@ -6864,17 +6888,20 @@
       <c r="J27" s="147">
         <v>0</v>
       </c>
-      <c r="K27" s="174"/>
-      <c r="L27" s="171">
+      <c r="K27" s="147">
+        <v>0</v>
+      </c>
+      <c r="L27" s="174"/>
+      <c r="M27" s="171">
         <f t="shared" si="0"/>
         <v>39000</v>
       </c>
-      <c r="M27" s="149">
+      <c r="N27" s="149">
         <f t="shared" si="1"/>
         <v>7.8E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28" s="142" t="s">
         <v>28</v>
       </c>
@@ -6903,17 +6930,20 @@
       <c r="J28" s="147">
         <v>184400</v>
       </c>
-      <c r="K28" s="174"/>
-      <c r="L28" s="171">
+      <c r="K28" s="147">
+        <v>-205430</v>
+      </c>
+      <c r="L28" s="174"/>
+      <c r="M28" s="171">
         <f t="shared" si="0"/>
-        <v>72755</v>
-      </c>
-      <c r="M28" s="149">
+        <v>-132675</v>
+      </c>
+      <c r="N28" s="149">
         <f t="shared" si="1"/>
-        <v>7.2755E-2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+        <v>-0.13267499999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29" s="142" t="s">
         <v>65</v>
       </c>
@@ -6942,17 +6972,20 @@
       <c r="J29" s="147">
         <v>-20000</v>
       </c>
-      <c r="K29" s="174"/>
-      <c r="L29" s="171">
+      <c r="K29" s="147">
+        <v>0</v>
+      </c>
+      <c r="L29" s="174"/>
+      <c r="M29" s="171">
         <f t="shared" si="0"/>
         <v>-475000</v>
       </c>
-      <c r="M29" s="149">
+      <c r="N29" s="149">
         <f t="shared" si="1"/>
         <v>-0.95</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30" s="141" t="s">
         <v>34</v>
       </c>
@@ -6981,17 +7014,20 @@
       <c r="J30" s="147">
         <v>-135</v>
       </c>
-      <c r="K30" s="174"/>
-      <c r="L30" s="171">
+      <c r="K30" s="147">
+        <v>163183</v>
+      </c>
+      <c r="L30" s="174"/>
+      <c r="M30" s="171">
         <f t="shared" si="0"/>
-        <v>-172907</v>
-      </c>
-      <c r="M30" s="149">
+        <v>-9724</v>
+      </c>
+      <c r="N30" s="149">
         <f t="shared" si="1"/>
-        <v>-0.34581400000000001</v>
-      </c>
-    </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+        <v>-1.9448E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31" s="141" t="s">
         <v>131</v>
       </c>
@@ -7020,17 +7056,20 @@
       <c r="J31" s="147">
         <v>-18371</v>
       </c>
-      <c r="K31" s="174"/>
-      <c r="L31" s="171">
-        <f t="shared" ref="L31:L56" si="2">SUM(H31:K31)</f>
-        <v>-98118</v>
-      </c>
-      <c r="M31" s="149">
-        <f t="shared" ref="M31:M56" si="3">IFERROR(L31/F31*100,0)/10000000</f>
-        <v>-1.9623600000000001</v>
-      </c>
-    </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="K31" s="147">
+        <v>-5269</v>
+      </c>
+      <c r="L31" s="174"/>
+      <c r="M31" s="171">
+        <f t="shared" ref="M31:M56" si="2">SUM(H31:L31)</f>
+        <v>-103387</v>
+      </c>
+      <c r="N31" s="149">
+        <f t="shared" ref="N31:N56" si="3">IFERROR(M31/F31*100,0)/10000000</f>
+        <v>-2.0677400000000001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32" s="43" t="s">
         <v>67</v>
       </c>
@@ -7059,18 +7098,21 @@
       <c r="J32" s="147">
         <v>-924</v>
       </c>
-      <c r="K32" s="174"/>
-      <c r="L32" s="171">
+      <c r="K32" s="147">
+        <v>-9429</v>
+      </c>
+      <c r="L32" s="174"/>
+      <c r="M32" s="171">
         <f t="shared" si="2"/>
-        <v>8586</v>
-      </c>
-      <c r="M32" s="149">
+        <v>-843</v>
+      </c>
+      <c r="N32" s="149">
         <f t="shared" si="3"/>
-        <v>0.21465000000000001</v>
-      </c>
-      <c r="P32" s="134"/>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+        <v>-2.1075E-2</v>
+      </c>
+      <c r="Q32" s="134"/>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="43" t="s">
         <v>143</v>
       </c>
@@ -7099,21 +7141,24 @@
       <c r="J33" s="147">
         <v>0</v>
       </c>
-      <c r="K33" s="174"/>
-      <c r="L33" s="171">
+      <c r="K33" s="147">
+        <v>0</v>
+      </c>
+      <c r="L33" s="174"/>
+      <c r="M33" s="171">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M33" s="149">
+      <c r="N33" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O33" s="5"/>
-      <c r="P33" s="134">
-        <v>6971</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P33" s="5"/>
+      <c r="Q33" s="134">
+        <v>6680</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="43" t="s">
         <v>144</v>
       </c>
@@ -7142,19 +7187,22 @@
       <c r="J34" s="147">
         <v>0</v>
       </c>
-      <c r="K34" s="174"/>
-      <c r="L34" s="171">
+      <c r="K34" s="147">
+        <v>0</v>
+      </c>
+      <c r="L34" s="174"/>
+      <c r="M34" s="171">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M34" s="149">
+      <c r="N34" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O34" s="5"/>
-      <c r="P34" s="134"/>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P34" s="5"/>
+      <c r="Q34" s="134"/>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="142" t="s">
         <v>31</v>
       </c>
@@ -7183,24 +7231,27 @@
       <c r="J35" s="147">
         <v>49649</v>
       </c>
-      <c r="K35" s="174"/>
-      <c r="L35" s="171">
+      <c r="K35" s="147">
+        <v>-54126</v>
+      </c>
+      <c r="L35" s="174"/>
+      <c r="M35" s="171">
         <f t="shared" si="2"/>
-        <v>-84252</v>
-      </c>
-      <c r="M35" s="149">
+        <v>-138378</v>
+      </c>
+      <c r="N35" s="149">
         <f t="shared" si="3"/>
-        <v>-0.21063000000000001</v>
-      </c>
-      <c r="O35" s="134">
-        <v>327210</v>
+        <v>-0.345945</v>
       </c>
       <c r="P35" s="134">
-        <f>(O36+O35)/10000000*13780</f>
-        <v>911.3967980000001</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+        <v>198924</v>
+      </c>
+      <c r="Q35" s="134">
+        <f>(P36+P35)/10000000*13780</f>
+        <v>557.61872400000004</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="142" t="s">
         <v>104</v>
       </c>
@@ -7229,21 +7280,24 @@
       <c r="J36" s="147">
         <v>47158</v>
       </c>
-      <c r="K36" s="174"/>
-      <c r="L36" s="171">
+      <c r="K36" s="147">
+        <v>3870</v>
+      </c>
+      <c r="L36" s="174"/>
+      <c r="M36" s="171">
         <f t="shared" si="2"/>
-        <v>-7417</v>
-      </c>
-      <c r="M36" s="149">
+        <v>-3547</v>
+      </c>
+      <c r="N36" s="149">
         <f t="shared" si="3"/>
-        <v>-7.417E-2</v>
-      </c>
-      <c r="O36" s="134">
-        <v>334181</v>
-      </c>
-      <c r="P36" s="134"/>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+        <v>-3.5470000000000002E-2</v>
+      </c>
+      <c r="P36" s="134">
+        <v>205734</v>
+      </c>
+      <c r="Q36" s="134"/>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="142" t="s">
         <v>314</v>
       </c>
@@ -7270,22 +7324,25 @@
       <c r="J37" s="147">
         <v>0</v>
       </c>
-      <c r="K37" s="174"/>
-      <c r="L37" s="171">
+      <c r="K37" s="147">
+        <v>0</v>
+      </c>
+      <c r="L37" s="174"/>
+      <c r="M37" s="171">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M37" s="149">
+      <c r="N37" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O37" s="134"/>
-      <c r="P37" s="134">
-        <f>+P33-P35</f>
-        <v>6059.6032020000002</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P37" s="134"/>
+      <c r="Q37" s="134">
+        <f>+Q33-Q35</f>
+        <v>6122.3812760000001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="142" t="s">
         <v>229</v>
       </c>
@@ -7314,19 +7371,22 @@
       <c r="J38" s="147">
         <v>-15600</v>
       </c>
-      <c r="K38" s="174"/>
-      <c r="L38" s="171">
+      <c r="K38" s="147">
+        <v>-680</v>
+      </c>
+      <c r="L38" s="174"/>
+      <c r="M38" s="171">
         <f t="shared" si="2"/>
-        <v>-28760</v>
-      </c>
-      <c r="M38" s="149">
+        <v>-29440</v>
+      </c>
+      <c r="N38" s="149">
         <f t="shared" si="3"/>
-        <v>-0.57520000000000004</v>
-      </c>
-      <c r="O38" s="134"/>
+        <v>-0.58879999999999999</v>
+      </c>
       <c r="P38" s="134"/>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q38" s="134"/>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="142" t="s">
         <v>52</v>
       </c>
@@ -7355,19 +7415,22 @@
       <c r="J39" s="147">
         <v>0</v>
       </c>
-      <c r="K39" s="174"/>
-      <c r="L39" s="171">
+      <c r="K39" s="147">
+        <v>0</v>
+      </c>
+      <c r="L39" s="174"/>
+      <c r="M39" s="171">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M39" s="149">
+      <c r="N39" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O39" s="134"/>
       <c r="P39" s="134"/>
-    </row>
-    <row r="40" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q39" s="134"/>
+    </row>
+    <row r="40" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="142" t="s">
         <v>45</v>
       </c>
@@ -7396,19 +7459,22 @@
       <c r="J40" s="147">
         <v>2300</v>
       </c>
-      <c r="K40" s="174"/>
-      <c r="L40" s="171">
+      <c r="K40" s="147">
+        <v>-48027</v>
+      </c>
+      <c r="L40" s="174"/>
+      <c r="M40" s="171">
         <f t="shared" si="2"/>
-        <v>-56406</v>
-      </c>
-      <c r="M40" s="149">
+        <v>-104433</v>
+      </c>
+      <c r="N40" s="149">
         <f t="shared" si="3"/>
-        <v>-0.18801999999999999</v>
-      </c>
-      <c r="O40" s="134"/>
+        <v>-0.34810999999999998</v>
+      </c>
       <c r="P40" s="134"/>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q40" s="134"/>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="142" t="s">
         <v>292</v>
       </c>
@@ -7435,18 +7501,21 @@
       <c r="J41" s="147">
         <v>-1079</v>
       </c>
-      <c r="K41" s="174"/>
-      <c r="L41" s="171">
+      <c r="K41" s="147">
+        <v>14970</v>
+      </c>
+      <c r="L41" s="174"/>
+      <c r="M41" s="171">
         <f t="shared" si="2"/>
-        <v>20345</v>
-      </c>
-      <c r="M41" s="149">
+        <v>35315</v>
+      </c>
+      <c r="N41" s="149">
         <f t="shared" si="3"/>
-        <v>2.0345</v>
-      </c>
-      <c r="O41" s="134"/>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+        <v>3.5314999999999999</v>
+      </c>
+      <c r="P41" s="134"/>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="142" t="s">
         <v>132</v>
       </c>
@@ -7475,17 +7544,20 @@
       <c r="J42" s="147">
         <v>6275</v>
       </c>
-      <c r="K42" s="174"/>
-      <c r="L42" s="171">
+      <c r="K42" s="147">
+        <v>-1908</v>
+      </c>
+      <c r="L42" s="174"/>
+      <c r="M42" s="171">
         <f t="shared" si="2"/>
-        <v>2285</v>
-      </c>
-      <c r="M42" s="149">
+        <v>377</v>
+      </c>
+      <c r="N42" s="149">
         <f t="shared" si="3"/>
-        <v>4.5699999999999998E-2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+        <v>7.5399999999999998E-3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="142" t="s">
         <v>48</v>
       </c>
@@ -7514,17 +7586,20 @@
       <c r="J43" s="147">
         <v>80500</v>
       </c>
-      <c r="K43" s="174"/>
-      <c r="L43" s="171">
+      <c r="K43" s="147">
+        <v>-34150</v>
+      </c>
+      <c r="L43" s="174"/>
+      <c r="M43" s="171">
         <f t="shared" si="2"/>
-        <v>-35567</v>
-      </c>
-      <c r="M43" s="149">
+        <v>-69717</v>
+      </c>
+      <c r="N43" s="149">
         <f t="shared" si="3"/>
-        <v>-0.35566999999999999</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+        <v>-0.69716999999999996</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="142" t="s">
         <v>301</v>
       </c>
@@ -7551,17 +7626,20 @@
       <c r="J44" s="147">
         <v>3264</v>
       </c>
-      <c r="K44" s="174"/>
-      <c r="L44" s="171">
+      <c r="K44" s="147">
+        <v>974</v>
+      </c>
+      <c r="L44" s="174"/>
+      <c r="M44" s="171">
         <f t="shared" si="2"/>
-        <v>6480</v>
-      </c>
-      <c r="M44" s="149">
+        <v>7454</v>
+      </c>
+      <c r="N44" s="149">
         <f t="shared" si="3"/>
-        <v>0.64800000000000002</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.74539999999999995</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="143" t="s">
         <v>168</v>
       </c>
@@ -7590,17 +7668,20 @@
       <c r="J45" s="147">
         <v>-161258</v>
       </c>
-      <c r="K45" s="174"/>
-      <c r="L45" s="171">
+      <c r="K45" s="147">
+        <v>0</v>
+      </c>
+      <c r="L45" s="174"/>
+      <c r="M45" s="171">
         <f t="shared" si="2"/>
         <v>-156125</v>
       </c>
-      <c r="M45" s="149">
+      <c r="N45" s="149">
         <f t="shared" si="3"/>
         <v>-0.39031250000000001</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="143" t="s">
         <v>202</v>
       </c>
@@ -7629,17 +7710,20 @@
       <c r="J46" s="147">
         <v>5300</v>
       </c>
-      <c r="K46" s="174"/>
-      <c r="L46" s="171">
+      <c r="K46" s="147">
+        <v>8481</v>
+      </c>
+      <c r="L46" s="174"/>
+      <c r="M46" s="171">
         <f t="shared" si="2"/>
-        <v>31259</v>
-      </c>
-      <c r="M46" s="149">
+        <v>39740</v>
+      </c>
+      <c r="N46" s="149">
         <f t="shared" si="3"/>
-        <v>7.8147499999999995E-2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+        <v>9.9349999999999994E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="143" t="s">
         <v>33</v>
       </c>
@@ -7668,17 +7752,20 @@
       <c r="J47" s="147">
         <v>79536</v>
       </c>
-      <c r="K47" s="174"/>
-      <c r="L47" s="171">
+      <c r="K47" s="147">
+        <v>-16640</v>
+      </c>
+      <c r="L47" s="174"/>
+      <c r="M47" s="171">
         <f t="shared" si="2"/>
-        <v>32664</v>
-      </c>
-      <c r="M47" s="149">
+        <v>16024</v>
+      </c>
+      <c r="N47" s="149">
         <f t="shared" si="3"/>
-        <v>0.10888</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+        <v>5.3413333333333327E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="59" t="s">
         <v>306</v>
       </c>
@@ -7705,17 +7792,20 @@
       <c r="J48" s="151">
         <v>-30800</v>
       </c>
-      <c r="K48" s="174"/>
-      <c r="L48" s="171">
+      <c r="K48" s="151">
+        <v>86600</v>
+      </c>
+      <c r="L48" s="174"/>
+      <c r="M48" s="171">
         <f t="shared" si="2"/>
-        <v>-371500</v>
-      </c>
-      <c r="M48" s="149">
+        <v>-284900</v>
+      </c>
+      <c r="N48" s="149">
         <f t="shared" si="3"/>
-        <v>-0.3715</v>
-      </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+        <v>-0.28489999999999999</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" s="59" t="s">
         <v>320</v>
       </c>
@@ -7740,17 +7830,20 @@
       <c r="J49" s="151">
         <v>0</v>
       </c>
-      <c r="K49" s="174"/>
-      <c r="L49" s="171">
+      <c r="K49" s="151">
+        <v>0</v>
+      </c>
+      <c r="L49" s="174"/>
+      <c r="M49" s="171">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M49" s="149">
+      <c r="N49" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" s="59" t="s">
         <v>197</v>
       </c>
@@ -7779,17 +7872,20 @@
       <c r="J50" s="151">
         <v>335</v>
       </c>
-      <c r="K50" s="174"/>
-      <c r="L50" s="171">
+      <c r="K50" s="151">
+        <v>-10394</v>
+      </c>
+      <c r="L50" s="174"/>
+      <c r="M50" s="171">
         <f t="shared" si="2"/>
-        <v>14932</v>
-      </c>
-      <c r="M50" s="149">
+        <v>4538</v>
+      </c>
+      <c r="N50" s="149">
         <f t="shared" si="3"/>
-        <v>0.29864000000000002</v>
-      </c>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+        <v>9.0759999999999993E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51" s="59" t="s">
         <v>213</v>
       </c>
@@ -7818,17 +7914,20 @@
       <c r="J51" s="151">
         <v>0</v>
       </c>
-      <c r="K51" s="174"/>
-      <c r="L51" s="171">
+      <c r="K51" s="151">
+        <v>0</v>
+      </c>
+      <c r="L51" s="174"/>
+      <c r="M51" s="171">
         <f t="shared" si="2"/>
         <v>-152273</v>
       </c>
-      <c r="M51" s="149">
+      <c r="N51" s="149">
         <f t="shared" si="3"/>
         <v>-0.23426615384615385</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" s="59" t="s">
         <v>214</v>
       </c>
@@ -7857,17 +7956,20 @@
       <c r="J52" s="151">
         <v>-160784</v>
       </c>
-      <c r="K52" s="174"/>
-      <c r="L52" s="171">
+      <c r="K52" s="151">
+        <v>0</v>
+      </c>
+      <c r="L52" s="174"/>
+      <c r="M52" s="171">
         <f t="shared" si="2"/>
         <v>-157736</v>
       </c>
-      <c r="M52" s="149">
+      <c r="N52" s="149">
         <f t="shared" si="3"/>
         <v>-1.2618879999999999</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53" s="59" t="s">
         <v>49</v>
       </c>
@@ -7896,17 +7998,20 @@
       <c r="J53" s="151">
         <v>14450</v>
       </c>
-      <c r="K53" s="174"/>
-      <c r="L53" s="171">
+      <c r="K53" s="151">
+        <v>0</v>
+      </c>
+      <c r="L53" s="174"/>
+      <c r="M53" s="171">
         <f t="shared" si="2"/>
         <v>-106641</v>
       </c>
-      <c r="M53" s="149">
+      <c r="N53" s="149">
         <f t="shared" si="3"/>
         <v>-0.35547000000000001</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54" s="59" t="s">
         <v>300</v>
       </c>
@@ -7933,17 +8038,20 @@
       <c r="J54" s="151">
         <v>13380</v>
       </c>
-      <c r="K54" s="174"/>
-      <c r="L54" s="171">
+      <c r="K54" s="151">
+        <v>0</v>
+      </c>
+      <c r="L54" s="174"/>
+      <c r="M54" s="171">
         <f t="shared" si="2"/>
         <v>8135</v>
       </c>
-      <c r="M54" s="149">
+      <c r="N54" s="149">
         <f t="shared" si="3"/>
         <v>5.4233333333333328E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:17" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="59" t="s">
         <v>288</v>
       </c>
@@ -7970,17 +8078,20 @@
       <c r="J55" s="151">
         <v>43947</v>
       </c>
-      <c r="K55" s="174"/>
-      <c r="L55" s="171">
+      <c r="K55" s="151">
+        <v>6100</v>
+      </c>
+      <c r="L55" s="174"/>
+      <c r="M55" s="171">
         <f t="shared" si="2"/>
-        <v>42146</v>
-      </c>
-      <c r="M55" s="149">
+        <v>48246</v>
+      </c>
+      <c r="N55" s="149">
         <f t="shared" si="3"/>
-        <v>8.4292000000000006E-2</v>
-      </c>
-    </row>
-    <row r="56" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>9.6492000000000008E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="24"/>
       <c r="B56" s="25"/>
       <c r="C56" s="26"/>
@@ -8002,18 +8113,22 @@
       </c>
       <c r="K56" s="254">
         <f>SUM(K4:K55)</f>
-        <v>0</v>
+        <v>-88507</v>
       </c>
       <c r="L56" s="254">
+        <f>SUM(L4:L55)</f>
+        <v>0</v>
+      </c>
+      <c r="M56" s="254">
         <f t="shared" si="2"/>
-        <v>-2508428</v>
-      </c>
-      <c r="M56" s="255">
+        <v>-2596935</v>
+      </c>
+      <c r="N56" s="255">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:17" s="249" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" s="249" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="250"/>
       <c r="B57" s="250"/>
       <c r="C57" s="250"/>
@@ -8026,9 +8141,10 @@
       <c r="J57" s="250"/>
       <c r="K57" s="250"/>
       <c r="L57" s="250"/>
-      <c r="M57" s="252"/>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M57" s="250"/>
+      <c r="N57" s="252"/>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58" s="202" t="s">
         <v>241</v>
       </c>
@@ -8057,18 +8173,21 @@
       <c r="J58" s="162">
         <v>-17480</v>
       </c>
-      <c r="K58" s="246"/>
-      <c r="L58" s="247">
-        <f>SUM(H58:K58)</f>
+      <c r="K58" s="162">
+        <v>0</v>
+      </c>
+      <c r="L58" s="246"/>
+      <c r="M58" s="247">
+        <f>SUM(H58:L58)</f>
         <v>-387560</v>
       </c>
-      <c r="M58" s="248">
-        <f>IFERROR(L58/F58*100,0)/10000000</f>
+      <c r="N58" s="248">
+        <f>IFERROR(M58/F58*100,0)/10000000</f>
         <v>-1.2918666666666667</v>
       </c>
-      <c r="P58" s="134"/>
-    </row>
-    <row r="59" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Q58" s="134"/>
+    </row>
+    <row r="59" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="202" t="s">
         <v>273</v>
       </c>
@@ -8095,18 +8214,21 @@
       <c r="J59" s="162">
         <v>0</v>
       </c>
-      <c r="K59" s="174"/>
-      <c r="L59" s="171">
-        <f>SUM(H59:K59)</f>
+      <c r="K59" s="162">
+        <v>0</v>
+      </c>
+      <c r="L59" s="174"/>
+      <c r="M59" s="171">
+        <f>SUM(H59:L59)</f>
         <v>-246000</v>
       </c>
-      <c r="M59" s="149">
-        <f>IFERROR(L59/F59*100,0)/10000000</f>
-        <v>0</v>
-      </c>
-      <c r="O59" s="134"/>
-    </row>
-    <row r="60" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N59" s="149">
+        <f>IFERROR(M59/F59*100,0)/10000000</f>
+        <v>0</v>
+      </c>
+      <c r="P59" s="134"/>
+    </row>
+    <row r="60" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="200"/>
       <c r="B60" s="16"/>
       <c r="C60" s="16"/>
@@ -8130,128 +8252,132 @@
         <f>SUM(K58:K59)</f>
         <v>0</v>
       </c>
-      <c r="L60" s="254">
-        <f>SUM(H60:K60)</f>
+      <c r="L60" s="170">
+        <f>SUM(L58:L59)</f>
+        <v>0</v>
+      </c>
+      <c r="M60" s="254">
+        <f>SUM(H60:L60)</f>
         <v>-633560</v>
       </c>
-      <c r="M60" s="19"/>
-      <c r="O60" s="5"/>
-      <c r="P60" s="134"/>
-      <c r="Q60" s="237"/>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="O61" s="134"/>
+      <c r="N60" s="19"/>
+      <c r="P60" s="5"/>
+      <c r="Q60" s="134"/>
+      <c r="R60" s="237"/>
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="P61" s="134"/>
-      <c r="Q61" s="237"/>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="O62" s="134"/>
+      <c r="Q61" s="134"/>
+      <c r="R61" s="237"/>
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="P62" s="134"/>
-      <c r="Q62" s="237"/>
-    </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="O63" s="134"/>
+      <c r="Q62" s="134"/>
+      <c r="R62" s="237"/>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="P63" s="134"/>
-      <c r="Q63" s="237"/>
-    </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="O64" s="134"/>
+      <c r="Q63" s="134"/>
+      <c r="R63" s="237"/>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="P64" s="134"/>
-      <c r="Q64" s="237"/>
-    </row>
-    <row r="65" spans="15:17" x14ac:dyDescent="0.25">
-      <c r="O65" s="134"/>
-      <c r="P65" s="237"/>
+      <c r="Q64" s="134"/>
+      <c r="R64" s="237"/>
+    </row>
+    <row r="65" spans="16:18" x14ac:dyDescent="0.25">
+      <c r="P65" s="134"/>
       <c r="Q65" s="237"/>
-    </row>
-    <row r="66" spans="15:17" x14ac:dyDescent="0.25">
-      <c r="O66" s="237"/>
+      <c r="R65" s="237"/>
+    </row>
+    <row r="66" spans="16:18" x14ac:dyDescent="0.25">
       <c r="P66" s="237"/>
       <c r="Q66" s="237"/>
+      <c r="R66" s="237"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G2 A3:G3 M56:M57 L55:M55 M60 L43:M43 L5:M10 L24:M25 H2:M3 A58:M59 A37:L37 M11:M21 L11:L22 L45:M53 L27:L36 M27:M35 A4:K36 L38:L41 A38:K39 G40:K40 A41:K56 A60:K60">
-    <cfRule type="expression" dxfId="449" priority="21">
+  <conditionalFormatting sqref="G2 A3:G3 N56:N57 M55:N55 N60 M43:N43 M5:N10 M24:N25 H2:N3 A58:N59 A37:M37 N11:N21 M11:M22 M45:N53 M27:M36 N27:N35 A4:L36 M38:M41 A38:L39 G40:L40 A41:L56 A60:L60">
+    <cfRule type="expression" dxfId="446" priority="21">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M36">
-    <cfRule type="expression" dxfId="448" priority="20">
+  <conditionalFormatting sqref="N36">
+    <cfRule type="expression" dxfId="445" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M39:M40">
-    <cfRule type="expression" dxfId="447" priority="19">
+  <conditionalFormatting sqref="N39:N40">
+    <cfRule type="expression" dxfId="444" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L4:M4">
-    <cfRule type="expression" dxfId="446" priority="18">
+  <conditionalFormatting sqref="M4:N4">
+    <cfRule type="expression" dxfId="443" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M38">
-    <cfRule type="expression" dxfId="445" priority="17">
+  <conditionalFormatting sqref="N38">
+    <cfRule type="expression" dxfId="442" priority="17">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M22">
-    <cfRule type="expression" dxfId="444" priority="14">
+  <conditionalFormatting sqref="N22">
+    <cfRule type="expression" dxfId="441" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L56">
-    <cfRule type="expression" dxfId="443" priority="13">
+  <conditionalFormatting sqref="M56">
+    <cfRule type="expression" dxfId="440" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M41">
-    <cfRule type="expression" dxfId="442" priority="12">
+  <conditionalFormatting sqref="N41">
+    <cfRule type="expression" dxfId="439" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L26:M26">
-    <cfRule type="expression" dxfId="441" priority="11">
+  <conditionalFormatting sqref="M26:N26">
+    <cfRule type="expression" dxfId="438" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L54:M54">
-    <cfRule type="expression" dxfId="440" priority="10">
+  <conditionalFormatting sqref="M54:N54">
+    <cfRule type="expression" dxfId="437" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L44:M44">
-    <cfRule type="expression" dxfId="439" priority="9">
+  <conditionalFormatting sqref="M44:N44">
+    <cfRule type="expression" dxfId="436" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L60">
-    <cfRule type="expression" dxfId="438" priority="8">
+  <conditionalFormatting sqref="M60">
+    <cfRule type="expression" dxfId="435" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L42:M42">
-    <cfRule type="expression" dxfId="437" priority="6">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L23">
-    <cfRule type="expression" dxfId="436" priority="5">
+  <conditionalFormatting sqref="M42:N42">
+    <cfRule type="expression" dxfId="434" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M23">
-    <cfRule type="expression" dxfId="435" priority="4">
+    <cfRule type="expression" dxfId="433" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M37">
-    <cfRule type="expression" dxfId="434" priority="2">
+  <conditionalFormatting sqref="N23">
+    <cfRule type="expression" dxfId="432" priority="4">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N37">
+    <cfRule type="expression" dxfId="431" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40:F40">
-    <cfRule type="expression" dxfId="433" priority="1">
+    <cfRule type="expression" dxfId="430" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14718,112 +14844,112 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2 A3:G3 AD47:AD48 AD55:AD57 AD68:AD69 AD50 AD11:AD19 AD21:AD23 AC11:AC24 AC29:AC43 AD29:AD42 AC66:AD67 AC54:AC57 AD73 H2:AD3 A68:G68 AC52:AD52 AC5:AD10 AC58:AD64 AC26:AD27 A70:AD72 A4:AB22 A44:S44 A45:AC50 A73:AB73 A26:AB43 B23:AB25 A52:AB67 B51:AB51">
-    <cfRule type="expression" dxfId="432" priority="22">
+    <cfRule type="expression" dxfId="429" priority="22">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD43">
-    <cfRule type="expression" dxfId="431" priority="21">
+    <cfRule type="expression" dxfId="428" priority="21">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD46">
-    <cfRule type="expression" dxfId="430" priority="20">
+    <cfRule type="expression" dxfId="427" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC4:AD4">
-    <cfRule type="expression" dxfId="429" priority="19">
+    <cfRule type="expression" dxfId="426" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD45">
-    <cfRule type="expression" dxfId="428" priority="18">
+    <cfRule type="expression" dxfId="425" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD20">
-    <cfRule type="expression" dxfId="427" priority="17">
+    <cfRule type="expression" dxfId="424" priority="17">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD54">
-    <cfRule type="expression" dxfId="426" priority="16">
+    <cfRule type="expression" dxfId="423" priority="16">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD24">
-    <cfRule type="expression" dxfId="425" priority="15">
+    <cfRule type="expression" dxfId="422" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC68">
-    <cfRule type="expression" dxfId="424" priority="14">
+    <cfRule type="expression" dxfId="421" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD49">
-    <cfRule type="expression" dxfId="423" priority="13">
+    <cfRule type="expression" dxfId="420" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC28:AD28">
-    <cfRule type="expression" dxfId="422" priority="12">
+    <cfRule type="expression" dxfId="419" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC65:AD65">
-    <cfRule type="expression" dxfId="421" priority="11">
+    <cfRule type="expression" dxfId="418" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC53:AD53">
-    <cfRule type="expression" dxfId="420" priority="10">
+    <cfRule type="expression" dxfId="417" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC73">
-    <cfRule type="expression" dxfId="419" priority="9">
+    <cfRule type="expression" dxfId="416" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H68:AB68">
-    <cfRule type="expression" dxfId="418" priority="8">
+    <cfRule type="expression" dxfId="415" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC51:AD51">
-    <cfRule type="expression" dxfId="417" priority="7">
+    <cfRule type="expression" dxfId="414" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC25">
-    <cfRule type="expression" dxfId="416" priority="6">
+    <cfRule type="expression" dxfId="413" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD25">
-    <cfRule type="expression" dxfId="415" priority="5">
+    <cfRule type="expression" dxfId="412" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T44:AC44">
-    <cfRule type="expression" dxfId="414" priority="4">
+    <cfRule type="expression" dxfId="411" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD44">
-    <cfRule type="expression" dxfId="413" priority="3">
+    <cfRule type="expression" dxfId="410" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A23:A25">
-    <cfRule type="expression" dxfId="412" priority="2">
+    <cfRule type="expression" dxfId="409" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A51">
-    <cfRule type="expression" dxfId="411" priority="1">
+    <cfRule type="expression" dxfId="408" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21123,82 +21249,82 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2 A3:G3 AF43:AF44 AF50:AF52 AF62:AF63 H2:AF3 AF46:AF47 AF9:AF17 AF23:AF24 AF19:AF21 AE9:AE24 AE5:AF8 AE26:AE47 AF26:AF39 AE60:AF61 AE49:AE52 A64:AF66 AF67 A67:AD67 AE53:AF58 A4:AD20 A23:AD62 C21:AD21 B22:AD22">
-    <cfRule type="expression" dxfId="410" priority="20">
+    <cfRule type="expression" dxfId="407" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF40">
-    <cfRule type="expression" dxfId="409" priority="19">
+    <cfRule type="expression" dxfId="406" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF42">
-    <cfRule type="expression" dxfId="408" priority="18">
+    <cfRule type="expression" dxfId="405" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE4:AF4">
-    <cfRule type="expression" dxfId="407" priority="16">
+    <cfRule type="expression" dxfId="404" priority="16">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF41">
-    <cfRule type="expression" dxfId="406" priority="14">
+    <cfRule type="expression" dxfId="403" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF18">
-    <cfRule type="expression" dxfId="405" priority="13">
+    <cfRule type="expression" dxfId="402" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF49">
-    <cfRule type="expression" dxfId="404" priority="12">
+    <cfRule type="expression" dxfId="401" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF22">
-    <cfRule type="expression" dxfId="403" priority="11">
+    <cfRule type="expression" dxfId="400" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE62">
-    <cfRule type="expression" dxfId="402" priority="10">
+    <cfRule type="expression" dxfId="399" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF45">
-    <cfRule type="expression" dxfId="401" priority="9">
+    <cfRule type="expression" dxfId="398" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE25:AF25">
-    <cfRule type="expression" dxfId="400" priority="6">
+    <cfRule type="expression" dxfId="397" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE59:AF59">
-    <cfRule type="expression" dxfId="399" priority="5">
+    <cfRule type="expression" dxfId="396" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE48:AF48">
-    <cfRule type="expression" dxfId="398" priority="4">
+    <cfRule type="expression" dxfId="395" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE67">
-    <cfRule type="expression" dxfId="397" priority="3">
+    <cfRule type="expression" dxfId="394" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21">
-    <cfRule type="expression" dxfId="396" priority="2">
+    <cfRule type="expression" dxfId="393" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:A22">
-    <cfRule type="expression" dxfId="395" priority="1">
+    <cfRule type="expression" dxfId="392" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21322,20 +21448,20 @@
         <v>-0.20805999999999999</v>
       </c>
       <c r="K4" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>-11762</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>-12411</v>
       </c>
       <c r="L4" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>-0.23524</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>-0.24822</v>
       </c>
       <c r="M4" s="71">
         <f t="shared" ref="M4:N62" si="0">G4+I4+K4</f>
-        <v>-38806</v>
+        <v>-39455</v>
       </c>
       <c r="N4" s="166">
         <f t="shared" si="0"/>
-        <v>-0.77612000000000003</v>
+        <v>-0.78910000000000002</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -21374,20 +21500,20 @@
         <v>-1.2725900000000001</v>
       </c>
       <c r="K5" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>-108180</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>-34831</v>
       </c>
       <c r="L5" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>-0.36059999999999998</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>-0.11610333333333335</v>
       </c>
       <c r="M5" s="71">
         <f t="shared" si="0"/>
-        <v>-359151</v>
+        <v>-285802</v>
       </c>
       <c r="N5" s="166">
         <f t="shared" si="0"/>
-        <v>-1.1971700000000001</v>
+        <v>-0.95267333333333337</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -21426,11 +21552,11 @@
         <v>1.16185</v>
       </c>
       <c r="K6" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L6" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M6" s="71">
@@ -21476,11 +21602,11 @@
         <v>0</v>
       </c>
       <c r="K7" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L7" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M7" s="71">
@@ -21528,20 +21654,20 @@
         <v>-1.6494500000000001</v>
       </c>
       <c r="K8" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>107757</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>61757</v>
       </c>
       <c r="L8" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>0.35919000000000001</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>0.20585666666666669</v>
       </c>
       <c r="M8" s="71">
         <f t="shared" si="0"/>
-        <v>-347340</v>
+        <v>-393340</v>
       </c>
       <c r="N8" s="166">
         <f t="shared" si="0"/>
-        <v>-1.1577999999999999</v>
+        <v>-1.3111333333333333</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -21580,20 +21706,20 @@
         <v>0.16230666666666665</v>
       </c>
       <c r="K9" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>81548</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>76523</v>
       </c>
       <c r="L9" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>0.54365333333333343</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>0.51015333333333335</v>
       </c>
       <c r="M9" s="71">
         <f t="shared" si="0"/>
-        <v>-212588</v>
+        <v>-217613</v>
       </c>
       <c r="N9" s="166">
         <f t="shared" si="0"/>
-        <v>-1.4172533333333335</v>
+        <v>-1.4507533333333336</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -21632,20 +21758,20 @@
         <v>-1.1035999999999999</v>
       </c>
       <c r="K10" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>8274</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>10274</v>
       </c>
       <c r="L10" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>0.13789999999999999</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>0.17123333333333335</v>
       </c>
       <c r="M10" s="71">
         <f t="shared" ref="M10" si="3">G10+I10+K10</f>
-        <v>-183975</v>
+        <v>-181975</v>
       </c>
       <c r="N10" s="166">
         <f t="shared" ref="N10" si="4">H10+J10+L10</f>
-        <v>-3.0662500000000001</v>
+        <v>-3.0329166666666669</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -21684,20 +21810,20 @@
         <v>-0.91267399999999999</v>
       </c>
       <c r="K11" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>-413740</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>-386040</v>
       </c>
       <c r="L11" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>-0.27582666666666672</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>-0.25735999999999998</v>
       </c>
       <c r="M11" s="71">
         <f t="shared" si="0"/>
-        <v>553525</v>
+        <v>581225</v>
       </c>
       <c r="N11" s="166">
         <f t="shared" si="0"/>
-        <v>0.36901666666666672</v>
+        <v>0.38748333333333346</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -21736,11 +21862,11 @@
         <v>3.0566666666666667E-3</v>
       </c>
       <c r="K12" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
         <v>-112135</v>
       </c>
       <c r="L12" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
         <v>-0.18689166666666668</v>
       </c>
       <c r="M12" s="71">
@@ -21788,20 +21914,20 @@
         <v>0.12322</v>
       </c>
       <c r="K13" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>-4107</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>-2640</v>
       </c>
       <c r="L13" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>-4.1070000000000002E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>-2.64E-2</v>
       </c>
       <c r="M13" s="71">
         <f t="shared" si="0"/>
-        <v>9309</v>
+        <v>10776</v>
       </c>
       <c r="N13" s="166">
         <f t="shared" si="0"/>
-        <v>9.3090000000000006E-2</v>
+        <v>0.10775999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -21840,20 +21966,20 @@
         <v>-0.65036000000000005</v>
       </c>
       <c r="K14" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>-3104</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>5194</v>
       </c>
       <c r="L14" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>-1.2415999999999998E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>2.0775999999999999E-2</v>
       </c>
       <c r="M14" s="71">
         <f t="shared" si="0"/>
-        <v>41816</v>
+        <v>50114</v>
       </c>
       <c r="N14" s="166">
         <f t="shared" si="0"/>
-        <v>0.16726399999999994</v>
+        <v>0.20045599999999994</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
@@ -21892,11 +22018,11 @@
         <v>0</v>
       </c>
       <c r="K15" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L15" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M15" s="71">
@@ -21944,20 +22070,20 @@
         <v>0.33139000000000002</v>
       </c>
       <c r="K16" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>-6421</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>-1356</v>
       </c>
       <c r="L16" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>-6.4210000000000003E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>-1.3559999999999999E-2</v>
       </c>
       <c r="M16" s="71">
         <f t="shared" si="0"/>
-        <v>66986</v>
+        <v>72051</v>
       </c>
       <c r="N16" s="166">
         <f t="shared" si="0"/>
-        <v>0.66986000000000001</v>
+        <v>0.72050999999999998</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -21996,20 +22122,20 @@
         <v>-0.4931636363636363</v>
       </c>
       <c r="K17" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>-4997</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>6197</v>
       </c>
       <c r="L17" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>-2.2713636363636359E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>2.8168181818181818E-2</v>
       </c>
       <c r="M17" s="71">
         <f t="shared" ref="M17" si="5">G17+I17+K17</f>
-        <v>-92905</v>
+        <v>-81711</v>
       </c>
       <c r="N17" s="166">
         <f t="shared" ref="N17" si="6">H17+J17+L17</f>
-        <v>-0.42229545454545453</v>
+        <v>-0.37141363636363633</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
@@ -22048,11 +22174,11 @@
         <v>-0.44636399999999998</v>
       </c>
       <c r="K18" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L18" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M18" s="71">
@@ -22100,11 +22226,11 @@
         <v>-0.20675499999999999</v>
       </c>
       <c r="K19" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L19" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M19" s="71">
@@ -22152,11 +22278,11 @@
         <v>0.25088181818181815</v>
       </c>
       <c r="K20" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
         <v>-2058</v>
       </c>
       <c r="L20" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
         <v>-1.8709090909090908E-2</v>
       </c>
       <c r="M20" s="71">
@@ -22204,20 +22330,20 @@
         <v>-2.8835999999999999</v>
       </c>
       <c r="K21" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>3771</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>-4799</v>
       </c>
       <c r="L21" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>0.15084</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>-0.19195999999999999</v>
       </c>
       <c r="M21" s="71">
         <f t="shared" ref="M21:M22" si="7">G21+I21+K21</f>
-        <v>-39775</v>
+        <v>-48345</v>
       </c>
       <c r="N21" s="166">
         <f t="shared" ref="N21:N22" si="8">H21+J21+L21</f>
-        <v>-1.5909999999999997</v>
+        <v>-1.9337999999999997</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
@@ -22256,20 +22382,20 @@
         <v>0.15673999999999999</v>
       </c>
       <c r="K22" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>8479</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>7135</v>
       </c>
       <c r="L22" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>4.2395000000000002E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>3.5674999999999998E-2</v>
       </c>
       <c r="M22" s="71">
         <f t="shared" si="7"/>
-        <v>24611</v>
+        <v>23267</v>
       </c>
       <c r="N22" s="166">
         <f t="shared" si="8"/>
-        <v>0.123055</v>
+        <v>0.11633499999999999</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
@@ -22308,20 +22434,20 @@
         <v>9.7766666666666668E-2</v>
       </c>
       <c r="K23" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>2934</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>10520</v>
       </c>
       <c r="L23" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>1.9560000000000001E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>7.0133333333333325E-2</v>
       </c>
       <c r="M23" s="71">
         <f t="shared" si="0"/>
-        <v>117947</v>
+        <v>125533</v>
       </c>
       <c r="N23" s="166">
         <f t="shared" si="0"/>
-        <v>0.78631333333333342</v>
+        <v>0.83688666666666678</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -22360,11 +22486,11 @@
         <v>0</v>
       </c>
       <c r="K24" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L24" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M24" s="71">
@@ -22412,20 +22538,20 @@
         <v>-1.1453363636363634</v>
       </c>
       <c r="K25" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>15968</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>24445</v>
       </c>
       <c r="L25" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>0.14516363636363636</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>0.22222727272727272</v>
       </c>
       <c r="M25" s="71">
         <f t="shared" si="0"/>
-        <v>220672</v>
+        <v>229149</v>
       </c>
       <c r="N25" s="166">
         <f t="shared" si="0"/>
-        <v>2.0061090909090904</v>
+        <v>2.0831727272727267</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
@@ -22464,20 +22590,20 @@
         <v>-2.2903086956521741</v>
       </c>
       <c r="K26" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>-406900</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>-512700</v>
       </c>
       <c r="L26" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>-1.7691304347826089</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>-2.2291304347826091</v>
       </c>
       <c r="M26" s="71">
         <f t="shared" si="0"/>
-        <v>-52839</v>
+        <v>-158639</v>
       </c>
       <c r="N26" s="166">
         <f t="shared" si="0"/>
-        <v>-0.2297347826086964</v>
+        <v>-0.68973478260869658</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
@@ -22514,20 +22640,20 @@
         <v>-0.8901</v>
       </c>
       <c r="K27" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>5060</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>3420</v>
       </c>
       <c r="L27" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>0.253</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>0.17100000000000001</v>
       </c>
       <c r="M27" s="71">
         <f t="shared" ref="M27" si="9">G27+I27+K27</f>
-        <v>-15236</v>
+        <v>-16876</v>
       </c>
       <c r="N27" s="166">
         <f t="shared" ref="N27" si="10">H27+J27+L27</f>
-        <v>-0.76179999999999992</v>
+        <v>-0.84379999999999988</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
@@ -22566,11 +22692,11 @@
         <v>-0.33289600000000003</v>
       </c>
       <c r="K28" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
         <v>39000</v>
       </c>
       <c r="L28" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
         <v>7.8E-2</v>
       </c>
       <c r="M28" s="71">
@@ -22618,20 +22744,20 @@
         <v>0.19531499999999999</v>
       </c>
       <c r="K29" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>72755</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>-132675</v>
       </c>
       <c r="L29" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>7.2755E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>-0.13267499999999999</v>
       </c>
       <c r="M29" s="71">
         <f t="shared" si="0"/>
-        <v>3540167</v>
+        <v>3334737</v>
       </c>
       <c r="N29" s="166">
         <f t="shared" si="0"/>
-        <v>3.5401669999999998</v>
+        <v>3.3347370000000001</v>
       </c>
       <c r="O29" s="131"/>
     </row>
@@ -22671,11 +22797,11 @@
         <v>-0.60594000000000003</v>
       </c>
       <c r="K30" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L30" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M30" s="71">
@@ -22723,11 +22849,11 @@
         <v>-0.58230000000000004</v>
       </c>
       <c r="K31" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L31" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M31" s="71">
@@ -22775,11 +22901,11 @@
         <v>-0.58148999999999995</v>
       </c>
       <c r="K32" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L32" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M32" s="71">
@@ -22827,11 +22953,11 @@
         <v>-0.69791999999999998</v>
       </c>
       <c r="K33" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L33" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M33" s="71">
@@ -22879,11 +23005,11 @@
         <v>-0.58009333333333335</v>
       </c>
       <c r="K34" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L34" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M34" s="71">
@@ -22931,11 +23057,11 @@
         <v>-1.010926</v>
       </c>
       <c r="K35" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
         <v>-475000</v>
       </c>
       <c r="L35" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
         <v>-0.95</v>
       </c>
       <c r="M35" s="71">
@@ -22983,20 +23109,20 @@
         <v>1.1398239999999999</v>
       </c>
       <c r="K36" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>-172907</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>-9724</v>
       </c>
       <c r="L36" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>-0.34581400000000001</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>-1.9448E-2</v>
       </c>
       <c r="M36" s="71">
         <f t="shared" si="0"/>
-        <v>854500</v>
+        <v>1017683</v>
       </c>
       <c r="N36" s="166">
         <f t="shared" si="0"/>
-        <v>1.7089999999999999</v>
+        <v>2.0353659999999998</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
@@ -23035,20 +23161,20 @@
         <v>-1.28678</v>
       </c>
       <c r="K37" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>-98118</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>-103387</v>
       </c>
       <c r="L37" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>-1.9623600000000001</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>-2.0677400000000001</v>
       </c>
       <c r="M37" s="71">
         <f t="shared" si="0"/>
-        <v>-177482</v>
+        <v>-182751</v>
       </c>
       <c r="N37" s="166">
         <f t="shared" si="0"/>
-        <v>-3.5496400000000001</v>
+        <v>-3.6550200000000004</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
@@ -23087,20 +23213,20 @@
         <v>1.3305</v>
       </c>
       <c r="K38" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>8586</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>-843</v>
       </c>
       <c r="L38" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>0.21465000000000001</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>-2.1075E-2</v>
       </c>
       <c r="M38" s="71">
         <f t="shared" si="0"/>
-        <v>-56939</v>
+        <v>-66368</v>
       </c>
       <c r="N38" s="166">
         <f t="shared" si="0"/>
-        <v>-1.4234749999999998</v>
+        <v>-1.6591999999999998</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
@@ -23139,11 +23265,11 @@
         <v>0.12665999999999999</v>
       </c>
       <c r="K39" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L39" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M39" s="71">
@@ -23191,11 +23317,11 @@
         <v>0</v>
       </c>
       <c r="K40" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L40" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M40" s="71">
@@ -23243,20 +23369,20 @@
         <v>0.8756275</v>
       </c>
       <c r="K41" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>-84252</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>-138378</v>
       </c>
       <c r="L41" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>-0.21063000000000001</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>-0.345945</v>
       </c>
       <c r="M41" s="71">
         <f t="shared" si="0"/>
-        <v>626684</v>
+        <v>572558</v>
       </c>
       <c r="N41" s="166">
         <f t="shared" si="0"/>
-        <v>1.56671</v>
+        <v>1.4313950000000002</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
@@ -23295,20 +23421,20 @@
         <v>0.53249000000000002</v>
       </c>
       <c r="K42" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>-7417</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>-3547</v>
       </c>
       <c r="L42" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>-7.417E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>-3.5470000000000002E-2</v>
       </c>
       <c r="M42" s="71">
         <f t="shared" si="0"/>
-        <v>196215</v>
+        <v>200085</v>
       </c>
       <c r="N42" s="166">
         <f t="shared" si="0"/>
-        <v>1.9621499999999998</v>
+        <v>2.0008499999999998</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
@@ -23345,11 +23471,11 @@
         <v>0</v>
       </c>
       <c r="K43" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L43" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M43" s="71">
@@ -23397,20 +23523,20 @@
         <v>-0.28554000000000002</v>
       </c>
       <c r="K44" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>-28760</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>-29440</v>
       </c>
       <c r="L44" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>-0.57520000000000004</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>-0.58879999999999999</v>
       </c>
       <c r="M44" s="71">
         <f t="shared" si="0"/>
-        <v>-95143</v>
+        <v>-95823</v>
       </c>
       <c r="N44" s="166">
         <f t="shared" si="0"/>
-        <v>-1.90286</v>
+        <v>-1.9164599999999998</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
@@ -23449,20 +23575,20 @@
         <v>-0.63329999999999997</v>
       </c>
       <c r="K45" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>-56406</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>-104433</v>
       </c>
       <c r="L45" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>-0.18801999999999999</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>-0.34810999999999998</v>
       </c>
       <c r="M45" s="71">
         <f t="shared" si="0"/>
-        <v>-167198</v>
+        <v>-215225</v>
       </c>
       <c r="N45" s="166">
         <f t="shared" si="0"/>
-        <v>-0.55732666666666664</v>
+        <v>-0.71741666666666659</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
@@ -23501,11 +23627,11 @@
         <v>-0.34641333333333335</v>
       </c>
       <c r="K46" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L46" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M46" s="71">
@@ -23553,11 +23679,11 @@
         <v>-0.37293333333333334</v>
       </c>
       <c r="K47" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L47" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M47" s="71">
@@ -23603,20 +23729,20 @@
         <v>-0.49170000000000003</v>
       </c>
       <c r="K48" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>20345</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>35315</v>
       </c>
       <c r="L48" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>2.0345</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>3.5314999999999999</v>
       </c>
       <c r="M48" s="71">
         <f t="shared" ref="M48" si="15">G48+I48+K48</f>
-        <v>3413</v>
+        <v>18383</v>
       </c>
       <c r="N48" s="166">
         <f t="shared" ref="N48" si="16">H48+J48+L48</f>
-        <v>0.34129999999999994</v>
+        <v>1.8382999999999998</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
@@ -23655,20 +23781,20 @@
         <v>4.5359999999999998E-2</v>
       </c>
       <c r="K49" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>2285</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>377</v>
       </c>
       <c r="L49" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>4.5699999999999998E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>7.5399999999999998E-3</v>
       </c>
       <c r="M49" s="71">
         <f t="shared" si="0"/>
-        <v>36613</v>
+        <v>34705</v>
       </c>
       <c r="N49" s="166">
         <f t="shared" si="0"/>
-        <v>0.41166000000000003</v>
+        <v>0.3735</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
@@ -23707,20 +23833,20 @@
         <v>7.0315700000000003</v>
       </c>
       <c r="K50" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>-35567</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>-69717</v>
       </c>
       <c r="L50" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>-0.35566999999999999</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>-0.69716999999999996</v>
       </c>
       <c r="M50" s="71">
         <f t="shared" si="0"/>
-        <v>851807</v>
+        <v>817657</v>
       </c>
       <c r="N50" s="166">
         <f t="shared" si="0"/>
-        <v>8.5180699999999998</v>
+        <v>8.1765699999999999</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
@@ -23757,20 +23883,20 @@
         <v>9.1899999999999996E-2</v>
       </c>
       <c r="K51" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>6480</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>7454</v>
       </c>
       <c r="L51" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>0.64800000000000002</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>0.74539999999999995</v>
       </c>
       <c r="M51" s="71">
         <f t="shared" ref="M51" si="17">G51+I51+K51</f>
-        <v>2934</v>
+        <v>3908</v>
       </c>
       <c r="N51" s="166">
         <f t="shared" ref="N51" si="18">H51+J51+L51</f>
-        <v>0.29339999999999999</v>
+        <v>0.39079999999999993</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
@@ -23809,20 +23935,20 @@
         <v>-1.2057033333333331</v>
       </c>
       <c r="K52" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>32664</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>16024</v>
       </c>
       <c r="L52" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>0.10888</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>5.3413333333333327E-2</v>
       </c>
       <c r="M52" s="71">
         <f t="shared" si="0"/>
-        <v>23931</v>
+        <v>7291</v>
       </c>
       <c r="N52" s="166">
         <f t="shared" si="0"/>
-        <v>7.9770000000000035E-2</v>
+        <v>2.4303333333333357E-2</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
@@ -23855,11 +23981,11 @@
         <v>-9.0149999999999994E-2</v>
       </c>
       <c r="K53" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L53" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M53" s="71">
@@ -23907,11 +24033,11 @@
         <v>0.15198</v>
       </c>
       <c r="K54" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
         <v>-156125</v>
       </c>
       <c r="L54" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
         <v>-0.39031250000000001</v>
       </c>
       <c r="M54" s="71">
@@ -23959,20 +24085,20 @@
         <v>-0.25410250000000001</v>
       </c>
       <c r="K55" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>31259</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>39740</v>
       </c>
       <c r="L55" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>7.8147499999999995E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>9.9349999999999994E-2</v>
       </c>
       <c r="M55" s="71">
         <f t="shared" si="0"/>
-        <v>373533</v>
+        <v>382014</v>
       </c>
       <c r="N55" s="166">
         <f t="shared" si="0"/>
-        <v>0.93383249999999995</v>
+        <v>0.95503499999999986</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
@@ -24009,20 +24135,20 @@
         <v>-1.03518</v>
       </c>
       <c r="K56" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>-371500</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>-284900</v>
       </c>
       <c r="L56" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
-        <v>-0.3715</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>-0.28489999999999999</v>
       </c>
       <c r="M56" s="71">
         <f t="shared" ref="M56" si="21">G56+I56+K56</f>
-        <v>-1406580</v>
+        <v>-1319980</v>
       </c>
       <c r="N56" s="166">
         <f t="shared" ref="N56" si="22">H56+J56+L56</f>
-        <v>-1.4066799999999999</v>
+        <v>-1.3200799999999999</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
@@ -24055,11 +24181,11 @@
         <v>0</v>
       </c>
       <c r="K57" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L57" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADN$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DO$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M57" s="71">
@@ -24107,20 +24233,20 @@
         <v>-0.14384</v>
       </c>
       <c r="K58" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>4538</v>
       </c>
       <c r="L58" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>9.0759999999999993E-2</v>
       </c>
       <c r="M58" s="71">
         <f t="shared" si="0"/>
-        <v>-34295</v>
+        <v>-29757</v>
       </c>
       <c r="N58" s="166">
         <f t="shared" si="0"/>
-        <v>-0.68589999999999995</v>
+        <v>-0.59514</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
@@ -24159,20 +24285,20 @@
         <v>0.10279846153846153</v>
       </c>
       <c r="K59" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>-152273</v>
       </c>
       <c r="L59" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>-0.23426615384615385</v>
       </c>
       <c r="M59" s="71">
         <f t="shared" si="0"/>
-        <v>943944</v>
+        <v>791671</v>
       </c>
       <c r="N59" s="166">
         <f t="shared" si="0"/>
-        <v>2.2956109615384617</v>
+        <v>2.0613448076923078</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
@@ -24211,20 +24337,20 @@
         <v>-0.20608799999999999</v>
       </c>
       <c r="K60" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>-157736</v>
       </c>
       <c r="L60" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>-1.2618879999999999</v>
       </c>
       <c r="M60" s="71">
         <f t="shared" si="0"/>
-        <v>183258</v>
+        <v>25522</v>
       </c>
       <c r="N60" s="166">
         <f t="shared" si="0"/>
-        <v>1.466064</v>
+        <v>0.20417600000000014</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
@@ -24263,20 +24389,20 @@
         <v>-0.86802666666666684</v>
       </c>
       <c r="K61" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>-106641</v>
       </c>
       <c r="L61" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>-0.35547000000000001</v>
       </c>
       <c r="M61" s="71">
         <f t="shared" si="0"/>
-        <v>704073</v>
+        <v>597432</v>
       </c>
       <c r="N61" s="166">
         <f t="shared" si="0"/>
-        <v>2.3469100000000003</v>
+        <v>1.9914400000000003</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
@@ -24315,11 +24441,11 @@
         <v>-0.31176799999999999</v>
       </c>
       <c r="K62" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L62" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M62" s="71">
@@ -24365,20 +24491,20 @@
         <v>0.55113999999999996</v>
       </c>
       <c r="K63" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>8135</v>
       </c>
       <c r="L63" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>5.4233333333333328E-2</v>
       </c>
       <c r="M63" s="71">
         <f t="shared" ref="M63" si="25">G63+I63+K63</f>
-        <v>80165</v>
+        <v>88300</v>
       </c>
       <c r="N63" s="166">
         <f t="shared" ref="N63" si="26">H63+J63+L63</f>
-        <v>0.45089999999999997</v>
+        <v>0.50513333333333332</v>
       </c>
     </row>
     <row r="64" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -24415,20 +24541,20 @@
         <v>0.43251600000000001</v>
       </c>
       <c r="K64" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>48246</v>
       </c>
       <c r="L64" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>9.6492000000000008E-2</v>
       </c>
       <c r="M64" s="71">
         <f t="shared" ref="M64" si="27">G64+I64+K64</f>
-        <v>489405</v>
+        <v>537651</v>
       </c>
       <c r="N64" s="166">
         <f t="shared" ref="N64" si="28">H64+J64+L64</f>
-        <v>0.97880999999999996</v>
+        <v>1.075302</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
@@ -24450,12 +24576,12 @@
       <c r="J65" s="100"/>
       <c r="K65" s="109">
         <f>SUM(K4:K62)</f>
-        <v>-2112291</v>
+        <v>-2645876</v>
       </c>
       <c r="L65" s="109"/>
       <c r="M65" s="154">
         <f>SUM(M4:M62)</f>
-        <v>9667746</v>
+        <v>9134161</v>
       </c>
       <c r="N65" s="235"/>
     </row>
@@ -24527,28 +24653,28 @@
         <v>2.0499333333333336</v>
       </c>
       <c r="I69" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'[2]AUG-2026'!$A$4:$ACP$113,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'[2]AUG-2026'!$A$2:$CQ$2,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'AUG-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DM$2,0),0),0)</f>
+        <v>71530</v>
       </c>
       <c r="J69" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'[2]AUG-2026'!$A$4:$ACP$113,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'[2]AUG-2026'!$A$2:$CQ$2,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'AUG-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DM$2,0),0),0)</f>
+        <v>0.2384333333333333</v>
       </c>
       <c r="K69" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>-387560</v>
       </c>
       <c r="L69" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>-1.2918666666666667</v>
       </c>
       <c r="M69" s="153">
         <f t="shared" ref="M69:N69" si="29">G69+I69+K69</f>
-        <v>614980</v>
+        <v>298950</v>
       </c>
       <c r="N69" s="167">
         <f t="shared" si="29"/>
-        <v>2.0499333333333336</v>
+        <v>0.99650000000000039</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
@@ -24577,24 +24703,24 @@
         <v>0</v>
       </c>
       <c r="I70" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'[2]AUG-2026'!$A$4:$ACP$113,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'[2]AUG-2026'!$A$2:$CQ$2,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'AUG-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DM$2,0),0),0)</f>
+        <v>197439</v>
       </c>
       <c r="J70" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'[2]AUG-2026'!$A$4:$ACP$113,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'[2]AUG-2026'!$A$2:$CQ$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'AUG-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DM$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="K70" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <v>-246000</v>
       </c>
       <c r="L70" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'[1]SEP-2026'!$A$4:$ADI$113,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'[1]SEP-2026'!$A$2:$DJ$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M70" s="153">
         <f t="shared" ref="M70" si="30">G70+I70+K70</f>
-        <v>971446</v>
+        <v>922885</v>
       </c>
       <c r="N70" s="167">
         <f t="shared" ref="N70" si="31">H70+J70+L70</f>
@@ -24602,506 +24728,520 @@
       </c>
     </row>
     <row r="71" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G71" s="93"/>
+      <c r="G71" s="93">
+        <f>SUM(G69:G70)</f>
+        <v>1586426</v>
+      </c>
       <c r="H71" s="94"/>
-      <c r="I71" s="103"/>
+      <c r="I71" s="93">
+        <f>SUM(I69:I70)</f>
+        <v>268969</v>
+      </c>
       <c r="J71" s="104"/>
-      <c r="K71" s="112"/>
+      <c r="K71" s="93">
+        <f>SUM(K69:K70)</f>
+        <v>-633560</v>
+      </c>
       <c r="L71" s="113"/>
       <c r="M71" s="93">
         <f>SUM(M69:M70)</f>
-        <v>1586426</v>
+        <v>1221835</v>
       </c>
       <c r="N71" s="236"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A45:C45 A11:C11 A3:F3 L2:L3 A41:C41 A5 A32:F32 F11 F42:F43 F45 A61:C61 A62:E62 A34:F36 E41:F41 A50:F50 A23 A38:F39 A55:F55 F59:F62 E61 G65:N66 A25:F26 M25:N26 A65:E65 C53:F53 M23:N23 G23:H26 A28:F29 A52:F52 G41:H42 G28:H39 G69:N71 F56:F57 G54:H56 A14:H16 M14:N16 K58:N63 M28:N39 M41:N42 M5:N9 G8:J9 G11:I13 M11:N12 I44:J56 M44:N52 G44:H52 G4:L4 C5:J5 M54:N56 A18:F19 G18:H20 M18:N20 I14:I42 J11:J42 K5:L56 I58:J64 G58:H63">
-    <cfRule type="expression" dxfId="394" priority="228">
+  <conditionalFormatting sqref="A45:C45 A11:C11 A3:F3 L2:L3 A41:C41 A5 A32:F32 F11 F42:F43 F45 A61:C61 A62:E62 A34:F36 E41:F41 A50:F50 A23 A38:F39 A55:F55 F59:F62 E61 G65:N66 A25:F26 M25:N26 A65:E65 C53:F53 M23:N23 G23:H26 A28:F29 A52:F52 G41:H42 G28:H39 F56:F57 G54:H56 A14:H16 M14:N16 M58:N63 M28:N39 M41:N42 M5:N9 G8:J9 G11:I13 M11:N12 I44:J56 M44:N52 G44:H52 G4:L4 C5:J5 M54:N56 A18:F19 G18:H20 M18:N20 I14:I42 J11:J42 I58:J64 G58:H63 K5:L64 G69:H70 M69:N70 G71:N71">
+    <cfRule type="expression" dxfId="391" priority="229">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:I3">
-    <cfRule type="expression" dxfId="393" priority="227">
+    <cfRule type="expression" dxfId="390" priority="228">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J3">
-    <cfRule type="expression" dxfId="392" priority="226">
+    <cfRule type="expression" dxfId="389" priority="227">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K3">
-    <cfRule type="expression" dxfId="391" priority="225">
+    <cfRule type="expression" dxfId="388" priority="226">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A42:C42 E42 A43">
-    <cfRule type="expression" dxfId="390" priority="221">
+    <cfRule type="expression" dxfId="387" priority="222">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E45">
-    <cfRule type="expression" dxfId="389" priority="219">
+    <cfRule type="expression" dxfId="386" priority="220">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A20:F20">
-    <cfRule type="expression" dxfId="388" priority="217">
+    <cfRule type="expression" dxfId="385" priority="218">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:C47 E47:F47">
-    <cfRule type="expression" dxfId="387" priority="211">
+    <cfRule type="expression" dxfId="384" priority="212">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M25:N25">
-    <cfRule type="expression" dxfId="386" priority="201">
+    <cfRule type="expression" dxfId="383" priority="202">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12:C12 E12:F12">
-    <cfRule type="expression" dxfId="385" priority="206">
+    <cfRule type="expression" dxfId="382" priority="207">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N25">
-    <cfRule type="expression" dxfId="384" priority="202">
+    <cfRule type="expression" dxfId="381" priority="203">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M12:N12">
-    <cfRule type="expression" dxfId="383" priority="187">
+    <cfRule type="expression" dxfId="380" priority="188">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23:C23 E23:F23">
-    <cfRule type="expression" dxfId="382" priority="182">
+    <cfRule type="expression" dxfId="379" priority="183">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N12">
-    <cfRule type="expression" dxfId="381" priority="188">
+    <cfRule type="expression" dxfId="378" priority="189">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A8:C8 E8:F8 A9:F9 A10:B10 D10:F10">
-    <cfRule type="expression" dxfId="380" priority="173">
+    <cfRule type="expression" dxfId="377" priority="174">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N8:N9">
-    <cfRule type="expression" dxfId="379" priority="171">
+    <cfRule type="expression" dxfId="376" priority="172">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M8:N9">
-    <cfRule type="expression" dxfId="378" priority="170">
+    <cfRule type="expression" dxfId="375" priority="171">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A37:C37 E37:F37">
-    <cfRule type="expression" dxfId="377" priority="165">
+    <cfRule type="expression" dxfId="374" priority="166">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M37:N37">
-    <cfRule type="expression" dxfId="376" priority="161">
+    <cfRule type="expression" dxfId="373" priority="162">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N37">
-    <cfRule type="expression" dxfId="375" priority="162">
+    <cfRule type="expression" dxfId="372" priority="163">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A49:C49 E49:F49">
-    <cfRule type="expression" dxfId="374" priority="156">
+    <cfRule type="expression" dxfId="371" priority="157">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N23">
-    <cfRule type="expression" dxfId="373" priority="142">
+    <cfRule type="expression" dxfId="370" priority="143">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M23:N23">
-    <cfRule type="expression" dxfId="372" priority="141">
+    <cfRule type="expression" dxfId="369" priority="142">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58:C58 E58:F58">
-    <cfRule type="expression" dxfId="371" priority="131">
+    <cfRule type="expression" dxfId="368" priority="132">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L67:L68">
-    <cfRule type="expression" dxfId="370" priority="125">
+    <cfRule type="expression" dxfId="367" priority="126">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G67:I68">
-    <cfRule type="expression" dxfId="369" priority="124">
+    <cfRule type="expression" dxfId="366" priority="125">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J67:J68">
-    <cfRule type="expression" dxfId="368" priority="123">
+    <cfRule type="expression" dxfId="365" priority="124">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K67:K68">
-    <cfRule type="expression" dxfId="367" priority="122">
+    <cfRule type="expression" dxfId="364" priority="123">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A30:F30">
-    <cfRule type="expression" dxfId="366" priority="121">
+    <cfRule type="expression" dxfId="363" priority="122">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A31:F31">
-    <cfRule type="expression" dxfId="365" priority="120">
+    <cfRule type="expression" dxfId="362" priority="121">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A33:F33">
-    <cfRule type="expression" dxfId="364" priority="119">
+    <cfRule type="expression" dxfId="361" priority="120">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D11:E11">
-    <cfRule type="expression" dxfId="363" priority="108">
+    <cfRule type="expression" dxfId="360" priority="109">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A59:C60 E59:E60">
-    <cfRule type="expression" dxfId="362" priority="104">
+    <cfRule type="expression" dxfId="359" priority="105">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M59:N60">
-    <cfRule type="expression" dxfId="361" priority="103">
+    <cfRule type="expression" dxfId="358" priority="104">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A46:C46 E46:F46">
-    <cfRule type="expression" dxfId="360" priority="100">
+    <cfRule type="expression" dxfId="357" priority="101">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A54:B54">
-    <cfRule type="expression" dxfId="359" priority="96">
+    <cfRule type="expression" dxfId="356" priority="97">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4:C4 E4:F4">
-    <cfRule type="expression" dxfId="358" priority="91">
+    <cfRule type="expression" dxfId="355" priority="92">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M4:N4">
-    <cfRule type="expression" dxfId="357" priority="90">
+    <cfRule type="expression" dxfId="354" priority="91">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M4:N4">
-    <cfRule type="expression" dxfId="356" priority="87">
+    <cfRule type="expression" dxfId="353" priority="88">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N4">
-    <cfRule type="expression" dxfId="355" priority="88">
+    <cfRule type="expression" dxfId="352" priority="89">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A44:C44 E44:F44">
-    <cfRule type="expression" dxfId="354" priority="82">
+    <cfRule type="expression" dxfId="351" priority="83">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A69:F69 F70">
-    <cfRule type="expression" dxfId="353" priority="81">
+    <cfRule type="expression" dxfId="350" priority="82">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:F13">
-    <cfRule type="expression" dxfId="352" priority="73">
+    <cfRule type="expression" dxfId="349" priority="74">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M13:N13">
-    <cfRule type="expression" dxfId="351" priority="72">
+    <cfRule type="expression" dxfId="348" priority="73">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M13:N13">
-    <cfRule type="expression" dxfId="350" priority="69">
+    <cfRule type="expression" dxfId="347" priority="70">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N13">
-    <cfRule type="expression" dxfId="349" priority="70">
+    <cfRule type="expression" dxfId="346" priority="71">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F54">
-    <cfRule type="expression" dxfId="348" priority="62">
+    <cfRule type="expression" dxfId="345" priority="63">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D54:E54">
-    <cfRule type="expression" dxfId="347" priority="61">
+    <cfRule type="expression" dxfId="344" priority="62">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="346" priority="60">
+    <cfRule type="expression" dxfId="343" priority="61">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4">
-    <cfRule type="expression" dxfId="345" priority="59">
+    <cfRule type="expression" dxfId="342" priority="60">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D12">
-    <cfRule type="expression" dxfId="344" priority="58">
+    <cfRule type="expression" dxfId="341" priority="59">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D23">
-    <cfRule type="expression" dxfId="343" priority="57">
+    <cfRule type="expression" dxfId="340" priority="58">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D59:D60">
-    <cfRule type="expression" dxfId="342" priority="46">
+    <cfRule type="expression" dxfId="339" priority="47">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D37">
-    <cfRule type="expression" dxfId="341" priority="56">
+    <cfRule type="expression" dxfId="338" priority="57">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D42 D44">
-    <cfRule type="expression" dxfId="340" priority="55">
+    <cfRule type="expression" dxfId="337" priority="56">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D41">
-    <cfRule type="expression" dxfId="339" priority="54">
+    <cfRule type="expression" dxfId="336" priority="55">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D45">
-    <cfRule type="expression" dxfId="338" priority="53">
+    <cfRule type="expression" dxfId="335" priority="54">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D46">
-    <cfRule type="expression" dxfId="337" priority="52">
+    <cfRule type="expression" dxfId="334" priority="53">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D47">
-    <cfRule type="expression" dxfId="336" priority="51">
+    <cfRule type="expression" dxfId="333" priority="52">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D49">
-    <cfRule type="expression" dxfId="335" priority="50">
+    <cfRule type="expression" dxfId="332" priority="51">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D61">
-    <cfRule type="expression" dxfId="334" priority="49">
+    <cfRule type="expression" dxfId="331" priority="50">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D58">
-    <cfRule type="expression" dxfId="333" priority="47">
+    <cfRule type="expression" dxfId="330" priority="48">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:F24">
-    <cfRule type="expression" dxfId="332" priority="45">
+    <cfRule type="expression" dxfId="329" priority="46">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M24:N24">
-    <cfRule type="expression" dxfId="331" priority="44">
+    <cfRule type="expression" dxfId="328" priority="45">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N24">
-    <cfRule type="expression" dxfId="330" priority="41">
+    <cfRule type="expression" dxfId="327" priority="42">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M24:N24">
-    <cfRule type="expression" dxfId="329" priority="40">
+    <cfRule type="expression" dxfId="326" priority="41">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A64:F64">
-    <cfRule type="expression" dxfId="328" priority="33">
+    <cfRule type="expression" dxfId="325" priority="34">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G64:H64 K64:N64">
-    <cfRule type="expression" dxfId="327" priority="32">
+  <conditionalFormatting sqref="G64:H64 M64:N64">
+    <cfRule type="expression" dxfId="324" priority="33">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A53:B53">
-    <cfRule type="expression" dxfId="326" priority="31">
+    <cfRule type="expression" dxfId="323" priority="32">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G53:H53 M53:N53">
-    <cfRule type="expression" dxfId="325" priority="30">
+    <cfRule type="expression" dxfId="322" priority="31">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40:F40">
-    <cfRule type="expression" dxfId="324" priority="29">
+    <cfRule type="expression" dxfId="321" priority="30">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G40:H40 M40:N40">
-    <cfRule type="expression" dxfId="323" priority="28">
+    <cfRule type="expression" dxfId="320" priority="29">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A48:F48">
-    <cfRule type="expression" dxfId="322" priority="27">
+    <cfRule type="expression" dxfId="319" priority="28">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:F17">
-    <cfRule type="expression" dxfId="321" priority="26">
+    <cfRule type="expression" dxfId="318" priority="27">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G17:H17 M17:N17">
-    <cfRule type="expression" dxfId="320" priority="25">
+    <cfRule type="expression" dxfId="317" priority="26">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:F22 C21:F21">
-    <cfRule type="expression" dxfId="319" priority="24">
+    <cfRule type="expression" dxfId="316" priority="25">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G21:H22 M21:N22">
-    <cfRule type="expression" dxfId="318" priority="23">
+    <cfRule type="expression" dxfId="315" priority="24">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G27:H27 M27:N27">
-    <cfRule type="expression" dxfId="317" priority="19">
+    <cfRule type="expression" dxfId="314" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27:F27">
-    <cfRule type="expression" dxfId="316" priority="22">
+    <cfRule type="expression" dxfId="313" priority="23">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A51:F51">
-    <cfRule type="expression" dxfId="315" priority="21">
+    <cfRule type="expression" dxfId="312" priority="22">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A63:F63">
-    <cfRule type="expression" dxfId="314" priority="20">
+    <cfRule type="expression" dxfId="311" priority="21">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A70:E70">
-    <cfRule type="expression" dxfId="313" priority="18">
+    <cfRule type="expression" dxfId="310" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A56:E56 A57">
-    <cfRule type="expression" dxfId="312" priority="16">
+    <cfRule type="expression" dxfId="309" priority="17">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A6:F7">
-    <cfRule type="expression" dxfId="311" priority="15">
+    <cfRule type="expression" dxfId="308" priority="16">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G6:J7">
-    <cfRule type="expression" dxfId="310" priority="14">
+    <cfRule type="expression" dxfId="307" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B57:E57">
-    <cfRule type="expression" dxfId="309" priority="13">
+    <cfRule type="expression" dxfId="306" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5">
-    <cfRule type="expression" dxfId="308" priority="12">
+    <cfRule type="expression" dxfId="305" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C10">
-    <cfRule type="expression" dxfId="307" priority="11">
+    <cfRule type="expression" dxfId="304" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G10:J10 M10:N10">
-    <cfRule type="expression" dxfId="306" priority="10">
+    <cfRule type="expression" dxfId="303" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N10">
-    <cfRule type="expression" dxfId="305" priority="9">
+    <cfRule type="expression" dxfId="302" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M10:N10">
-    <cfRule type="expression" dxfId="304" priority="8">
+    <cfRule type="expression" dxfId="301" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="expression" dxfId="303" priority="7">
+    <cfRule type="expression" dxfId="300" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C43">
-    <cfRule type="expression" dxfId="302" priority="6">
+    <cfRule type="expression" dxfId="299" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D43:E43">
-    <cfRule type="expression" dxfId="301" priority="5">
+    <cfRule type="expression" dxfId="298" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G43:J43 M43:N43">
-    <cfRule type="expression" dxfId="300" priority="4">
+    <cfRule type="expression" dxfId="297" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21">
-    <cfRule type="expression" dxfId="299" priority="3">
+    <cfRule type="expression" dxfId="296" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:A22">
-    <cfRule type="expression" dxfId="298" priority="2">
+    <cfRule type="expression" dxfId="295" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G57:N57">
-    <cfRule type="expression" dxfId="297" priority="1">
+  <conditionalFormatting sqref="G57:J57 M57:N57">
+    <cfRule type="expression" dxfId="294" priority="2">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I69:L70">
+    <cfRule type="expression" dxfId="293" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -30792,42 +30932,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2 A48:A49 AE58 AD56:AE57 AE43:AE55 AD42:AD55 A3:G4 AD6:AE9 AD12:AE19 AD21:AD40 AE21:AE39 H2:AE4 A10:AE11 C48:AC49 A5:AC9 A50:AC57 A12:AC47 A59:AE63">
-    <cfRule type="expression" dxfId="296" priority="13">
+    <cfRule type="expression" dxfId="292" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE40">
-    <cfRule type="expression" dxfId="295" priority="12">
+    <cfRule type="expression" dxfId="291" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE42">
-    <cfRule type="expression" dxfId="294" priority="11">
+    <cfRule type="expression" dxfId="290" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48:B49">
-    <cfRule type="expression" dxfId="293" priority="5">
+    <cfRule type="expression" dxfId="289" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD5:AE5">
-    <cfRule type="expression" dxfId="292" priority="4">
+    <cfRule type="expression" dxfId="288" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD41">
-    <cfRule type="expression" dxfId="291" priority="3">
+    <cfRule type="expression" dxfId="287" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE41">
-    <cfRule type="expression" dxfId="290" priority="2">
+    <cfRule type="expression" dxfId="286" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD20:AE20">
-    <cfRule type="expression" dxfId="289" priority="1">
+    <cfRule type="expression" dxfId="285" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -36865,112 +37005,112 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G30 G14:G15 G2 A57:G57 G58 A55:A56 H2:AC4 A17:G27 H57:AA62 AC67 AC50:AC64 AB5:AC5 A53:G53 H49:AA54 AB49:AB64 A37:AA40 H5:AA15 AB7:AC15 A16:AC16 A31:G36 H17:AA36 AB65:AC66 AC17:AC46 AB17:AB47 A68:AC71 A54:B54 D54:G54 C55:AA56 A3:G5 A7:G8 A6:C6 E6:G6 A10:G13 A9:C9 E9:G9 A29:G29 A28:C28 E28:G28 A42:AA45 A41:C41 E41:AA41 A47:AA48 A46:C46 E46:AA46 A49:C52 E49:G52 A64:AA66 A59:C63 E63:AA63 E59:G62">
-    <cfRule type="expression" dxfId="288" priority="28">
+    <cfRule type="expression" dxfId="284" priority="28">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC47">
-    <cfRule type="expression" dxfId="287" priority="27">
+    <cfRule type="expression" dxfId="283" priority="27">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC49">
-    <cfRule type="expression" dxfId="286" priority="26">
+    <cfRule type="expression" dxfId="282" priority="26">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A30:C30 F30">
-    <cfRule type="expression" dxfId="285" priority="25">
+    <cfRule type="expression" dxfId="281" priority="25">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14:F14 A15:C15 E15:F15">
-    <cfRule type="expression" dxfId="284" priority="23">
+    <cfRule type="expression" dxfId="280" priority="23">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D30:E30">
-    <cfRule type="expression" dxfId="283" priority="22">
+    <cfRule type="expression" dxfId="279" priority="22">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58:F58">
-    <cfRule type="expression" dxfId="282" priority="20">
+    <cfRule type="expression" dxfId="278" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55:B56">
-    <cfRule type="expression" dxfId="281" priority="19">
+    <cfRule type="expression" dxfId="277" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB6:AC6">
-    <cfRule type="expression" dxfId="280" priority="15">
+    <cfRule type="expression" dxfId="276" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB48">
-    <cfRule type="expression" dxfId="279" priority="14">
+    <cfRule type="expression" dxfId="275" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC48">
-    <cfRule type="expression" dxfId="278" priority="13">
+    <cfRule type="expression" dxfId="274" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6">
-    <cfRule type="expression" dxfId="277" priority="12">
+    <cfRule type="expression" dxfId="273" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9">
-    <cfRule type="expression" dxfId="276" priority="11">
+    <cfRule type="expression" dxfId="272" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D15">
-    <cfRule type="expression" dxfId="275" priority="10">
+    <cfRule type="expression" dxfId="271" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D28">
-    <cfRule type="expression" dxfId="274" priority="9">
+    <cfRule type="expression" dxfId="270" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D41">
-    <cfRule type="expression" dxfId="273" priority="8">
+    <cfRule type="expression" dxfId="269" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D46">
-    <cfRule type="expression" dxfId="272" priority="7">
+    <cfRule type="expression" dxfId="268" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D49">
-    <cfRule type="expression" dxfId="271" priority="6">
+    <cfRule type="expression" dxfId="267" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D60:D63">
-    <cfRule type="expression" dxfId="270" priority="1">
+    <cfRule type="expression" dxfId="266" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D50:D51">
-    <cfRule type="expression" dxfId="269" priority="5">
+    <cfRule type="expression" dxfId="265" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D52">
-    <cfRule type="expression" dxfId="268" priority="4">
+    <cfRule type="expression" dxfId="264" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D59">
-    <cfRule type="expression" dxfId="267" priority="2">
+    <cfRule type="expression" dxfId="263" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -42885,107 +43025,107 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G29 G13:G14 G2 A30:G36 A39:G40 G53 A58:C61 G57 H39:AA53 H56:AA59 A54:A55 F54:AA55 A37:AA38 H2:AC4 A15:G26 H5:AA36 AC49:AC58 AC60:AC64 AC5:AC46 AB5:AB61 A62:AB63 A65:AC68 A3:G7 A9:G12 A8:C8 E8:G8 A28:G28 A27:C27 E27:G27 A42:G45 A41:C41 E41:G41 A52:G52 A46:C51 E46:G51 A56:G56 E58:G59 E60:AA61">
-    <cfRule type="expression" dxfId="266" priority="24">
+    <cfRule type="expression" dxfId="262" priority="24">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC47">
-    <cfRule type="expression" dxfId="265" priority="23">
+    <cfRule type="expression" dxfId="261" priority="23">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC48">
-    <cfRule type="expression" dxfId="264" priority="22">
+    <cfRule type="expression" dxfId="260" priority="22">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A29:C29 F29">
-    <cfRule type="expression" dxfId="263" priority="21">
+    <cfRule type="expression" dxfId="259" priority="21">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC59">
-    <cfRule type="expression" dxfId="262" priority="20">
+    <cfRule type="expression" dxfId="258" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:F13 A14:C14 E14:F14">
-    <cfRule type="expression" dxfId="261" priority="19">
+    <cfRule type="expression" dxfId="257" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D29:E29">
-    <cfRule type="expression" dxfId="260" priority="18">
+    <cfRule type="expression" dxfId="256" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A53:B53 F53">
-    <cfRule type="expression" dxfId="259" priority="15">
+    <cfRule type="expression" dxfId="255" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A57:F57">
-    <cfRule type="expression" dxfId="258" priority="14">
+    <cfRule type="expression" dxfId="254" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54:B55">
-    <cfRule type="expression" dxfId="257" priority="13">
+    <cfRule type="expression" dxfId="253" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D53:E53 C54:E55">
-    <cfRule type="expression" dxfId="256" priority="12">
+    <cfRule type="expression" dxfId="252" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D58:D61">
-    <cfRule type="expression" dxfId="255" priority="1">
+    <cfRule type="expression" dxfId="251" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="254" priority="10">
+    <cfRule type="expression" dxfId="250" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="253" priority="9">
+    <cfRule type="expression" dxfId="249" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D27">
-    <cfRule type="expression" dxfId="252" priority="8">
+    <cfRule type="expression" dxfId="248" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D41">
-    <cfRule type="expression" dxfId="251" priority="7">
+    <cfRule type="expression" dxfId="247" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D47:D48">
-    <cfRule type="expression" dxfId="250" priority="6">
+    <cfRule type="expression" dxfId="246" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D46">
-    <cfRule type="expression" dxfId="249" priority="5">
+    <cfRule type="expression" dxfId="245" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D49">
-    <cfRule type="expression" dxfId="248" priority="4">
+    <cfRule type="expression" dxfId="244" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D50">
-    <cfRule type="expression" dxfId="247" priority="3">
+    <cfRule type="expression" dxfId="243" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D51">
-    <cfRule type="expression" dxfId="246" priority="2">
+    <cfRule type="expression" dxfId="242" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -43007,22 +43147,22 @@
     <col min="4" max="4" width="17.28515625" customWidth="1"/>
     <col min="5" max="5" width="14.5703125" style="132" customWidth="1"/>
     <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="8" width="9.42578125" customWidth="1" outlineLevel="1"/>
-    <col min="9" max="9" width="11.28515625" customWidth="1" outlineLevel="1"/>
-    <col min="10" max="10" width="10" customWidth="1" outlineLevel="1"/>
-    <col min="11" max="11" width="11.140625" customWidth="1" outlineLevel="1"/>
-    <col min="12" max="12" width="10.5703125" customWidth="1" outlineLevel="1"/>
-    <col min="13" max="14" width="10.5703125" style="1" customWidth="1" outlineLevel="1"/>
-    <col min="15" max="15" width="10.5703125" style="132" customWidth="1"/>
+    <col min="7" max="7" width="11" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="8" width="9.42578125" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="9" max="9" width="11.28515625" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="10" max="10" width="10" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="11" max="11" width="11.140625" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="12" max="12" width="10.5703125" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="13" max="14" width="10.5703125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="15" max="15" width="10.5703125" style="132" customWidth="1" collapsed="1"/>
     <col min="16" max="16" width="12.140625" style="1" customWidth="1" outlineLevel="1"/>
     <col min="17" max="17" width="10.5703125" style="1" customWidth="1" outlineLevel="1"/>
     <col min="18" max="18" width="10.5703125" style="132" customWidth="1"/>
-    <col min="19" max="20" width="10.5703125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="21" max="21" width="10.5703125" style="132" customWidth="1" collapsed="1"/>
-    <col min="22" max="22" width="10.5703125" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="23" max="23" width="9.140625" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="24" max="24" width="8.5703125" customWidth="1" collapsed="1"/>
+    <col min="19" max="20" width="10.5703125" style="1" customWidth="1" outlineLevel="1"/>
+    <col min="21" max="21" width="10.5703125" style="132" customWidth="1"/>
+    <col min="22" max="22" width="10.5703125" customWidth="1" outlineLevel="1"/>
+    <col min="23" max="23" width="9.140625" customWidth="1" outlineLevel="1"/>
+    <col min="24" max="24" width="8.5703125" customWidth="1"/>
     <col min="25" max="25" width="13.85546875" style="2" customWidth="1" outlineLevel="1"/>
     <col min="26" max="26" width="9.140625" style="2" customWidth="1" outlineLevel="1"/>
     <col min="28" max="28" width="19.7109375" customWidth="1"/>
@@ -43337,11 +43477,11 @@
       <c r="O6" s="215"/>
       <c r="P6" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-38806</v>
+        <v>-39455</v>
       </c>
       <c r="Q6" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.77612000000000003</v>
+        <v>-0.78910000000000002</v>
       </c>
       <c r="R6" s="159"/>
       <c r="S6" s="153">
@@ -43358,11 +43498,11 @@
       <c r="X6" s="132"/>
       <c r="Y6" s="154">
         <f t="shared" si="0"/>
-        <v>-87142</v>
+        <v>-87791</v>
       </c>
       <c r="Z6" s="168">
         <f t="shared" si="1"/>
-        <v>-1.7428400000000002</v>
+        <v>-1.7558199999999999</v>
       </c>
     </row>
     <row r="7" spans="1:26" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -43419,11 +43559,11 @@
       <c r="O7" s="215"/>
       <c r="P7" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-359151</v>
+        <v>-285802</v>
       </c>
       <c r="Q7" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1.1971700000000001</v>
+        <v>-0.95267333333333337</v>
       </c>
       <c r="R7" s="159"/>
       <c r="S7" s="88">
@@ -43440,11 +43580,11 @@
       <c r="X7"/>
       <c r="Y7" s="154">
         <f t="shared" si="0"/>
-        <v>975123</v>
+        <v>1048472</v>
       </c>
       <c r="Z7" s="168">
         <f t="shared" si="1"/>
-        <v>3.2504100000000005</v>
+        <v>3.494906666666667</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -43616,11 +43756,11 @@
       <c r="O10" s="215"/>
       <c r="P10" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-347340</v>
+        <v>-393340</v>
       </c>
       <c r="Q10" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1.1577999999999999</v>
+        <v>-1.3111333333333333</v>
       </c>
       <c r="R10" s="159"/>
       <c r="S10" s="88">
@@ -43636,11 +43776,11 @@
       <c r="W10" s="72"/>
       <c r="Y10" s="154">
         <f t="shared" si="0"/>
-        <v>-706249</v>
+        <v>-752249</v>
       </c>
       <c r="Z10" s="168">
         <f t="shared" si="1"/>
-        <v>-3.7984800000000001</v>
+        <v>-3.9518133333333334</v>
       </c>
     </row>
     <row r="11" spans="1:26" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -43697,11 +43837,11 @@
       <c r="O11" s="215"/>
       <c r="P11" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-212588</v>
+        <v>-217613</v>
       </c>
       <c r="Q11" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1.4172533333333335</v>
+        <v>-1.4507533333333336</v>
       </c>
       <c r="R11" s="159"/>
       <c r="S11" s="153">
@@ -43717,11 +43857,11 @@
       <c r="W11" s="150"/>
       <c r="Y11" s="154">
         <f t="shared" si="0"/>
-        <v>-387550</v>
+        <v>-392575</v>
       </c>
       <c r="Z11" s="168">
         <f t="shared" si="1"/>
-        <v>-2.5836666666666668</v>
+        <v>-2.6171666666666669</v>
       </c>
     </row>
     <row r="12" spans="1:26" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -43778,11 +43918,11 @@
       <c r="O12" s="215"/>
       <c r="P12" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-183975</v>
+        <v>-181975</v>
       </c>
       <c r="Q12" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-3.0662500000000001</v>
+        <v>-3.0329166666666669</v>
       </c>
       <c r="R12" s="159"/>
       <c r="S12" s="153">
@@ -43798,11 +43938,11 @@
       <c r="W12" s="150"/>
       <c r="Y12" s="154">
         <f t="shared" ref="Y12" si="10">M12+P12+S12+V12</f>
-        <v>-183975</v>
+        <v>-181975</v>
       </c>
       <c r="Z12" s="168">
         <f t="shared" ref="Z12" si="11">(N12+Q12+T12+W12)</f>
-        <v>-3.0662500000000001</v>
+        <v>-3.0329166666666669</v>
       </c>
     </row>
     <row r="13" spans="1:26" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -43859,11 +43999,11 @@
       <c r="O13" s="215"/>
       <c r="P13" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>553525</v>
+        <v>581225</v>
       </c>
       <c r="Q13" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.36901666666666672</v>
+        <v>0.38748333333333346</v>
       </c>
       <c r="R13" s="159"/>
       <c r="S13" s="88">
@@ -43880,11 +44020,11 @@
       <c r="X13"/>
       <c r="Y13" s="154">
         <f t="shared" si="0"/>
-        <v>-814674</v>
+        <v>-786974</v>
       </c>
       <c r="Z13" s="168">
         <f t="shared" si="1"/>
-        <v>-0.54311599999999993</v>
+        <v>-0.5246493333333333</v>
       </c>
     </row>
     <row r="14" spans="1:26" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -44349,11 +44489,11 @@
       <c r="O19" s="215"/>
       <c r="P19" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>9309</v>
+        <v>10776</v>
       </c>
       <c r="Q19" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>9.3090000000000006E-2</v>
+        <v>0.10775999999999999</v>
       </c>
       <c r="R19" s="159"/>
       <c r="S19" s="153">
@@ -44369,11 +44509,11 @@
       <c r="W19" s="150"/>
       <c r="Y19" s="154">
         <f t="shared" si="0"/>
-        <v>12988</v>
+        <v>14455</v>
       </c>
       <c r="Z19" s="168">
         <f t="shared" si="1"/>
-        <v>0.12988</v>
+        <v>0.14455000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -44520,11 +44660,11 @@
       <c r="O21" s="215"/>
       <c r="P21" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>41816</v>
+        <v>50114</v>
       </c>
       <c r="Q21" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.16726399999999994</v>
+        <v>0.20045599999999994</v>
       </c>
       <c r="R21" s="159"/>
       <c r="S21" s="88">
@@ -44540,11 +44680,11 @@
       <c r="W21" s="72"/>
       <c r="Y21" s="154">
         <f t="shared" si="0"/>
-        <v>-225600</v>
+        <v>-217302</v>
       </c>
       <c r="Z21" s="168">
         <f t="shared" si="1"/>
-        <v>-2.5068960000000002</v>
+        <v>-2.4737040000000001</v>
       </c>
     </row>
     <row r="22" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -44601,11 +44741,11 @@
       <c r="O22" s="215"/>
       <c r="P22" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-92905</v>
+        <v>-81711</v>
       </c>
       <c r="Q22" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.42229545454545453</v>
+        <v>-0.37141363636363633</v>
       </c>
       <c r="R22" s="159"/>
       <c r="S22" s="88">
@@ -44621,11 +44761,11 @@
       <c r="W22" s="72"/>
       <c r="Y22" s="154">
         <f t="shared" si="0"/>
-        <v>-181805</v>
+        <v>-170611</v>
       </c>
       <c r="Z22" s="168">
         <f t="shared" si="1"/>
-        <v>-1.3112954545454545</v>
+        <v>-1.2604136363636362</v>
       </c>
     </row>
     <row r="23" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -44763,11 +44903,11 @@
       <c r="O24" s="215"/>
       <c r="P24" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>66986</v>
+        <v>72051</v>
       </c>
       <c r="Q24" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.66986000000000001</v>
+        <v>0.72050999999999998</v>
       </c>
       <c r="R24" s="159"/>
       <c r="S24" s="88">
@@ -44783,11 +44923,11 @@
       <c r="W24" s="72"/>
       <c r="Y24" s="154">
         <f t="shared" si="0"/>
-        <v>1782331</v>
+        <v>1787396</v>
       </c>
       <c r="Z24" s="168">
         <f t="shared" si="1"/>
-        <v>17.823309999999999</v>
+        <v>17.87396</v>
       </c>
     </row>
     <row r="25" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45419,11 +45559,11 @@
       <c r="O32" s="215"/>
       <c r="P32" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>117947</v>
+        <v>125533</v>
       </c>
       <c r="Q32" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.78631333333333342</v>
+        <v>0.83688666666666678</v>
       </c>
       <c r="R32" s="159"/>
       <c r="S32" s="88">
@@ -45440,11 +45580,11 @@
       <c r="X32"/>
       <c r="Y32" s="154">
         <f t="shared" si="0"/>
-        <v>-387122</v>
+        <v>-379536</v>
       </c>
       <c r="Z32" s="168">
         <f t="shared" si="1"/>
-        <v>-2.5808133333333343</v>
+        <v>-2.5302400000000009</v>
       </c>
     </row>
     <row r="33" spans="1:34" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45582,11 +45722,11 @@
       <c r="O34" s="215"/>
       <c r="P34" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>220672</v>
+        <v>229149</v>
       </c>
       <c r="Q34" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>2.0061090909090904</v>
+        <v>2.0831727272727267</v>
       </c>
       <c r="R34" s="159"/>
       <c r="S34" s="88">
@@ -45602,11 +45742,11 @@
       <c r="W34" s="72"/>
       <c r="Y34" s="154">
         <f t="shared" si="0"/>
-        <v>-98268</v>
+        <v>-89791</v>
       </c>
       <c r="Z34" s="168">
         <f t="shared" si="1"/>
-        <v>-0.89334545454545466</v>
+        <v>-0.81628181818181833</v>
       </c>
       <c r="AB34" s="1"/>
       <c r="AC34" s="1"/>
@@ -45751,11 +45891,11 @@
       <c r="O36" s="215"/>
       <c r="P36" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-52839</v>
+        <v>-158639</v>
       </c>
       <c r="Q36" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.2297347826086964</v>
+        <v>-0.68973478260869658</v>
       </c>
       <c r="R36" s="159"/>
       <c r="S36" s="88">
@@ -45771,11 +45911,11 @@
       <c r="W36" s="72"/>
       <c r="Y36" s="154">
         <f t="shared" si="0"/>
-        <v>4108264</v>
+        <v>4002464</v>
       </c>
       <c r="Z36" s="168">
         <f t="shared" si="1"/>
-        <v>17.862017391304349</v>
+        <v>17.402017391304348</v>
       </c>
     </row>
     <row r="37" spans="1:34" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45830,11 +45970,11 @@
       <c r="O37" s="215"/>
       <c r="P37" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-15236</v>
+        <v>-16876</v>
       </c>
       <c r="Q37" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.76179999999999992</v>
+        <v>-0.84379999999999988</v>
       </c>
       <c r="R37" s="159"/>
       <c r="S37" s="153">
@@ -45850,11 +45990,11 @@
       <c r="W37" s="150"/>
       <c r="Y37" s="154">
         <f t="shared" ref="Y37" si="20">M37+P37+S37+V37</f>
-        <v>-15236</v>
+        <v>-16876</v>
       </c>
       <c r="Z37" s="168">
         <f t="shared" ref="Z37" si="21">(N37+Q37+T37+W37)</f>
-        <v>-0.76179999999999992</v>
+        <v>-0.84379999999999988</v>
       </c>
     </row>
     <row r="38" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45992,11 +46132,11 @@
       <c r="O39" s="215"/>
       <c r="P39" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>3540167</v>
+        <v>3334737</v>
       </c>
       <c r="Q39" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>3.5401669999999998</v>
+        <v>3.3347370000000001</v>
       </c>
       <c r="R39" s="159"/>
       <c r="S39" s="88">
@@ -46013,11 +46153,11 @@
       <c r="X39" s="132"/>
       <c r="Y39" s="154">
         <f t="shared" ref="Y39:Y74" si="22">M39+P39+S39+V39</f>
-        <v>7133573</v>
+        <v>6928143</v>
       </c>
       <c r="Z39" s="168">
         <f t="shared" ref="Z39:Z74" si="23">(N39+Q39+T39+W39)</f>
-        <v>7.1335730000000002</v>
+        <v>6.9281430000000004</v>
       </c>
       <c r="AB39" s="131"/>
     </row>
@@ -46589,11 +46729,11 @@
       <c r="O46" s="215"/>
       <c r="P46" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>854500</v>
+        <v>1017683</v>
       </c>
       <c r="Q46" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1.7089999999999999</v>
+        <v>2.0353659999999998</v>
       </c>
       <c r="R46" s="159"/>
       <c r="S46" s="88">
@@ -46610,11 +46750,11 @@
       <c r="X46" s="1"/>
       <c r="Y46" s="154">
         <f t="shared" si="22"/>
-        <v>806762</v>
+        <v>969945</v>
       </c>
       <c r="Z46" s="168">
         <f t="shared" si="23"/>
-        <v>1.6135239999999997</v>
+        <v>1.9398899999999997</v>
       </c>
       <c r="AA46" s="1"/>
     </row>
@@ -46672,11 +46812,11 @@
       <c r="O47" s="215"/>
       <c r="P47" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-177482</v>
+        <v>-182751</v>
       </c>
       <c r="Q47" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-3.5496400000000001</v>
+        <v>-3.6550200000000004</v>
       </c>
       <c r="R47" s="159"/>
       <c r="S47" s="88">
@@ -46692,11 +46832,11 @@
       <c r="W47" s="72"/>
       <c r="Y47" s="154">
         <f t="shared" si="22"/>
-        <v>-60587</v>
+        <v>-65856</v>
       </c>
       <c r="Z47" s="168">
         <f t="shared" si="23"/>
-        <v>-1.2117400000000003</v>
+        <v>-1.3171200000000005</v>
       </c>
       <c r="AD47" s="1"/>
       <c r="AE47" s="1"/>
@@ -46841,11 +46981,11 @@
       <c r="O49" s="215"/>
       <c r="P49" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-56939</v>
+        <v>-66368</v>
       </c>
       <c r="Q49" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1.4234749999999998</v>
+        <v>-1.6591999999999998</v>
       </c>
       <c r="R49" s="159"/>
       <c r="S49" s="88">
@@ -46861,11 +47001,11 @@
       <c r="W49" s="72"/>
       <c r="Y49" s="154">
         <f t="shared" si="22"/>
-        <v>-68767</v>
+        <v>-78196</v>
       </c>
       <c r="Z49" s="168">
         <f t="shared" si="23"/>
-        <v>-1.7191749999999999</v>
+        <v>-1.9548999999999999</v>
       </c>
       <c r="AD49"/>
       <c r="AE49"/>
@@ -47096,11 +47236,11 @@
       <c r="O52" s="215"/>
       <c r="P52" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>626684</v>
+        <v>572558</v>
       </c>
       <c r="Q52" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1.56671</v>
+        <v>1.4313950000000002</v>
       </c>
       <c r="R52" s="159"/>
       <c r="S52" s="88">
@@ -47116,11 +47256,11 @@
       <c r="W52" s="72"/>
       <c r="Y52" s="154">
         <f t="shared" si="22"/>
-        <v>226385</v>
+        <v>172259</v>
       </c>
       <c r="Z52" s="168">
         <f t="shared" si="23"/>
-        <v>0.56596249999999992</v>
+        <v>0.43064750000000007</v>
       </c>
     </row>
     <row r="53" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -47177,11 +47317,11 @@
       <c r="O53" s="215"/>
       <c r="P53" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>196215</v>
+        <v>200085</v>
       </c>
       <c r="Q53" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1.9621499999999998</v>
+        <v>2.0008499999999998</v>
       </c>
       <c r="R53" s="159"/>
       <c r="S53" s="88">
@@ -47197,11 +47337,11 @@
       <c r="W53" s="72"/>
       <c r="Y53" s="154">
         <f t="shared" si="22"/>
-        <v>942008</v>
+        <v>945878</v>
       </c>
       <c r="Z53" s="168">
         <f t="shared" si="23"/>
-        <v>9.4200800000000005</v>
+        <v>9.4587800000000009</v>
       </c>
     </row>
     <row r="54" spans="1:34" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -47339,11 +47479,11 @@
       <c r="O55" s="215"/>
       <c r="P55" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-95143</v>
+        <v>-95823</v>
       </c>
       <c r="Q55" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1.90286</v>
+        <v>-1.9164599999999998</v>
       </c>
       <c r="R55" s="159"/>
       <c r="S55" s="153">
@@ -47360,11 +47500,11 @@
       <c r="X55" s="132"/>
       <c r="Y55" s="154">
         <f t="shared" si="22"/>
-        <v>-340921</v>
+        <v>-341601</v>
       </c>
       <c r="Z55" s="168">
         <f t="shared" si="23"/>
-        <v>-6.8184199999999997</v>
+        <v>-6.83202</v>
       </c>
       <c r="AA55" s="132"/>
     </row>
@@ -47422,11 +47562,11 @@
       <c r="O56" s="215"/>
       <c r="P56" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-167198</v>
+        <v>-215225</v>
       </c>
       <c r="Q56" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.55732666666666664</v>
+        <v>-0.71741666666666659</v>
       </c>
       <c r="R56" s="159"/>
       <c r="S56" s="88">
@@ -47442,11 +47582,11 @@
       <c r="W56" s="72"/>
       <c r="Y56" s="154">
         <f t="shared" si="22"/>
-        <v>-4866173</v>
+        <v>-4914200</v>
       </c>
       <c r="Z56" s="168">
         <f t="shared" si="23"/>
-        <v>-16.22057666666667</v>
+        <v>-16.38066666666667</v>
       </c>
       <c r="AB56" s="132"/>
       <c r="AC56" s="132"/>
@@ -47676,11 +47816,11 @@
       <c r="O59" s="215"/>
       <c r="P59" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>36613</v>
+        <v>34705</v>
       </c>
       <c r="Q59" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.41166000000000003</v>
+        <v>0.3735</v>
       </c>
       <c r="R59" s="159"/>
       <c r="S59" s="88">
@@ -47697,11 +47837,11 @@
       <c r="X59" s="1"/>
       <c r="Y59" s="154">
         <f t="shared" si="22"/>
-        <v>73336</v>
+        <v>71428</v>
       </c>
       <c r="Z59" s="168">
         <f t="shared" si="23"/>
-        <v>0.74049333333333334</v>
+        <v>0.70233333333333325</v>
       </c>
       <c r="AB59" s="1"/>
       <c r="AC59" s="1"/>
@@ -47765,11 +47905,11 @@
       <c r="O60" s="215"/>
       <c r="P60" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>851807</v>
+        <v>817657</v>
       </c>
       <c r="Q60" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>8.5180699999999998</v>
+        <v>8.1765699999999999</v>
       </c>
       <c r="R60" s="159"/>
       <c r="S60" s="88">
@@ -47785,11 +47925,11 @@
       <c r="W60" s="72"/>
       <c r="Y60" s="154">
         <f t="shared" si="22"/>
-        <v>4401876</v>
+        <v>4367726</v>
       </c>
       <c r="Z60" s="168">
         <f t="shared" si="23"/>
-        <v>44.01876</v>
+        <v>43.677259999999997</v>
       </c>
       <c r="AB60" s="132"/>
       <c r="AC60" s="132"/>
@@ -47851,11 +47991,11 @@
       <c r="O61" s="215"/>
       <c r="P61" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>2934</v>
+        <v>3908</v>
       </c>
       <c r="Q61" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.29339999999999999</v>
+        <v>0.39079999999999993</v>
       </c>
       <c r="R61" s="159"/>
       <c r="S61" s="153">
@@ -47871,11 +48011,11 @@
       <c r="W61" s="150"/>
       <c r="Y61" s="154">
         <f t="shared" ref="Y61" si="37">M61+P61+S61+V61</f>
-        <v>2934</v>
+        <v>3908</v>
       </c>
       <c r="Z61" s="168">
         <f t="shared" ref="Z61" si="38">(N61+Q61+T61+W61)</f>
-        <v>0.29339999999999999</v>
+        <v>0.39079999999999993</v>
       </c>
     </row>
     <row r="62" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -47932,11 +48072,11 @@
       <c r="O62" s="215"/>
       <c r="P62" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>23931</v>
+        <v>7291</v>
       </c>
       <c r="Q62" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>7.9770000000000035E-2</v>
+        <v>2.4303333333333357E-2</v>
       </c>
       <c r="R62" s="159"/>
       <c r="S62" s="88">
@@ -47952,11 +48092,11 @@
       <c r="W62" s="72"/>
       <c r="Y62" s="154">
         <f t="shared" si="22"/>
-        <v>696780</v>
+        <v>680140</v>
       </c>
       <c r="Z62" s="168">
         <f t="shared" si="23"/>
-        <v>2.3225999999999996</v>
+        <v>2.2671333333333332</v>
       </c>
       <c r="AB62" s="1"/>
       <c r="AC62" s="1"/>
@@ -48183,11 +48323,11 @@
       <c r="O65" s="215"/>
       <c r="P65" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>373533</v>
+        <v>382014</v>
       </c>
       <c r="Q65" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.93383249999999995</v>
+        <v>0.95503499999999986</v>
       </c>
       <c r="R65" s="159"/>
       <c r="S65" s="153">
@@ -48204,11 +48344,11 @@
       <c r="X65" s="132"/>
       <c r="Y65" s="154">
         <f t="shared" si="22"/>
-        <v>897945</v>
+        <v>906426</v>
       </c>
       <c r="Z65" s="168">
         <f t="shared" si="23"/>
-        <v>2.2448625</v>
+        <v>2.2660650000000002</v>
       </c>
     </row>
     <row r="66" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -48345,11 +48485,11 @@
       <c r="O67" s="215"/>
       <c r="P67" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1406580</v>
+        <v>-1319980</v>
       </c>
       <c r="Q67" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1.4066799999999999</v>
+        <v>-1.3200799999999999</v>
       </c>
       <c r="R67" s="159"/>
       <c r="S67" s="153">
@@ -48365,11 +48505,11 @@
       <c r="W67" s="150"/>
       <c r="Y67" s="154">
         <f t="shared" ref="Y67" si="43">M67+P67+S67+V67</f>
-        <v>-1406580</v>
+        <v>-1319980</v>
       </c>
       <c r="Z67" s="168">
         <f t="shared" ref="Z67" si="44">(N67+Q67+T67+W67)</f>
-        <v>-1.4066799999999999</v>
+        <v>-1.3200799999999999</v>
       </c>
     </row>
     <row r="68" spans="1:26" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -48483,11 +48623,11 @@
       <c r="O69" s="215"/>
       <c r="P69" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-34295</v>
+        <v>-29757</v>
       </c>
       <c r="Q69" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.68589999999999995</v>
+        <v>-0.59514</v>
       </c>
       <c r="R69" s="159"/>
       <c r="S69" s="153">
@@ -48503,11 +48643,11 @@
       <c r="W69" s="150"/>
       <c r="Y69" s="154">
         <f t="shared" si="22"/>
-        <v>-80949</v>
+        <v>-76411</v>
       </c>
       <c r="Z69" s="168">
         <f t="shared" si="23"/>
-        <v>-1.6189800000000001</v>
+        <v>-1.5282200000000001</v>
       </c>
     </row>
     <row r="70" spans="1:26" x14ac:dyDescent="0.25">
@@ -48564,11 +48704,11 @@
       <c r="O70" s="215"/>
       <c r="P70" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>943944</v>
+        <v>791671</v>
       </c>
       <c r="Q70" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>2.2956109615384617</v>
+        <v>2.0613448076923078</v>
       </c>
       <c r="R70" s="159"/>
       <c r="S70" s="153">
@@ -48584,11 +48724,11 @@
       <c r="W70" s="150"/>
       <c r="Y70" s="154">
         <f t="shared" si="22"/>
-        <v>535992</v>
+        <v>383719</v>
       </c>
       <c r="Z70" s="168">
         <f t="shared" si="23"/>
-        <v>1.2757309615384615</v>
+        <v>1.0414648076923076</v>
       </c>
     </row>
     <row r="71" spans="1:26" x14ac:dyDescent="0.25">
@@ -48645,11 +48785,11 @@
       <c r="O71" s="215"/>
       <c r="P71" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>183258</v>
+        <v>25522</v>
       </c>
       <c r="Q71" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1.466064</v>
+        <v>0.20417600000000014</v>
       </c>
       <c r="R71" s="159"/>
       <c r="S71" s="153">
@@ -48665,11 +48805,11 @@
       <c r="W71" s="150"/>
       <c r="Y71" s="154">
         <f t="shared" si="22"/>
-        <v>159976</v>
+        <v>2240</v>
       </c>
       <c r="Z71" s="168">
         <f t="shared" si="23"/>
-        <v>1.233244</v>
+        <v>-2.8643999999999892E-2</v>
       </c>
     </row>
     <row r="72" spans="1:26" x14ac:dyDescent="0.25">
@@ -48807,11 +48947,11 @@
       <c r="O73" s="215"/>
       <c r="P73" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>704073</v>
+        <v>597432</v>
       </c>
       <c r="Q73" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>2.3469100000000003</v>
+        <v>1.9914400000000003</v>
       </c>
       <c r="R73" s="159"/>
       <c r="S73" s="88">
@@ -48827,11 +48967,11 @@
       <c r="W73" s="72"/>
       <c r="Y73" s="154">
         <f t="shared" si="22"/>
-        <v>536691</v>
+        <v>430050</v>
       </c>
       <c r="Z73" s="168">
         <f t="shared" si="23"/>
-        <v>1.7889700000000004</v>
+        <v>1.4335000000000004</v>
       </c>
     </row>
     <row r="74" spans="1:26" x14ac:dyDescent="0.25">
@@ -48967,11 +49107,11 @@
       <c r="O75" s="215"/>
       <c r="P75" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>80165</v>
+        <v>88300</v>
       </c>
       <c r="Q75" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.45089999999999997</v>
+        <v>0.50513333333333332</v>
       </c>
       <c r="R75" s="159"/>
       <c r="S75" s="153">
@@ -48987,11 +49127,11 @@
       <c r="W75" s="150"/>
       <c r="Y75" s="154">
         <f t="shared" ref="Y75:Y76" si="53">M75+P75+S75+V75</f>
-        <v>80165</v>
+        <v>88300</v>
       </c>
       <c r="Z75" s="168">
         <f t="shared" ref="Z75:Z76" si="54">(N75+Q75+T75+W75)</f>
-        <v>0.45089999999999997</v>
+        <v>0.50513333333333332</v>
       </c>
     </row>
     <row r="76" spans="1:26" s="132" customFormat="1" x14ac:dyDescent="0.25">
@@ -49046,11 +49186,11 @@
       <c r="O76" s="215"/>
       <c r="P76" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>489405</v>
+        <v>537651</v>
       </c>
       <c r="Q76" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.97880999999999996</v>
+        <v>1.075302</v>
       </c>
       <c r="R76" s="159"/>
       <c r="S76" s="153">
@@ -49066,11 +49206,11 @@
       <c r="W76" s="150"/>
       <c r="Y76" s="154">
         <f t="shared" si="53"/>
-        <v>489405</v>
+        <v>537651</v>
       </c>
       <c r="Z76" s="168">
         <f t="shared" si="54"/>
-        <v>0.97880999999999996</v>
+        <v>1.075302</v>
       </c>
     </row>
     <row r="77" spans="1:26" x14ac:dyDescent="0.25">
@@ -49095,12 +49235,15 @@
         <v>1801210</v>
       </c>
       <c r="L77" s="109"/>
-      <c r="M77" s="122"/>
+      <c r="M77" s="109">
+        <f>SUM(M4:M74)</f>
+        <v>19357535</v>
+      </c>
       <c r="N77" s="122"/>
       <c r="O77" s="122"/>
       <c r="P77" s="109">
         <f>SUM(P4:P74)</f>
-        <v>9679497</v>
+        <v>9140856</v>
       </c>
       <c r="Q77" s="122"/>
       <c r="R77" s="122"/>
@@ -49111,7 +49254,7 @@
       <c r="W77" s="50"/>
       <c r="Y77" s="154">
         <f>SUM(Y4:Y76)</f>
-        <v>29606602</v>
+        <v>29124342</v>
       </c>
       <c r="Z77" s="161"/>
     </row>
@@ -49407,11 +49550,11 @@
       <c r="O82" s="167"/>
       <c r="P82" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>614980</v>
+        <v>298950</v>
       </c>
       <c r="Q82" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>2.0499333333333336</v>
+        <v>0.99650000000000039</v>
       </c>
       <c r="R82" s="159"/>
       <c r="S82" s="153">
@@ -49428,11 +49571,11 @@
       <c r="X82" s="132"/>
       <c r="Y82" s="52">
         <f t="shared" si="56"/>
-        <v>826480</v>
+        <v>510450</v>
       </c>
       <c r="Z82" s="53">
         <f t="shared" si="56"/>
-        <v>2.0499333333333336</v>
+        <v>0.99650000000000039</v>
       </c>
       <c r="AA82" s="132"/>
     </row>
@@ -49488,7 +49631,7 @@
       <c r="O83" s="167"/>
       <c r="P83" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>971446</v>
+        <v>922885</v>
       </c>
       <c r="Q83" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
@@ -49508,7 +49651,7 @@
       <c r="W83" s="53"/>
       <c r="Y83" s="52">
         <f t="shared" ref="Y83" si="59">M83+P83+S83+V83</f>
-        <v>561446</v>
+        <v>512885</v>
       </c>
       <c r="Z83" s="53">
         <f t="shared" ref="Z83" si="60">N83+Q83+T83+W83</f>
@@ -49542,7 +49685,7 @@
       <c r="O84" s="123"/>
       <c r="P84" s="112">
         <f>SUM(P80:P83)</f>
-        <v>1586426</v>
+        <v>1221835</v>
       </c>
       <c r="Q84" s="123"/>
       <c r="R84" s="123"/>
@@ -49565,1223 +49708,1213 @@
       <c r="A85" s="1"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A56:C56 V4:W4 A27:F29 V20:W21 A13:C13 W48:W49 A3:F4 L2:L3 A48:F49 A52:C52 W22:W30 A80:F81 C16 W45:W46 W42 A42:H42 G41:H41 F16 F13 F70:F71 W58:W60 G58:J60 A66:J66 Y58:Y60 Y77:Z77 G13:H14 G7:J11 F53 F56:J56 Y56 W52:W53 H4:O4 M5:O5 G16:H18 Y4:Z11 K5:L11 A20:F24 D5:J5 F72:J74 A44:J44 Y66 Z56:Z60 G45:J53 K44:L53 A73:C73 A74:E74 A45:F46 E52:F52 A60:F60 Y34:Z36 M80:O82 M7:O11 A34:O36 R44:W44 R72:W74 R7:W9 R13:W16 R34:W36 R45:U46 R17:U17 R22:U30 R48:U53 U80:U82 A77:E77 A38:H39 A62:F62 K62:O66 Z62:Z66 Y62:Y63 G62:J63 R38:U43 M38:O53 I38:L43 Y38:Z53 W38:W39 G77:W78 G84:W84 K69:O74 G69:J69 W66:W68 R62:U71 G67:O68 Y67:Z74 A9 F9 I13:O18 Y13:Z18 Y55:Z55 R55:U60 K55:O60 G55:J55 W55:W56 Y20:Z32 G20:O32 A31:A32 P13:Q36 A7:F8">
-    <cfRule type="expression" dxfId="245" priority="448">
+  <conditionalFormatting sqref="A56:C56 V4:W4 A27:F29 V20:W21 A13:C13 W48:W49 A3:F4 L2:L3 A48:F49 A52:C52 W22:W30 A80:F81 C16 W45:W46 W42 A42:H42 G41:H41 F16 F13 F70:F71 W58:W60 G58:J60 A66:J66 Y58:Y60 Y77:Z77 G13:H14 G7:J11 F53 F56:J56 Y56 W52:W53 H4:O4 M5:O5 G16:H18 Y4:Z11 K5:L11 A20:F24 D5:J5 F72:J74 A44:J44 Y66 Z56:Z60 G45:J53 K44:L53 A73:C73 A74:E74 A45:F46 E52:F52 A60:F60 Y34:Z36 M80:O82 M7:O11 A34:O36 R44:W44 R72:W74 R7:W9 R13:W16 R34:W36 R45:U46 R17:U17 R22:U30 R48:U53 U80:U82 A77:E77 A38:H39 A62:F62 K62:O66 Z62:Z66 Y62:Y63 G62:J63 R38:U43 M38:O53 I38:L43 Y38:Z53 W38:W39 G84:W84 K69:O74 G69:J69 W66:W68 R62:U71 G67:O68 Y67:Z74 A9 F9 I13:O18 Y13:Z18 Y55:Z55 R55:U60 K55:O60 G55:J55 W55:W56 Y20:Z32 G20:O32 A31:A32 P13:Q36 A7:F8 G77:W78">
+    <cfRule type="expression" dxfId="241" priority="448">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V38:V39 V23:V24 V59 V48:V49 V56 V45:V46 V27:V29 G2:I3 V52 G4:H4">
-    <cfRule type="expression" dxfId="244" priority="447">
+    <cfRule type="expression" dxfId="240" priority="447">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J3">
-    <cfRule type="expression" dxfId="243" priority="444">
+    <cfRule type="expression" dxfId="239" priority="444">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V80:W81">
-    <cfRule type="expression" dxfId="242" priority="441">
+    <cfRule type="expression" dxfId="238" priority="441">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K3">
-    <cfRule type="expression" dxfId="241" priority="442">
+    <cfRule type="expression" dxfId="237" priority="442">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V60">
-    <cfRule type="expression" dxfId="240" priority="432">
+    <cfRule type="expression" dxfId="236" priority="432">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V22">
-    <cfRule type="expression" dxfId="239" priority="433">
+    <cfRule type="expression" dxfId="235" priority="433">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A53:C53 E53">
-    <cfRule type="expression" dxfId="238" priority="422">
+    <cfRule type="expression" dxfId="234" priority="422">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V53 V55">
-    <cfRule type="expression" dxfId="237" priority="420">
+    <cfRule type="expression" dxfId="233" priority="420">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E56">
-    <cfRule type="expression" dxfId="236" priority="418">
+    <cfRule type="expression" dxfId="232" priority="418">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V42">
-    <cfRule type="expression" dxfId="235" priority="409">
+    <cfRule type="expression" dxfId="231" priority="409">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A30:F30">
-    <cfRule type="expression" dxfId="234" priority="408">
+    <cfRule type="expression" dxfId="230" priority="408">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B72:C72">
-    <cfRule type="expression" dxfId="233" priority="380">
+    <cfRule type="expression" dxfId="229" priority="380">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V30">
-    <cfRule type="expression" dxfId="232" priority="406">
+    <cfRule type="expression" dxfId="228" priority="406">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26:E26">
-    <cfRule type="expression" dxfId="231" priority="405">
+    <cfRule type="expression" dxfId="227" priority="405">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V26">
-    <cfRule type="expression" dxfId="230" priority="403">
+    <cfRule type="expression" dxfId="226" priority="403">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A25:E25">
-    <cfRule type="expression" dxfId="229" priority="402">
+    <cfRule type="expression" dxfId="225" priority="402">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V25">
-    <cfRule type="expression" dxfId="228" priority="400">
+    <cfRule type="expression" dxfId="224" priority="400">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58:C58 E58:F58">
-    <cfRule type="expression" dxfId="227" priority="387">
+    <cfRule type="expression" dxfId="223" priority="387">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T4:U4 T20:U21">
-    <cfRule type="expression" dxfId="226" priority="331">
+    <cfRule type="expression" dxfId="222" priority="331">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A72">
-    <cfRule type="expression" dxfId="225" priority="378">
+    <cfRule type="expression" dxfId="221" priority="378">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S4:U4 S20:U21">
-    <cfRule type="expression" dxfId="224" priority="330">
+    <cfRule type="expression" dxfId="220" priority="330">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V58">
-    <cfRule type="expression" dxfId="223" priority="383">
+    <cfRule type="expression" dxfId="219" priority="383">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F25">
-    <cfRule type="expression" dxfId="222" priority="349">
+    <cfRule type="expression" dxfId="218" priority="349">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M20:O21 M34:O34">
-    <cfRule type="expression" dxfId="221" priority="347">
+    <cfRule type="expression" dxfId="217" priority="347">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:F17 A18:C18 E18:F18">
-    <cfRule type="expression" dxfId="220" priority="355">
+    <cfRule type="expression" dxfId="216" priority="355">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V17:W17">
-    <cfRule type="expression" dxfId="219" priority="354">
+    <cfRule type="expression" dxfId="215" priority="354">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R4 R20:R21">
-    <cfRule type="expression" dxfId="218" priority="339">
+    <cfRule type="expression" dxfId="214" priority="339">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R4 R20:R21">
-    <cfRule type="expression" dxfId="217" priority="338">
+    <cfRule type="expression" dxfId="213" priority="338">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V66:V68">
-    <cfRule type="expression" dxfId="216" priority="369">
+    <cfRule type="expression" dxfId="212" priority="369">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W62">
-    <cfRule type="expression" dxfId="215" priority="329">
+    <cfRule type="expression" dxfId="211" priority="329">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M35:O35">
-    <cfRule type="expression" dxfId="214" priority="340">
+    <cfRule type="expression" dxfId="210" priority="340">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F26">
-    <cfRule type="expression" dxfId="213" priority="350">
+    <cfRule type="expression" dxfId="209" priority="350">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N20:O21 N34:O34">
-    <cfRule type="expression" dxfId="212" priority="348">
+    <cfRule type="expression" dxfId="208" priority="348">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N35:O35">
-    <cfRule type="expression" dxfId="211" priority="341">
+    <cfRule type="expression" dxfId="207" priority="341">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V62">
-    <cfRule type="expression" dxfId="210" priority="328">
+    <cfRule type="expression" dxfId="206" priority="328">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M18:O18">
-    <cfRule type="expression" dxfId="209" priority="286">
+    <cfRule type="expression" dxfId="205" priority="286">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R18">
-    <cfRule type="expression" dxfId="208" priority="285">
+    <cfRule type="expression" dxfId="204" priority="285">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T18:U18">
-    <cfRule type="expression" dxfId="207" priority="283">
+    <cfRule type="expression" dxfId="203" priority="283">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31:F31 B32:C32 E32:F32">
-    <cfRule type="expression" dxfId="206" priority="275">
+    <cfRule type="expression" dxfId="202" priority="275">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W31">
-    <cfRule type="expression" dxfId="205" priority="274">
+    <cfRule type="expression" dxfId="201" priority="274">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V18:W18">
-    <cfRule type="expression" dxfId="204" priority="288">
+    <cfRule type="expression" dxfId="200" priority="288">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N18:O18">
-    <cfRule type="expression" dxfId="203" priority="287">
+    <cfRule type="expression" dxfId="199" priority="287">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R18">
-    <cfRule type="expression" dxfId="202" priority="284">
+    <cfRule type="expression" dxfId="198" priority="284">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S18:U18">
-    <cfRule type="expression" dxfId="201" priority="282">
+    <cfRule type="expression" dxfId="197" priority="282">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V31">
-    <cfRule type="expression" dxfId="200" priority="273">
+    <cfRule type="expression" dxfId="196" priority="273">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S31:U31">
-    <cfRule type="expression" dxfId="199" priority="267">
+    <cfRule type="expression" dxfId="195" priority="267">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N31:O31">
-    <cfRule type="expression" dxfId="198" priority="272">
+    <cfRule type="expression" dxfId="194" priority="272">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M31:O31">
-    <cfRule type="expression" dxfId="197" priority="271">
+    <cfRule type="expression" dxfId="193" priority="271">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T31:U31">
-    <cfRule type="expression" dxfId="196" priority="268">
+    <cfRule type="expression" dxfId="192" priority="268">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R31">
-    <cfRule type="expression" dxfId="195" priority="270">
+    <cfRule type="expression" dxfId="191" priority="270">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R31">
-    <cfRule type="expression" dxfId="194" priority="269">
+    <cfRule type="expression" dxfId="190" priority="269">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11:F11 A10:C10 E10:F10 F12">
-    <cfRule type="expression" dxfId="193" priority="260">
+    <cfRule type="expression" dxfId="189" priority="260">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V10:W11">
-    <cfRule type="expression" dxfId="192" priority="259">
+    <cfRule type="expression" dxfId="188" priority="259">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R10:R11">
-    <cfRule type="expression" dxfId="191" priority="256">
+    <cfRule type="expression" dxfId="187" priority="256">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R10:R11">
-    <cfRule type="expression" dxfId="190" priority="255">
+    <cfRule type="expression" dxfId="186" priority="255">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S10:U11">
-    <cfRule type="expression" dxfId="189" priority="253">
+    <cfRule type="expression" dxfId="185" priority="253">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N10:O11">
-    <cfRule type="expression" dxfId="188" priority="258">
+    <cfRule type="expression" dxfId="184" priority="258">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M10:O11">
-    <cfRule type="expression" dxfId="187" priority="257">
+    <cfRule type="expression" dxfId="183" priority="257">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T10:U11">
-    <cfRule type="expression" dxfId="186" priority="254">
+    <cfRule type="expression" dxfId="182" priority="254">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:C47 E47:F47">
-    <cfRule type="expression" dxfId="185" priority="246">
+    <cfRule type="expression" dxfId="181" priority="246">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W47">
-    <cfRule type="expression" dxfId="184" priority="245">
+    <cfRule type="expression" dxfId="180" priority="245">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V47">
-    <cfRule type="expression" dxfId="183" priority="244">
+    <cfRule type="expression" dxfId="179" priority="244">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T47:U47">
-    <cfRule type="expression" dxfId="182" priority="239">
+    <cfRule type="expression" dxfId="178" priority="239">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S47:U47">
-    <cfRule type="expression" dxfId="181" priority="238">
+    <cfRule type="expression" dxfId="177" priority="238">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M47:O47">
-    <cfRule type="expression" dxfId="180" priority="242">
+    <cfRule type="expression" dxfId="176" priority="242">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R47">
-    <cfRule type="expression" dxfId="179" priority="241">
+    <cfRule type="expression" dxfId="175" priority="241">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R47">
-    <cfRule type="expression" dxfId="178" priority="240">
+    <cfRule type="expression" dxfId="174" priority="240">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N47:O47">
-    <cfRule type="expression" dxfId="177" priority="243">
+    <cfRule type="expression" dxfId="173" priority="243">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A59:C59 E59:F59">
-    <cfRule type="expression" dxfId="176" priority="231">
+    <cfRule type="expression" dxfId="172" priority="231">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:C5">
-    <cfRule type="expression" dxfId="175" priority="227">
+    <cfRule type="expression" dxfId="171" priority="227">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V5:W5">
-    <cfRule type="expression" dxfId="174" priority="226">
+    <cfRule type="expression" dxfId="170" priority="226">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T5:U5">
-    <cfRule type="expression" dxfId="173" priority="220">
+    <cfRule type="expression" dxfId="169" priority="220">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S5:U5">
-    <cfRule type="expression" dxfId="172" priority="219">
+    <cfRule type="expression" dxfId="168" priority="219">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5:O5">
-    <cfRule type="expression" dxfId="171" priority="223">
+    <cfRule type="expression" dxfId="167" priority="223">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R5">
-    <cfRule type="expression" dxfId="170" priority="222">
+    <cfRule type="expression" dxfId="166" priority="222">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R5">
-    <cfRule type="expression" dxfId="169" priority="221">
+    <cfRule type="expression" dxfId="165" priority="221">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N5:O5">
-    <cfRule type="expression" dxfId="168" priority="224">
+    <cfRule type="expression" dxfId="164" priority="224">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A50:F51">
-    <cfRule type="expression" dxfId="167" priority="208">
+    <cfRule type="expression" dxfId="163" priority="208">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W50:W51">
-    <cfRule type="expression" dxfId="166" priority="207">
+    <cfRule type="expression" dxfId="162" priority="207">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V50:V51">
-    <cfRule type="expression" dxfId="165" priority="206">
+    <cfRule type="expression" dxfId="161" priority="206">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W32">
-    <cfRule type="expression" dxfId="164" priority="200">
+    <cfRule type="expression" dxfId="160" priority="200">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V32">
-    <cfRule type="expression" dxfId="163" priority="199">
+    <cfRule type="expression" dxfId="159" priority="199">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S32:U32">
-    <cfRule type="expression" dxfId="162" priority="193">
+    <cfRule type="expression" dxfId="158" priority="193">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N32:O32">
-    <cfRule type="expression" dxfId="161" priority="198">
+    <cfRule type="expression" dxfId="157" priority="198">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M32:O32">
-    <cfRule type="expression" dxfId="160" priority="197">
+    <cfRule type="expression" dxfId="156" priority="197">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T32:U32">
-    <cfRule type="expression" dxfId="159" priority="194">
+    <cfRule type="expression" dxfId="155" priority="194">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R32">
-    <cfRule type="expression" dxfId="158" priority="196">
+    <cfRule type="expression" dxfId="154" priority="196">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R32">
-    <cfRule type="expression" dxfId="157" priority="195">
+    <cfRule type="expression" dxfId="153" priority="195">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W63">
-    <cfRule type="expression" dxfId="156" priority="191">
+    <cfRule type="expression" dxfId="152" priority="191">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V63">
-    <cfRule type="expression" dxfId="155" priority="190">
+    <cfRule type="expression" dxfId="151" priority="190">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14:F14">
-    <cfRule type="expression" dxfId="154" priority="177">
+    <cfRule type="expression" dxfId="150" priority="177">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W41">
-    <cfRule type="expression" dxfId="153" priority="186">
+    <cfRule type="expression" dxfId="149" priority="186">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V41">
-    <cfRule type="expression" dxfId="152" priority="185">
+    <cfRule type="expression" dxfId="148" priority="185">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A69:C69 E69:F69">
-    <cfRule type="expression" dxfId="151" priority="175">
+    <cfRule type="expression" dxfId="147" priority="175">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W69">
-    <cfRule type="expression" dxfId="150" priority="174">
+    <cfRule type="expression" dxfId="146" priority="174">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V69">
-    <cfRule type="expression" dxfId="149" priority="173">
+    <cfRule type="expression" dxfId="145" priority="173">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G80:G81">
-    <cfRule type="expression" dxfId="148" priority="168">
+    <cfRule type="expression" dxfId="144" priority="168">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H80">
-    <cfRule type="expression" dxfId="147" priority="165">
+    <cfRule type="expression" dxfId="143" priority="165">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H81">
-    <cfRule type="expression" dxfId="146" priority="164">
+    <cfRule type="expression" dxfId="142" priority="164">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L79">
-    <cfRule type="expression" dxfId="145" priority="163">
+    <cfRule type="expression" dxfId="141" priority="163">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G79:I79">
-    <cfRule type="expression" dxfId="144" priority="162">
+    <cfRule type="expression" dxfId="140" priority="162">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J79">
-    <cfRule type="expression" dxfId="143" priority="161">
+    <cfRule type="expression" dxfId="139" priority="161">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K79">
-    <cfRule type="expression" dxfId="142" priority="160">
+    <cfRule type="expression" dxfId="138" priority="160">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y80:Z81">
-    <cfRule type="expression" dxfId="141" priority="147">
+    <cfRule type="expression" dxfId="137" priority="147">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40:F40">
-    <cfRule type="expression" dxfId="140" priority="157">
+    <cfRule type="expression" dxfId="136" priority="157">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A41:F41">
-    <cfRule type="expression" dxfId="139" priority="156">
+    <cfRule type="expression" dxfId="135" priority="156">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A43:F43">
-    <cfRule type="expression" dxfId="138" priority="155">
+    <cfRule type="expression" dxfId="134" priority="155">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W43 G43:H43">
-    <cfRule type="expression" dxfId="137" priority="154">
+    <cfRule type="expression" dxfId="133" priority="154">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V43">
-    <cfRule type="expression" dxfId="136" priority="153">
+    <cfRule type="expression" dxfId="132" priority="153">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W40 G40:H40">
-    <cfRule type="expression" dxfId="135" priority="152">
+    <cfRule type="expression" dxfId="131" priority="152">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V40">
-    <cfRule type="expression" dxfId="134" priority="151">
+    <cfRule type="expression" dxfId="130" priority="151">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D13:E13">
-    <cfRule type="expression" dxfId="133" priority="142">
+    <cfRule type="expression" dxfId="129" priority="142">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y84:Z84">
-    <cfRule type="expression" dxfId="132" priority="148">
+    <cfRule type="expression" dxfId="128" priority="148">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:B16">
-    <cfRule type="expression" dxfId="131" priority="146">
+    <cfRule type="expression" dxfId="127" priority="146">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15">
-    <cfRule type="expression" dxfId="130" priority="145">
+    <cfRule type="expression" dxfId="126" priority="145">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15">
-    <cfRule type="expression" dxfId="129" priority="144">
+    <cfRule type="expression" dxfId="125" priority="144">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D15:E16">
-    <cfRule type="expression" dxfId="128" priority="143">
+    <cfRule type="expression" dxfId="124" priority="143">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G15:H15">
-    <cfRule type="expression" dxfId="127" priority="141">
+    <cfRule type="expression" dxfId="123" priority="141">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J80:J81">
-    <cfRule type="expression" dxfId="126" priority="138">
+    <cfRule type="expression" dxfId="122" priority="138">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I80:J81">
-    <cfRule type="expression" dxfId="125" priority="137">
+    <cfRule type="expression" dxfId="121" priority="137">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A70:C71 E70:E71">
-    <cfRule type="expression" dxfId="124" priority="136">
+    <cfRule type="expression" dxfId="120" priority="136">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G70:J71 M70:O71">
-    <cfRule type="expression" dxfId="123" priority="135">
+    <cfRule type="expression" dxfId="119" priority="135">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W70:W71">
-    <cfRule type="expression" dxfId="122" priority="134">
+    <cfRule type="expression" dxfId="118" priority="134">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V70:V71">
-    <cfRule type="expression" dxfId="121" priority="133">
+    <cfRule type="expression" dxfId="117" priority="133">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V57">
-    <cfRule type="expression" dxfId="120" priority="130">
+    <cfRule type="expression" dxfId="116" priority="130">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A57:C57 E57:F57">
-    <cfRule type="expression" dxfId="119" priority="132">
+    <cfRule type="expression" dxfId="115" priority="132">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W57 Y57 G57:J57">
-    <cfRule type="expression" dxfId="118" priority="131">
+    <cfRule type="expression" dxfId="114" priority="131">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A64:A65">
-    <cfRule type="expression" dxfId="117" priority="129">
+    <cfRule type="expression" dxfId="113" priority="129">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A63:B63">
-    <cfRule type="expression" dxfId="116" priority="128">
+    <cfRule type="expression" dxfId="112" priority="128">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B64:B65">
-    <cfRule type="expression" dxfId="115" priority="127">
+    <cfRule type="expression" dxfId="111" priority="127">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M64:O65 G64:J65 Y64:Y65">
-    <cfRule type="expression" dxfId="114" priority="126">
+    <cfRule type="expression" dxfId="110" priority="126">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W64:W65">
-    <cfRule type="expression" dxfId="113" priority="124">
+    <cfRule type="expression" dxfId="109" priority="124">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V64:V65">
-    <cfRule type="expression" dxfId="112" priority="123">
+    <cfRule type="expression" dxfId="108" priority="123">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A6:C6 E6:F6">
-    <cfRule type="expression" dxfId="111" priority="122">
+    <cfRule type="expression" dxfId="107" priority="122">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G6:J6 M6:O6">
-    <cfRule type="expression" dxfId="110" priority="121">
+    <cfRule type="expression" dxfId="106" priority="121">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V6:W6">
-    <cfRule type="expression" dxfId="109" priority="120">
+    <cfRule type="expression" dxfId="105" priority="120">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T6:U6">
-    <cfRule type="expression" dxfId="108" priority="115">
+    <cfRule type="expression" dxfId="104" priority="115">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S6:U6">
-    <cfRule type="expression" dxfId="107" priority="114">
+    <cfRule type="expression" dxfId="103" priority="114">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M6:O6">
-    <cfRule type="expression" dxfId="106" priority="118">
+    <cfRule type="expression" dxfId="102" priority="118">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R6">
-    <cfRule type="expression" dxfId="105" priority="117">
+    <cfRule type="expression" dxfId="101" priority="117">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R6">
-    <cfRule type="expression" dxfId="104" priority="116">
+    <cfRule type="expression" dxfId="100" priority="116">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N6:O6">
-    <cfRule type="expression" dxfId="103" priority="119">
+    <cfRule type="expression" dxfId="99" priority="119">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A55:C55 E55:F55">
-    <cfRule type="expression" dxfId="102" priority="113">
+    <cfRule type="expression" dxfId="98" priority="113">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A82:F82">
-    <cfRule type="expression" dxfId="101" priority="111">
+    <cfRule type="expression" dxfId="97" priority="111">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V82:W82">
-    <cfRule type="expression" dxfId="100" priority="109">
+    <cfRule type="expression" dxfId="96" priority="109">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G82">
-    <cfRule type="expression" dxfId="99" priority="108">
+    <cfRule type="expression" dxfId="95" priority="108">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H82">
-    <cfRule type="expression" dxfId="98" priority="107">
+    <cfRule type="expression" dxfId="94" priority="107">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y82:Z82">
-    <cfRule type="expression" dxfId="97" priority="106">
+    <cfRule type="expression" dxfId="93" priority="106">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J82">
-    <cfRule type="expression" dxfId="96" priority="105">
+    <cfRule type="expression" dxfId="92" priority="105">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I82:J82">
-    <cfRule type="expression" dxfId="95" priority="104">
+    <cfRule type="expression" dxfId="91" priority="104">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K80:L82">
-    <cfRule type="expression" dxfId="94" priority="102">
+    <cfRule type="expression" dxfId="90" priority="102">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S19:U19">
-    <cfRule type="expression" dxfId="93" priority="92">
+    <cfRule type="expression" dxfId="89" priority="92">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19:F19">
-    <cfRule type="expression" dxfId="92" priority="100">
+    <cfRule type="expression" dxfId="88" priority="100">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y19:Z19 G19:O19">
-    <cfRule type="expression" dxfId="91" priority="99">
+    <cfRule type="expression" dxfId="87" priority="99">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M19:O19">
-    <cfRule type="expression" dxfId="90" priority="96">
+    <cfRule type="expression" dxfId="86" priority="96">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R19">
-    <cfRule type="expression" dxfId="89" priority="95">
+    <cfRule type="expression" dxfId="85" priority="95">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T19:U19">
-    <cfRule type="expression" dxfId="88" priority="93">
+    <cfRule type="expression" dxfId="84" priority="93">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V19:W19">
-    <cfRule type="expression" dxfId="87" priority="98">
+    <cfRule type="expression" dxfId="83" priority="98">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N19:O19">
-    <cfRule type="expression" dxfId="86" priority="97">
+    <cfRule type="expression" dxfId="82" priority="97">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R19">
-    <cfRule type="expression" dxfId="85" priority="94">
+    <cfRule type="expression" dxfId="81" priority="94">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E72:E73">
-    <cfRule type="expression" dxfId="84" priority="91">
+    <cfRule type="expression" dxfId="80" priority="91">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F64:F65">
-    <cfRule type="expression" dxfId="83" priority="90">
+    <cfRule type="expression" dxfId="79" priority="90">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F63">
-    <cfRule type="expression" dxfId="82" priority="89">
+    <cfRule type="expression" dxfId="78" priority="89">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D63:E63 C64:E65">
-    <cfRule type="expression" dxfId="81" priority="88">
+    <cfRule type="expression" dxfId="77" priority="88">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D10">
-    <cfRule type="expression" dxfId="80" priority="87">
+    <cfRule type="expression" dxfId="76" priority="87">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6">
-    <cfRule type="expression" dxfId="79" priority="86">
+    <cfRule type="expression" dxfId="75" priority="86">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D18">
-    <cfRule type="expression" dxfId="78" priority="85">
+    <cfRule type="expression" dxfId="74" priority="85">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D32">
-    <cfRule type="expression" dxfId="77" priority="84">
+    <cfRule type="expression" dxfId="73" priority="84">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D70:D71">
-    <cfRule type="expression" dxfId="76" priority="72">
+    <cfRule type="expression" dxfId="72" priority="72">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D47">
-    <cfRule type="expression" dxfId="75" priority="82">
+    <cfRule type="expression" dxfId="71" priority="82">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D53 D55">
-    <cfRule type="expression" dxfId="74" priority="81">
+    <cfRule type="expression" dxfId="70" priority="81">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D52">
-    <cfRule type="expression" dxfId="73" priority="80">
+    <cfRule type="expression" dxfId="69" priority="80">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D56">
-    <cfRule type="expression" dxfId="72" priority="79">
+    <cfRule type="expression" dxfId="68" priority="79">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D57">
-    <cfRule type="expression" dxfId="71" priority="78">
+    <cfRule type="expression" dxfId="67" priority="78">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D58">
-    <cfRule type="expression" dxfId="70" priority="77">
+    <cfRule type="expression" dxfId="66" priority="77">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D59">
-    <cfRule type="expression" dxfId="69" priority="76">
+    <cfRule type="expression" dxfId="65" priority="76">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D73">
-    <cfRule type="expression" dxfId="68" priority="75">
+    <cfRule type="expression" dxfId="64" priority="75">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D72">
-    <cfRule type="expression" dxfId="67" priority="74">
+    <cfRule type="expression" dxfId="63" priority="74">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D69">
-    <cfRule type="expression" dxfId="66" priority="73">
+    <cfRule type="expression" dxfId="62" priority="73">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A33:F33">
-    <cfRule type="expression" dxfId="65" priority="71">
+    <cfRule type="expression" dxfId="61" priority="71">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G33:O33 Y33:Z33">
-    <cfRule type="expression" dxfId="64" priority="70">
+    <cfRule type="expression" dxfId="60" priority="70">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W33">
-    <cfRule type="expression" dxfId="63" priority="69">
+    <cfRule type="expression" dxfId="59" priority="69">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V33">
-    <cfRule type="expression" dxfId="62" priority="68">
+    <cfRule type="expression" dxfId="58" priority="68">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S33:U33">
-    <cfRule type="expression" dxfId="61" priority="62">
+    <cfRule type="expression" dxfId="57" priority="62">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N33:O33">
-    <cfRule type="expression" dxfId="60" priority="67">
+    <cfRule type="expression" dxfId="56" priority="67">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M33:O33">
-    <cfRule type="expression" dxfId="59" priority="66">
+    <cfRule type="expression" dxfId="55" priority="66">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T33:U33">
-    <cfRule type="expression" dxfId="58" priority="63">
+    <cfRule type="expression" dxfId="54" priority="63">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R33">
-    <cfRule type="expression" dxfId="57" priority="65">
+    <cfRule type="expression" dxfId="53" priority="65">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R33">
-    <cfRule type="expression" dxfId="56" priority="64">
+    <cfRule type="expression" dxfId="52" priority="64">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q4:Q11 Q38:Q53 Q62:Q74 Q55:Q60">
-    <cfRule type="expression" dxfId="55" priority="59">
+  <conditionalFormatting sqref="Q4:Q11 Q38:Q53 Q55:Q60 Q62:Q76">
+    <cfRule type="expression" dxfId="51" priority="59">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P4:Q11 P38:Q53 P62:Q74 P55:Q60">
-    <cfRule type="expression" dxfId="54" priority="58">
+  <conditionalFormatting sqref="P4:Q11 P38:Q53 P55:Q60 P62:Q76">
+    <cfRule type="expression" dxfId="50" priority="58">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R80:T82">
-    <cfRule type="expression" dxfId="53" priority="57">
+    <cfRule type="expression" dxfId="49" priority="57">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q80:Q82">
-    <cfRule type="expression" dxfId="52" priority="56">
+    <cfRule type="expression" dxfId="48" priority="56">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P80:Q82">
-    <cfRule type="expression" dxfId="51" priority="55">
+    <cfRule type="expression" dxfId="47" priority="55">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A76:F76">
-    <cfRule type="expression" dxfId="50" priority="54">
+    <cfRule type="expression" dxfId="46" priority="54">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A75:F75">
-    <cfRule type="expression" dxfId="49" priority="53">
+    <cfRule type="expression" dxfId="45" priority="53">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G75:O76 Y75:Z76 R75:W76">
-    <cfRule type="expression" dxfId="48" priority="52">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q75:Q76">
-    <cfRule type="expression" dxfId="47" priority="51">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P75:Q76">
-    <cfRule type="expression" dxfId="46" priority="50">
+    <cfRule type="expression" dxfId="44" priority="52">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P37:Q37">
-    <cfRule type="expression" dxfId="45" priority="39">
+    <cfRule type="expression" dxfId="43" priority="39">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A37:F37">
-    <cfRule type="expression" dxfId="44" priority="48">
+    <cfRule type="expression" dxfId="42" priority="48">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P83:Q83">
-    <cfRule type="expression" dxfId="43" priority="24">
+    <cfRule type="expression" dxfId="41" priority="24">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61:F61">
-    <cfRule type="expression" dxfId="42" priority="46">
+    <cfRule type="expression" dxfId="40" priority="46">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W61 Y61:Z61 G61:O61 R61:U61">
-    <cfRule type="expression" dxfId="41" priority="45">
+    <cfRule type="expression" dxfId="39" priority="45">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V61">
-    <cfRule type="expression" dxfId="40" priority="44">
+    <cfRule type="expression" dxfId="38" priority="44">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q61">
-    <cfRule type="expression" dxfId="39" priority="43">
+    <cfRule type="expression" dxfId="37" priority="43">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P61:Q61">
-    <cfRule type="expression" dxfId="38" priority="42">
+    <cfRule type="expression" dxfId="36" priority="42">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y37:Z37 G37:O37 R37:W37">
-    <cfRule type="expression" dxfId="37" priority="41">
+    <cfRule type="expression" dxfId="35" priority="41">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q37">
-    <cfRule type="expression" dxfId="36" priority="40">
+    <cfRule type="expression" dxfId="34" priority="40">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q83">
-    <cfRule type="expression" dxfId="35" priority="25">
+    <cfRule type="expression" dxfId="33" priority="25">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F83">
-    <cfRule type="expression" dxfId="34" priority="36">
+    <cfRule type="expression" dxfId="32" priority="36">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A83:E83">
-    <cfRule type="expression" dxfId="33" priority="35">
+    <cfRule type="expression" dxfId="31" priority="35">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M83:O83 U83">
-    <cfRule type="expression" dxfId="32" priority="34">
+    <cfRule type="expression" dxfId="30" priority="34">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V83:W83">
-    <cfRule type="expression" dxfId="31" priority="33">
+    <cfRule type="expression" dxfId="29" priority="33">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G83">
-    <cfRule type="expression" dxfId="30" priority="32">
+    <cfRule type="expression" dxfId="28" priority="32">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H83">
-    <cfRule type="expression" dxfId="29" priority="31">
+    <cfRule type="expression" dxfId="27" priority="31">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y83:Z83">
-    <cfRule type="expression" dxfId="28" priority="30">
+    <cfRule type="expression" dxfId="26" priority="30">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J83">
-    <cfRule type="expression" dxfId="27" priority="29">
+    <cfRule type="expression" dxfId="25" priority="29">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I83:J83">
-    <cfRule type="expression" dxfId="26" priority="28">
+    <cfRule type="expression" dxfId="24" priority="28">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K83:L83">
-    <cfRule type="expression" dxfId="25" priority="27">
+    <cfRule type="expression" dxfId="23" priority="27">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R83:T83">
-    <cfRule type="expression" dxfId="24" priority="26">
+    <cfRule type="expression" dxfId="22" priority="26">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F67:F68">
-    <cfRule type="expression" dxfId="23" priority="23">
+    <cfRule type="expression" dxfId="21" priority="23">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A67:E67 A68">
-    <cfRule type="expression" dxfId="22" priority="22">
+    <cfRule type="expression" dxfId="20" priority="22">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68:E68">
-    <cfRule type="expression" dxfId="21" priority="21">
+    <cfRule type="expression" dxfId="19" priority="21">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9:E9">
-    <cfRule type="expression" dxfId="20" priority="20">
+    <cfRule type="expression" dxfId="18" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12:B12 D12:E12">
-    <cfRule type="expression" dxfId="19" priority="19">
+    <cfRule type="expression" dxfId="17" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C12">
-    <cfRule type="expression" dxfId="18" priority="18">
+    <cfRule type="expression" dxfId="16" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y12:Z12 G12:O12">
-    <cfRule type="expression" dxfId="17" priority="17">
+    <cfRule type="expression" dxfId="15" priority="17">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V12:W12">
-    <cfRule type="expression" dxfId="16" priority="16">
+    <cfRule type="expression" dxfId="14" priority="16">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R12">
-    <cfRule type="expression" dxfId="15" priority="13">
+    <cfRule type="expression" dxfId="13" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R12">
-    <cfRule type="expression" dxfId="14" priority="12">
+    <cfRule type="expression" dxfId="12" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S12:U12">
-    <cfRule type="expression" dxfId="13" priority="10">
+    <cfRule type="expression" dxfId="11" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N12:O12">
-    <cfRule type="expression" dxfId="12" priority="15">
+    <cfRule type="expression" dxfId="10" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M12:O12">
-    <cfRule type="expression" dxfId="11" priority="14">
+    <cfRule type="expression" dxfId="9" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T12:U12">
-    <cfRule type="expression" dxfId="10" priority="11">
+    <cfRule type="expression" dxfId="8" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q12">
-    <cfRule type="expression" dxfId="9" priority="9">
+    <cfRule type="expression" dxfId="7" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P12:Q12">
-    <cfRule type="expression" dxfId="8" priority="8">
+    <cfRule type="expression" dxfId="6" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A54:C54 E54:F54">
-    <cfRule type="expression" dxfId="7" priority="7">
+    <cfRule type="expression" dxfId="5" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P54:Q54">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D54">
-    <cfRule type="expression" dxfId="5" priority="5">
+    <cfRule type="expression" dxfId="3" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W54 R54:U54 G54:O54 Y54:Z54">
-    <cfRule type="expression" dxfId="4" priority="4">
+    <cfRule type="expression" dxfId="2" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V54">
-    <cfRule type="expression" dxfId="3" priority="3">
+    <cfRule type="expression" dxfId="1" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q54">
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
